--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -4568,56 +4568,56 @@
         <v>4465</v>
       </c>
       <c r="C54" s="9" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.01</v>
+        <v>7.35</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>0.01</v>
+        <v>13.73</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>0.01</v>
+        <v>10.7</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>0.01</v>
+        <v>9.98</v>
       </c>
       <c r="I54" s="10" t="n"/>
       <c r="J54" s="9" t="n">
-        <v>0.68</v>
+        <v>3.59</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.01</v>
+        <v>3.14</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.16</v>
+        <v>3.61</v>
       </c>
       <c r="M54" s="9" t="n">
-        <v>-0.28</v>
+        <v>5.3</v>
       </c>
       <c r="N54" s="10" t="n"/>
       <c r="O54" s="10" t="n"/>
       <c r="P54" s="10" t="n"/>
       <c r="Q54" s="9" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R54" s="9" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="S54" s="9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="T54" s="9" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="U54" s="10" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W54" s="10" t="n"/>
       <c r="X54" s="11" t="n">
@@ -4640,22 +4640,22 @@
       </c>
       <c r="AD54" s="12" t="n"/>
       <c r="AE54" s="9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AF54" s="9" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AG54" s="9" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AH54" s="9" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AI54" s="10" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="AJ54" s="10" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AK54" s="10" t="n"/>
     </row>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>172406</v>
+        <v>25569</v>
       </c>
       <c r="C70" s="9" t="n">
         <v>31.28</v>
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>93906</v>
+        <v>13927</v>
       </c>
       <c r="C71" s="9" t="n">
         <v>13.89</v>
@@ -5959,32 +5959,32 @@
         <v>6.51</v>
       </c>
       <c r="D72" s="15" t="n">
-        <v>6</v>
+        <v>6.27</v>
       </c>
       <c r="E72" s="15" t="n">
-        <v>5.58</v>
+        <v>7.35</v>
       </c>
       <c r="F72" s="15" t="n">
-        <v>5.89</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>8.390000000000001</v>
+        <v>10.29</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>6.89</v>
+        <v>9.34</v>
       </c>
       <c r="I72" s="15" t="n"/>
       <c r="J72" s="15" t="n">
-        <v>3.48</v>
+        <v>3.77</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>3.03</v>
+        <v>3.35</v>
       </c>
       <c r="L72" s="15" t="n">
-        <v>2.65</v>
+        <v>3.56</v>
       </c>
       <c r="M72" s="15" t="n">
-        <v>3.77</v>
+        <v>5.07</v>
       </c>
       <c r="N72" s="15" t="n"/>
       <c r="O72" s="15" t="n"/>
@@ -5993,13 +5993,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="R72" s="15" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="S72" s="15" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="T72" s="15" t="n">
-        <v>0.52</v>
+        <v>0.66</v>
       </c>
       <c r="U72" s="15" t="n">
         <v>0.9</v>
@@ -6028,22 +6028,22 @@
       </c>
       <c r="AD72" s="16" t="n"/>
       <c r="AE72" s="15" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="AF72" s="15" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="AG72" s="15" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="AH72" s="15" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="AI72" s="15" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="AJ72" s="15" t="n">
-        <v>0.51</v>
+        <v>0.64</v>
       </c>
       <c r="AK72" s="15" t="n"/>
     </row>
@@ -7823,22 +7823,22 @@
         <v>4465</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01</v>
+        <v>7.35</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0.01</v>
+        <v>13.73</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.01</v>
+        <v>10.7</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.01</v>
+        <v>9.98</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>172406</v>
+        <v>25569</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>31.28</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>93906</v>
+        <v>13927</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>13.89</v>
@@ -9573,16 +9573,16 @@
         <v>4465</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0.68</v>
+        <v>3.59</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.01</v>
+        <v>3.14</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.16</v>
+        <v>3.61</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-0.28</v>
+        <v>5.3</v>
       </c>
       <c r="J29" s="9" t="n"/>
       <c r="K29" s="9" t="n"/>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>172406</v>
+        <v>25569</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>18.39</v>
@@ -9930,7 +9930,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>93906</v>
+        <v>13927</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>7.78</v>
@@ -11397,22 +11397,22 @@
         <v>4465</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -11742,7 +11742,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>172406</v>
+        <v>25569</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>2.06</v>
@@ -11786,7 +11786,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>93906</v>
+        <v>13927</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>1.12</v>
@@ -13620,7 +13620,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>172406</v>
+        <v>25569</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>6.6</v>
@@ -13664,7 +13664,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>93906</v>
+        <v>13927</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>8.1</v>
@@ -15143,22 +15143,22 @@
         <v>4465</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -15488,7 +15488,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>172406</v>
+        <v>25569</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1.66</v>
@@ -15532,7 +15532,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>93906</v>
+        <v>13927</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.64</v>
@@ -24633,7 +24633,7 @@
         <v>60.72</v>
       </c>
       <c r="J126" s="18" t="n">
-        <v>85308163680</v>
+        <v>85308175580</v>
       </c>
       <c r="K126" s="18" t="n">
         <v>7485538259.999999</v>
@@ -29259,19 +29259,19 @@
         <v>5024387667000</v>
       </c>
       <c r="M191" s="7" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="N191" s="7" t="n">
-        <v>0.68</v>
+        <v>3.59</v>
       </c>
       <c r="O191" s="7" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P191" s="7" t="n">
         <v>12.82</v>
       </c>
       <c r="Q191" s="7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R191" s="7" t="inlineStr">
         <is>
@@ -29334,19 +29334,19 @@
         <v>5954812811000</v>
       </c>
       <c r="M192" s="7" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="N192" s="7" t="n">
-        <v>0.01</v>
+        <v>3.14</v>
       </c>
       <c r="O192" s="7" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="P192" s="7" t="n">
         <v>16.79</v>
       </c>
       <c r="Q192" s="7" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="R192" s="7" t="inlineStr">
         <is>
@@ -29409,19 +29409,19 @@
         <v>6894504330000</v>
       </c>
       <c r="M193" s="7" t="n">
-        <v>0.01</v>
+        <v>7.35</v>
       </c>
       <c r="N193" s="7" t="n">
-        <v>0.16</v>
+        <v>3.61</v>
       </c>
       <c r="O193" s="7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="P193" s="7" t="n">
         <v>8.77</v>
       </c>
       <c r="Q193" s="7" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="R193" s="7" t="inlineStr">
         <is>
@@ -29484,19 +29484,19 @@
         <v>7191120447000</v>
       </c>
       <c r="M194" s="7" t="n">
-        <v>0.01</v>
+        <v>13.73</v>
       </c>
       <c r="N194" s="7" t="n">
-        <v>-0.28</v>
+        <v>5.3</v>
       </c>
       <c r="O194" s="7" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="P194" s="7" t="n">
         <v>5.71</v>
       </c>
       <c r="Q194" s="7" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="R194" s="7" t="inlineStr">
         <is>
@@ -29559,17 +29559,17 @@
         <v>7555178683298.183</v>
       </c>
       <c r="M195" s="17" t="n">
-        <v>0.01</v>
+        <v>10.7</v>
       </c>
       <c r="N195" s="17" t="n"/>
       <c r="O195" s="17" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="P195" s="17" t="n">
         <v>8.02</v>
       </c>
       <c r="Q195" s="17" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="R195" s="17" t="inlineStr">
         <is>
@@ -29632,17 +29632,17 @@
         <v>7945504639144.696</v>
       </c>
       <c r="M196" s="17" t="n">
-        <v>0.01</v>
+        <v>9.98</v>
       </c>
       <c r="N196" s="17" t="n"/>
       <c r="O196" s="17" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="P196" s="17" t="n">
         <v>8.18</v>
       </c>
       <c r="Q196" s="17" t="n">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="R196" s="17" t="inlineStr">
         <is>
@@ -36337,7 +36337,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15T21:51:46+09:00</t>
+          <t>2026-08-15T21:58:11+09:00</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -36337,7 +36337,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15T21:58:11+09:00</t>
+          <t>2026-08-15T22:09:38+09:00</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -815,7 +815,7 @@
         <v>37.73</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>16.36</v>
+        <v>16.58</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>14.29</v>
@@ -847,7 +847,7 @@
         <v>5.72</v>
       </c>
       <c r="U5" s="10" t="n">
-        <v>4.58</v>
+        <v>4.62</v>
       </c>
       <c r="V5" s="10" t="n">
         <v>3.73</v>
@@ -866,7 +866,7 @@
         <v>18.82</v>
       </c>
       <c r="AB5" s="12" t="n">
-        <v>31.12</v>
+        <v>30.86</v>
       </c>
       <c r="AC5" s="12" t="n">
         <v>28.77</v>
@@ -912,7 +912,7 @@
         <v>27.94</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>15.05</v>
+        <v>14.91</v>
       </c>
       <c r="H6" s="10" t="n">
         <v>14.95</v>
@@ -944,7 +944,7 @@
         <v>5.64</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="V6" s="10" t="n">
         <v>2.91</v>
@@ -963,7 +963,7 @@
         <v>22.59</v>
       </c>
       <c r="AB6" s="12" t="n">
-        <v>27.3</v>
+        <v>27.32</v>
       </c>
       <c r="AC6" s="12" t="n">
         <v>21.57</v>
@@ -1007,7 +1007,7 @@
         <v>37.73</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>18.73</v>
+        <v>20.88</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>13.14</v>
@@ -1039,7 +1039,7 @@
         <v>4.96</v>
       </c>
       <c r="U7" s="10" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="V7" s="10" t="n">
         <v>2.88</v>
@@ -1058,7 +1058,7 @@
         <v>13.74</v>
       </c>
       <c r="AB7" s="12" t="n">
-        <v>21.83</v>
+        <v>20.28</v>
       </c>
       <c r="AC7" s="12" t="n">
         <v>24.6</v>
@@ -1104,7 +1104,7 @@
         <v>13.27</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>7.46</v>
+        <v>7.12</v>
       </c>
       <c r="H8" s="10" t="n">
         <v>6.56</v>
@@ -1138,7 +1138,7 @@
         <v>2.17</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V8" s="10" t="n">
         <v>1.48</v>
@@ -1157,7 +1157,7 @@
         <v>17.78</v>
       </c>
       <c r="AB8" s="12" t="n">
-        <v>25.26</v>
+        <v>26.78</v>
       </c>
       <c r="AC8" s="12" t="n">
         <v>24.42</v>
@@ -1199,7 +1199,7 @@
         <v>10.3</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>7.48</v>
+        <v>6.89</v>
       </c>
       <c r="H9" s="10" t="n">
         <v>7.14</v>
@@ -1221,7 +1221,7 @@
         <v>2.35</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="V9" s="10" t="n">
         <v>1.27</v>
@@ -1240,7 +1240,7 @@
         <v>32.19</v>
       </c>
       <c r="AB9" s="12" t="n">
-        <v>22.8</v>
+        <v>24.95</v>
       </c>
       <c r="AC9" s="12" t="n">
         <v>19.49</v>
@@ -1277,7 +1277,9 @@
       <c r="F10" s="9" t="n">
         <v>36.95</v>
       </c>
-      <c r="G10" s="10" t="n"/>
+      <c r="G10" s="10" t="n">
+        <v>10.23</v>
+      </c>
       <c r="H10" s="10" t="n"/>
       <c r="I10" s="10" t="n"/>
       <c r="J10" s="9" t="n">
@@ -1305,7 +1307,9 @@
       <c r="T10" s="9" t="n">
         <v>2.84</v>
       </c>
-      <c r="U10" s="10" t="n"/>
+      <c r="U10" s="10" t="n">
+        <v>2.12</v>
+      </c>
       <c r="V10" s="10" t="n"/>
       <c r="W10" s="10" t="n"/>
       <c r="X10" s="11" t="n">
@@ -1320,7 +1324,9 @@
       <c r="AA10" s="11" t="n">
         <v>10.15</v>
       </c>
-      <c r="AB10" s="12" t="n"/>
+      <c r="AB10" s="12" t="n">
+        <v>22.04</v>
+      </c>
       <c r="AC10" s="12" t="n"/>
       <c r="AD10" s="12" t="n"/>
       <c r="AE10" s="9" t="n">
@@ -1357,7 +1363,7 @@
         <v>32.18</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>24.74</v>
+        <v>25.11</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>20.82</v>
@@ -1383,7 +1389,7 @@
         <v>10.52</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>8.73</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="V11" s="10" t="n">
         <v>7.16</v>
@@ -1402,7 +1408,7 @@
         <v>33.73</v>
       </c>
       <c r="AB11" s="12" t="n">
-        <v>38.87</v>
+        <v>38.43</v>
       </c>
       <c r="AC11" s="12" t="n">
         <v>37.8</v>
@@ -1446,7 +1452,7 @@
         <v>18.39</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>14.23</v>
+        <v>15.27</v>
       </c>
       <c r="H12" s="10" t="n">
         <v>10.63</v>
@@ -1480,7 +1486,7 @@
         <v>6.21</v>
       </c>
       <c r="U12" s="10" t="n">
-        <v>3.15</v>
+        <v>4.04</v>
       </c>
       <c r="V12" s="10" t="n">
         <v>2.43</v>
@@ -1499,7 +1505,7 @@
         <v>41.36</v>
       </c>
       <c r="AB12" s="12" t="n">
-        <v>24.85</v>
+        <v>26.46</v>
       </c>
       <c r="AC12" s="12" t="n">
         <v>25.78</v>
@@ -1543,7 +1549,7 @@
         <v>20.62</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>20.06</v>
+        <v>20.33</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>14.54</v>
@@ -1575,7 +1581,7 @@
         <v>6.44</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="V13" s="10" t="n">
         <v>3.93</v>
@@ -1594,7 +1600,7 @@
         <v>36.6</v>
       </c>
       <c r="AB13" s="12" t="n">
-        <v>30.99</v>
+        <v>30.6</v>
       </c>
       <c r="AC13" s="12" t="n">
         <v>31.24</v>
@@ -1640,7 +1646,7 @@
         <v>14.78</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>10.51</v>
+        <v>11.05</v>
       </c>
       <c r="H14" s="10" t="n">
         <v>8.92</v>
@@ -1674,7 +1680,7 @@
         <v>2.59</v>
       </c>
       <c r="U14" s="10" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="V14" s="10" t="n">
         <v>1.59</v>
@@ -1693,7 +1699,7 @@
         <v>19.3</v>
       </c>
       <c r="AB14" s="12" t="n">
-        <v>19.13</v>
+        <v>18.68</v>
       </c>
       <c r="AC14" s="12" t="n">
         <v>19.2</v>
@@ -1741,7 +1747,7 @@
         <v>13.58</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>7.1</v>
+        <v>6.76</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>5.98</v>
@@ -1775,7 +1781,7 @@
         <v>2.93</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="V15" s="10" t="n">
         <v>1.24</v>
@@ -1794,7 +1800,7 @@
         <v>24.23</v>
       </c>
       <c r="AB15" s="12" t="n">
-        <v>24.74</v>
+        <v>26.33</v>
       </c>
       <c r="AC15" s="12" t="n">
         <v>23.13</v>
@@ -1944,7 +1950,7 @@
         <v>20.62</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>14.64</v>
+        <v>14.91</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>11.89</v>
@@ -1978,7 +1984,7 @@
         <v>4.96</v>
       </c>
       <c r="U18" s="15" t="n">
-        <v>3.38</v>
+        <v>3.56</v>
       </c>
       <c r="V18" s="15" t="n">
         <v>2.66</v>
@@ -1997,7 +2003,7 @@
         <v>22.59</v>
       </c>
       <c r="AB18" s="16" t="n">
-        <v>25.05</v>
+        <v>26.46</v>
       </c>
       <c r="AC18" s="16" t="n">
         <v>24.51</v>
@@ -2138,7 +2144,7 @@
         <v>24.28</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>15.05</v>
+        <v>15.09</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>13.14</v>
@@ -2172,7 +2178,7 @@
         <v>5.2</v>
       </c>
       <c r="U20" s="15" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="V20" s="15" t="n">
         <v>2.88</v>
@@ -2191,7 +2197,7 @@
         <v>20.95</v>
       </c>
       <c r="AB20" s="16" t="n">
-        <v>24.85</v>
+        <v>26.39</v>
       </c>
       <c r="AC20" s="16" t="n">
         <v>24.42</v>
@@ -2289,7 +2295,7 @@
         <v>59.99</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>62.41</v>
+        <v>56.76</v>
       </c>
       <c r="H24" s="10" t="n">
         <v>32.13</v>
@@ -2323,7 +2329,7 @@
         <v>6.09</v>
       </c>
       <c r="U24" s="10" t="n">
-        <v>7.13</v>
+        <v>7</v>
       </c>
       <c r="V24" s="10" t="n">
         <v>6.11</v>
@@ -2342,7 +2348,7 @@
         <v>10.51</v>
       </c>
       <c r="AB24" s="12" t="n">
-        <v>11.93</v>
+        <v>13</v>
       </c>
       <c r="AC24" s="12" t="n">
         <v>20.47</v>
@@ -2390,7 +2396,7 @@
         <v>34.46</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>24.55</v>
+        <v>25.91</v>
       </c>
       <c r="H25" s="10" t="n">
         <v>19.93</v>
@@ -2424,7 +2430,7 @@
         <v>5</v>
       </c>
       <c r="U25" s="10" t="n">
-        <v>5.15</v>
+        <v>5.04</v>
       </c>
       <c r="V25" s="10" t="n">
         <v>4.28</v>
@@ -2443,7 +2449,7 @@
         <v>19.14</v>
       </c>
       <c r="AB25" s="12" t="n">
-        <v>22.85</v>
+        <v>21.45</v>
       </c>
       <c r="AC25" s="12" t="n">
         <v>23.46</v>
@@ -2491,7 +2497,7 @@
         <v>36.3</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>48.64</v>
+        <v>49.8</v>
       </c>
       <c r="H26" s="10" t="n">
         <v>33.79</v>
@@ -2525,7 +2531,7 @@
         <v>6.43</v>
       </c>
       <c r="U26" s="10" t="n">
-        <v>10.35</v>
+        <v>10.39</v>
       </c>
       <c r="V26" s="10" t="n">
         <v>8.33</v>
@@ -2544,7 +2550,7 @@
         <v>19.2</v>
       </c>
       <c r="AB26" s="12" t="n">
-        <v>23.24</v>
+        <v>22.68</v>
       </c>
       <c r="AC26" s="12" t="n">
         <v>27.32</v>
@@ -2590,7 +2596,7 @@
         <v>41.99</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>101.58</v>
+        <v>99.44</v>
       </c>
       <c r="H27" s="10" t="n">
         <v>34.48</v>
@@ -2624,7 +2630,7 @@
         <v>2.1</v>
       </c>
       <c r="U27" s="10" t="n">
-        <v>3.06</v>
+        <v>2.76</v>
       </c>
       <c r="V27" s="10" t="n">
         <v>2.94</v>
@@ -2643,7 +2649,7 @@
         <v>6.6</v>
       </c>
       <c r="AB27" s="12" t="n">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="AC27" s="12" t="n">
         <v>8.699999999999999</v>
@@ -2691,7 +2697,7 @@
         <v>26.64</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>18.1</v>
+        <v>17.91</v>
       </c>
       <c r="H28" s="10" t="n">
         <v>12.63</v>
@@ -2744,7 +2750,7 @@
         <v>30.05</v>
       </c>
       <c r="AB28" s="12" t="n">
-        <v>25.4</v>
+        <v>25.69</v>
       </c>
       <c r="AC28" s="12" t="n">
         <v>28.35</v>
@@ -3734,7 +3740,7 @@
         <v>36.3</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>48.64</v>
+        <v>49.8</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>32.13</v>
@@ -3768,7 +3774,7 @@
         <v>6.09</v>
       </c>
       <c r="U43" s="15" t="n">
-        <v>5.15</v>
+        <v>5.04</v>
       </c>
       <c r="V43" s="15" t="n">
         <v>4.28</v>
@@ -3787,7 +3793,7 @@
         <v>19.14</v>
       </c>
       <c r="AB43" s="16" t="n">
-        <v>22.85</v>
+        <v>21.45</v>
       </c>
       <c r="AC43" s="16" t="n">
         <v>23.46</v>
@@ -4328,7 +4334,7 @@
         <v>30.55</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>25.95</v>
+        <v>26.43</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>21.86</v>
@@ -4362,7 +4368,7 @@
         <v>4.93</v>
       </c>
       <c r="U49" s="15" t="n">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
       <c r="V49" s="15" t="n">
         <v>4.12</v>
@@ -4479,7 +4485,7 @@
         <v>47.5</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>10.29</v>
+        <v>11.28</v>
       </c>
       <c r="H53" s="10" t="n">
         <v>9.34</v>
@@ -4513,7 +4519,7 @@
         <v>2.61</v>
       </c>
       <c r="U53" s="10" t="n">
-        <v>2.76</v>
+        <v>1.21</v>
       </c>
       <c r="V53" s="10" t="n">
         <v>2.17</v>
@@ -4532,7 +4538,7 @@
         <v>5.74</v>
       </c>
       <c r="AB53" s="12" t="n">
-        <v>30.69</v>
+        <v>16.32</v>
       </c>
       <c r="AC53" s="12" t="n">
         <v>26.02</v>
@@ -4580,7 +4586,7 @@
         <v>13.73</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>10.7</v>
+        <v>11.26</v>
       </c>
       <c r="H54" s="10" t="n">
         <v>9.98</v>
@@ -4614,7 +4620,7 @@
         <v>0.77</v>
       </c>
       <c r="U54" s="10" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="V54" s="10" t="n">
         <v>0.8</v>
@@ -4633,7 +4639,7 @@
         <v>5.71</v>
       </c>
       <c r="AB54" s="12" t="n">
-        <v>8.02</v>
+        <v>7.52</v>
       </c>
       <c r="AC54" s="12" t="n">
         <v>8.18</v>
@@ -4762,7 +4768,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>8.390000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H56" s="10" t="n">
         <v>6.89</v>
@@ -5968,7 +5974,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>10.29</v>
+        <v>11.26</v>
       </c>
       <c r="H72" s="15" t="n">
         <v>9.34</v>
@@ -6501,7 +6507,7 @@
         <v>1.48</v>
       </c>
       <c r="U77" s="15" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="V77" s="15" t="n">
         <v>1.79</v>
@@ -6685,7 +6691,7 @@
         <v>37.73</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>16.36</v>
+        <v>16.58</v>
       </c>
       <c r="K2" s="9" t="n">
         <v>14.29</v>
@@ -6727,7 +6733,7 @@
         <v>27.94</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>15.05</v>
+        <v>14.91</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>14.95</v>
@@ -6767,7 +6773,7 @@
         <v>37.73</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>18.73</v>
+        <v>20.88</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>13.14</v>
@@ -6809,7 +6815,7 @@
         <v>13.27</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>7.46</v>
+        <v>7.12</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>6.56</v>
@@ -6847,7 +6853,7 @@
         <v>10.3</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>7.48</v>
+        <v>6.89</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>7.14</v>
@@ -6886,7 +6892,9 @@
       <c r="I7" s="9" t="n">
         <v>36.95</v>
       </c>
-      <c r="J7" s="9" t="n"/>
+      <c r="J7" s="9" t="n">
+        <v>10.23</v>
+      </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
     </row>
@@ -6963,7 +6971,7 @@
         <v>32.18</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>24.74</v>
+        <v>25.11</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>20.82</v>
@@ -7007,7 +7015,7 @@
         <v>18.39</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>14.23</v>
+        <v>15.27</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>10.63</v>
@@ -7047,7 +7055,7 @@
         <v>20.62</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>20.06</v>
+        <v>20.33</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>14.54</v>
@@ -7089,7 +7097,7 @@
         <v>14.78</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>10.51</v>
+        <v>11.05</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>8.92</v>
@@ -7133,7 +7141,7 @@
         <v>13.58</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>7.1</v>
+        <v>6.76</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>5.98</v>
@@ -7177,7 +7185,7 @@
         <v>59.99</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>62.41</v>
+        <v>56.76</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>32.13</v>
@@ -7221,7 +7229,7 @@
         <v>34.46</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>24.55</v>
+        <v>25.91</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>19.93</v>
@@ -7265,7 +7273,7 @@
         <v>36.3</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>48.64</v>
+        <v>49.8</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>33.79</v>
@@ -7307,7 +7315,7 @@
         <v>41.99</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>101.58</v>
+        <v>99.44</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>34.48</v>
@@ -7351,7 +7359,7 @@
         <v>26.64</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>18.1</v>
+        <v>17.91</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>12.63</v>
@@ -7791,7 +7799,7 @@
         <v>47.5</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>10.29</v>
+        <v>11.28</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>9.34</v>
@@ -7835,7 +7843,7 @@
         <v>13.73</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>10.7</v>
+        <v>11.26</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>9.98</v>
@@ -8267,7 +8275,7 @@
         <v>8.390000000000001</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>8.390000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>6.89</v>
@@ -10235,7 +10243,7 @@
         <v>5.72</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>4.58</v>
+        <v>4.62</v>
       </c>
       <c r="K2" s="9" t="n">
         <v>3.73</v>
@@ -10279,7 +10287,7 @@
         <v>5.64</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>2.91</v>
@@ -10323,7 +10331,7 @@
         <v>4.96</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>2.88</v>
@@ -10367,7 +10375,7 @@
         <v>2.17</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="K5" s="9" t="n">
         <v>1.48</v>
@@ -10405,7 +10413,7 @@
         <v>2.35</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>1.27</v>
@@ -10448,7 +10456,9 @@
       <c r="I7" s="9" t="n">
         <v>2.84</v>
       </c>
-      <c r="J7" s="9" t="n"/>
+      <c r="J7" s="9" t="n">
+        <v>2.12</v>
+      </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
     </row>
@@ -10529,7 +10539,7 @@
         <v>10.52</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>8.73</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>7.16</v>
@@ -10573,7 +10583,7 @@
         <v>6.21</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>3.15</v>
+        <v>4.04</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>2.43</v>
@@ -10617,7 +10627,7 @@
         <v>6.44</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>3.93</v>
@@ -10661,7 +10671,7 @@
         <v>2.59</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>1.59</v>
@@ -10705,7 +10715,7 @@
         <v>2.93</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>1.24</v>
@@ -10749,7 +10759,7 @@
         <v>6.09</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>7.13</v>
+        <v>7</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>6.11</v>
@@ -10793,7 +10803,7 @@
         <v>5</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>5.15</v>
+        <v>5.04</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>4.28</v>
@@ -10837,7 +10847,7 @@
         <v>6.43</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>10.35</v>
+        <v>10.39</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>8.33</v>
@@ -10881,7 +10891,7 @@
         <v>2.1</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>3.06</v>
+        <v>2.76</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>2.94</v>
@@ -11365,7 +11375,7 @@
         <v>2.61</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>2.76</v>
+        <v>1.21</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>2.17</v>
@@ -11409,7 +11419,7 @@
         <v>0.77</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0.8</v>
@@ -12103,7 +12113,7 @@
         <v>18.82</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>31.12</v>
+        <v>30.86</v>
       </c>
       <c r="K2" s="11" t="n">
         <v>28.77</v>
@@ -12147,7 +12157,7 @@
         <v>22.59</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>27.3</v>
+        <v>27.32</v>
       </c>
       <c r="K3" s="11" t="n">
         <v>21.57</v>
@@ -12191,7 +12201,7 @@
         <v>13.74</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>21.83</v>
+        <v>20.28</v>
       </c>
       <c r="K4" s="11" t="n">
         <v>24.6</v>
@@ -12235,7 +12245,7 @@
         <v>17.78</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>25.26</v>
+        <v>26.78</v>
       </c>
       <c r="K5" s="11" t="n">
         <v>24.42</v>
@@ -12279,7 +12289,7 @@
         <v>32.19</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>22.8</v>
+        <v>24.95</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>19.49</v>
@@ -12322,7 +12332,9 @@
       <c r="I7" s="11" t="n">
         <v>10.15</v>
       </c>
-      <c r="J7" s="11" t="n"/>
+      <c r="J7" s="11" t="n">
+        <v>22.04</v>
+      </c>
       <c r="K7" s="11" t="n"/>
       <c r="L7" s="11" t="n"/>
     </row>
@@ -12407,7 +12419,7 @@
         <v>33.73</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>38.87</v>
+        <v>38.43</v>
       </c>
       <c r="K9" s="11" t="n">
         <v>37.8</v>
@@ -12451,7 +12463,7 @@
         <v>41.36</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>24.85</v>
+        <v>26.46</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>25.78</v>
@@ -12495,7 +12507,7 @@
         <v>36.6</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>30.99</v>
+        <v>30.6</v>
       </c>
       <c r="K11" s="11" t="n">
         <v>31.24</v>
@@ -12539,7 +12551,7 @@
         <v>19.3</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>19.13</v>
+        <v>18.68</v>
       </c>
       <c r="K12" s="11" t="n">
         <v>19.2</v>
@@ -12583,7 +12595,7 @@
         <v>24.23</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>24.74</v>
+        <v>26.33</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>23.13</v>
@@ -12627,7 +12639,7 @@
         <v>10.51</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>11.93</v>
+        <v>13</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>20.47</v>
@@ -12671,7 +12683,7 @@
         <v>19.14</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>22.85</v>
+        <v>21.45</v>
       </c>
       <c r="K15" s="11" t="n">
         <v>23.46</v>
@@ -12715,7 +12727,7 @@
         <v>19.2</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>23.24</v>
+        <v>22.68</v>
       </c>
       <c r="K16" s="11" t="n">
         <v>27.32</v>
@@ -12759,7 +12771,7 @@
         <v>6.6</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="K17" s="11" t="n">
         <v>8.699999999999999</v>
@@ -12803,7 +12815,7 @@
         <v>30.05</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>25.4</v>
+        <v>25.69</v>
       </c>
       <c r="K18" s="11" t="n">
         <v>28.35</v>
@@ -13243,7 +13255,7 @@
         <v>5.74</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>30.69</v>
+        <v>16.32</v>
       </c>
       <c r="K28" s="11" t="n">
         <v>26.02</v>
@@ -13287,7 +13299,7 @@
         <v>5.71</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>8.02</v>
+        <v>7.52</v>
       </c>
       <c r="K29" s="11" t="n">
         <v>8.18</v>
@@ -16200,14 +16212,14 @@
         <v>11681253647342.87</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>16.36</v>
+        <v>16.58</v>
       </c>
       <c r="N6" s="17" t="n"/>
       <c r="O6" s="17" t="n">
-        <v>4.58</v>
+        <v>4.62</v>
       </c>
       <c r="P6" s="17" t="n">
-        <v>31.12</v>
+        <v>30.86</v>
       </c>
       <c r="Q6" s="17" t="n">
         <v>2.14</v>
@@ -16695,14 +16707,14 @@
         <v>8121009511148.494</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>15.05</v>
+        <v>14.91</v>
       </c>
       <c r="N13" s="17" t="n"/>
       <c r="O13" s="17" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="P13" s="17" t="n">
-        <v>27.3</v>
+        <v>27.32</v>
       </c>
       <c r="Q13" s="17" t="n">
         <v>1.85</v>
@@ -17188,14 +17200,14 @@
         <v>5165719366941.109</v>
       </c>
       <c r="M20" s="17" t="n">
-        <v>18.73</v>
+        <v>20.88</v>
       </c>
       <c r="N20" s="17" t="n"/>
       <c r="O20" s="17" t="n">
-        <v>3.69</v>
+        <v>3.72</v>
       </c>
       <c r="P20" s="17" t="n">
-        <v>21.83</v>
+        <v>20.28</v>
       </c>
       <c r="Q20" s="17" t="n">
         <v>1.48</v>
@@ -17685,14 +17697,14 @@
         <v>15680079391022.62</v>
       </c>
       <c r="M27" s="17" t="n">
-        <v>7.46</v>
+        <v>7.12</v>
       </c>
       <c r="N27" s="17" t="n"/>
       <c r="O27" s="17" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="P27" s="17" t="n">
-        <v>25.26</v>
+        <v>26.78</v>
       </c>
       <c r="Q27" s="17" t="n">
         <v>0.78</v>
@@ -18154,14 +18166,14 @@
         <v>1362707980317.154</v>
       </c>
       <c r="M34" s="17" t="n">
-        <v>7.48</v>
+        <v>6.89</v>
       </c>
       <c r="N34" s="17" t="n"/>
       <c r="O34" s="17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P34" s="17" t="n">
-        <v>22.8</v>
+        <v>24.95</v>
       </c>
       <c r="Q34" s="17" t="n">
         <v>1.56</v>
@@ -18638,10 +18650,16 @@
       </c>
       <c r="K41" s="18" t="n"/>
       <c r="L41" s="18" t="n"/>
-      <c r="M41" s="17" t="n"/>
+      <c r="M41" s="17" t="n">
+        <v>10.23</v>
+      </c>
       <c r="N41" s="17" t="n"/>
-      <c r="O41" s="17" t="n"/>
-      <c r="P41" s="17" t="n"/>
+      <c r="O41" s="17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="P41" s="17" t="n">
+        <v>22.04</v>
+      </c>
       <c r="Q41" s="17" t="n"/>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -19589,14 +19607,14 @@
         <v>1010701492468.578</v>
       </c>
       <c r="M55" s="17" t="n">
-        <v>24.74</v>
+        <v>25.11</v>
       </c>
       <c r="N55" s="17" t="n"/>
       <c r="O55" s="17" t="n">
-        <v>8.73</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="P55" s="17" t="n">
-        <v>38.87</v>
+        <v>38.43</v>
       </c>
       <c r="Q55" s="17" t="n">
         <v>3.72</v>
@@ -20088,14 +20106,14 @@
         <v>627617114397</v>
       </c>
       <c r="M62" s="17" t="n">
-        <v>14.23</v>
+        <v>15.27</v>
       </c>
       <c r="N62" s="17" t="n"/>
       <c r="O62" s="17" t="n">
-        <v>3.15</v>
+        <v>4.04</v>
       </c>
       <c r="P62" s="17" t="n">
-        <v>24.85</v>
+        <v>26.46</v>
       </c>
       <c r="Q62" s="17" t="n">
         <v>3.19</v>
@@ -20581,14 +20599,14 @@
         <v>760045029521.428</v>
       </c>
       <c r="M69" s="17" t="n">
-        <v>20.06</v>
+        <v>20.33</v>
       </c>
       <c r="N69" s="17" t="n"/>
       <c r="O69" s="17" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="P69" s="17" t="n">
-        <v>30.99</v>
+        <v>30.6</v>
       </c>
       <c r="Q69" s="17" t="n">
         <v>2.54</v>
@@ -21078,14 +21096,14 @@
         <v>680508493974.6207</v>
       </c>
       <c r="M76" s="17" t="n">
-        <v>10.51</v>
+        <v>11.05</v>
       </c>
       <c r="N76" s="17" t="n"/>
       <c r="O76" s="17" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="P76" s="17" t="n">
-        <v>19.13</v>
+        <v>18.68</v>
       </c>
       <c r="Q76" s="17" t="n">
         <v>1.32</v>
@@ -21577,14 +21595,14 @@
         <v>331992443278</v>
       </c>
       <c r="M83" s="17" t="n">
-        <v>7.1</v>
+        <v>6.76</v>
       </c>
       <c r="N83" s="17" t="n"/>
       <c r="O83" s="17" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="P83" s="17" t="n">
-        <v>24.74</v>
+        <v>26.33</v>
       </c>
       <c r="Q83" s="17" t="n">
         <v>0.61</v>
@@ -22076,14 +22094,14 @@
         <v>2002502407859.624</v>
       </c>
       <c r="M90" s="17" t="n">
-        <v>62.41</v>
+        <v>56.76</v>
       </c>
       <c r="N90" s="17" t="n"/>
       <c r="O90" s="17" t="n">
-        <v>7.13</v>
+        <v>7</v>
       </c>
       <c r="P90" s="17" t="n">
-        <v>11.93</v>
+        <v>13</v>
       </c>
       <c r="Q90" s="17" t="n">
         <v>2.66</v>
@@ -22575,14 +22593,14 @@
         <v>11587926646827.09</v>
       </c>
       <c r="M97" s="17" t="n">
-        <v>24.55</v>
+        <v>25.91</v>
       </c>
       <c r="N97" s="17" t="n"/>
       <c r="O97" s="17" t="n">
-        <v>5.15</v>
+        <v>5.04</v>
       </c>
       <c r="P97" s="17" t="n">
-        <v>22.85</v>
+        <v>21.45</v>
       </c>
       <c r="Q97" s="17" t="n">
         <v>1.85</v>
@@ -23074,14 +23092,14 @@
         <v>1720239057954.933</v>
       </c>
       <c r="M104" s="17" t="n">
-        <v>48.64</v>
+        <v>49.8</v>
       </c>
       <c r="N104" s="17" t="n"/>
       <c r="O104" s="17" t="n">
-        <v>10.35</v>
+        <v>10.39</v>
       </c>
       <c r="P104" s="17" t="n">
-        <v>23.24</v>
+        <v>22.68</v>
       </c>
       <c r="Q104" s="17" t="n">
         <v>3.45</v>
@@ -23571,14 +23589,14 @@
         <v>4913056594443.892</v>
       </c>
       <c r="M111" s="17" t="n">
-        <v>101.58</v>
+        <v>99.44</v>
       </c>
       <c r="N111" s="17" t="n"/>
       <c r="O111" s="17" t="n">
-        <v>3.06</v>
+        <v>2.76</v>
       </c>
       <c r="P111" s="17" t="n">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="Q111" s="17" t="n">
         <v>3.36</v>
@@ -24070,14 +24088,14 @@
         <v>3893313034361.641</v>
       </c>
       <c r="M118" s="17" t="n">
-        <v>18.1</v>
+        <v>17.91</v>
       </c>
       <c r="N118" s="17" t="n"/>
       <c r="O118" s="17" t="n">
         <v>4.12</v>
       </c>
       <c r="P118" s="17" t="n">
-        <v>25.4</v>
+        <v>25.69</v>
       </c>
       <c r="Q118" s="17" t="n">
         <v>2.36</v>
@@ -29060,14 +29078,14 @@
         <v>2405327680283.352</v>
       </c>
       <c r="M188" s="17" t="n">
-        <v>10.29</v>
+        <v>11.28</v>
       </c>
       <c r="N188" s="17" t="n"/>
       <c r="O188" s="17" t="n">
-        <v>2.76</v>
+        <v>1.21</v>
       </c>
       <c r="P188" s="17" t="n">
-        <v>30.69</v>
+        <v>16.32</v>
       </c>
       <c r="Q188" s="17" t="n">
         <v>0.7</v>
@@ -29559,14 +29577,14 @@
         <v>7555178683298.183</v>
       </c>
       <c r="M195" s="17" t="n">
-        <v>10.7</v>
+        <v>11.26</v>
       </c>
       <c r="N195" s="17" t="n"/>
       <c r="O195" s="17" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="P195" s="17" t="n">
-        <v>8.02</v>
+        <v>7.52</v>
       </c>
       <c r="Q195" s="17" t="n">
         <v>0.66</v>
@@ -34513,7 +34531,7 @@
         <v>326589024162.7744</v>
       </c>
       <c r="M265" s="17" t="n">
-        <v>8.390000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="N265" s="17" t="n"/>
       <c r="O265" s="17" t="n">
@@ -36337,7 +36355,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15T22:09:38+09:00</t>
+          <t>2026-08-15T23:41:33+09:00</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>37771</v>
+        <v>34297</v>
       </c>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n">
@@ -815,10 +815,10 @@
         <v>37.73</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>16.58</v>
+        <v>15.31</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>14.29</v>
+        <v>12.69</v>
       </c>
       <c r="I5" s="10" t="n"/>
       <c r="J5" s="9" t="n"/>
@@ -847,10 +847,10 @@
         <v>5.72</v>
       </c>
       <c r="U5" s="10" t="n">
-        <v>4.62</v>
+        <v>4.3</v>
       </c>
       <c r="V5" s="10" t="n">
-        <v>3.73</v>
+        <v>3.12</v>
       </c>
       <c r="W5" s="10" t="n"/>
       <c r="X5" s="11" t="n">
@@ -866,10 +866,10 @@
         <v>18.82</v>
       </c>
       <c r="AB5" s="12" t="n">
-        <v>30.86</v>
+        <v>31.14</v>
       </c>
       <c r="AC5" s="12" t="n">
-        <v>28.77</v>
+        <v>27.39</v>
       </c>
       <c r="AD5" s="12" t="n"/>
       <c r="AE5" s="9" t="n">
@@ -885,10 +885,10 @@
         <v>3.04</v>
       </c>
       <c r="AI5" s="10" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="AJ5" s="10" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AK5" s="10" t="n"/>
     </row>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>20717</v>
+        <v>18614</v>
       </c>
       <c r="C6" s="9" t="n"/>
       <c r="D6" s="9" t="n">
@@ -912,10 +912,10 @@
         <v>27.94</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>14.91</v>
+        <v>13.78</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>14.95</v>
+        <v>13.14</v>
       </c>
       <c r="I6" s="10" t="n"/>
       <c r="J6" s="9" t="n"/>
@@ -944,10 +944,10 @@
         <v>5.64</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>3.56</v>
+        <v>3.29</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>2.91</v>
+        <v>2.56</v>
       </c>
       <c r="W6" s="10" t="n"/>
       <c r="X6" s="11" t="n">
@@ -982,10 +982,10 @@
         <v>2.72</v>
       </c>
       <c r="AI6" s="10" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AJ6" s="10" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AK6" s="10" t="n"/>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>13444</v>
+        <v>12449</v>
       </c>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
@@ -1007,10 +1007,10 @@
         <v>37.73</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>20.88</v>
+        <v>19.47</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>13.14</v>
+        <v>11.91</v>
       </c>
       <c r="I7" s="10" t="n"/>
       <c r="J7" s="9" t="n"/>
@@ -1039,10 +1039,10 @@
         <v>4.96</v>
       </c>
       <c r="U7" s="10" t="n">
-        <v>3.72</v>
+        <v>3.47</v>
       </c>
       <c r="V7" s="10" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="W7" s="10" t="n"/>
       <c r="X7" s="11" t="n">
@@ -1077,10 +1077,10 @@
         <v>1.93</v>
       </c>
       <c r="AI7" s="10" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AJ7" s="10" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" s="10" t="n"/>
     </row>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>19265</v>
+        <v>17781</v>
       </c>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n">
@@ -1104,10 +1104,10 @@
         <v>13.27</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>7.12</v>
+        <v>6.67</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>6.56</v>
+        <v>5.88</v>
       </c>
       <c r="I8" s="10" t="n"/>
       <c r="J8" s="9" t="n">
@@ -1138,10 +1138,10 @@
         <v>2.17</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="W8" s="10" t="n"/>
       <c r="X8" s="11" t="n">
@@ -1157,10 +1157,10 @@
         <v>17.78</v>
       </c>
       <c r="AB8" s="12" t="n">
-        <v>26.78</v>
+        <v>26.62</v>
       </c>
       <c r="AC8" s="12" t="n">
-        <v>24.42</v>
+        <v>23.41</v>
       </c>
       <c r="AD8" s="12" t="n"/>
       <c r="AE8" s="9" t="n">
@@ -1176,10 +1176,10 @@
         <v>0.96</v>
       </c>
       <c r="AI8" s="10" t="n">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
       <c r="AJ8" s="10" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="AK8" s="10" t="n"/>
     </row>
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1477</v>
+        <v>1354</v>
       </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
@@ -1199,10 +1199,10 @@
         <v>10.3</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>6.89</v>
+        <v>6.35</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>7.14</v>
+        <v>6.4</v>
       </c>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="9" t="n"/>
@@ -1221,10 +1221,10 @@
         <v>2.35</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="V9" s="10" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="W9" s="10" t="n"/>
       <c r="X9" s="11" t="n">
@@ -1243,7 +1243,7 @@
         <v>24.95</v>
       </c>
       <c r="AC9" s="12" t="n">
-        <v>19.49</v>
+        <v>19.48</v>
       </c>
       <c r="AD9" s="12" t="n"/>
       <c r="AE9" s="9" t="n"/>
@@ -1253,10 +1253,10 @@
         <v>2.09</v>
       </c>
       <c r="AI9" s="10" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AJ9" s="10" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AK9" s="10" t="n"/>
     </row>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1141</v>
+        <v>1104</v>
       </c>
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="9" t="n"/>
@@ -1278,7 +1278,7 @@
         <v>36.95</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>10.23</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H10" s="10" t="n"/>
       <c r="I10" s="10" t="n"/>
@@ -1308,7 +1308,7 @@
         <v>2.84</v>
       </c>
       <c r="U10" s="10" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="V10" s="10" t="n"/>
       <c r="W10" s="10" t="n"/>
@@ -1325,7 +1325,7 @@
         <v>10.15</v>
       </c>
       <c r="AB10" s="12" t="n">
-        <v>22.04</v>
+        <v>24.85</v>
       </c>
       <c r="AC10" s="12" t="n"/>
       <c r="AD10" s="12" t="n"/>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>6227</v>
+        <v>6395</v>
       </c>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
@@ -1363,10 +1363,10 @@
         <v>32.18</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>25.11</v>
+        <v>25.9</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>20.82</v>
+        <v>20.91</v>
       </c>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="9" t="n"/>
@@ -1389,10 +1389,10 @@
         <v>10.52</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>8.789999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="V11" s="10" t="n">
-        <v>7.16</v>
+        <v>7.12</v>
       </c>
       <c r="W11" s="10" t="n"/>
       <c r="X11" s="11" t="n">
@@ -1411,7 +1411,7 @@
         <v>38.43</v>
       </c>
       <c r="AC11" s="12" t="n">
-        <v>37.8</v>
+        <v>37.49</v>
       </c>
       <c r="AD11" s="12" t="n"/>
       <c r="AE11" s="9" t="n"/>
@@ -1423,10 +1423,10 @@
         <v>4.38</v>
       </c>
       <c r="AI11" s="10" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="AJ11" s="10" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="AK11" s="10" t="n"/>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>1393</v>
+        <v>1216</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>14.21</v>
@@ -1452,10 +1452,10 @@
         <v>18.39</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>15.27</v>
+        <v>14.04</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>10.63</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="I12" s="10" t="n"/>
       <c r="J12" s="9" t="n">
@@ -1486,10 +1486,10 @@
         <v>6.21</v>
       </c>
       <c r="U12" s="10" t="n">
-        <v>4.04</v>
+        <v>3.72</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="W12" s="10" t="n"/>
       <c r="X12" s="11" t="n">
@@ -1508,7 +1508,7 @@
         <v>26.46</v>
       </c>
       <c r="AC12" s="12" t="n">
-        <v>25.78</v>
+        <v>25.85</v>
       </c>
       <c r="AD12" s="12" t="n"/>
       <c r="AE12" s="9" t="n">
@@ -1524,10 +1524,10 @@
         <v>7.54</v>
       </c>
       <c r="AI12" s="10" t="n">
-        <v>3.19</v>
+        <v>2.77</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="AK12" s="10" t="n"/>
     </row>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>2888</v>
+        <v>2654</v>
       </c>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
@@ -1549,10 +1549,10 @@
         <v>20.62</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>20.33</v>
+        <v>19.32</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>14.54</v>
+        <v>13.07</v>
       </c>
       <c r="I13" s="10" t="n"/>
       <c r="J13" s="9" t="n"/>
@@ -1581,10 +1581,10 @@
         <v>6.44</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>5.36</v>
+        <v>5.1</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>3.93</v>
+        <v>3.53</v>
       </c>
       <c r="W13" s="10" t="n"/>
       <c r="X13" s="11" t="n">
@@ -1619,10 +1619,10 @@
         <v>2.61</v>
       </c>
       <c r="AI13" s="10" t="n">
-        <v>2.54</v>
+        <v>2.29</v>
       </c>
       <c r="AJ13" s="10" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AK13" s="10" t="n"/>
     </row>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>894</v>
+        <v>819</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>23.46</v>
@@ -1646,10 +1646,10 @@
         <v>14.78</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>11.05</v>
+        <v>10.26</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>8.92</v>
+        <v>8</v>
       </c>
       <c r="I14" s="10" t="n"/>
       <c r="J14" s="9" t="n">
@@ -1680,10 +1680,10 @@
         <v>2.59</v>
       </c>
       <c r="U14" s="10" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="W14" s="10" t="n"/>
       <c r="X14" s="11" t="n">
@@ -1699,10 +1699,10 @@
         <v>19.3</v>
       </c>
       <c r="AB14" s="12" t="n">
-        <v>18.68</v>
+        <v>18.75</v>
       </c>
       <c r="AC14" s="12" t="n">
-        <v>19.2</v>
+        <v>19.15</v>
       </c>
       <c r="AD14" s="12" t="n"/>
       <c r="AE14" s="9" t="n">
@@ -1718,10 +1718,10 @@
         <v>1.65</v>
       </c>
       <c r="AI14" s="10" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AJ14" s="10" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AK14" s="10" t="n"/>
     </row>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>37.11</v>
@@ -1747,10 +1747,10 @@
         <v>13.58</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>6.76</v>
+        <v>6.23</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>5.98</v>
+        <v>5.76</v>
       </c>
       <c r="I15" s="10" t="n"/>
       <c r="J15" s="9" t="n">
@@ -1781,10 +1781,10 @@
         <v>2.93</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V15" s="10" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="W15" s="10" t="n"/>
       <c r="X15" s="11" t="n">
@@ -1800,7 +1800,7 @@
         <v>24.23</v>
       </c>
       <c r="AB15" s="12" t="n">
-        <v>26.33</v>
+        <v>28.53</v>
       </c>
       <c r="AC15" s="12" t="n">
         <v>23.13</v>
@@ -1819,10 +1819,10 @@
         <v>1.02</v>
       </c>
       <c r="AI15" s="10" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="AJ15" s="10" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AK15" s="10" t="n"/>
     </row>
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>4967</v>
+        <v>5241</v>
       </c>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="9" t="n"/>
@@ -1850,12 +1850,8 @@
       <c r="F17" s="9" t="n">
         <v>44.03</v>
       </c>
-      <c r="G17" s="10" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
       <c r="I17" s="10" t="n"/>
       <c r="J17" s="9" t="n">
         <v>991.9299999999999</v>
@@ -1885,10 +1881,10 @@
         <v>5.43</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>3.64</v>
+        <v>3.81</v>
       </c>
       <c r="V17" s="10" t="n">
-        <v>2.98</v>
+        <v>3.12</v>
       </c>
       <c r="W17" s="10" t="n"/>
       <c r="X17" s="11" t="n">
@@ -1923,10 +1919,10 @@
         <v>0.61</v>
       </c>
       <c r="AI17" s="10" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="AJ17" s="10" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="AK17" s="10" t="n"/>
     </row>
@@ -1950,10 +1946,10 @@
         <v>20.62</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>14.91</v>
+        <v>13.78</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>11.89</v>
+        <v>10.52</v>
       </c>
       <c r="I18" s="15" t="n"/>
       <c r="J18" s="15" t="n">
@@ -1984,10 +1980,10 @@
         <v>4.96</v>
       </c>
       <c r="U18" s="15" t="n">
-        <v>3.56</v>
+        <v>3.29</v>
       </c>
       <c r="V18" s="15" t="n">
-        <v>2.66</v>
+        <v>2.33</v>
       </c>
       <c r="W18" s="15" t="n"/>
       <c r="X18" s="16" t="n">
@@ -2003,10 +1999,10 @@
         <v>22.59</v>
       </c>
       <c r="AB18" s="16" t="n">
-        <v>26.46</v>
+        <v>26.62</v>
       </c>
       <c r="AC18" s="16" t="n">
-        <v>24.51</v>
+        <v>24.01</v>
       </c>
       <c r="AD18" s="16" t="n"/>
       <c r="AE18" s="15" t="n">
@@ -2022,10 +2018,10 @@
         <v>2.09</v>
       </c>
       <c r="AI18" s="15" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AJ18" s="15" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AK18" s="15" t="n"/>
     </row>
@@ -2044,12 +2040,8 @@
       <c r="F19" s="15" t="n">
         <v>44.03</v>
       </c>
-      <c r="G19" s="15" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="H19" s="15" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n"/>
       <c r="I19" s="15" t="n"/>
       <c r="J19" s="15" t="n">
         <v>991.9299999999999</v>
@@ -2079,10 +2071,10 @@
         <v>5.43</v>
       </c>
       <c r="U19" s="15" t="n">
-        <v>3.64</v>
+        <v>3.81</v>
       </c>
       <c r="V19" s="15" t="n">
-        <v>2.98</v>
+        <v>3.12</v>
       </c>
       <c r="W19" s="15" t="n"/>
       <c r="X19" s="16" t="n">
@@ -2117,10 +2109,10 @@
         <v>0.61</v>
       </c>
       <c r="AI19" s="15" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="AJ19" s="15" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="AK19" s="15" t="n"/>
     </row>
@@ -2144,10 +2136,10 @@
         <v>24.28</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>15.09</v>
+        <v>13.78</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>13.14</v>
+        <v>10.52</v>
       </c>
       <c r="I20" s="15" t="n"/>
       <c r="J20" s="15" t="n">
@@ -2178,10 +2170,10 @@
         <v>5.2</v>
       </c>
       <c r="U20" s="15" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="V20" s="15" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="W20" s="15" t="n"/>
       <c r="X20" s="16" t="n">
@@ -2197,10 +2189,10 @@
         <v>20.95</v>
       </c>
       <c r="AB20" s="16" t="n">
-        <v>26.39</v>
+        <v>26.54</v>
       </c>
       <c r="AC20" s="16" t="n">
-        <v>24.42</v>
+        <v>23.41</v>
       </c>
       <c r="AD20" s="16" t="n"/>
       <c r="AE20" s="15" t="n">
@@ -2216,10 +2208,10 @@
         <v>2.01</v>
       </c>
       <c r="AI20" s="15" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AJ20" s="15" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AK20" s="15" t="n"/>
     </row>
@@ -2280,7 +2272,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>10072</v>
+        <v>9143</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>41.88</v>
@@ -2295,10 +2287,10 @@
         <v>59.99</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>56.76</v>
+        <v>52.22</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>32.13</v>
+        <v>28.53</v>
       </c>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="9" t="n">
@@ -2329,10 +2321,10 @@
         <v>6.09</v>
       </c>
       <c r="U24" s="10" t="n">
-        <v>7</v>
+        <v>6.44</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>6.11</v>
+        <v>5.47</v>
       </c>
       <c r="W24" s="10" t="n"/>
       <c r="X24" s="11" t="n">
@@ -2351,7 +2343,7 @@
         <v>13</v>
       </c>
       <c r="AC24" s="12" t="n">
-        <v>20.47</v>
+        <v>20.59</v>
       </c>
       <c r="AD24" s="12" t="n"/>
       <c r="AE24" s="9" t="n">
@@ -2367,10 +2359,10 @@
         <v>3.02</v>
       </c>
       <c r="AI24" s="10" t="n">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="AJ24" s="10" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AK24" s="10" t="n"/>
     </row>
@@ -2381,7 +2373,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>42122</v>
+        <v>40276</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>19.31</v>
@@ -2396,10 +2388,10 @@
         <v>34.46</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>25.91</v>
+        <v>26.05</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>19.93</v>
+        <v>18.65</v>
       </c>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="9" t="n">
@@ -2430,10 +2422,10 @@
         <v>5</v>
       </c>
       <c r="U25" s="10" t="n">
-        <v>5.04</v>
+        <v>5.07</v>
       </c>
       <c r="V25" s="10" t="n">
-        <v>4.28</v>
+        <v>3.94</v>
       </c>
       <c r="W25" s="10" t="n"/>
       <c r="X25" s="11" t="n">
@@ -2449,10 +2441,10 @@
         <v>19.14</v>
       </c>
       <c r="AB25" s="12" t="n">
-        <v>21.45</v>
+        <v>21.47</v>
       </c>
       <c r="AC25" s="12" t="n">
-        <v>23.46</v>
+        <v>23.14</v>
       </c>
       <c r="AD25" s="12" t="n"/>
       <c r="AE25" s="9" t="n">
@@ -2468,10 +2460,10 @@
         <v>1.81</v>
       </c>
       <c r="AI25" s="10" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AJ25" s="10" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AK25" s="10" t="n"/>
     </row>
@@ -2482,7 +2474,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>12566</v>
+        <v>10954</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>16.34</v>
@@ -2497,10 +2489,10 @@
         <v>36.3</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>49.8</v>
+        <v>48.09</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>33.79</v>
+        <v>28.81</v>
       </c>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="9" t="n">
@@ -2531,10 +2523,10 @@
         <v>6.43</v>
       </c>
       <c r="U26" s="10" t="n">
-        <v>10.39</v>
+        <v>10.03</v>
       </c>
       <c r="V26" s="10" t="n">
-        <v>8.33</v>
+        <v>7.15</v>
       </c>
       <c r="W26" s="10" t="n"/>
       <c r="X26" s="11" t="n">
@@ -2553,7 +2545,7 @@
         <v>22.68</v>
       </c>
       <c r="AC26" s="12" t="n">
-        <v>27.32</v>
+        <v>27.48</v>
       </c>
       <c r="AD26" s="12" t="n"/>
       <c r="AE26" s="9" t="n">
@@ -2569,10 +2561,10 @@
         <v>2.14</v>
       </c>
       <c r="AI26" s="10" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="AJ26" s="10" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="AK26" s="10" t="n"/>
     </row>
@@ -2583,7 +2575,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>10598</v>
+        <v>9485</v>
       </c>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n">
@@ -2596,10 +2588,10 @@
         <v>41.99</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>99.44</v>
+        <v>97.16</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>34.48</v>
+        <v>30.18</v>
       </c>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="9" t="n">
@@ -2630,10 +2622,10 @@
         <v>2.1</v>
       </c>
       <c r="U27" s="10" t="n">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="V27" s="10" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="11" t="n">
@@ -2649,10 +2641,10 @@
         <v>6.6</v>
       </c>
       <c r="AB27" s="12" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="AC27" s="12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="AD27" s="12" t="n"/>
       <c r="AE27" s="9" t="n">
@@ -2668,10 +2660,10 @@
         <v>2.78</v>
       </c>
       <c r="AI27" s="10" t="n">
-        <v>3.36</v>
+        <v>2.94</v>
       </c>
       <c r="AJ27" s="10" t="n">
-        <v>2.94</v>
+        <v>2.57</v>
       </c>
       <c r="AK27" s="10" t="n"/>
     </row>
@@ -2682,7 +2674,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>11316</v>
+        <v>10245</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>15.67</v>
@@ -2697,10 +2689,10 @@
         <v>26.64</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>17.91</v>
+        <v>16.73</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>12.63</v>
+        <v>11.19</v>
       </c>
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="9" t="n">
@@ -2731,10 +2723,10 @@
         <v>6.66</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>4.12</v>
+        <v>3.85</v>
       </c>
       <c r="V28" s="10" t="n">
-        <v>3.17</v>
+        <v>2.81</v>
       </c>
       <c r="W28" s="10" t="n"/>
       <c r="X28" s="11" t="n">
@@ -2753,7 +2745,7 @@
         <v>25.69</v>
       </c>
       <c r="AC28" s="12" t="n">
-        <v>28.35</v>
+        <v>28.36</v>
       </c>
       <c r="AD28" s="12" t="n"/>
       <c r="AE28" s="9" t="n">
@@ -2769,10 +2761,10 @@
         <v>3.51</v>
       </c>
       <c r="AI28" s="10" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="AJ28" s="10" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AK28" s="10" t="n"/>
     </row>
@@ -2790,7 +2782,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>139388</v>
+        <v>129058</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>21.56</v>
@@ -2805,10 +2797,10 @@
         <v>22.08</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>19.98</v>
+        <v>18.5</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>18.62</v>
+        <v>17.24</v>
       </c>
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="9" t="n">
@@ -2839,10 +2831,10 @@
         <v>16.48</v>
       </c>
       <c r="U30" s="10" t="n">
-        <v>13.68</v>
+        <v>12.67</v>
       </c>
       <c r="V30" s="10" t="n">
-        <v>10.02</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="W30" s="10" t="n"/>
       <c r="X30" s="11" t="n">
@@ -2877,10 +2869,10 @@
         <v>1.48</v>
       </c>
       <c r="AI30" s="10" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AJ30" s="10" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AK30" s="10" t="n"/>
     </row>
@@ -2891,7 +2883,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>83192</v>
+        <v>78245</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>17.07</v>
@@ -2906,10 +2898,10 @@
         <v>19.36</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>20.19</v>
+        <v>19.01</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>19.25</v>
+        <v>18.1</v>
       </c>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="9" t="n">
@@ -2940,10 +2932,10 @@
         <v>4.86</v>
       </c>
       <c r="U31" s="10" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="V31" s="10" t="n">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="W31" s="10" t="n"/>
       <c r="X31" s="11" t="n">
@@ -2959,10 +2951,10 @@
         <v>26.17</v>
       </c>
       <c r="AB31" s="12" t="n">
-        <v>22.74</v>
+        <v>22.72</v>
       </c>
       <c r="AC31" s="12" t="n">
-        <v>20.5</v>
+        <v>20.51</v>
       </c>
       <c r="AD31" s="12" t="n"/>
       <c r="AE31" s="9" t="n">
@@ -2978,10 +2970,10 @@
         <v>1.93</v>
       </c>
       <c r="AI31" s="10" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AJ31" s="10" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AK31" s="10" t="n"/>
     </row>
@@ -2992,7 +2984,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>107015</v>
+        <v>103908</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>20.08</v>
@@ -3007,10 +2999,10 @@
         <v>21.62</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>23.28</v>
+        <v>22.61</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>21.28</v>
+        <v>20.67</v>
       </c>
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="9" t="n">
@@ -3041,10 +3033,10 @@
         <v>3.55</v>
       </c>
       <c r="U32" s="10" t="n">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
       <c r="V32" s="10" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="W32" s="10" t="n"/>
       <c r="X32" s="11" t="n">
@@ -3079,10 +3071,10 @@
         <v>1.73</v>
       </c>
       <c r="AI32" s="10" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AJ32" s="10" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AK32" s="10" t="n"/>
     </row>
@@ -3093,7 +3085,7 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>299290</v>
+        <v>281760</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>28.47</v>
@@ -3108,10 +3100,10 @@
         <v>36.57</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>30.79</v>
+        <v>28.98</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>28.39</v>
+        <v>26.72</v>
       </c>
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="9" t="n">
@@ -3142,10 +3134,10 @@
         <v>3.77</v>
       </c>
       <c r="U33" s="10" t="n">
-        <v>4.26</v>
+        <v>4.01</v>
       </c>
       <c r="V33" s="10" t="n">
-        <v>3.96</v>
+        <v>3.73</v>
       </c>
       <c r="W33" s="10" t="n"/>
       <c r="X33" s="11" t="n">
@@ -3164,7 +3156,7 @@
         <v>14.35</v>
       </c>
       <c r="AC33" s="12" t="n">
-        <v>14.45</v>
+        <v>14.46</v>
       </c>
       <c r="AD33" s="12" t="n"/>
       <c r="AE33" s="9" t="n">
@@ -3180,10 +3172,10 @@
         <v>2.78</v>
       </c>
       <c r="AI33" s="10" t="n">
-        <v>3.11</v>
+        <v>2.93</v>
       </c>
       <c r="AJ33" s="10" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="AK33" s="10" t="n"/>
     </row>
@@ -3194,7 +3186,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>12860</v>
+        <v>11702</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>15.9</v>
@@ -3209,10 +3201,10 @@
         <v>22.06</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>17.68</v>
+        <v>16.09</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>15.73</v>
+        <v>14.31</v>
       </c>
       <c r="I34" s="10" t="n"/>
       <c r="J34" s="9" t="n">
@@ -3243,10 +3235,10 @@
         <v>2.63</v>
       </c>
       <c r="U34" s="10" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="V34" s="10" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="W34" s="10" t="n"/>
       <c r="X34" s="11" t="n">
@@ -3281,10 +3273,10 @@
         <v>1.07</v>
       </c>
       <c r="AI34" s="10" t="n">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="AJ34" s="10" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AK34" s="10" t="n"/>
     </row>
@@ -3302,7 +3294,7 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>63822</v>
+        <v>62969</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>17.03</v>
@@ -3316,12 +3308,8 @@
       <c r="F36" s="9" t="n">
         <v>102.9</v>
       </c>
-      <c r="G36" s="10" t="n">
-        <v>32.41</v>
-      </c>
-      <c r="H36" s="10" t="n">
-        <v>22.44</v>
-      </c>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="10" t="n"/>
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="9" t="n">
         <v>8.5</v>
@@ -3351,10 +3339,10 @@
         <v>14.29</v>
       </c>
       <c r="U36" s="10" t="n">
-        <v>9.25</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>7.52</v>
+        <v>7.35</v>
       </c>
       <c r="W36" s="10" t="n"/>
       <c r="X36" s="11" t="n">
@@ -3370,10 +3358,10 @@
         <v>15.36</v>
       </c>
       <c r="AB36" s="12" t="n">
-        <v>31.02</v>
+        <v>31.06</v>
       </c>
       <c r="AC36" s="12" t="n">
-        <v>36.97</v>
+        <v>36.92</v>
       </c>
       <c r="AD36" s="12" t="n"/>
       <c r="AE36" s="9" t="n">
@@ -3389,10 +3377,10 @@
         <v>7.21</v>
       </c>
       <c r="AI36" s="10" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="AJ36" s="10" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AK36" s="10" t="n"/>
     </row>
@@ -3410,7 +3398,7 @@
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>89469</v>
+        <v>84937</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>16.56</v>
@@ -3425,10 +3413,10 @@
         <v>24.33</v>
       </c>
       <c r="G38" s="10" t="n">
-        <v>26.94</v>
+        <v>25.35</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>23.59</v>
+        <v>22.21</v>
       </c>
       <c r="I38" s="10" t="n"/>
       <c r="J38" s="9" t="n">
@@ -3459,10 +3447,10 @@
         <v>4.26</v>
       </c>
       <c r="U38" s="10" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="V38" s="10" t="n">
-        <v>4.62</v>
+        <v>4.35</v>
       </c>
       <c r="W38" s="10" t="n"/>
       <c r="X38" s="11" t="n">
@@ -3478,7 +3466,7 @@
         <v>17.62</v>
       </c>
       <c r="AB38" s="12" t="n">
-        <v>19.83</v>
+        <v>19.84</v>
       </c>
       <c r="AC38" s="12" t="n">
         <v>20.55</v>
@@ -3497,10 +3485,10 @@
         <v>1.77</v>
       </c>
       <c r="AI38" s="10" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AJ38" s="10" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AK38" s="10" t="n"/>
     </row>
@@ -3518,7 +3506,7 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>39994</v>
+        <v>37895</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>5</v>
@@ -3532,12 +3520,8 @@
       <c r="F40" s="9" t="n">
         <v>23.17</v>
       </c>
-      <c r="G40" s="10" t="n">
-        <v>24.95</v>
-      </c>
-      <c r="H40" s="10" t="n">
-        <v>21.08</v>
-      </c>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
       <c r="I40" s="10" t="n"/>
       <c r="J40" s="9" t="n">
         <v>4.69</v>
@@ -3567,10 +3551,10 @@
         <v>2.97</v>
       </c>
       <c r="U40" s="10" t="n">
-        <v>3.29</v>
+        <v>3.09</v>
       </c>
       <c r="V40" s="10" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="W40" s="10" t="n"/>
       <c r="X40" s="11" t="n">
@@ -3586,10 +3570,10 @@
         <v>13.2</v>
       </c>
       <c r="AB40" s="12" t="n">
-        <v>13.81</v>
+        <v>13.64</v>
       </c>
       <c r="AC40" s="12" t="n">
-        <v>14.83</v>
+        <v>14.87</v>
       </c>
       <c r="AD40" s="12" t="n"/>
       <c r="AE40" s="9" t="n">
@@ -3605,10 +3589,10 @@
         <v>1.45</v>
       </c>
       <c r="AI40" s="10" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AJ40" s="10" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AK40" s="10" t="n"/>
     </row>
@@ -3626,7 +3610,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>39062</v>
+        <v>37248</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>24.79</v>
@@ -3640,12 +3624,8 @@
       <c r="F42" s="9" t="n">
         <v>45.89</v>
       </c>
-      <c r="G42" s="10" t="n">
-        <v>46.45</v>
-      </c>
-      <c r="H42" s="10" t="n">
-        <v>36.87</v>
-      </c>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
       <c r="I42" s="10" t="n"/>
       <c r="J42" s="9" t="n">
         <v>11.71</v>
@@ -3675,10 +3655,10 @@
         <v>6.69</v>
       </c>
       <c r="U42" s="10" t="n">
-        <v>7.46</v>
+        <v>7.05</v>
       </c>
       <c r="V42" s="10" t="n">
-        <v>6.39</v>
+        <v>6.04</v>
       </c>
       <c r="W42" s="10" t="n"/>
       <c r="X42" s="11" t="n">
@@ -3713,10 +3693,10 @@
         <v>3.66</v>
       </c>
       <c r="AI42" s="10" t="n">
-        <v>3.82</v>
+        <v>3.61</v>
       </c>
       <c r="AJ42" s="10" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AK42" s="10" t="n"/>
     </row>
@@ -3740,10 +3720,10 @@
         <v>36.3</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>49.8</v>
+        <v>48.09</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>32.13</v>
+        <v>28.53</v>
       </c>
       <c r="I43" s="15" t="n"/>
       <c r="J43" s="15" t="n">
@@ -3774,10 +3754,10 @@
         <v>6.09</v>
       </c>
       <c r="U43" s="15" t="n">
-        <v>5.04</v>
+        <v>5.07</v>
       </c>
       <c r="V43" s="15" t="n">
-        <v>4.28</v>
+        <v>3.94</v>
       </c>
       <c r="W43" s="15" t="n"/>
       <c r="X43" s="16" t="n">
@@ -3793,10 +3773,10 @@
         <v>19.14</v>
       </c>
       <c r="AB43" s="16" t="n">
-        <v>21.45</v>
+        <v>21.47</v>
       </c>
       <c r="AC43" s="16" t="n">
-        <v>23.46</v>
+        <v>23.14</v>
       </c>
       <c r="AD43" s="16" t="n"/>
       <c r="AE43" s="15" t="n">
@@ -3812,10 +3792,10 @@
         <v>2.78</v>
       </c>
       <c r="AI43" s="15" t="n">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="AJ43" s="15" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AK43" s="15" t="n"/>
     </row>
@@ -3839,10 +3819,10 @@
         <v>22.06</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>20.19</v>
+        <v>19.01</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>19.25</v>
+        <v>18.1</v>
       </c>
       <c r="I44" s="15" t="n"/>
       <c r="J44" s="15" t="n">
@@ -3873,10 +3853,10 @@
         <v>3.77</v>
       </c>
       <c r="U44" s="15" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="V44" s="15" t="n">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="W44" s="15" t="n"/>
       <c r="X44" s="16" t="n">
@@ -3911,10 +3891,10 @@
         <v>1.73</v>
       </c>
       <c r="AI44" s="15" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AJ44" s="15" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AK44" s="15" t="n"/>
     </row>
@@ -3937,12 +3917,8 @@
       <c r="F45" s="15" t="n">
         <v>102.9</v>
       </c>
-      <c r="G45" s="15" t="n">
-        <v>32.41</v>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>22.44</v>
-      </c>
+      <c r="G45" s="15" t="n"/>
+      <c r="H45" s="15" t="n"/>
       <c r="I45" s="15" t="n"/>
       <c r="J45" s="15" t="n">
         <v>8.5</v>
@@ -3972,10 +3948,10 @@
         <v>14.29</v>
       </c>
       <c r="U45" s="15" t="n">
-        <v>9.25</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="V45" s="15" t="n">
-        <v>7.52</v>
+        <v>7.35</v>
       </c>
       <c r="W45" s="15" t="n"/>
       <c r="X45" s="16" t="n">
@@ -3991,10 +3967,10 @@
         <v>15.36</v>
       </c>
       <c r="AB45" s="16" t="n">
-        <v>31.02</v>
+        <v>31.06</v>
       </c>
       <c r="AC45" s="16" t="n">
-        <v>36.97</v>
+        <v>36.92</v>
       </c>
       <c r="AD45" s="16" t="n"/>
       <c r="AE45" s="15" t="n">
@@ -4010,10 +3986,10 @@
         <v>7.21</v>
       </c>
       <c r="AI45" s="15" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="AJ45" s="15" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AK45" s="15" t="n"/>
     </row>
@@ -4037,10 +4013,10 @@
         <v>24.33</v>
       </c>
       <c r="G46" s="15" t="n">
-        <v>26.94</v>
+        <v>25.35</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>23.59</v>
+        <v>22.21</v>
       </c>
       <c r="I46" s="15" t="n"/>
       <c r="J46" s="15" t="n">
@@ -4071,10 +4047,10 @@
         <v>4.26</v>
       </c>
       <c r="U46" s="15" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="V46" s="15" t="n">
-        <v>4.62</v>
+        <v>4.35</v>
       </c>
       <c r="W46" s="15" t="n"/>
       <c r="X46" s="16" t="n">
@@ -4090,7 +4066,7 @@
         <v>17.62</v>
       </c>
       <c r="AB46" s="16" t="n">
-        <v>19.83</v>
+        <v>19.84</v>
       </c>
       <c r="AC46" s="16" t="n">
         <v>20.55</v>
@@ -4109,10 +4085,10 @@
         <v>1.77</v>
       </c>
       <c r="AI46" s="15" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AJ46" s="15" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AK46" s="15" t="n"/>
     </row>
@@ -4135,12 +4111,8 @@
       <c r="F47" s="15" t="n">
         <v>23.17</v>
       </c>
-      <c r="G47" s="15" t="n">
-        <v>24.95</v>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>21.08</v>
-      </c>
+      <c r="G47" s="15" t="n"/>
+      <c r="H47" s="15" t="n"/>
       <c r="I47" s="15" t="n"/>
       <c r="J47" s="15" t="n">
         <v>4.69</v>
@@ -4170,10 +4142,10 @@
         <v>2.97</v>
       </c>
       <c r="U47" s="15" t="n">
-        <v>3.29</v>
+        <v>3.09</v>
       </c>
       <c r="V47" s="15" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="W47" s="15" t="n"/>
       <c r="X47" s="16" t="n">
@@ -4189,10 +4161,10 @@
         <v>13.2</v>
       </c>
       <c r="AB47" s="16" t="n">
-        <v>13.81</v>
+        <v>13.64</v>
       </c>
       <c r="AC47" s="16" t="n">
-        <v>14.83</v>
+        <v>14.87</v>
       </c>
       <c r="AD47" s="16" t="n"/>
       <c r="AE47" s="15" t="n">
@@ -4208,10 +4180,10 @@
         <v>1.45</v>
       </c>
       <c r="AI47" s="15" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AJ47" s="15" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AK47" s="15" t="n"/>
     </row>
@@ -4234,12 +4206,8 @@
       <c r="F48" s="15" t="n">
         <v>45.89</v>
       </c>
-      <c r="G48" s="15" t="n">
-        <v>46.45</v>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>36.87</v>
-      </c>
+      <c r="G48" s="15" t="n"/>
+      <c r="H48" s="15" t="n"/>
       <c r="I48" s="15" t="n"/>
       <c r="J48" s="15" t="n">
         <v>11.71</v>
@@ -4269,10 +4237,10 @@
         <v>6.69</v>
       </c>
       <c r="U48" s="15" t="n">
-        <v>7.46</v>
+        <v>7.05</v>
       </c>
       <c r="V48" s="15" t="n">
-        <v>6.39</v>
+        <v>6.04</v>
       </c>
       <c r="W48" s="15" t="n"/>
       <c r="X48" s="16" t="n">
@@ -4307,10 +4275,10 @@
         <v>3.66</v>
       </c>
       <c r="AI48" s="15" t="n">
-        <v>3.82</v>
+        <v>3.61</v>
       </c>
       <c r="AJ48" s="15" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AK48" s="15" t="n"/>
     </row>
@@ -4334,10 +4302,10 @@
         <v>30.55</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>26.43</v>
+        <v>25.35</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>21.86</v>
+        <v>20.67</v>
       </c>
       <c r="I49" s="15" t="n"/>
       <c r="J49" s="15" t="n">
@@ -4368,10 +4336,10 @@
         <v>4.93</v>
       </c>
       <c r="U49" s="15" t="n">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="V49" s="15" t="n">
-        <v>4.12</v>
+        <v>3.83</v>
       </c>
       <c r="W49" s="15" t="n"/>
       <c r="X49" s="16" t="n">
@@ -4387,10 +4355,10 @@
         <v>16.82</v>
       </c>
       <c r="AB49" s="16" t="n">
-        <v>18.52</v>
+        <v>18.53</v>
       </c>
       <c r="AC49" s="16" t="n">
-        <v>20.48</v>
+        <v>20.53</v>
       </c>
       <c r="AD49" s="16" t="n"/>
       <c r="AE49" s="15" t="n">
@@ -4406,10 +4374,10 @@
         <v>2.04</v>
       </c>
       <c r="AI49" s="15" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="AJ49" s="15" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AK49" s="15" t="n"/>
     </row>
@@ -4470,7 +4438,7 @@
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>4693</v>
+        <v>3998</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>10.61</v>
@@ -4485,10 +4453,10 @@
         <v>47.5</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>11.28</v>
+        <v>9.92</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>9.34</v>
+        <v>7.78</v>
       </c>
       <c r="I53" s="10" t="n"/>
       <c r="J53" s="9" t="n">
@@ -4519,10 +4487,10 @@
         <v>2.61</v>
       </c>
       <c r="U53" s="10" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="V53" s="10" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="W53" s="10" t="n"/>
       <c r="X53" s="11" t="n">
@@ -4541,7 +4509,7 @@
         <v>16.32</v>
       </c>
       <c r="AC53" s="12" t="n">
-        <v>26.02</v>
+        <v>25.82</v>
       </c>
       <c r="AD53" s="12" t="n"/>
       <c r="AE53" s="9" t="n">
@@ -4557,10 +4525,10 @@
         <v>1.25</v>
       </c>
       <c r="AI53" s="10" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="AJ53" s="10" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="AK53" s="10" t="n"/>
     </row>
@@ -4571,7 +4539,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>4465</v>
+        <v>3998</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>5.38</v>
@@ -4586,10 +4554,10 @@
         <v>13.73</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>11.26</v>
+        <v>10.02</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>9.98</v>
+        <v>8.74</v>
       </c>
       <c r="I54" s="10" t="n"/>
       <c r="J54" s="9" t="n">
@@ -4620,10 +4588,10 @@
         <v>0.77</v>
       </c>
       <c r="U54" s="10" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="W54" s="10" t="n"/>
       <c r="X54" s="11" t="n">
@@ -4642,7 +4610,7 @@
         <v>7.52</v>
       </c>
       <c r="AC54" s="12" t="n">
-        <v>8.18</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AD54" s="12" t="n"/>
       <c r="AE54" s="9" t="n">
@@ -4658,10 +4626,10 @@
         <v>0.63</v>
       </c>
       <c r="AI54" s="10" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="AJ54" s="10" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AK54" s="10" t="n"/>
     </row>
@@ -4672,7 +4640,7 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>7.23</v>
@@ -4753,7 +4721,7 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>5.78</v>
@@ -4768,10 +4736,10 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>9.119999999999999</v>
+        <v>6.89</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>6.89</v>
+        <v>5.66</v>
       </c>
       <c r="I56" s="10" t="n"/>
       <c r="J56" s="9" t="n">
@@ -4802,10 +4770,10 @@
         <v>0.92</v>
       </c>
       <c r="U56" s="10" t="n">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="V56" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="W56" s="10" t="n"/>
       <c r="X56" s="11" t="n">
@@ -4821,10 +4789,10 @@
         <v>11.66</v>
       </c>
       <c r="AB56" s="12" t="n">
-        <v>11.23</v>
+        <v>11.18</v>
       </c>
       <c r="AC56" s="12" t="n">
-        <v>12.38</v>
+        <v>12.24</v>
       </c>
       <c r="AD56" s="12" t="n"/>
       <c r="AE56" s="9" t="n">
@@ -4840,10 +4808,10 @@
         <v>0.59</v>
       </c>
       <c r="AI56" s="10" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
       <c r="AJ56" s="10" t="n">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="AK56" s="10" t="n"/>
     </row>
@@ -4854,7 +4822,7 @@
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>7.57</v>
@@ -5031,7 +4999,7 @@
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>398551</v>
+        <v>385211</v>
       </c>
       <c r="C60" s="9" t="n">
         <v>18.45</v>
@@ -5046,10 +5014,10 @@
         <v>30</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>31.8</v>
+        <v>30.32</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>26.76</v>
+        <v>25.65</v>
       </c>
       <c r="I60" s="10" t="n"/>
       <c r="J60" s="9" t="n">
@@ -5080,10 +5048,10 @@
         <v>12.5</v>
       </c>
       <c r="U60" s="10" t="n">
-        <v>13.03</v>
+        <v>12.54</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>9.58</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="W60" s="10" t="n"/>
       <c r="X60" s="11" t="n">
@@ -5099,10 +5067,10 @@
         <v>43.54</v>
       </c>
       <c r="AB60" s="12" t="n">
-        <v>48.29</v>
+        <v>48.83</v>
       </c>
       <c r="AC60" s="12" t="n">
-        <v>41.25</v>
+        <v>41.41</v>
       </c>
       <c r="AD60" s="12" t="n"/>
       <c r="AE60" s="9" t="n">
@@ -5118,10 +5086,10 @@
         <v>3.94</v>
       </c>
       <c r="AI60" s="10" t="n">
-        <v>5.05</v>
+        <v>4.87</v>
       </c>
       <c r="AJ60" s="10" t="n">
-        <v>4.58</v>
+        <v>4.38</v>
       </c>
       <c r="AK60" s="10" t="n"/>
     </row>
@@ -5132,7 +5100,7 @@
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>164604</v>
+        <v>175045</v>
       </c>
       <c r="C61" s="9" t="n">
         <v>16.58</v>
@@ -5147,10 +5115,10 @@
         <v>24.83</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>33.63</v>
+        <v>36.08</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>26.78</v>
+        <v>28.85</v>
       </c>
       <c r="I61" s="10" t="n"/>
       <c r="J61" s="9" t="n">
@@ -5181,10 +5149,10 @@
         <v>4.81</v>
       </c>
       <c r="U61" s="10" t="n">
-        <v>5.67</v>
+        <v>6.03</v>
       </c>
       <c r="V61" s="10" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="W61" s="10" t="n"/>
       <c r="X61" s="11" t="n">
@@ -5200,10 +5168,10 @@
         <v>20.61</v>
       </c>
       <c r="AB61" s="12" t="n">
-        <v>17.8</v>
+        <v>17.65</v>
       </c>
       <c r="AC61" s="12" t="n">
-        <v>19.83</v>
+        <v>19.61</v>
       </c>
       <c r="AD61" s="12" t="n"/>
       <c r="AE61" s="9" t="n">
@@ -5219,10 +5187,10 @@
         <v>2.79</v>
       </c>
       <c r="AI61" s="10" t="n">
-        <v>3.97</v>
+        <v>4.02</v>
       </c>
       <c r="AJ61" s="10" t="n">
-        <v>3.68</v>
+        <v>3.89</v>
       </c>
       <c r="AK61" s="10" t="n"/>
     </row>
@@ -5233,7 +5201,7 @@
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>12967</v>
+        <v>14743</v>
       </c>
       <c r="C62" s="9" t="n">
         <v>10.64</v>
@@ -5248,10 +5216,10 @@
         <v>22.45</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>23.2</v>
+        <v>26.27</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>14.97</v>
+        <v>17.29</v>
       </c>
       <c r="I62" s="10" t="n"/>
       <c r="J62" s="9" t="n">
@@ -5282,10 +5250,10 @@
         <v>1.48</v>
       </c>
       <c r="U62" s="10" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="V62" s="10" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="W62" s="10" t="n"/>
       <c r="X62" s="11" t="n">
@@ -5301,10 +5269,10 @@
         <v>6.63</v>
       </c>
       <c r="AB62" s="12" t="n">
-        <v>7.08</v>
+        <v>7.11</v>
       </c>
       <c r="AC62" s="12" t="n">
-        <v>10.41</v>
+        <v>10.24</v>
       </c>
       <c r="AD62" s="12" t="n"/>
       <c r="AE62" s="9" t="n">
@@ -5320,10 +5288,10 @@
         <v>0.63</v>
       </c>
       <c r="AI62" s="10" t="n">
-        <v>0.71</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AJ62" s="10" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="AK62" s="10" t="n"/>
     </row>
@@ -5334,7 +5302,7 @@
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>72802</v>
+        <v>69312</v>
       </c>
       <c r="C63" s="9" t="n">
         <v>11.71</v>
@@ -5349,10 +5317,10 @@
         <v>20.48</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>23.49</v>
+        <v>22.31</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>20.21</v>
+        <v>19.21</v>
       </c>
       <c r="I63" s="10" t="n"/>
       <c r="J63" s="9" t="n">
@@ -5383,10 +5351,10 @@
         <v>5.69</v>
       </c>
       <c r="U63" s="10" t="n">
-        <v>6.33</v>
+        <v>6.02</v>
       </c>
       <c r="V63" s="10" t="n">
-        <v>5.04</v>
+        <v>4.79</v>
       </c>
       <c r="W63" s="10" t="n"/>
       <c r="X63" s="11" t="n">
@@ -5402,10 +5370,10 @@
         <v>28.36</v>
       </c>
       <c r="AB63" s="12" t="n">
-        <v>30.28</v>
+        <v>30.34</v>
       </c>
       <c r="AC63" s="12" t="n">
-        <v>27.75</v>
+        <v>27.78</v>
       </c>
       <c r="AD63" s="12" t="n"/>
       <c r="AE63" s="9" t="n">
@@ -5421,10 +5389,10 @@
         <v>3.17</v>
       </c>
       <c r="AI63" s="10" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="AJ63" s="10" t="n">
-        <v>3.78</v>
+        <v>3.59</v>
       </c>
       <c r="AK63" s="10" t="n"/>
     </row>
@@ -5442,7 +5410,7 @@
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>41272</v>
+        <v>40074</v>
       </c>
       <c r="C65" s="9" t="n"/>
       <c r="D65" s="9" t="n">
@@ -5458,10 +5426,10 @@
         <v>14.4</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>16.87</v>
+        <v>16.32</v>
       </c>
       <c r="I65" s="10" t="n">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
       <c r="J65" s="9" t="n"/>
       <c r="K65" s="9" t="n">
@@ -5492,10 +5460,10 @@
         <v>1.54</v>
       </c>
       <c r="V65" s="10" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="W65" s="10" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="X65" s="11" t="n"/>
       <c r="Y65" s="11" t="n">
@@ -5530,10 +5498,10 @@
         <v>1.31</v>
       </c>
       <c r="AJ65" s="10" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AK65" s="10" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="66">
@@ -5543,7 +5511,7 @@
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>7414</v>
+        <v>7558</v>
       </c>
       <c r="C66" s="9" t="n"/>
       <c r="D66" s="9" t="n">
@@ -5559,10 +5527,10 @@
         <v>15.32</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>13.17</v>
+        <v>13.42</v>
       </c>
       <c r="I66" s="10" t="n">
-        <v>11.31</v>
+        <v>11.6</v>
       </c>
       <c r="J66" s="9" t="n"/>
       <c r="K66" s="9" t="n">
@@ -5593,10 +5561,10 @@
         <v>1.25</v>
       </c>
       <c r="V66" s="10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W66" s="10" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X66" s="11" t="n"/>
       <c r="Y66" s="11" t="n">
@@ -5612,10 +5580,10 @@
         <v>8.56</v>
       </c>
       <c r="AC66" s="12" t="n">
-        <v>9.73</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD66" s="12" t="n">
-        <v>10.77</v>
+        <v>10.68</v>
       </c>
       <c r="AE66" s="9" t="n"/>
       <c r="AF66" s="9" t="n">
@@ -5631,10 +5599,10 @@
         <v>0.8</v>
       </c>
       <c r="AJ66" s="10" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AK66" s="10" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="67">
@@ -5651,7 +5619,7 @@
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>72383</v>
+        <v>73570</v>
       </c>
       <c r="C68" s="9" t="n">
         <v>11.71</v>
@@ -5665,12 +5633,8 @@
       <c r="F68" s="9" t="n">
         <v>17.46</v>
       </c>
-      <c r="G68" s="10" t="n">
-        <v>15.73</v>
-      </c>
-      <c r="H68" s="10" t="n">
-        <v>13.35</v>
-      </c>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
       <c r="I68" s="10" t="n"/>
       <c r="J68" s="9" t="n">
         <v>7.78</v>
@@ -5700,10 +5664,10 @@
         <v>3.37</v>
       </c>
       <c r="U68" s="10" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="V68" s="10" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="W68" s="10" t="n"/>
       <c r="X68" s="11" t="n">
@@ -5738,10 +5702,10 @@
         <v>1.26</v>
       </c>
       <c r="AI68" s="10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AJ68" s="10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK68" s="10" t="n"/>
     </row>
@@ -5759,7 +5723,7 @@
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>25569</v>
+        <v>25756</v>
       </c>
       <c r="C70" s="9" t="n">
         <v>31.28</v>
@@ -5774,10 +5738,10 @@
         <v>23.11</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>12.17</v>
+        <v>12.43</v>
       </c>
       <c r="I70" s="10" t="n"/>
       <c r="J70" s="9" t="n">
@@ -5808,7 +5772,7 @@
         <v>2.2</v>
       </c>
       <c r="U70" s="10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V70" s="10" t="n">
         <v>1.8</v>
@@ -5827,10 +5791,10 @@
         <v>10.49</v>
       </c>
       <c r="AB70" s="12" t="n">
-        <v>11.98</v>
+        <v>11.93</v>
       </c>
       <c r="AC70" s="12" t="n">
-        <v>15.11</v>
+        <v>14.84</v>
       </c>
       <c r="AD70" s="12" t="n"/>
       <c r="AE70" s="9" t="n">
@@ -5860,7 +5824,7 @@
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>13927</v>
+        <v>14026</v>
       </c>
       <c r="C71" s="9" t="n">
         <v>13.89</v>
@@ -5875,10 +5839,10 @@
         <v>20.71</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>10.75</v>
+        <v>10.77</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>8.529999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="I71" s="10" t="n"/>
       <c r="J71" s="9" t="n">
@@ -5909,7 +5873,7 @@
         <v>2.25</v>
       </c>
       <c r="U71" s="10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V71" s="10" t="n">
         <v>1.27</v>
@@ -5974,10 +5938,10 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>11.26</v>
+        <v>9.92</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>9.34</v>
+        <v>7.78</v>
       </c>
       <c r="I72" s="15" t="n"/>
       <c r="J72" s="15" t="n">
@@ -6008,10 +5972,10 @@
         <v>0.66</v>
       </c>
       <c r="U72" s="15" t="n">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="V72" s="15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="W72" s="15" t="n"/>
       <c r="X72" s="16" t="n">
@@ -6027,10 +5991,10 @@
         <v>7.02</v>
       </c>
       <c r="AB72" s="16" t="n">
-        <v>11.23</v>
+        <v>11.18</v>
       </c>
       <c r="AC72" s="16" t="n">
-        <v>12.38</v>
+        <v>12.24</v>
       </c>
       <c r="AD72" s="16" t="n"/>
       <c r="AE72" s="15" t="n">
@@ -6046,10 +6010,10 @@
         <v>0.53</v>
       </c>
       <c r="AI72" s="15" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="AJ72" s="15" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="AK72" s="15" t="n"/>
     </row>
@@ -6073,10 +6037,10 @@
         <v>23.64</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>27.64</v>
+        <v>28.3</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>23.48</v>
+        <v>22.43</v>
       </c>
       <c r="I73" s="15" t="n"/>
       <c r="J73" s="15" t="n">
@@ -6107,10 +6071,10 @@
         <v>5.25</v>
       </c>
       <c r="U73" s="15" t="n">
-        <v>6</v>
+        <v>6.03</v>
       </c>
       <c r="V73" s="15" t="n">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
       <c r="W73" s="15" t="n"/>
       <c r="X73" s="16" t="n">
@@ -6126,10 +6090,10 @@
         <v>24.48</v>
       </c>
       <c r="AB73" s="16" t="n">
-        <v>24.04</v>
+        <v>23.99</v>
       </c>
       <c r="AC73" s="16" t="n">
-        <v>23.79</v>
+        <v>23.7</v>
       </c>
       <c r="AD73" s="16" t="n"/>
       <c r="AE73" s="15" t="n">
@@ -6145,10 +6109,10 @@
         <v>2.98</v>
       </c>
       <c r="AI73" s="15" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="AJ73" s="15" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="AK73" s="15" t="n"/>
     </row>
@@ -6173,10 +6137,10 @@
         <v>14.86</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>15.02</v>
+        <v>14.87</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>13.46</v>
+        <v>13.35</v>
       </c>
       <c r="J74" s="15" t="n"/>
       <c r="K74" s="15" t="n">
@@ -6207,10 +6171,10 @@
         <v>1.4</v>
       </c>
       <c r="V74" s="15" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W74" s="15" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X74" s="16" t="n"/>
       <c r="Y74" s="16" t="n">
@@ -6226,10 +6190,10 @@
         <v>9.91</v>
       </c>
       <c r="AC74" s="16" t="n">
-        <v>10.26</v>
+        <v>10.24</v>
       </c>
       <c r="AD74" s="16" t="n">
-        <v>10.88</v>
+        <v>10.84</v>
       </c>
       <c r="AE74" s="15" t="n"/>
       <c r="AF74" s="15" t="n">
@@ -6245,10 +6209,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ74" s="15" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK74" s="15" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="75">
@@ -6270,12 +6234,8 @@
       <c r="F75" s="15" t="n">
         <v>17.46</v>
       </c>
-      <c r="G75" s="15" t="n">
-        <v>15.73</v>
-      </c>
-      <c r="H75" s="15" t="n">
-        <v>13.35</v>
-      </c>
+      <c r="G75" s="15" t="n"/>
+      <c r="H75" s="15" t="n"/>
       <c r="I75" s="15" t="n"/>
       <c r="J75" s="15" t="n">
         <v>7.78</v>
@@ -6305,10 +6265,10 @@
         <v>3.37</v>
       </c>
       <c r="U75" s="15" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="V75" s="15" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="W75" s="15" t="n"/>
       <c r="X75" s="16" t="n">
@@ -6343,10 +6303,10 @@
         <v>1.26</v>
       </c>
       <c r="AI75" s="15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AJ75" s="15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK75" s="15" t="n"/>
     </row>
@@ -6370,10 +6330,10 @@
         <v>21.91</v>
       </c>
       <c r="G76" s="15" t="n">
-        <v>13.38</v>
+        <v>13.44</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>10.35</v>
+        <v>10.5</v>
       </c>
       <c r="I76" s="15" t="n"/>
       <c r="J76" s="15" t="n">
@@ -6423,10 +6383,10 @@
         <v>10.73</v>
       </c>
       <c r="AB76" s="16" t="n">
-        <v>12.88</v>
+        <v>12.85</v>
       </c>
       <c r="AC76" s="16" t="n">
-        <v>15.39</v>
+        <v>15.25</v>
       </c>
       <c r="AD76" s="16" t="n"/>
       <c r="AE76" s="15" t="n">
@@ -6469,13 +6429,13 @@
         <v>18.97</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>15.53</v>
+        <v>15.32</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>13.26</v>
+        <v>13.42</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>13.46</v>
+        <v>13.35</v>
       </c>
       <c r="J77" s="15" t="n">
         <v>7.18</v>
@@ -6507,13 +6467,13 @@
         <v>1.48</v>
       </c>
       <c r="U77" s="15" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="V77" s="15" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="W77" s="15" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X77" s="16" t="n">
         <v>15.47</v>
@@ -6528,13 +6488,13 @@
         <v>10.49</v>
       </c>
       <c r="AB77" s="16" t="n">
-        <v>12.88</v>
+        <v>12.85</v>
       </c>
       <c r="AC77" s="16" t="n">
-        <v>15.39</v>
+        <v>15.25</v>
       </c>
       <c r="AD77" s="16" t="n">
-        <v>10.88</v>
+        <v>10.84</v>
       </c>
       <c r="AE77" s="15" t="n">
         <v>0.64</v>
@@ -6552,10 +6512,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ77" s="15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK77" s="15" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -6678,7 +6638,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>37771</v>
+        <v>34297</v>
       </c>
       <c r="F2" s="9" t="n"/>
       <c r="G2" s="9" t="n">
@@ -6691,10 +6651,10 @@
         <v>37.73</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>16.58</v>
+        <v>15.31</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>14.29</v>
+        <v>12.69</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -6720,7 +6680,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>20717</v>
+        <v>18614</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n">
@@ -6733,10 +6693,10 @@
         <v>27.94</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>14.91</v>
+        <v>13.78</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>14.95</v>
+        <v>13.14</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -6762,7 +6722,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13444</v>
+        <v>12449</v>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n"/>
@@ -6773,10 +6733,10 @@
         <v>37.73</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>20.88</v>
+        <v>19.47</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>13.14</v>
+        <v>11.91</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -6802,7 +6762,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19265</v>
+        <v>17781</v>
       </c>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n">
@@ -6815,10 +6775,10 @@
         <v>13.27</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>7.12</v>
+        <v>6.67</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>6.56</v>
+        <v>5.88</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -6844,7 +6804,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1477</v>
+        <v>1354</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -6853,10 +6813,10 @@
         <v>10.3</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>6.89</v>
+        <v>6.35</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>7.14</v>
+        <v>6.4</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -6882,7 +6842,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1141</v>
+        <v>1104</v>
       </c>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
@@ -6893,7 +6853,7 @@
         <v>36.95</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>10.23</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -6920,7 +6880,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4967</v>
+        <v>5241</v>
       </c>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="9" t="n"/>
@@ -6930,12 +6890,8 @@
       <c r="I8" s="9" t="n">
         <v>44.03</v>
       </c>
-      <c r="J8" s="9" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
       <c r="L8" s="9" t="n"/>
     </row>
     <row r="9">
@@ -6960,7 +6916,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6227</v>
+        <v>6395</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -6971,10 +6927,10 @@
         <v>32.18</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>25.11</v>
+        <v>25.9</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>20.82</v>
+        <v>20.91</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -7000,7 +6956,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1393</v>
+        <v>1216</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>14.21</v>
@@ -7015,10 +6971,10 @@
         <v>18.39</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>15.27</v>
+        <v>14.04</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>10.63</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -7044,7 +7000,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2888</v>
+        <v>2654</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
@@ -7055,10 +7011,10 @@
         <v>20.62</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>20.33</v>
+        <v>19.32</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>14.54</v>
+        <v>13.07</v>
       </c>
       <c r="L11" s="9" t="n"/>
     </row>
@@ -7084,7 +7040,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>894</v>
+        <v>819</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>23.46</v>
@@ -7097,10 +7053,10 @@
         <v>14.78</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>11.05</v>
+        <v>10.26</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>8.92</v>
+        <v>8</v>
       </c>
       <c r="L12" s="9" t="n"/>
     </row>
@@ -7126,7 +7082,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>37.11</v>
@@ -7141,10 +7097,10 @@
         <v>13.58</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>6.76</v>
+        <v>6.23</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>5.98</v>
+        <v>5.76</v>
       </c>
       <c r="L13" s="9" t="n"/>
     </row>
@@ -7170,7 +7126,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>10072</v>
+        <v>9143</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>41.88</v>
@@ -7185,10 +7141,10 @@
         <v>59.99</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>56.76</v>
+        <v>52.22</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>32.13</v>
+        <v>28.53</v>
       </c>
       <c r="L14" s="9" t="n"/>
     </row>
@@ -7214,7 +7170,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>42122</v>
+        <v>40276</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>19.31</v>
@@ -7229,10 +7185,10 @@
         <v>34.46</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>25.91</v>
+        <v>26.05</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>19.93</v>
+        <v>18.65</v>
       </c>
       <c r="L15" s="9" t="n"/>
     </row>
@@ -7258,7 +7214,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>12566</v>
+        <v>10954</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>16.34</v>
@@ -7273,10 +7229,10 @@
         <v>36.3</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>49.8</v>
+        <v>48.09</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>33.79</v>
+        <v>28.81</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -7302,7 +7258,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10598</v>
+        <v>9485</v>
       </c>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n">
@@ -7315,10 +7271,10 @@
         <v>41.99</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>99.44</v>
+        <v>97.16</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>34.48</v>
+        <v>30.18</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -7344,7 +7300,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>11316</v>
+        <v>10245</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>15.67</v>
@@ -7359,10 +7315,10 @@
         <v>26.64</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>17.91</v>
+        <v>16.73</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>12.63</v>
+        <v>11.19</v>
       </c>
       <c r="L18" s="9" t="n"/>
     </row>
@@ -7388,7 +7344,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>139388</v>
+        <v>129058</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>21.56</v>
@@ -7403,10 +7359,10 @@
         <v>22.08</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>19.98</v>
+        <v>18.5</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>18.62</v>
+        <v>17.24</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -7432,7 +7388,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>83192</v>
+        <v>78245</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>17.07</v>
@@ -7447,10 +7403,10 @@
         <v>19.36</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>20.19</v>
+        <v>19.01</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>19.25</v>
+        <v>18.1</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -7476,7 +7432,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>107015</v>
+        <v>103908</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>20.08</v>
@@ -7491,10 +7447,10 @@
         <v>21.62</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>23.28</v>
+        <v>22.61</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>21.28</v>
+        <v>20.67</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -7520,7 +7476,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>299290</v>
+        <v>281760</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>28.47</v>
@@ -7535,10 +7491,10 @@
         <v>36.57</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>30.79</v>
+        <v>28.98</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>28.39</v>
+        <v>26.72</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -7564,7 +7520,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>12860</v>
+        <v>11702</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>15.9</v>
@@ -7579,10 +7535,10 @@
         <v>22.06</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>17.68</v>
+        <v>16.09</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>15.73</v>
+        <v>14.31</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -7608,7 +7564,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>63822</v>
+        <v>62969</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>17.03</v>
@@ -7622,12 +7578,8 @@
       <c r="I24" s="9" t="n">
         <v>102.9</v>
       </c>
-      <c r="J24" s="9" t="n">
-        <v>32.41</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <v>22.44</v>
-      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
     </row>
     <row r="25">
@@ -7652,7 +7604,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>89469</v>
+        <v>84937</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>16.56</v>
@@ -7667,10 +7619,10 @@
         <v>24.33</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>26.94</v>
+        <v>25.35</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>23.59</v>
+        <v>22.21</v>
       </c>
       <c r="L25" s="9" t="n"/>
     </row>
@@ -7696,7 +7648,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>39994</v>
+        <v>37895</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>5</v>
@@ -7710,12 +7662,8 @@
       <c r="I26" s="9" t="n">
         <v>23.17</v>
       </c>
-      <c r="J26" s="9" t="n">
-        <v>24.95</v>
-      </c>
-      <c r="K26" s="9" t="n">
-        <v>21.08</v>
-      </c>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
       <c r="L26" s="9" t="n"/>
     </row>
     <row r="27">
@@ -7740,7 +7688,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>39062</v>
+        <v>37248</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>24.79</v>
@@ -7754,12 +7702,8 @@
       <c r="I27" s="9" t="n">
         <v>45.89</v>
       </c>
-      <c r="J27" s="9" t="n">
-        <v>46.45</v>
-      </c>
-      <c r="K27" s="9" t="n">
-        <v>36.87</v>
-      </c>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
     </row>
     <row r="28">
@@ -7784,7 +7728,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4693</v>
+        <v>3998</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>10.61</v>
@@ -7799,10 +7743,10 @@
         <v>47.5</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>11.28</v>
+        <v>9.92</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>9.34</v>
+        <v>7.78</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -7828,7 +7772,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4465</v>
+        <v>3998</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>5.38</v>
@@ -7843,10 +7787,10 @@
         <v>13.73</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>11.26</v>
+        <v>10.02</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>9.98</v>
+        <v>8.74</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -7872,7 +7816,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>7.23</v>
@@ -7908,7 +7852,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>398551</v>
+        <v>385211</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>18.45</v>
@@ -7923,10 +7867,10 @@
         <v>30</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>31.8</v>
+        <v>30.32</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>26.76</v>
+        <v>25.65</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -7952,7 +7896,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>164604</v>
+        <v>175045</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>16.58</v>
@@ -7967,10 +7911,10 @@
         <v>24.83</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>33.63</v>
+        <v>36.08</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>26.78</v>
+        <v>28.85</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -7996,7 +7940,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>12967</v>
+        <v>14743</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>10.64</v>
@@ -8011,10 +7955,10 @@
         <v>22.45</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>23.2</v>
+        <v>26.27</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>14.97</v>
+        <v>17.29</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -8040,7 +7984,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41272</v>
+        <v>40074</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -8056,10 +8000,10 @@
         <v>14.4</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>16.87</v>
+        <v>16.32</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="35">
@@ -8084,7 +8028,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7414</v>
+        <v>7558</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -8100,10 +8044,10 @@
         <v>15.32</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>13.17</v>
+        <v>13.42</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>11.31</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="36">
@@ -8128,7 +8072,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>72383</v>
+        <v>73570</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>11.71</v>
@@ -8142,12 +8086,8 @@
       <c r="I36" s="9" t="n">
         <v>17.46</v>
       </c>
-      <c r="J36" s="9" t="n">
-        <v>15.73</v>
-      </c>
-      <c r="K36" s="9" t="n">
-        <v>13.35</v>
-      </c>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="n"/>
       <c r="L36" s="9" t="n"/>
     </row>
     <row r="37">
@@ -8172,7 +8112,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>25569</v>
+        <v>25756</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>31.28</v>
@@ -8187,10 +8127,10 @@
         <v>23.11</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>12.17</v>
+        <v>12.43</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -8216,7 +8156,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>13927</v>
+        <v>14026</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>13.89</v>
@@ -8231,10 +8171,10 @@
         <v>20.71</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>10.75</v>
+        <v>10.77</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>8.529999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -8260,7 +8200,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>5.78</v>
@@ -8275,10 +8215,10 @@
         <v>8.390000000000001</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>9.119999999999999</v>
+        <v>6.89</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>6.89</v>
+        <v>5.66</v>
       </c>
       <c r="L39" s="9" t="n"/>
     </row>
@@ -8304,7 +8244,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>7.57</v>
@@ -8384,7 +8324,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>72802</v>
+        <v>69312</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>11.71</v>
@@ -8399,10 +8339,10 @@
         <v>20.48</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>23.49</v>
+        <v>22.31</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>20.21</v>
+        <v>19.21</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -8518,7 +8458,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>37771</v>
+        <v>34297</v>
       </c>
       <c r="F2" s="9" t="n"/>
       <c r="G2" s="9" t="n">
@@ -8556,7 +8496,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>20717</v>
+        <v>18614</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n">
@@ -8594,7 +8534,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13444</v>
+        <v>12449</v>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n">
@@ -8632,7 +8572,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19265</v>
+        <v>17781</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>40.3</v>
@@ -8672,7 +8612,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1477</v>
+        <v>1354</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -8706,7 +8646,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1141</v>
+        <v>1104</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>87.52</v>
@@ -8744,7 +8684,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4967</v>
+        <v>5241</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>991.9299999999999</v>
@@ -8784,7 +8724,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6227</v>
+        <v>6395</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -8820,7 +8760,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1393</v>
+        <v>1216</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>11.7</v>
@@ -8860,7 +8800,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2888</v>
+        <v>2654</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -8898,7 +8838,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>894</v>
+        <v>819</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>11.21</v>
@@ -8938,7 +8878,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>15.59</v>
@@ -8978,7 +8918,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>10072</v>
+        <v>9143</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>14.66</v>
@@ -9018,7 +8958,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>42122</v>
+        <v>40276</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>7.97</v>
@@ -9058,7 +8998,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>12566</v>
+        <v>10954</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>9.449999999999999</v>
@@ -9098,7 +9038,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10598</v>
+        <v>9485</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>13.88</v>
@@ -9138,7 +9078,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>11316</v>
+        <v>10245</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>20.45</v>
@@ -9178,7 +9118,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>139388</v>
+        <v>129058</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>15.68</v>
@@ -9218,7 +9158,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>83192</v>
+        <v>78245</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>12.31</v>
@@ -9258,7 +9198,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>107015</v>
+        <v>103908</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>14.87</v>
@@ -9298,7 +9238,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>299290</v>
+        <v>281760</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>15.21</v>
@@ -9338,7 +9278,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>12860</v>
+        <v>11702</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>10.08</v>
@@ -9378,7 +9318,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>63822</v>
+        <v>62969</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>8.5</v>
@@ -9418,7 +9358,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>89469</v>
+        <v>84937</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>9.84</v>
@@ -9458,7 +9398,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>39994</v>
+        <v>37895</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>4.69</v>
@@ -9498,7 +9438,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>39062</v>
+        <v>37248</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>11.71</v>
@@ -9538,7 +9478,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4693</v>
+        <v>3998</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>7.18</v>
@@ -9578,7 +9518,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4465</v>
+        <v>3998</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>3.59</v>
@@ -9618,7 +9558,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>6.74</v>
@@ -9658,7 +9598,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>398551</v>
+        <v>385211</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>13.46</v>
@@ -9698,7 +9638,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>164604</v>
+        <v>175045</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>13.71</v>
@@ -9738,7 +9678,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>12967</v>
+        <v>14743</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>10.23</v>
@@ -9778,7 +9718,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41272</v>
+        <v>40074</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -9818,7 +9758,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7414</v>
+        <v>7558</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -9858,7 +9798,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>72383</v>
+        <v>73570</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>7.78</v>
@@ -9898,7 +9838,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>25569</v>
+        <v>25756</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>18.39</v>
@@ -9938,7 +9878,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>13927</v>
+        <v>14026</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>7.78</v>
@@ -9978,7 +9918,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>3.96</v>
@@ -10018,7 +9958,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>2.92</v>
@@ -10098,7 +10038,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>72802</v>
+        <v>69312</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>6.73</v>
@@ -10228,7 +10168,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>37771</v>
+        <v>34297</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>1.95</v>
@@ -10243,10 +10183,10 @@
         <v>5.72</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>4.62</v>
+        <v>4.3</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>3.73</v>
+        <v>3.12</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -10272,7 +10212,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>20717</v>
+        <v>18614</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>2.73</v>
@@ -10287,10 +10227,10 @@
         <v>5.64</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>3.56</v>
+        <v>3.29</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>2.91</v>
+        <v>2.56</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -10316,7 +10256,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13444</v>
+        <v>12449</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>1.21</v>
@@ -10331,10 +10271,10 @@
         <v>4.96</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>3.72</v>
+        <v>3.47</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -10360,7 +10300,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19265</v>
+        <v>17781</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.51</v>
@@ -10375,10 +10315,10 @@
         <v>2.17</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -10404,7 +10344,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1477</v>
+        <v>1354</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -10413,10 +10353,10 @@
         <v>2.35</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -10442,7 +10382,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1141</v>
+        <v>1104</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.85</v>
@@ -10457,7 +10397,7 @@
         <v>2.84</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -10484,7 +10424,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4967</v>
+        <v>5241</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>1.54</v>
@@ -10499,10 +10439,10 @@
         <v>5.43</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>3.64</v>
+        <v>3.81</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>2.98</v>
+        <v>3.12</v>
       </c>
       <c r="L8" s="9" t="n"/>
     </row>
@@ -10528,7 +10468,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6227</v>
+        <v>6395</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -10539,10 +10479,10 @@
         <v>10.52</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>8.789999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>7.16</v>
+        <v>7.12</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -10568,7 +10508,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1393</v>
+        <v>1216</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1.05</v>
@@ -10583,10 +10523,10 @@
         <v>6.21</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>4.04</v>
+        <v>3.72</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -10612,7 +10552,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2888</v>
+        <v>2654</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>2.39</v>
@@ -10627,10 +10567,10 @@
         <v>6.44</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>5.36</v>
+        <v>5.1</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>3.93</v>
+        <v>3.53</v>
       </c>
       <c r="L11" s="9" t="n"/>
     </row>
@@ -10656,7 +10596,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>894</v>
+        <v>819</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>1.18</v>
@@ -10671,10 +10611,10 @@
         <v>2.59</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="L12" s="9" t="n"/>
     </row>
@@ -10700,7 +10640,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>2.1</v>
@@ -10715,10 +10655,10 @@
         <v>2.93</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="L13" s="9" t="n"/>
     </row>
@@ -10744,7 +10684,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>10072</v>
+        <v>9143</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>3.47</v>
@@ -10759,10 +10699,10 @@
         <v>6.09</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>7</v>
+        <v>6.44</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>6.11</v>
+        <v>5.47</v>
       </c>
       <c r="L14" s="9" t="n"/>
     </row>
@@ -10788,7 +10728,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>42122</v>
+        <v>40276</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>1.32</v>
@@ -10803,10 +10743,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>5.04</v>
+        <v>5.07</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>4.28</v>
+        <v>3.94</v>
       </c>
       <c r="L15" s="9" t="n"/>
     </row>
@@ -10832,7 +10772,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>12566</v>
+        <v>10954</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>2.15</v>
@@ -10847,10 +10787,10 @@
         <v>6.43</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>10.39</v>
+        <v>10.03</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>8.33</v>
+        <v>7.15</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -10876,7 +10816,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10598</v>
+        <v>9485</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.99</v>
@@ -10891,10 +10831,10 @@
         <v>2.1</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -10920,7 +10860,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>11316</v>
+        <v>10245</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>2.04</v>
@@ -10935,10 +10875,10 @@
         <v>6.66</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>4.12</v>
+        <v>3.85</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>3.17</v>
+        <v>2.81</v>
       </c>
       <c r="L18" s="9" t="n"/>
     </row>
@@ -10964,7 +10904,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>139388</v>
+        <v>129058</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>13.34</v>
@@ -10979,10 +10919,10 @@
         <v>16.48</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>13.68</v>
+        <v>12.67</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>10.02</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -11008,7 +10948,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>83192</v>
+        <v>78245</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>5.46</v>
@@ -11023,10 +10963,10 @@
         <v>4.86</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -11052,7 +10992,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>107015</v>
+        <v>103908</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>3.67</v>
@@ -11067,10 +11007,10 @@
         <v>3.55</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -11096,7 +11036,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>299290</v>
+        <v>281760</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>2.04</v>
@@ -11111,10 +11051,10 @@
         <v>3.77</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>4.26</v>
+        <v>4.01</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>3.96</v>
+        <v>3.73</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -11140,7 +11080,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>12860</v>
+        <v>11702</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>2.64</v>
@@ -11155,10 +11095,10 @@
         <v>2.63</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -11184,7 +11124,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>63822</v>
+        <v>62969</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>2.86</v>
@@ -11199,10 +11139,10 @@
         <v>14.29</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>9.25</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>7.52</v>
+        <v>7.35</v>
       </c>
       <c r="L24" s="9" t="n"/>
     </row>
@@ -11228,7 +11168,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>89469</v>
+        <v>84937</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>2.35</v>
@@ -11243,10 +11183,10 @@
         <v>4.26</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>4.62</v>
+        <v>4.35</v>
       </c>
       <c r="L25" s="9" t="n"/>
     </row>
@@ -11272,7 +11212,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>39994</v>
+        <v>37895</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.65</v>
@@ -11287,10 +11227,10 @@
         <v>2.97</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>3.29</v>
+        <v>3.09</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -11316,7 +11256,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>39062</v>
+        <v>37248</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1.85</v>
@@ -11331,10 +11271,10 @@
         <v>6.69</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>7.46</v>
+        <v>7.05</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>6.39</v>
+        <v>6.04</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -11360,7 +11300,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4693</v>
+        <v>3998</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -11375,10 +11315,10 @@
         <v>2.61</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -11404,7 +11344,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4465</v>
+        <v>3998</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -11419,10 +11359,10 @@
         <v>0.77</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -11448,7 +11388,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -11488,7 +11428,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>398551</v>
+        <v>385211</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>7.79</v>
@@ -11503,10 +11443,10 @@
         <v>12.5</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>13.03</v>
+        <v>12.54</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>9.58</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -11532,7 +11472,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>164604</v>
+        <v>175045</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>5.84</v>
@@ -11547,10 +11487,10 @@
         <v>4.81</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>5.67</v>
+        <v>6.03</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -11576,7 +11516,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>12967</v>
+        <v>14743</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>3.12</v>
@@ -11591,10 +11531,10 @@
         <v>1.48</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -11620,7 +11560,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41272</v>
+        <v>40074</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -11636,10 +11576,10 @@
         <v>1.54</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="35">
@@ -11664,7 +11604,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7414</v>
+        <v>7558</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -11680,10 +11620,10 @@
         <v>1.25</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="36">
@@ -11708,7 +11648,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>72383</v>
+        <v>73570</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>2.36</v>
@@ -11723,10 +11663,10 @@
         <v>3.37</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="L36" s="9" t="n"/>
     </row>
@@ -11752,7 +11692,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>25569</v>
+        <v>25756</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>2.06</v>
@@ -11767,7 +11707,7 @@
         <v>2.2</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>1.8</v>
@@ -11796,7 +11736,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>13927</v>
+        <v>14026</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>1.12</v>
@@ -11811,7 +11751,7 @@
         <v>2.25</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>1.27</v>
@@ -11840,7 +11780,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>1.25</v>
@@ -11855,10 +11795,10 @@
         <v>0.92</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="L39" s="9" t="n"/>
     </row>
@@ -11884,7 +11824,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.5600000000000001</v>
@@ -11964,7 +11904,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>72802</v>
+        <v>69312</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>3.49</v>
@@ -11979,10 +11919,10 @@
         <v>5.69</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>6.33</v>
+        <v>6.02</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>5.04</v>
+        <v>4.79</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -12098,7 +12038,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>37771</v>
+        <v>34297</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>-6.66</v>
@@ -12113,10 +12053,10 @@
         <v>18.82</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>30.86</v>
+        <v>31.14</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>28.77</v>
+        <v>27.39</v>
       </c>
       <c r="L2" s="11" t="n"/>
     </row>
@@ -12142,7 +12082,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>20717</v>
+        <v>18614</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>-234.21</v>
@@ -12186,7 +12126,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13444</v>
+        <v>12449</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>-17.23</v>
@@ -12230,7 +12170,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19265</v>
+        <v>17781</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>-2.23</v>
@@ -12245,10 +12185,10 @@
         <v>17.78</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>26.78</v>
+        <v>26.62</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>24.42</v>
+        <v>23.41</v>
       </c>
       <c r="L5" s="11" t="n"/>
     </row>
@@ -12274,7 +12214,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1477</v>
+        <v>1354</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>-7.73</v>
@@ -12292,7 +12232,7 @@
         <v>24.95</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>19.49</v>
+        <v>19.48</v>
       </c>
       <c r="L6" s="11" t="n"/>
     </row>
@@ -12318,7 +12258,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1141</v>
+        <v>1104</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>-13.03</v>
@@ -12333,7 +12273,7 @@
         <v>10.15</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>22.04</v>
+        <v>24.85</v>
       </c>
       <c r="K7" s="11" t="n"/>
       <c r="L7" s="11" t="n"/>
@@ -12360,7 +12300,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4967</v>
+        <v>5241</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>-52.75</v>
@@ -12404,7 +12344,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6227</v>
+        <v>6395</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>57.58</v>
@@ -12422,7 +12362,7 @@
         <v>38.43</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>37.8</v>
+        <v>37.49</v>
       </c>
       <c r="L9" s="11" t="n"/>
     </row>
@@ -12448,7 +12388,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1393</v>
+        <v>1216</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>7.36</v>
@@ -12466,7 +12406,7 @@
         <v>26.46</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>25.78</v>
+        <v>25.85</v>
       </c>
       <c r="L10" s="11" t="n"/>
     </row>
@@ -12492,7 +12432,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2888</v>
+        <v>2654</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>-18.17</v>
@@ -12536,7 +12476,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>894</v>
+        <v>819</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>5.01</v>
@@ -12551,10 +12491,10 @@
         <v>19.3</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>18.68</v>
+        <v>18.75</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>19.2</v>
+        <v>19.15</v>
       </c>
       <c r="L12" s="11" t="n"/>
     </row>
@@ -12580,7 +12520,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>5.67</v>
@@ -12595,7 +12535,7 @@
         <v>24.23</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>26.33</v>
+        <v>28.53</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>23.13</v>
@@ -12624,7 +12564,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>10072</v>
+        <v>9143</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>8.300000000000001</v>
@@ -12642,7 +12582,7 @@
         <v>13</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>20.47</v>
+        <v>20.59</v>
       </c>
       <c r="L14" s="11" t="n"/>
     </row>
@@ -12668,7 +12608,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>42122</v>
+        <v>40276</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>6.84</v>
@@ -12683,10 +12623,10 @@
         <v>19.14</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>21.45</v>
+        <v>21.47</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>23.46</v>
+        <v>23.14</v>
       </c>
       <c r="L15" s="11" t="n"/>
     </row>
@@ -12712,7 +12652,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>12566</v>
+        <v>10954</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>13.15</v>
@@ -12730,7 +12670,7 @@
         <v>22.68</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>27.32</v>
+        <v>27.48</v>
       </c>
       <c r="L16" s="11" t="n"/>
     </row>
@@ -12756,7 +12696,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10598</v>
+        <v>9485</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>-3.83</v>
@@ -12771,10 +12711,10 @@
         <v>6.6</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="L17" s="11" t="n"/>
     </row>
@@ -12800,7 +12740,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>11316</v>
+        <v>10245</v>
       </c>
       <c r="F18" s="11" t="n">
         <v>13.01</v>
@@ -12818,7 +12758,7 @@
         <v>25.69</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>28.35</v>
+        <v>28.36</v>
       </c>
       <c r="L18" s="11" t="n"/>
     </row>
@@ -12844,7 +12784,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>139388</v>
+        <v>129058</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>61.86</v>
@@ -12888,7 +12828,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>83192</v>
+        <v>78245</v>
       </c>
       <c r="F20" s="11" t="n">
         <v>31.97</v>
@@ -12903,10 +12843,10 @@
         <v>26.17</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>22.74</v>
+        <v>22.72</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>20.5</v>
+        <v>20.51</v>
       </c>
       <c r="L20" s="11" t="n"/>
     </row>
@@ -12932,7 +12872,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>107015</v>
+        <v>103908</v>
       </c>
       <c r="F21" s="11" t="n">
         <v>18.26</v>
@@ -12976,7 +12916,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>299290</v>
+        <v>281760</v>
       </c>
       <c r="F22" s="11" t="n">
         <v>7.16</v>
@@ -12994,7 +12934,7 @@
         <v>14.35</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>14.45</v>
+        <v>14.46</v>
       </c>
       <c r="L22" s="11" t="n"/>
     </row>
@@ -13020,7 +12960,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>12860</v>
+        <v>11702</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>16.6</v>
@@ -13064,7 +13004,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>63822</v>
+        <v>62969</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>16.81</v>
@@ -13079,10 +13019,10 @@
         <v>15.36</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>31.02</v>
+        <v>31.06</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>36.97</v>
+        <v>36.92</v>
       </c>
       <c r="L24" s="11" t="n"/>
     </row>
@@ -13108,7 +13048,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>89469</v>
+        <v>84937</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>14.19</v>
@@ -13123,7 +13063,7 @@
         <v>17.62</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>19.83</v>
+        <v>19.84</v>
       </c>
       <c r="K25" s="11" t="n">
         <v>20.55</v>
@@ -13152,7 +13092,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>39994</v>
+        <v>37895</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>12.91</v>
@@ -13167,10 +13107,10 @@
         <v>13.2</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>13.81</v>
+        <v>13.64</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>14.83</v>
+        <v>14.87</v>
       </c>
       <c r="L26" s="11" t="n"/>
     </row>
@@ -13196,7 +13136,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>39062</v>
+        <v>37248</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>7.44</v>
@@ -13240,7 +13180,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4693</v>
+        <v>3998</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>7.62</v>
@@ -13258,7 +13198,7 @@
         <v>16.32</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>26.02</v>
+        <v>25.82</v>
       </c>
       <c r="L28" s="11" t="n"/>
     </row>
@@ -13284,7 +13224,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4465</v>
+        <v>3998</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>12.82</v>
@@ -13302,7 +13242,7 @@
         <v>7.52</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>8.18</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L29" s="11" t="n"/>
     </row>
@@ -13328,7 +13268,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F30" s="11" t="n">
         <v>11.21</v>
@@ -13368,7 +13308,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>398551</v>
+        <v>385211</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>42.25</v>
@@ -13383,10 +13323,10 @@
         <v>43.54</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>48.29</v>
+        <v>48.83</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>41.25</v>
+        <v>41.41</v>
       </c>
       <c r="L31" s="11" t="n"/>
     </row>
@@ -13412,7 +13352,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>164604</v>
+        <v>175045</v>
       </c>
       <c r="F32" s="11" t="n">
         <v>35.19</v>
@@ -13427,10 +13367,10 @@
         <v>20.61</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>17.8</v>
+        <v>17.65</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>19.83</v>
+        <v>19.61</v>
       </c>
       <c r="L32" s="11" t="n"/>
     </row>
@@ -13456,7 +13396,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>12967</v>
+        <v>14743</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>29.29</v>
@@ -13471,10 +13411,10 @@
         <v>6.63</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>7.08</v>
+        <v>7.11</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>10.41</v>
+        <v>10.24</v>
       </c>
       <c r="L33" s="11" t="n"/>
     </row>
@@ -13500,7 +13440,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41272</v>
+        <v>40074</v>
       </c>
       <c r="F34" s="11" t="n"/>
       <c r="G34" s="11" t="n">
@@ -13544,7 +13484,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7414</v>
+        <v>7558</v>
       </c>
       <c r="F35" s="11" t="n"/>
       <c r="G35" s="11" t="n">
@@ -13560,10 +13500,10 @@
         <v>8.56</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>9.73</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L35" s="11" t="n">
-        <v>10.77</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="36">
@@ -13588,7 +13528,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>72383</v>
+        <v>73570</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>20.11</v>
@@ -13632,7 +13572,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>25569</v>
+        <v>25756</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>6.6</v>
@@ -13647,10 +13587,10 @@
         <v>10.49</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>11.98</v>
+        <v>11.93</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>15.11</v>
+        <v>14.84</v>
       </c>
       <c r="L37" s="11" t="n"/>
     </row>
@@ -13676,7 +13616,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>13927</v>
+        <v>14026</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>8.1</v>
@@ -13720,7 +13660,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="F39" s="11" t="n">
         <v>21.69</v>
@@ -13735,10 +13675,10 @@
         <v>11.66</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>11.23</v>
+        <v>11.18</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>12.38</v>
+        <v>12.24</v>
       </c>
       <c r="L39" s="11" t="n"/>
     </row>
@@ -13764,7 +13704,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>7.43</v>
@@ -13844,7 +13784,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>72802</v>
+        <v>69312</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>29.81</v>
@@ -13859,10 +13799,10 @@
         <v>28.36</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>30.28</v>
+        <v>30.34</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>27.75</v>
+        <v>27.78</v>
       </c>
       <c r="L42" s="11" t="n"/>
     </row>
@@ -13978,7 +13918,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>37771</v>
+        <v>34297</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>1.14</v>
@@ -13993,10 +13933,10 @@
         <v>3.04</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -14022,7 +13962,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>20717</v>
+        <v>18614</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>0.42</v>
@@ -14037,10 +13977,10 @@
         <v>2.72</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -14066,7 +14006,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13444</v>
+        <v>12449</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>0.73</v>
@@ -14081,10 +14021,10 @@
         <v>1.93</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -14110,7 +14050,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>19265</v>
+        <v>17781</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.29</v>
@@ -14125,10 +14065,10 @@
         <v>0.96</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -14154,7 +14094,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1477</v>
+        <v>1354</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -14163,10 +14103,10 @@
         <v>2.09</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -14192,7 +14132,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1141</v>
+        <v>1104</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.18</v>
@@ -14232,7 +14172,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4967</v>
+        <v>5241</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.12</v>
@@ -14247,10 +14187,10 @@
         <v>0.61</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="L8" s="9" t="n"/>
     </row>
@@ -14276,7 +14216,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6227</v>
+        <v>6395</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -14287,10 +14227,10 @@
         <v>4.38</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -14316,7 +14256,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1393</v>
+        <v>1216</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1.13</v>
@@ -14331,10 +14271,10 @@
         <v>7.54</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>3.19</v>
+        <v>2.77</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -14360,7 +14300,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2888</v>
+        <v>2654</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -14375,10 +14315,10 @@
         <v>2.61</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>2.54</v>
+        <v>2.29</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="L11" s="9" t="n"/>
     </row>
@@ -14404,7 +14344,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>894</v>
+        <v>819</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>1.29</v>
@@ -14419,10 +14359,10 @@
         <v>1.65</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="L12" s="9" t="n"/>
     </row>
@@ -14448,7 +14388,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.72</v>
@@ -14463,10 +14403,10 @@
         <v>1.02</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L13" s="9" t="n"/>
     </row>
@@ -14492,7 +14432,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>10072</v>
+        <v>9143</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>1.78</v>
@@ -14507,10 +14447,10 @@
         <v>3.02</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="L14" s="9" t="n"/>
     </row>
@@ -14536,7 +14476,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>42122</v>
+        <v>40276</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.53</v>
@@ -14551,10 +14491,10 @@
         <v>1.81</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="L15" s="9" t="n"/>
     </row>
@@ -14580,7 +14520,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>12566</v>
+        <v>10954</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.9</v>
@@ -14595,10 +14535,10 @@
         <v>2.14</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -14624,7 +14564,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10598</v>
+        <v>9485</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.9</v>
@@ -14639,10 +14579,10 @@
         <v>2.78</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>3.36</v>
+        <v>2.94</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2.94</v>
+        <v>2.57</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -14668,7 +14608,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>11316</v>
+        <v>10245</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.98</v>
@@ -14683,10 +14623,10 @@
         <v>3.51</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="L18" s="9" t="n"/>
     </row>
@@ -14712,7 +14652,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>139388</v>
+        <v>129058</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>1.87</v>
@@ -14727,10 +14667,10 @@
         <v>1.48</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -14756,7 +14696,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>83192</v>
+        <v>78245</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>2.28</v>
@@ -14771,10 +14711,10 @@
         <v>1.93</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -14800,7 +14740,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>107015</v>
+        <v>103908</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>1.73</v>
@@ -14815,10 +14755,10 @@
         <v>1.73</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -14844,7 +14784,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>299290</v>
+        <v>281760</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>2.21</v>
@@ -14859,10 +14799,10 @@
         <v>2.78</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>3.11</v>
+        <v>2.93</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -14888,7 +14828,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>12860</v>
+        <v>11702</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.86</v>
@@ -14903,10 +14843,10 @@
         <v>1.07</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -14932,7 +14872,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>63822</v>
+        <v>62969</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>1.26</v>
@@ -14947,10 +14887,10 @@
         <v>7.21</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="L24" s="9" t="n"/>
     </row>
@@ -14976,7 +14916,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>89469</v>
+        <v>84937</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>1.24</v>
@@ -14991,10 +14931,10 @@
         <v>1.77</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="L25" s="9" t="n"/>
     </row>
@@ -15020,7 +14960,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>39994</v>
+        <v>37895</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.32</v>
@@ -15035,10 +14975,10 @@
         <v>1.45</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -15064,7 +15004,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>39062</v>
+        <v>37248</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1.3</v>
@@ -15079,10 +15019,10 @@
         <v>3.66</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>3.82</v>
+        <v>3.61</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -15108,7 +15048,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4693</v>
+        <v>3998</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.34</v>
@@ -15123,10 +15063,10 @@
         <v>1.25</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -15152,7 +15092,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4465</v>
+        <v>3998</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.4</v>
@@ -15167,10 +15107,10 @@
         <v>0.63</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -15196,7 +15136,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.19</v>
@@ -15236,7 +15176,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>398551</v>
+        <v>385211</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>2.08</v>
@@ -15251,10 +15191,10 @@
         <v>3.94</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>5.05</v>
+        <v>4.87</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>4.58</v>
+        <v>4.38</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -15280,7 +15220,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>164604</v>
+        <v>175045</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>2.31</v>
@@ -15295,10 +15235,10 @@
         <v>2.79</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>3.97</v>
+        <v>4.02</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>3.68</v>
+        <v>3.89</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -15324,7 +15264,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>12967</v>
+        <v>14743</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.92</v>
@@ -15339,10 +15279,10 @@
         <v>0.63</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.71</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -15368,7 +15308,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41272</v>
+        <v>40074</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -15384,10 +15324,10 @@
         <v>1.31</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="35">
@@ -15412,7 +15352,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7414</v>
+        <v>7558</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -15428,10 +15368,10 @@
         <v>0.8</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="36">
@@ -15456,7 +15396,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>72383</v>
+        <v>73570</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -15471,10 +15411,10 @@
         <v>1.26</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="L36" s="9" t="n"/>
     </row>
@@ -15500,7 +15440,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>25569</v>
+        <v>25756</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1.66</v>
@@ -15544,7 +15484,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>13927</v>
+        <v>14026</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.64</v>
@@ -15588,7 +15528,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.49</v>
@@ -15603,10 +15543,10 @@
         <v>0.59</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="L39" s="9" t="n"/>
     </row>
@@ -15632,7 +15572,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.32</v>
@@ -15712,7 +15652,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>72802</v>
+        <v>69312</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>2.12</v>
@@ -15727,10 +15667,10 @@
         <v>3.17</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>3.78</v>
+        <v>3.59</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -16194,13 +16134,13 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>510000</v>
+        <v>453000</v>
       </c>
       <c r="H6" s="17" t="n">
         <v>31175.2</v>
       </c>
       <c r="I6" s="17" t="n">
-        <v>111321.31</v>
+        <v>115289.91</v>
       </c>
       <c r="J6" s="18" t="n">
         <v>24984976220000</v>
@@ -16209,20 +16149,20 @@
         <v>3271299901206.478</v>
       </c>
       <c r="L6" s="18" t="n">
-        <v>11681253647342.87</v>
+        <v>12097690124766.46</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>16.58</v>
+        <v>15.31</v>
       </c>
       <c r="N6" s="17" t="n"/>
       <c r="O6" s="17" t="n">
-        <v>4.62</v>
+        <v>4.3</v>
       </c>
       <c r="P6" s="17" t="n">
-        <v>30.86</v>
+        <v>31.14</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="R6" s="17" t="inlineStr">
         <is>
@@ -16267,13 +16207,13 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>510000</v>
+        <v>453000</v>
       </c>
       <c r="H7" s="17" t="n">
         <v>35696.77</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>136851.64</v>
+        <v>145364.44</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>26700164480000</v>
@@ -16282,20 +16222,20 @@
         <v>3745761098939.979</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>14360221985304.75</v>
+        <v>15253493850623.39</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>14.29</v>
+        <v>12.69</v>
       </c>
       <c r="N7" s="17" t="n"/>
       <c r="O7" s="17" t="n">
-        <v>3.73</v>
+        <v>3.12</v>
       </c>
       <c r="P7" s="17" t="n">
-        <v>28.77</v>
+        <v>27.39</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="R7" s="17" t="inlineStr">
         <is>
@@ -16689,7 +16629,7 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>95800</v>
+        <v>84200</v>
       </c>
       <c r="H13" s="17" t="n">
         <v>6366.76</v>
@@ -16707,17 +16647,17 @@
         <v>8121009511148.494</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>14.91</v>
+        <v>13.78</v>
       </c>
       <c r="N13" s="17" t="n"/>
       <c r="O13" s="17" t="n">
-        <v>3.56</v>
+        <v>3.29</v>
       </c>
       <c r="P13" s="17" t="n">
         <v>27.32</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="R13" s="17" t="inlineStr">
         <is>
@@ -16762,7 +16702,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>95800</v>
+        <v>84200</v>
       </c>
       <c r="H14" s="17" t="n">
         <v>6407.04</v>
@@ -16780,17 +16720,17 @@
         <v>10084109156939.35</v>
       </c>
       <c r="M14" s="17" t="n">
-        <v>14.95</v>
+        <v>13.14</v>
       </c>
       <c r="N14" s="17" t="n"/>
       <c r="O14" s="17" t="n">
-        <v>2.91</v>
+        <v>2.56</v>
       </c>
       <c r="P14" s="17" t="n">
         <v>21.57</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="R14" s="17" t="inlineStr">
         <is>
@@ -17182,7 +17122,7 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>22300</v>
+        <v>20200</v>
       </c>
       <c r="H20" s="17" t="n">
         <v>1190.4</v>
@@ -17200,17 +17140,17 @@
         <v>5165719366941.109</v>
       </c>
       <c r="M20" s="17" t="n">
-        <v>20.88</v>
+        <v>19.47</v>
       </c>
       <c r="N20" s="17" t="n"/>
       <c r="O20" s="17" t="n">
-        <v>3.72</v>
+        <v>3.47</v>
       </c>
       <c r="P20" s="17" t="n">
         <v>20.28</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="R20" s="17" t="inlineStr">
         <is>
@@ -17255,7 +17195,7 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>22300</v>
+        <v>20200</v>
       </c>
       <c r="H21" s="17" t="n">
         <v>1696.49</v>
@@ -17273,17 +17213,17 @@
         <v>6614780508197.654</v>
       </c>
       <c r="M21" s="17" t="n">
-        <v>13.14</v>
+        <v>11.91</v>
       </c>
       <c r="N21" s="17" t="n"/>
       <c r="O21" s="17" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="P21" s="17" t="n">
         <v>24.6</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="R21" s="17" t="inlineStr">
         <is>
@@ -17679,35 +17619,35 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>386000</v>
+        <v>348500</v>
       </c>
       <c r="H27" s="17" t="n">
-        <v>51725.6</v>
+        <v>50792.88</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>221737.42</v>
+        <v>229197.94</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>34992457100000</v>
+        <v>34862870089999</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>3657756524098.74</v>
+        <v>3591799715834.4</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>15680079391022.62</v>
+        <v>16207647634859.7</v>
       </c>
       <c r="M27" s="17" t="n">
-        <v>7.12</v>
+        <v>6.67</v>
       </c>
       <c r="N27" s="17" t="n"/>
       <c r="O27" s="17" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="P27" s="17" t="n">
-        <v>26.78</v>
+        <v>26.62</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
       <c r="R27" s="17" t="inlineStr">
         <is>
@@ -17752,35 +17692,35 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>386000</v>
+        <v>348500</v>
       </c>
       <c r="H28" s="17" t="n">
-        <v>58839.41</v>
+        <v>59289.32</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>260247.81</v>
+        <v>277423.87</v>
       </c>
       <c r="J28" s="18" t="n">
-        <v>37492708990000</v>
+        <v>37449280420000</v>
       </c>
       <c r="K28" s="18" t="n">
-        <v>4160806824709.78</v>
+        <v>4192622326751.6</v>
       </c>
       <c r="L28" s="18" t="n">
-        <v>18403327457795.18</v>
+        <v>19617926635439.45</v>
       </c>
       <c r="M28" s="17" t="n">
-        <v>6.56</v>
+        <v>5.88</v>
       </c>
       <c r="N28" s="17" t="n"/>
       <c r="O28" s="17" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="P28" s="17" t="n">
-        <v>24.42</v>
+        <v>23.41</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="R28" s="17" t="inlineStr">
         <is>
@@ -18148,13 +18088,13 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>54700</v>
+        <v>49050</v>
       </c>
       <c r="H34" s="17" t="n">
         <v>7317.5</v>
       </c>
       <c r="I34" s="17" t="n">
-        <v>35629.79</v>
+        <v>35650.28</v>
       </c>
       <c r="J34" s="18" t="n">
         <v>1338333330000</v>
@@ -18163,20 +18103,20 @@
         <v>279867388060</v>
       </c>
       <c r="L34" s="18" t="n">
-        <v>1362707980317.154</v>
+        <v>1363491609003.722</v>
       </c>
       <c r="M34" s="17" t="n">
-        <v>6.89</v>
+        <v>6.35</v>
       </c>
       <c r="N34" s="17" t="n"/>
       <c r="O34" s="17" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="P34" s="17" t="n">
         <v>24.95</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
@@ -18221,13 +18161,13 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>54700</v>
+        <v>49050</v>
       </c>
       <c r="H35" s="17" t="n">
         <v>7666.2</v>
       </c>
       <c r="I35" s="17" t="n">
-        <v>43034.57</v>
+        <v>43076.52</v>
       </c>
       <c r="J35" s="18" t="n">
         <v>1367800000000</v>
@@ -18236,20 +18176,20 @@
         <v>293203877054.4</v>
       </c>
       <c r="L35" s="18" t="n">
-        <v>1645913605163.999</v>
+        <v>1647518204706.319</v>
       </c>
       <c r="M35" s="17" t="n">
-        <v>7.14</v>
+        <v>6.4</v>
       </c>
       <c r="N35" s="17" t="n"/>
       <c r="O35" s="17" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="P35" s="17" t="n">
-        <v>19.49</v>
+        <v>19.48</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
@@ -18641,7 +18581,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>17900</v>
+        <v>16940</v>
       </c>
       <c r="H41" s="17" t="n"/>
       <c r="I41" s="17" t="n"/>
@@ -18651,14 +18591,14 @@
       <c r="K41" s="18" t="n"/>
       <c r="L41" s="18" t="n"/>
       <c r="M41" s="17" t="n">
-        <v>10.23</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N41" s="17" t="n"/>
       <c r="O41" s="17" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="P41" s="17" t="n">
-        <v>22.04</v>
+        <v>24.85</v>
       </c>
       <c r="Q41" s="17" t="n"/>
       <c r="R41" s="17" t="inlineStr">
@@ -18704,7 +18644,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>17900</v>
+        <v>16940</v>
       </c>
       <c r="H42" s="17" t="n"/>
       <c r="I42" s="17" t="n"/>
@@ -19109,9 +19049,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G48" s="17" t="n">
-        <v>13.23</v>
-      </c>
+      <c r="G48" s="17" t="n"/>
       <c r="H48" s="17" t="n">
         <v>0.5600000000000001</v>
       </c>
@@ -19127,18 +19065,16 @@
       <c r="L48" s="18" t="n">
         <v>1178011486.48528</v>
       </c>
-      <c r="M48" s="17" t="n">
-        <v>23.75</v>
-      </c>
+      <c r="M48" s="17" t="n"/>
       <c r="N48" s="17" t="n"/>
       <c r="O48" s="17" t="n">
-        <v>3.64</v>
+        <v>3.81</v>
       </c>
       <c r="P48" s="17" t="n">
         <v>16.62</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -19182,9 +19118,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G49" s="17" t="n">
-        <v>13.23</v>
-      </c>
+      <c r="G49" s="17" t="n"/>
       <c r="H49" s="17" t="n">
         <v>0.8100000000000001</v>
       </c>
@@ -19200,18 +19134,16 @@
       <c r="L49" s="18" t="n">
         <v>1439722451.2712</v>
       </c>
-      <c r="M49" s="17" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="M49" s="17" t="n"/>
       <c r="N49" s="17" t="n"/>
       <c r="O49" s="17" t="n">
-        <v>2.98</v>
+        <v>3.12</v>
       </c>
       <c r="P49" s="17" t="n">
         <v>20</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
@@ -19589,13 +19521,13 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>196800</v>
+        <v>197700</v>
       </c>
       <c r="H55" s="17" t="n">
         <v>7956.2</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>22544.53</v>
+        <v>22672.63</v>
       </c>
       <c r="J55" s="18" t="n">
         <v>2373493190000</v>
@@ -19604,20 +19536,20 @@
         <v>356687067527</v>
       </c>
       <c r="L55" s="18" t="n">
-        <v>1010701492468.578</v>
+        <v>1016444154255.762</v>
       </c>
       <c r="M55" s="17" t="n">
-        <v>25.11</v>
+        <v>25.9</v>
       </c>
       <c r="N55" s="17" t="n"/>
       <c r="O55" s="17" t="n">
-        <v>8.789999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="P55" s="17" t="n">
         <v>38.43</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="R55" s="17" t="inlineStr">
         <is>
@@ -19662,13 +19594,13 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>196800</v>
+        <v>197700</v>
       </c>
       <c r="H56" s="17" t="n">
         <v>9452.709999999999</v>
       </c>
       <c r="I56" s="17" t="n">
-        <v>27473.18</v>
+        <v>27753.46</v>
       </c>
       <c r="J56" s="18" t="n">
         <v>2676693990000</v>
@@ -19677,20 +19609,20 @@
         <v>423777698330.52</v>
       </c>
       <c r="L56" s="18" t="n">
-        <v>1231659184378.111</v>
+        <v>1244224667108.417</v>
       </c>
       <c r="M56" s="17" t="n">
-        <v>20.82</v>
+        <v>20.91</v>
       </c>
       <c r="N56" s="17" t="n"/>
       <c r="O56" s="17" t="n">
-        <v>7.16</v>
+        <v>7.12</v>
       </c>
       <c r="P56" s="17" t="n">
-        <v>37.8</v>
+        <v>37.49</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="R56" s="17" t="inlineStr">
         <is>
@@ -20088,35 +20020,35 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>58200</v>
+        <v>49700</v>
       </c>
       <c r="H62" s="17" t="n">
-        <v>4089</v>
+        <v>3930.5</v>
       </c>
       <c r="I62" s="17" t="n">
-        <v>18502.06</v>
+        <v>18343.56</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>618750000000</v>
+        <v>608766670000</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>138704903097</v>
+        <v>133328349626.5</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>627617114397</v>
+        <v>622240560926.5</v>
       </c>
       <c r="M62" s="17" t="n">
-        <v>15.27</v>
+        <v>14.04</v>
       </c>
       <c r="N62" s="17" t="n"/>
       <c r="O62" s="17" t="n">
-        <v>4.04</v>
+        <v>3.72</v>
       </c>
       <c r="P62" s="17" t="n">
         <v>26.46</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>3.19</v>
+        <v>2.77</v>
       </c>
       <c r="R62" s="17" t="inlineStr">
         <is>
@@ -20161,35 +20093,35 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>58200</v>
+        <v>49700</v>
       </c>
       <c r="H63" s="17" t="n">
-        <v>5476</v>
+        <v>5446</v>
       </c>
       <c r="I63" s="17" t="n">
-        <v>23978.06</v>
+        <v>23789.56</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>773225000000</v>
+        <v>759500000000</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>185753986148</v>
+        <v>184736341958</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>813371100545</v>
+        <v>806976902884.5</v>
       </c>
       <c r="M63" s="17" t="n">
-        <v>10.63</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="N63" s="17" t="n"/>
       <c r="O63" s="17" t="n">
-        <v>2.43</v>
+        <v>2.09</v>
       </c>
       <c r="P63" s="17" t="n">
-        <v>25.78</v>
+        <v>25.85</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="R63" s="17" t="inlineStr">
         <is>
@@ -20581,7 +20513,7 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>49050</v>
+        <v>44100</v>
       </c>
       <c r="H69" s="17" t="n">
         <v>2444.6</v>
@@ -20599,17 +20531,17 @@
         <v>760045029521.428</v>
       </c>
       <c r="M69" s="17" t="n">
-        <v>20.33</v>
+        <v>19.32</v>
       </c>
       <c r="N69" s="17" t="n"/>
       <c r="O69" s="17" t="n">
-        <v>5.36</v>
+        <v>5.1</v>
       </c>
       <c r="P69" s="17" t="n">
         <v>30.6</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>2.54</v>
+        <v>2.29</v>
       </c>
       <c r="R69" s="17" t="inlineStr">
         <is>
@@ -20654,7 +20586,7 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>49050</v>
+        <v>44100</v>
       </c>
       <c r="H70" s="17" t="n">
         <v>3373.17</v>
@@ -20672,17 +20604,17 @@
         <v>1041453266113.113</v>
       </c>
       <c r="M70" s="17" t="n">
-        <v>14.54</v>
+        <v>13.07</v>
       </c>
       <c r="N70" s="17" t="n"/>
       <c r="O70" s="17" t="n">
-        <v>3.93</v>
+        <v>3.53</v>
       </c>
       <c r="P70" s="17" t="n">
         <v>31.24</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="R70" s="17" t="inlineStr">
         <is>
@@ -21078,13 +21010,13 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>25150</v>
+        <v>22550</v>
       </c>
       <c r="H76" s="17" t="n">
         <v>2393.79</v>
       </c>
       <c r="I76" s="17" t="n">
-        <v>13510.8</v>
+        <v>13534.02</v>
       </c>
       <c r="J76" s="18" t="n">
         <v>956157510000</v>
@@ -21093,20 +21025,20 @@
         <v>120569796623.7908</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>680508493974.6207</v>
+        <v>681678021001.8715</v>
       </c>
       <c r="M76" s="17" t="n">
-        <v>11.05</v>
+        <v>10.26</v>
       </c>
       <c r="N76" s="17" t="n"/>
       <c r="O76" s="17" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="P76" s="17" t="n">
-        <v>18.68</v>
+        <v>18.75</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="R76" s="17" t="inlineStr">
         <is>
@@ -21151,13 +21083,13 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>25150</v>
+        <v>22550</v>
       </c>
       <c r="H77" s="17" t="n">
         <v>2818.93</v>
       </c>
       <c r="I77" s="17" t="n">
-        <v>15856.71</v>
+        <v>15907.28</v>
       </c>
       <c r="J77" s="18" t="n">
         <v>1016432640000</v>
@@ -21166,20 +21098,20 @@
         <v>141983281187.9196</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>798666979159.3746</v>
+        <v>801213744014.1482</v>
       </c>
       <c r="M77" s="17" t="n">
-        <v>8.92</v>
+        <v>8</v>
       </c>
       <c r="N77" s="17" t="n"/>
       <c r="O77" s="17" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="P77" s="17" t="n">
-        <v>19.2</v>
+        <v>19.15</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="R77" s="17" t="inlineStr">
         <is>
@@ -21577,7 +21509,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>17350</v>
+        <v>16700</v>
       </c>
       <c r="H83" s="17" t="n">
         <v>2442</v>
@@ -21595,17 +21527,17 @@
         <v>331992443278</v>
       </c>
       <c r="M83" s="17" t="n">
-        <v>6.76</v>
+        <v>6.23</v>
       </c>
       <c r="N83" s="17" t="n"/>
       <c r="O83" s="17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P83" s="17" t="n">
-        <v>26.33</v>
+        <v>28.53</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="R83" s="17" t="inlineStr">
         <is>
@@ -21650,7 +21582,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>17350</v>
+        <v>16700</v>
       </c>
       <c r="H84" s="17" t="n">
         <v>2901</v>
@@ -21668,17 +21600,17 @@
         <v>418828450507</v>
       </c>
       <c r="M84" s="17" t="n">
-        <v>5.98</v>
+        <v>5.76</v>
       </c>
       <c r="N84" s="17" t="n"/>
       <c r="O84" s="17" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="P84" s="17" t="n">
         <v>23.13</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R84" s="17" t="inlineStr">
         <is>
@@ -22076,13 +22008,13 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>146400</v>
+        <v>130000</v>
       </c>
       <c r="H90" s="17" t="n">
         <v>2345.72</v>
       </c>
       <c r="I90" s="17" t="n">
-        <v>20543.73</v>
+        <v>20476.64</v>
       </c>
       <c r="J90" s="18" t="n">
         <v>5369467450000</v>
@@ -22091,20 +22023,20 @@
         <v>228649113041.826</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>2002502407859.624</v>
+        <v>1995963043226.628</v>
       </c>
       <c r="M90" s="17" t="n">
-        <v>56.76</v>
+        <v>52.22</v>
       </c>
       <c r="N90" s="17" t="n"/>
       <c r="O90" s="17" t="n">
-        <v>7</v>
+        <v>6.44</v>
       </c>
       <c r="P90" s="17" t="n">
         <v>13</v>
       </c>
       <c r="Q90" s="17" t="n">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="R90" s="17" t="inlineStr">
         <is>
@@ -22149,13 +22081,13 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>146400</v>
+        <v>130000</v>
       </c>
       <c r="H91" s="17" t="n">
         <v>4555.93</v>
       </c>
       <c r="I91" s="17" t="n">
-        <v>23977.54</v>
+        <v>23780.15</v>
       </c>
       <c r="J91" s="18" t="n">
         <v>6652413670000</v>
@@ -22164,20 +22096,20 @@
         <v>444089959184.724</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>2337213010097.151</v>
+        <v>2317972672631.471</v>
       </c>
       <c r="M91" s="17" t="n">
-        <v>32.13</v>
+        <v>28.53</v>
       </c>
       <c r="N91" s="17" t="n"/>
       <c r="O91" s="17" t="n">
-        <v>6.11</v>
+        <v>5.47</v>
       </c>
       <c r="P91" s="17" t="n">
-        <v>20.47</v>
+        <v>20.59</v>
       </c>
       <c r="Q91" s="17" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="R91" s="17" t="inlineStr">
         <is>
@@ -22575,35 +22507,35 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>1160000</v>
+        <v>1085000</v>
       </c>
       <c r="H97" s="17" t="n">
-        <v>47245.66</v>
+        <v>47228.97</v>
       </c>
       <c r="I97" s="17" t="n">
-        <v>225232.26</v>
+        <v>227325.61</v>
       </c>
       <c r="J97" s="18" t="n">
-        <v>32240274030000</v>
+        <v>32235043260000</v>
       </c>
       <c r="K97" s="18" t="n">
-        <v>2430731739464.928</v>
+        <v>2429873419334.724</v>
       </c>
       <c r="L97" s="18" t="n">
-        <v>11587926646827.09</v>
+        <v>11695627022499.48</v>
       </c>
       <c r="M97" s="17" t="n">
-        <v>25.91</v>
+        <v>26.05</v>
       </c>
       <c r="N97" s="17" t="n"/>
       <c r="O97" s="17" t="n">
-        <v>5.04</v>
+        <v>5.07</v>
       </c>
       <c r="P97" s="17" t="n">
-        <v>21.45</v>
+        <v>21.47</v>
       </c>
       <c r="Q97" s="17" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="R97" s="17" t="inlineStr">
         <is>
@@ -22648,35 +22580,35 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>1160000</v>
+        <v>1085000</v>
       </c>
       <c r="H98" s="17" t="n">
-        <v>58195.62</v>
+        <v>58167.58</v>
       </c>
       <c r="I98" s="17" t="n">
-        <v>270793.61</v>
+        <v>275459.28</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>34524476160000</v>
+        <v>34513976160000</v>
       </c>
       <c r="K98" s="18" t="n">
-        <v>2994094373152.5</v>
+        <v>2992651491893.04</v>
       </c>
       <c r="L98" s="18" t="n">
-        <v>13932003131568.18</v>
+        <v>14172046132040.97</v>
       </c>
       <c r="M98" s="17" t="n">
-        <v>19.93</v>
+        <v>18.65</v>
       </c>
       <c r="N98" s="17" t="n"/>
       <c r="O98" s="17" t="n">
-        <v>4.28</v>
+        <v>3.94</v>
       </c>
       <c r="P98" s="17" t="n">
-        <v>23.46</v>
+        <v>23.14</v>
       </c>
       <c r="Q98" s="17" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="R98" s="17" t="inlineStr">
         <is>
@@ -23074,13 +23006,13 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>815000</v>
+        <v>695000</v>
       </c>
       <c r="H104" s="17" t="n">
         <v>16754.84</v>
       </c>
       <c r="I104" s="17" t="n">
-        <v>78746.60000000001</v>
+        <v>78450.03</v>
       </c>
       <c r="J104" s="18" t="n">
         <v>5160017030000</v>
@@ -23089,20 +23021,20 @@
         <v>366013755891</v>
       </c>
       <c r="L104" s="18" t="n">
-        <v>1720239057954.933</v>
+        <v>1713760610815.525</v>
       </c>
       <c r="M104" s="17" t="n">
-        <v>49.8</v>
+        <v>48.09</v>
       </c>
       <c r="N104" s="17" t="n"/>
       <c r="O104" s="17" t="n">
-        <v>10.39</v>
+        <v>10.03</v>
       </c>
       <c r="P104" s="17" t="n">
         <v>22.68</v>
       </c>
       <c r="Q104" s="17" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="R104" s="17" t="inlineStr">
         <is>
@@ -23147,13 +23079,13 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>815000</v>
+        <v>695000</v>
       </c>
       <c r="H105" s="17" t="n">
         <v>24122.73</v>
       </c>
       <c r="I105" s="17" t="n">
-        <v>97868.67999999999</v>
+        <v>97145.14999999999</v>
       </c>
       <c r="J105" s="18" t="n">
         <v>6147462670000</v>
@@ -23162,20 +23094,20 @@
         <v>526967045687.25</v>
       </c>
       <c r="L105" s="18" t="n">
-        <v>2137965840340.887</v>
+        <v>2122160071223.144</v>
       </c>
       <c r="M105" s="17" t="n">
-        <v>33.79</v>
+        <v>28.81</v>
       </c>
       <c r="N105" s="17" t="n"/>
       <c r="O105" s="17" t="n">
-        <v>8.33</v>
+        <v>7.15</v>
       </c>
       <c r="P105" s="17" t="n">
-        <v>27.32</v>
+        <v>27.48</v>
       </c>
       <c r="Q105" s="17" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="R105" s="17" t="inlineStr">
         <is>
@@ -23571,13 +23503,13 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>80300</v>
+        <v>70300</v>
       </c>
       <c r="H111" s="17" t="n">
         <v>790.5</v>
       </c>
       <c r="I111" s="17" t="n">
-        <v>26273.98</v>
+        <v>26332.55</v>
       </c>
       <c r="J111" s="18" t="n">
         <v>4471337600000</v>
@@ -23586,20 +23518,20 @@
         <v>147818172820.5</v>
       </c>
       <c r="L111" s="18" t="n">
-        <v>4913056594443.892</v>
+        <v>4924009921049.891</v>
       </c>
       <c r="M111" s="17" t="n">
-        <v>99.44</v>
+        <v>97.16</v>
       </c>
       <c r="N111" s="17" t="n"/>
       <c r="O111" s="17" t="n">
-        <v>2.76</v>
+        <v>2.59</v>
       </c>
       <c r="P111" s="17" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="Q111" s="17" t="n">
-        <v>3.36</v>
+        <v>2.94</v>
       </c>
       <c r="R111" s="17" t="inlineStr">
         <is>
@@ -23644,13 +23576,13 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>80300</v>
+        <v>70300</v>
       </c>
       <c r="H112" s="17" t="n">
         <v>2329</v>
       </c>
       <c r="I112" s="17" t="n">
-        <v>27279.64</v>
+        <v>27510.79</v>
       </c>
       <c r="J112" s="18" t="n">
         <v>5110915690000</v>
@@ -23659,20 +23591,20 @@
         <v>435507304869</v>
       </c>
       <c r="L112" s="18" t="n">
-        <v>5101108648686.326</v>
+        <v>5144333066583.118</v>
       </c>
       <c r="M112" s="17" t="n">
-        <v>34.48</v>
+        <v>30.18</v>
       </c>
       <c r="N112" s="17" t="n"/>
       <c r="O112" s="17" t="n">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="P112" s="17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="Q112" s="17" t="n">
-        <v>2.94</v>
+        <v>2.57</v>
       </c>
       <c r="R112" s="17" t="inlineStr">
         <is>
@@ -24070,13 +24002,13 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>146900</v>
+        <v>130100</v>
       </c>
       <c r="H118" s="17" t="n">
         <v>8113.99</v>
       </c>
       <c r="I118" s="17" t="n">
-        <v>35671.9</v>
+        <v>35667.03</v>
       </c>
       <c r="J118" s="18" t="n">
         <v>6781021630000</v>
@@ -24085,20 +24017,20 @@
         <v>885579179294.8789</v>
       </c>
       <c r="L118" s="18" t="n">
-        <v>3893313034361.641</v>
+        <v>3892781692167.539</v>
       </c>
       <c r="M118" s="17" t="n">
-        <v>17.91</v>
+        <v>16.73</v>
       </c>
       <c r="N118" s="17" t="n"/>
       <c r="O118" s="17" t="n">
-        <v>4.12</v>
+        <v>3.85</v>
       </c>
       <c r="P118" s="17" t="n">
         <v>25.69</v>
       </c>
       <c r="Q118" s="17" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="R118" s="17" t="inlineStr">
         <is>
@@ -24143,13 +24075,13 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>146900</v>
+        <v>130100</v>
       </c>
       <c r="H119" s="17" t="n">
         <v>11630.63</v>
       </c>
       <c r="I119" s="17" t="n">
-        <v>46366.27</v>
+        <v>46354.42</v>
       </c>
       <c r="J119" s="18" t="n">
         <v>8253101590000</v>
@@ -24158,20 +24090,20 @@
         <v>1269393736376.883</v>
       </c>
       <c r="L119" s="18" t="n">
-        <v>5060520574960.186</v>
+        <v>5059227604140.619</v>
       </c>
       <c r="M119" s="17" t="n">
-        <v>12.63</v>
+        <v>11.19</v>
       </c>
       <c r="N119" s="17" t="n"/>
       <c r="O119" s="17" t="n">
-        <v>3.17</v>
+        <v>2.81</v>
       </c>
       <c r="P119" s="17" t="n">
-        <v>28.35</v>
+        <v>28.36</v>
       </c>
       <c r="Q119" s="17" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="R119" s="17" t="inlineStr">
         <is>
@@ -24569,7 +24501,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>608.6799999999999</v>
+        <v>563.5700000000001</v>
       </c>
       <c r="H125" s="17" t="n">
         <v>30.46</v>
@@ -24587,17 +24519,17 @@
         <v>10186173464.337</v>
       </c>
       <c r="M125" s="17" t="n">
-        <v>19.98</v>
+        <v>18.5</v>
       </c>
       <c r="N125" s="17" t="n"/>
       <c r="O125" s="17" t="n">
-        <v>13.68</v>
+        <v>12.67</v>
       </c>
       <c r="P125" s="17" t="n">
         <v>82.53</v>
       </c>
       <c r="Q125" s="17" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="R125" s="17" t="inlineStr">
         <is>
@@ -24642,7 +24574,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>608.6799999999999</v>
+        <v>563.5700000000001</v>
       </c>
       <c r="H126" s="17" t="n">
         <v>32.69</v>
@@ -24660,17 +24592,17 @@
         <v>13904240318.079</v>
       </c>
       <c r="M126" s="17" t="n">
-        <v>18.62</v>
+        <v>17.24</v>
       </c>
       <c r="N126" s="17" t="n"/>
       <c r="O126" s="17" t="n">
-        <v>10.02</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="P126" s="17" t="n">
         <v>62.15</v>
       </c>
       <c r="Q126" s="17" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="R126" s="17" t="inlineStr">
         <is>
@@ -25068,35 +25000,35 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>585.87</v>
+        <v>551.03</v>
       </c>
       <c r="H132" s="17" t="n">
-        <v>29.01</v>
+        <v>28.99</v>
       </c>
       <c r="I132" s="17" t="n">
-        <v>137.77</v>
+        <v>137.75</v>
       </c>
       <c r="J132" s="18" t="n">
-        <v>44046717090</v>
+        <v>44056252090</v>
       </c>
       <c r="K132" s="18" t="n">
-        <v>4120011664.63956</v>
+        <v>4116937425.38946</v>
       </c>
       <c r="L132" s="18" t="n">
-        <v>19562952179.24526</v>
+        <v>19560796522.68309</v>
       </c>
       <c r="M132" s="17" t="n">
-        <v>20.19</v>
+        <v>19.01</v>
       </c>
       <c r="N132" s="17" t="n"/>
       <c r="O132" s="17" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="P132" s="17" t="n">
-        <v>22.74</v>
+        <v>22.72</v>
       </c>
       <c r="Q132" s="17" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="R132" s="17" t="inlineStr">
         <is>
@@ -25141,35 +25073,35 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>585.87</v>
+        <v>551.03</v>
       </c>
       <c r="H133" s="17" t="n">
-        <v>30.43</v>
+        <v>30.44</v>
       </c>
       <c r="I133" s="17" t="n">
-        <v>159.11</v>
+        <v>159.1</v>
       </c>
       <c r="J133" s="18" t="n">
-        <v>47003847290</v>
+        <v>47011270470</v>
       </c>
       <c r="K133" s="18" t="n">
-        <v>4321163469.68802</v>
+        <v>4322390325.44418</v>
       </c>
       <c r="L133" s="18" t="n">
-        <v>22592952004.1905</v>
+        <v>22591656618.88455</v>
       </c>
       <c r="M133" s="17" t="n">
-        <v>19.25</v>
+        <v>18.1</v>
       </c>
       <c r="N133" s="17" t="n"/>
       <c r="O133" s="17" t="n">
-        <v>3.68</v>
+        <v>3.46</v>
       </c>
       <c r="P133" s="17" t="n">
-        <v>20.5</v>
+        <v>20.51</v>
       </c>
       <c r="Q133" s="17" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="R133" s="17" t="inlineStr">
         <is>
@@ -25567,7 +25499,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>395.78</v>
+        <v>384.29</v>
       </c>
       <c r="H139" s="17" t="n">
         <v>17</v>
@@ -25585,17 +25517,17 @@
         <v>28486442015.57588</v>
       </c>
       <c r="M139" s="17" t="n">
-        <v>23.28</v>
+        <v>22.61</v>
       </c>
       <c r="N139" s="17" t="n"/>
       <c r="O139" s="17" t="n">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
       <c r="P139" s="17" t="n">
         <v>16.99</v>
       </c>
       <c r="Q139" s="17" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="R139" s="17" t="inlineStr">
         <is>
@@ -25640,7 +25572,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>395.78</v>
+        <v>384.29</v>
       </c>
       <c r="H140" s="17" t="n">
         <v>18.59</v>
@@ -25658,17 +25590,17 @@
         <v>31619750267.15752</v>
       </c>
       <c r="M140" s="17" t="n">
-        <v>21.28</v>
+        <v>20.67</v>
       </c>
       <c r="N140" s="17" t="n"/>
       <c r="O140" s="17" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="P140" s="17" t="n">
         <v>16.73</v>
       </c>
       <c r="Q140" s="17" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="R140" s="17" t="inlineStr">
         <is>
@@ -26066,7 +25998,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>222.97</v>
+        <v>209.91</v>
       </c>
       <c r="H146" s="17" t="n">
         <v>7.24</v>
@@ -26075,26 +26007,26 @@
         <v>52.32</v>
       </c>
       <c r="J146" s="18" t="n">
-        <v>96233678600</v>
+        <v>96144583660</v>
       </c>
       <c r="K146" s="18" t="n">
-        <v>9721424533.292679</v>
+        <v>9721867488.22576</v>
       </c>
       <c r="L146" s="18" t="n">
-        <v>70225285593.97736</v>
+        <v>70225512519.7807</v>
       </c>
       <c r="M146" s="17" t="n">
-        <v>30.79</v>
+        <v>28.98</v>
       </c>
       <c r="N146" s="17" t="n"/>
       <c r="O146" s="17" t="n">
-        <v>4.26</v>
+        <v>4.01</v>
       </c>
       <c r="P146" s="17" t="n">
         <v>14.35</v>
       </c>
       <c r="Q146" s="17" t="n">
-        <v>3.11</v>
+        <v>2.93</v>
       </c>
       <c r="R146" s="17" t="inlineStr">
         <is>
@@ -26139,35 +26071,35 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>222.97</v>
+        <v>209.91</v>
       </c>
       <c r="H147" s="17" t="n">
-        <v>7.85</v>
+        <v>7.86</v>
       </c>
       <c r="I147" s="17" t="n">
         <v>56.34</v>
       </c>
       <c r="J147" s="18" t="n">
-        <v>103136202870</v>
+        <v>103174696500</v>
       </c>
       <c r="K147" s="18" t="n">
-        <v>10541320691.547</v>
+        <v>10544824062.38136</v>
       </c>
       <c r="L147" s="18" t="n">
-        <v>75625603973.43047</v>
+        <v>75627625676.04219</v>
       </c>
       <c r="M147" s="17" t="n">
-        <v>28.39</v>
+        <v>26.72</v>
       </c>
       <c r="N147" s="17" t="n"/>
       <c r="O147" s="17" t="n">
-        <v>3.96</v>
+        <v>3.73</v>
       </c>
       <c r="P147" s="17" t="n">
-        <v>14.45</v>
+        <v>14.46</v>
       </c>
       <c r="Q147" s="17" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="R147" s="17" t="inlineStr">
         <is>
@@ -26565,7 +26497,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>327.71</v>
+        <v>298.2</v>
       </c>
       <c r="H153" s="17" t="n">
         <v>18.54</v>
@@ -26574,7 +26506,7 @@
         <v>141.75</v>
       </c>
       <c r="J153" s="18" t="n">
-        <v>13319714610</v>
+        <v>13331155060</v>
       </c>
       <c r="K153" s="18" t="n">
         <v>727415869.43103</v>
@@ -26583,17 +26515,17 @@
         <v>5562550865.578766</v>
       </c>
       <c r="M153" s="17" t="n">
-        <v>17.68</v>
+        <v>16.09</v>
       </c>
       <c r="N153" s="17" t="n"/>
       <c r="O153" s="17" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="P153" s="17" t="n">
         <v>13.68</v>
       </c>
       <c r="Q153" s="17" t="n">
-        <v>0.97</v>
+        <v>0.88</v>
       </c>
       <c r="R153" s="17" t="inlineStr">
         <is>
@@ -26638,7 +26570,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>327.71</v>
+        <v>298.2</v>
       </c>
       <c r="H154" s="17" t="n">
         <v>20.84</v>
@@ -26647,7 +26579,7 @@
         <v>155.77</v>
       </c>
       <c r="J154" s="18" t="n">
-        <v>14145427740</v>
+        <v>14177225420</v>
       </c>
       <c r="K154" s="18" t="n">
         <v>817658824.2423899</v>
@@ -26656,17 +26588,17 @@
         <v>6112835237.940718</v>
       </c>
       <c r="M154" s="17" t="n">
-        <v>15.73</v>
+        <v>14.31</v>
       </c>
       <c r="N154" s="17" t="n"/>
       <c r="O154" s="17" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="P154" s="17" t="n">
         <v>14.01</v>
       </c>
       <c r="Q154" s="17" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="R154" s="17" t="inlineStr">
         <is>
@@ -27063,36 +26995,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G160" s="17" t="n">
-        <v>1202</v>
-      </c>
+      <c r="G160" s="17" t="n"/>
       <c r="H160" s="17" t="n">
-        <v>37.09</v>
+        <v>37.14</v>
       </c>
       <c r="I160" s="17" t="n">
-        <v>129.94</v>
+        <v>129.97</v>
       </c>
       <c r="J160" s="18" t="n">
-        <v>13967629240</v>
+        <v>13968855280</v>
       </c>
       <c r="K160" s="18" t="n">
-        <v>1701656287.1035</v>
+        <v>1704045312.3356</v>
       </c>
       <c r="L160" s="18" t="n">
-        <v>5961715367.604726</v>
-      </c>
-      <c r="M160" s="17" t="n">
-        <v>32.41</v>
-      </c>
+        <v>5963050116.0019</v>
+      </c>
+      <c r="M160" s="17" t="n"/>
       <c r="N160" s="17" t="n"/>
       <c r="O160" s="17" t="n">
-        <v>9.25</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="P160" s="17" t="n">
-        <v>31.02</v>
+        <v>31.06</v>
       </c>
       <c r="Q160" s="17" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="R160" s="17" t="inlineStr">
         <is>
@@ -27136,36 +27064,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G161" s="17" t="n">
-        <v>1202</v>
-      </c>
+      <c r="G161" s="17" t="n"/>
       <c r="H161" s="17" t="n">
-        <v>53.57</v>
+        <v>53.51</v>
       </c>
       <c r="I161" s="17" t="n">
-        <v>159.87</v>
+        <v>159.86</v>
       </c>
       <c r="J161" s="18" t="n">
-        <v>18753488110</v>
+        <v>18732966500</v>
       </c>
       <c r="K161" s="18" t="n">
-        <v>2457911469.3523</v>
+        <v>2455049410.7009</v>
       </c>
       <c r="L161" s="18" t="n">
-        <v>7334950505.531856</v>
-      </c>
-      <c r="M161" s="17" t="n">
-        <v>22.44</v>
-      </c>
+        <v>7334686221.760492</v>
+      </c>
+      <c r="M161" s="17" t="n"/>
       <c r="N161" s="17" t="n"/>
       <c r="O161" s="17" t="n">
-        <v>7.52</v>
+        <v>7.35</v>
       </c>
       <c r="P161" s="17" t="n">
-        <v>36.97</v>
+        <v>36.92</v>
       </c>
       <c r="Q161" s="17" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="R161" s="17" t="inlineStr">
         <is>
@@ -27563,7 +27487,7 @@
         </is>
       </c>
       <c r="G167" s="17" t="n">
-        <v>22.58</v>
+        <v>21.26</v>
       </c>
       <c r="H167" s="17" t="n">
         <v>0.84</v>
@@ -27572,26 +27496,26 @@
         <v>4.43</v>
       </c>
       <c r="J167" s="18" t="n">
-        <v>33261955920</v>
+        <v>33295251610</v>
       </c>
       <c r="K167" s="18" t="n">
-        <v>2453770422.88768</v>
+        <v>2455321885.86264</v>
       </c>
       <c r="L167" s="18" t="n">
-        <v>12961564425.9438</v>
+        <v>12962308973.02548</v>
       </c>
       <c r="M167" s="17" t="n">
-        <v>26.94</v>
+        <v>25.35</v>
       </c>
       <c r="N167" s="17" t="n"/>
       <c r="O167" s="17" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="P167" s="17" t="n">
-        <v>19.83</v>
+        <v>19.84</v>
       </c>
       <c r="Q167" s="17" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="R167" s="17" t="inlineStr">
         <is>
@@ -27636,7 +27560,7 @@
         </is>
       </c>
       <c r="G168" s="17" t="n">
-        <v>22.58</v>
+        <v>21.26</v>
       </c>
       <c r="H168" s="17" t="n">
         <v>0.96</v>
@@ -27645,26 +27569,26 @@
         <v>4.89</v>
       </c>
       <c r="J168" s="18" t="n">
-        <v>36314049120</v>
+        <v>36342933340</v>
       </c>
       <c r="K168" s="18" t="n">
-        <v>2801766495.45984</v>
+        <v>2802088497.20936</v>
       </c>
       <c r="L168" s="18" t="n">
-        <v>14306132167.11497</v>
+        <v>14307031242.83625</v>
       </c>
       <c r="M168" s="17" t="n">
-        <v>23.59</v>
+        <v>22.21</v>
       </c>
       <c r="N168" s="17" t="n"/>
       <c r="O168" s="17" t="n">
-        <v>4.62</v>
+        <v>4.35</v>
       </c>
       <c r="P168" s="17" t="n">
         <v>20.55</v>
       </c>
       <c r="Q168" s="17" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="R168" s="17" t="inlineStr">
         <is>
@@ -28061,36 +27985,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G174" s="17" t="n">
-        <v>59.9</v>
-      </c>
+      <c r="G174" s="17" t="n"/>
       <c r="H174" s="17" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="I174" s="17" t="n">
-        <v>18.2</v>
+        <v>18.17</v>
       </c>
       <c r="J174" s="18" t="n">
-        <v>22303548350</v>
+        <v>22326243840</v>
       </c>
       <c r="K174" s="18" t="n">
-        <v>1385116031.65494</v>
+        <v>1367525003.82017</v>
       </c>
       <c r="L174" s="18" t="n">
-        <v>10497862065.03356</v>
-      </c>
-      <c r="M174" s="17" t="n">
-        <v>24.95</v>
-      </c>
+        <v>10485951180.08664</v>
+      </c>
+      <c r="M174" s="17" t="n"/>
       <c r="N174" s="17" t="n"/>
       <c r="O174" s="17" t="n">
-        <v>3.29</v>
+        <v>3.09</v>
       </c>
       <c r="P174" s="17" t="n">
-        <v>13.81</v>
+        <v>13.64</v>
       </c>
       <c r="Q174" s="17" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="R174" s="17" t="inlineStr">
         <is>
@@ -28134,36 +28054,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G175" s="17" t="n">
-        <v>59.9</v>
-      </c>
+      <c r="G175" s="17" t="n"/>
       <c r="H175" s="17" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="I175" s="17" t="n">
-        <v>20.12</v>
+        <v>20.1</v>
       </c>
       <c r="J175" s="18" t="n">
-        <v>24688113670</v>
+        <v>24744432810</v>
       </c>
       <c r="K175" s="18" t="n">
-        <v>1639381098.13777</v>
+        <v>1641435019.39365</v>
       </c>
       <c r="L175" s="18" t="n">
-        <v>11607887006.58264</v>
-      </c>
-      <c r="M175" s="17" t="n">
-        <v>21.08</v>
-      </c>
+        <v>11597366831.71808</v>
+      </c>
+      <c r="M175" s="17" t="n"/>
       <c r="N175" s="17" t="n"/>
       <c r="O175" s="17" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="P175" s="17" t="n">
-        <v>14.83</v>
+        <v>14.87</v>
       </c>
       <c r="Q175" s="17" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="R175" s="17" t="inlineStr">
         <is>
@@ -28560,9 +28476,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G181" s="17" t="n">
-        <v>692.7</v>
-      </c>
+      <c r="G181" s="17" t="n"/>
       <c r="H181" s="17" t="n">
         <v>14.91</v>
       </c>
@@ -28578,18 +28492,16 @@
       <c r="L181" s="18" t="n">
         <v>50027452520.55033</v>
       </c>
-      <c r="M181" s="17" t="n">
-        <v>46.45</v>
-      </c>
+      <c r="M181" s="17" t="n"/>
       <c r="N181" s="17" t="n"/>
       <c r="O181" s="17" t="n">
-        <v>7.46</v>
+        <v>7.05</v>
       </c>
       <c r="P181" s="17" t="n">
         <v>17.22</v>
       </c>
       <c r="Q181" s="17" t="n">
-        <v>3.82</v>
+        <v>3.61</v>
       </c>
       <c r="R181" s="17" t="inlineStr">
         <is>
@@ -28633,9 +28545,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G182" s="17" t="n">
-        <v>692.7</v>
-      </c>
+      <c r="G182" s="17" t="n"/>
       <c r="H182" s="17" t="n">
         <v>18.79</v>
       </c>
@@ -28651,18 +28561,16 @@
       <c r="L182" s="18" t="n">
         <v>58457648745.99268</v>
       </c>
-      <c r="M182" s="17" t="n">
-        <v>36.87</v>
-      </c>
+      <c r="M182" s="17" t="n"/>
       <c r="N182" s="17" t="n"/>
       <c r="O182" s="17" t="n">
-        <v>6.39</v>
+        <v>6.04</v>
       </c>
       <c r="P182" s="17" t="n">
         <v>18.67</v>
       </c>
       <c r="Q182" s="17" t="n">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="R182" s="17" t="inlineStr">
         <is>
@@ -29060,13 +28968,13 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>138600</v>
+        <v>115500</v>
       </c>
       <c r="H188" s="17" t="n">
         <v>13470</v>
       </c>
       <c r="I188" s="17" t="n">
-        <v>50140.48</v>
+        <v>50439.52</v>
       </c>
       <c r="J188" s="18" t="n">
         <v>9452525000000</v>
@@ -29075,20 +28983,20 @@
         <v>646179714960</v>
       </c>
       <c r="L188" s="18" t="n">
-        <v>2405327680283.352</v>
+        <v>2419672871894.003</v>
       </c>
       <c r="M188" s="17" t="n">
-        <v>11.28</v>
+        <v>9.92</v>
       </c>
       <c r="N188" s="17" t="n"/>
       <c r="O188" s="17" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="P188" s="17" t="n">
         <v>16.32</v>
       </c>
       <c r="Q188" s="17" t="n">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="R188" s="17" t="inlineStr">
         <is>
@@ -29133,13 +29041,13 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>138600</v>
+        <v>115500</v>
       </c>
       <c r="H189" s="17" t="n">
         <v>14842.75</v>
       </c>
       <c r="I189" s="17" t="n">
-        <v>63924.95</v>
+        <v>64553.49</v>
       </c>
       <c r="J189" s="18" t="n">
         <v>10403980000000</v>
@@ -29148,20 +29056,20 @@
         <v>712032959482</v>
       </c>
       <c r="L189" s="18" t="n">
-        <v>3066592689754.285</v>
+        <v>3096745015201.536</v>
       </c>
       <c r="M189" s="17" t="n">
-        <v>9.34</v>
+        <v>7.78</v>
       </c>
       <c r="N189" s="17" t="n"/>
       <c r="O189" s="17" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="P189" s="17" t="n">
-        <v>26.02</v>
+        <v>25.82</v>
       </c>
       <c r="Q189" s="17" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="R189" s="17" t="inlineStr">
         <is>
@@ -29559,13 +29467,13 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>66100</v>
+        <v>57900</v>
       </c>
       <c r="H195" s="17" t="n">
         <v>6179.71</v>
       </c>
       <c r="I195" s="17" t="n">
-        <v>78935.10000000001</v>
+        <v>79295.38</v>
       </c>
       <c r="J195" s="18" t="n">
         <v>9565166640000</v>
@@ -29574,20 +29482,20 @@
         <v>591483730785.024</v>
       </c>
       <c r="L195" s="18" t="n">
-        <v>7555178683298.183</v>
+        <v>7589662196632.624</v>
       </c>
       <c r="M195" s="17" t="n">
-        <v>11.26</v>
+        <v>10.02</v>
       </c>
       <c r="N195" s="17" t="n"/>
       <c r="O195" s="17" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="P195" s="17" t="n">
         <v>7.52</v>
       </c>
       <c r="Q195" s="17" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="R195" s="17" t="inlineStr">
         <is>
@@ -29632,13 +29540,13 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>66100</v>
+        <v>57900</v>
       </c>
       <c r="H196" s="17" t="n">
         <v>6625.59</v>
       </c>
       <c r="I196" s="17" t="n">
-        <v>83013.14999999999</v>
+        <v>83759.7</v>
       </c>
       <c r="J196" s="18" t="n">
         <v>9929985100000</v>
@@ -29647,20 +29555,20 @@
         <v>634160773105.6276</v>
       </c>
       <c r="L196" s="18" t="n">
-        <v>7945504639144.696</v>
+        <v>8016959738234.411</v>
       </c>
       <c r="M196" s="17" t="n">
-        <v>9.98</v>
+        <v>8.74</v>
       </c>
       <c r="N196" s="17" t="n"/>
       <c r="O196" s="17" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P196" s="17" t="n">
-        <v>8.18</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="Q196" s="17" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="R196" s="17" t="inlineStr">
         <is>
@@ -30054,7 +29962,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>8300</v>
+        <v>7550</v>
       </c>
       <c r="H202" s="17" t="n"/>
       <c r="I202" s="17" t="n"/>
@@ -30111,7 +30019,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>8300</v>
+        <v>7550</v>
       </c>
       <c r="H203" s="17" t="n"/>
       <c r="I203" s="17" t="n"/>
@@ -30521,35 +30429,35 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>856.5700000000001</v>
+        <v>827.9</v>
       </c>
       <c r="H209" s="17" t="n">
-        <v>26.94</v>
+        <v>27.3</v>
       </c>
       <c r="I209" s="17" t="n">
-        <v>65.75</v>
+        <v>66.02</v>
       </c>
       <c r="J209" s="18" t="n">
-        <v>78874211110</v>
+        <v>79160595630</v>
       </c>
       <c r="K209" s="18" t="n">
-        <v>12533868273.55612</v>
+        <v>12704517055.44044</v>
       </c>
       <c r="L209" s="18" t="n">
-        <v>30591809135.60417</v>
+        <v>30718072169.32038</v>
       </c>
       <c r="M209" s="17" t="n">
-        <v>31.8</v>
+        <v>30.32</v>
       </c>
       <c r="N209" s="17" t="n"/>
       <c r="O209" s="17" t="n">
-        <v>13.03</v>
+        <v>12.54</v>
       </c>
       <c r="P209" s="17" t="n">
-        <v>48.29</v>
+        <v>48.83</v>
       </c>
       <c r="Q209" s="17" t="n">
-        <v>5.05</v>
+        <v>4.87</v>
       </c>
       <c r="R209" s="17" t="inlineStr">
         <is>
@@ -30594,35 +30502,35 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>856.5700000000001</v>
+        <v>827.9</v>
       </c>
       <c r="H210" s="17" t="n">
-        <v>32.01</v>
+        <v>32.28</v>
       </c>
       <c r="I210" s="17" t="n">
-        <v>89.43000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J210" s="18" t="n">
-        <v>87025373200</v>
+        <v>87860975330</v>
       </c>
       <c r="K210" s="18" t="n">
-        <v>14893735828.36032</v>
+        <v>15020024116.01176</v>
       </c>
       <c r="L210" s="18" t="n">
-        <v>41611684275.00797</v>
+        <v>41831388012.75748</v>
       </c>
       <c r="M210" s="17" t="n">
-        <v>26.76</v>
+        <v>25.65</v>
       </c>
       <c r="N210" s="17" t="n"/>
       <c r="O210" s="17" t="n">
-        <v>9.58</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="P210" s="17" t="n">
-        <v>41.25</v>
+        <v>41.41</v>
       </c>
       <c r="Q210" s="17" t="n">
-        <v>4.58</v>
+        <v>4.38</v>
       </c>
       <c r="R210" s="17" t="inlineStr">
         <is>
@@ -31020,35 +30928,35 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>608.85</v>
+        <v>647.47</v>
       </c>
       <c r="H216" s="17" t="n">
-        <v>18.1</v>
+        <v>17.95</v>
       </c>
       <c r="I216" s="17" t="n">
-        <v>107.44</v>
+        <v>107.34</v>
       </c>
       <c r="J216" s="18" t="n">
-        <v>41418802070</v>
+        <v>43507800000</v>
       </c>
       <c r="K216" s="18" t="n">
-        <v>4894588508.18</v>
+        <v>4851716081.676801</v>
       </c>
       <c r="L216" s="18" t="n">
-        <v>29047785066.82712</v>
+        <v>29020651108.09325</v>
       </c>
       <c r="M216" s="17" t="n">
-        <v>33.63</v>
+        <v>36.08</v>
       </c>
       <c r="N216" s="17" t="n"/>
       <c r="O216" s="17" t="n">
-        <v>5.67</v>
+        <v>6.03</v>
       </c>
       <c r="P216" s="17" t="n">
-        <v>17.8</v>
+        <v>17.65</v>
       </c>
       <c r="Q216" s="17" t="n">
-        <v>3.97</v>
+        <v>4.02</v>
       </c>
       <c r="R216" s="17" t="inlineStr">
         <is>
@@ -31093,35 +31001,35 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>608.85</v>
+        <v>647.47</v>
       </c>
       <c r="H217" s="17" t="n">
-        <v>22.73</v>
+        <v>22.44</v>
       </c>
       <c r="I217" s="17" t="n">
-        <v>121.83</v>
+        <v>121.55</v>
       </c>
       <c r="J217" s="18" t="n">
-        <v>44677914000</v>
+        <v>44949674000</v>
       </c>
       <c r="K217" s="18" t="n">
-        <v>6145672312.004399</v>
+        <v>6066618671.988</v>
       </c>
       <c r="L217" s="18" t="n">
-        <v>32937381073.09471</v>
+        <v>32860214065.59445</v>
       </c>
       <c r="M217" s="17" t="n">
-        <v>26.78</v>
+        <v>28.85</v>
       </c>
       <c r="N217" s="17" t="n"/>
       <c r="O217" s="17" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="P217" s="17" t="n">
-        <v>19.83</v>
+        <v>19.61</v>
       </c>
       <c r="Q217" s="17" t="n">
-        <v>3.68</v>
+        <v>3.89</v>
       </c>
       <c r="R217" s="17" t="inlineStr">
         <is>
@@ -31519,7 +31427,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>10.44</v>
+        <v>11.87</v>
       </c>
       <c r="H223" s="17" t="n">
         <v>0.45</v>
@@ -31531,23 +31439,23 @@
         <v>18250445930</v>
       </c>
       <c r="K223" s="18" t="n">
-        <v>558904282.25562</v>
+        <v>561226943.2801499</v>
       </c>
       <c r="L223" s="18" t="n">
-        <v>8065342569.353372</v>
+        <v>8066736165.96809</v>
       </c>
       <c r="M223" s="17" t="n">
-        <v>23.2</v>
+        <v>26.27</v>
       </c>
       <c r="N223" s="17" t="n"/>
       <c r="O223" s="17" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="P223" s="17" t="n">
-        <v>7.08</v>
+        <v>7.11</v>
       </c>
       <c r="Q223" s="17" t="n">
-        <v>0.71</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R223" s="17" t="inlineStr">
         <is>
@@ -31592,35 +31500,35 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>10.44</v>
+        <v>11.87</v>
       </c>
       <c r="H224" s="17" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I224" s="17" t="n">
         <v>6.91</v>
       </c>
       <c r="J224" s="18" t="n">
-        <v>19169563820</v>
+        <v>19062563820</v>
       </c>
       <c r="K224" s="18" t="n">
-        <v>866352562.1496899</v>
+        <v>852466278.59127</v>
       </c>
       <c r="L224" s="18" t="n">
-        <v>8585154106.643186</v>
+        <v>8578215933.122852</v>
       </c>
       <c r="M224" s="17" t="n">
-        <v>14.97</v>
+        <v>17.29</v>
       </c>
       <c r="N224" s="17" t="n"/>
       <c r="O224" s="17" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="P224" s="17" t="n">
-        <v>10.41</v>
+        <v>10.24</v>
       </c>
       <c r="Q224" s="17" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="R224" s="17" t="inlineStr">
         <is>
@@ -32018,7 +31926,7 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>7302</v>
+        <v>7065</v>
       </c>
       <c r="H230" s="17" t="n">
         <v>432.91</v>
@@ -32027,7 +31935,7 @@
         <v>4130.3</v>
       </c>
       <c r="J230" s="18" t="n">
-        <v>4330142319400</v>
+        <v>4334484533599</v>
       </c>
       <c r="K230" s="18" t="n">
         <v>390091850394.128</v>
@@ -32036,17 +31944,17 @@
         <v>3721807683261.386</v>
       </c>
       <c r="M230" s="17" t="n">
-        <v>16.87</v>
+        <v>16.32</v>
       </c>
       <c r="N230" s="17" t="n"/>
       <c r="O230" s="17" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="P230" s="17" t="n">
         <v>10.79</v>
       </c>
       <c r="Q230" s="17" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="R230" s="17" t="inlineStr">
         <is>
@@ -32091,7 +31999,7 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>7302</v>
+        <v>7065</v>
       </c>
       <c r="H231" s="17" t="n">
         <v>468.02</v>
@@ -32100,7 +32008,7 @@
         <v>4383.5</v>
       </c>
       <c r="J231" s="18" t="n">
-        <v>4467881747270</v>
+        <v>4472040978550</v>
       </c>
       <c r="K231" s="18" t="n">
         <v>421729915712.8628</v>
@@ -32109,17 +32017,17 @@
         <v>3949963559227.447</v>
       </c>
       <c r="M231" s="17" t="n">
-        <v>15.6</v>
+        <v>15.1</v>
       </c>
       <c r="N231" s="17" t="n"/>
       <c r="O231" s="17" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="P231" s="17" t="n">
         <v>10.99</v>
       </c>
       <c r="Q231" s="17" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="R231" s="17" t="inlineStr">
         <is>
@@ -32517,35 +32425,35 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>5556</v>
+        <v>5644</v>
       </c>
       <c r="H237" s="17" t="n">
-        <v>421.98</v>
+        <v>420.47</v>
       </c>
       <c r="I237" s="17" t="n">
-        <v>4438.74</v>
+        <v>4437.99</v>
       </c>
       <c r="J237" s="18" t="n">
-        <v>1472052602140</v>
+        <v>1474454185460</v>
       </c>
       <c r="K237" s="18" t="n">
-        <v>89771061586.6935</v>
+        <v>89448496253.70444</v>
       </c>
       <c r="L237" s="18" t="n">
-        <v>944279499663.7012</v>
+        <v>944120991059.0703</v>
       </c>
       <c r="M237" s="17" t="n">
-        <v>13.17</v>
+        <v>13.42</v>
       </c>
       <c r="N237" s="17" t="n"/>
       <c r="O237" s="17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P237" s="17" t="n">
-        <v>9.73</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q237" s="17" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R237" s="17" t="inlineStr">
         <is>
@@ -32590,35 +32498,35 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>5556</v>
+        <v>5644</v>
       </c>
       <c r="H238" s="17" t="n">
-        <v>491.22</v>
+        <v>486.57</v>
       </c>
       <c r="I238" s="17" t="n">
-        <v>4680.12</v>
+        <v>4677.09</v>
       </c>
       <c r="J238" s="18" t="n">
-        <v>1509350388750</v>
+        <v>1513554307950</v>
       </c>
       <c r="K238" s="18" t="n">
-        <v>104499599300.5338</v>
+        <v>103509976594.0072</v>
       </c>
       <c r="L238" s="18" t="n">
-        <v>995630602759.9835</v>
+        <v>994985793557.3655</v>
       </c>
       <c r="M238" s="17" t="n">
-        <v>11.31</v>
+        <v>11.6</v>
       </c>
       <c r="N238" s="17" t="n"/>
       <c r="O238" s="17" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P238" s="17" t="n">
-        <v>10.77</v>
+        <v>10.68</v>
       </c>
       <c r="Q238" s="17" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="R238" s="17" t="inlineStr">
         <is>
@@ -33015,9 +32923,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G244" s="17" t="n">
-        <v>340.2</v>
-      </c>
+      <c r="G244" s="17" t="n"/>
       <c r="H244" s="17" t="n">
         <v>21.62</v>
       </c>
@@ -33033,18 +32939,16 @@
       <c r="L244" s="18" t="n">
         <v>201153210418.3217</v>
       </c>
-      <c r="M244" s="17" t="n">
-        <v>15.73</v>
-      </c>
+      <c r="M244" s="17" t="n"/>
       <c r="N244" s="17" t="n"/>
       <c r="O244" s="17" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="P244" s="17" t="n">
         <v>23.17</v>
       </c>
       <c r="Q244" s="17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R244" s="17" t="inlineStr">
         <is>
@@ -33088,9 +32992,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G245" s="17" t="n">
-        <v>340.2</v>
-      </c>
+      <c r="G245" s="17" t="n"/>
       <c r="H245" s="17" t="n">
         <v>25.48</v>
       </c>
@@ -33106,18 +33008,16 @@
       <c r="L245" s="18" t="n">
         <v>227966465416.778</v>
       </c>
-      <c r="M245" s="17" t="n">
-        <v>13.35</v>
-      </c>
+      <c r="M245" s="17" t="n"/>
       <c r="N245" s="17" t="n"/>
       <c r="O245" s="17" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="P245" s="17" t="n">
         <v>24.14</v>
       </c>
       <c r="Q245" s="17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="R245" s="17" t="inlineStr">
         <is>
@@ -33515,7 +33415,7 @@
         </is>
       </c>
       <c r="G251" s="17" t="n">
-        <v>18.75</v>
+        <v>18.8</v>
       </c>
       <c r="H251" s="17" t="n">
         <v>1.17</v>
@@ -33524,23 +33424,23 @@
         <v>9.960000000000001</v>
       </c>
       <c r="J251" s="18" t="n">
-        <v>102635907280</v>
+        <v>102780441360</v>
       </c>
       <c r="K251" s="18" t="n">
-        <v>10774982049.40971</v>
+        <v>10734432079.84254</v>
       </c>
       <c r="L251" s="18" t="n">
-        <v>91606838543.02055</v>
+        <v>91594511352.27213</v>
       </c>
       <c r="M251" s="17" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="N251" s="17" t="n"/>
       <c r="O251" s="17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="P251" s="17" t="n">
-        <v>11.98</v>
+        <v>11.93</v>
       </c>
       <c r="Q251" s="17" t="n">
         <v>1.68</v>
@@ -33588,32 +33488,32 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>18.75</v>
+        <v>18.8</v>
       </c>
       <c r="H252" s="17" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="I252" s="17" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="J252" s="18" t="n">
-        <v>116488181700</v>
+        <v>116607465970</v>
       </c>
       <c r="K252" s="18" t="n">
-        <v>14164168734.84354</v>
+        <v>13905237409.89762</v>
       </c>
       <c r="L252" s="18" t="n">
-        <v>95912745838.41299</v>
+        <v>95821703524.881</v>
       </c>
       <c r="M252" s="17" t="n">
-        <v>12.17</v>
+        <v>12.43</v>
       </c>
       <c r="N252" s="17" t="n"/>
       <c r="O252" s="17" t="n">
         <v>1.8</v>
       </c>
       <c r="P252" s="17" t="n">
-        <v>15.11</v>
+        <v>14.84</v>
       </c>
       <c r="Q252" s="17" t="n">
         <v>1.48</v>
@@ -34014,7 +33914,7 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>7.99</v>
+        <v>8.01</v>
       </c>
       <c r="H258" s="17" t="n">
         <v>0.74</v>
@@ -34032,11 +33932,11 @@
         <v>66454955184.60375</v>
       </c>
       <c r="M258" s="17" t="n">
-        <v>10.75</v>
+        <v>10.77</v>
       </c>
       <c r="N258" s="17" t="n"/>
       <c r="O258" s="17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P258" s="17" t="n">
         <v>13.77</v>
@@ -34087,7 +33987,7 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>7.99</v>
+        <v>8.01</v>
       </c>
       <c r="H259" s="17" t="n">
         <v>0.9399999999999999</v>
@@ -34105,7 +34005,7 @@
         <v>74002165225.2233</v>
       </c>
       <c r="M259" s="17" t="n">
-        <v>8.529999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="N259" s="17" t="n"/>
       <c r="O259" s="17" t="n">
@@ -34513,13 +34413,13 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>14490</v>
+        <v>11900</v>
       </c>
       <c r="H265" s="17" t="n">
         <v>1728</v>
       </c>
       <c r="I265" s="17" t="n">
-        <v>16107.58</v>
+        <v>16230.44</v>
       </c>
       <c r="J265" s="18" t="n">
         <v>518900000000</v>
@@ -34528,20 +34428,20 @@
         <v>35036039808</v>
       </c>
       <c r="L265" s="18" t="n">
-        <v>326589024162.7744</v>
+        <v>329080086593.1232</v>
       </c>
       <c r="M265" s="17" t="n">
-        <v>9.119999999999999</v>
+        <v>6.89</v>
       </c>
       <c r="N265" s="17" t="n"/>
       <c r="O265" s="17" t="n">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="P265" s="17" t="n">
-        <v>11.23</v>
+        <v>11.18</v>
       </c>
       <c r="Q265" s="17" t="n">
-        <v>0.57</v>
+        <v>0.46</v>
       </c>
       <c r="R265" s="17" t="inlineStr">
         <is>
@@ -34586,13 +34486,13 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>14490</v>
+        <v>11900</v>
       </c>
       <c r="H266" s="17" t="n">
         <v>2102</v>
       </c>
       <c r="I266" s="17" t="n">
-        <v>17850.77</v>
+        <v>18123.08</v>
       </c>
       <c r="J266" s="18" t="n">
         <v>579800000000</v>
@@ -34601,20 +34501,20 @@
         <v>42619071572</v>
       </c>
       <c r="L266" s="18" t="n">
-        <v>361933020217.434</v>
+        <v>367454298636.552</v>
       </c>
       <c r="M266" s="17" t="n">
-        <v>6.89</v>
+        <v>5.66</v>
       </c>
       <c r="N266" s="17" t="n"/>
       <c r="O266" s="17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="P266" s="17" t="n">
-        <v>12.38</v>
+        <v>12.24</v>
       </c>
       <c r="Q266" s="17" t="n">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="R266" s="17" t="inlineStr">
         <is>
@@ -35012,7 +34912,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>12000</v>
+        <v>11280</v>
       </c>
       <c r="H272" s="17" t="n"/>
       <c r="I272" s="17" t="n"/>
@@ -35069,7 +34969,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>12000</v>
+        <v>11280</v>
       </c>
       <c r="H273" s="17" t="n"/>
       <c r="I273" s="17" t="n"/>
@@ -35479,7 +35379,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>6200</v>
+        <v>6070</v>
       </c>
       <c r="H279" s="17" t="n"/>
       <c r="I279" s="17" t="n"/>
@@ -35536,7 +35436,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>6200</v>
+        <v>6070</v>
       </c>
       <c r="H280" s="17" t="n"/>
       <c r="I280" s="17" t="n"/>
@@ -35946,35 +35846,35 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1153.83</v>
+        <v>1098.51</v>
       </c>
       <c r="H286" s="17" t="n">
-        <v>49.13</v>
+        <v>49.24</v>
       </c>
       <c r="I286" s="17" t="n">
-        <v>182.37</v>
+        <v>182.46</v>
       </c>
       <c r="J286" s="18" t="n">
-        <v>17740637480</v>
+        <v>17739955600</v>
       </c>
       <c r="K286" s="18" t="n">
-        <v>3099829290.936</v>
+        <v>3106619048.2677</v>
       </c>
       <c r="L286" s="18" t="n">
-        <v>11507070141.20738</v>
+        <v>11512631631.36988</v>
       </c>
       <c r="M286" s="17" t="n">
-        <v>23.49</v>
+        <v>22.31</v>
       </c>
       <c r="N286" s="17" t="n"/>
       <c r="O286" s="17" t="n">
-        <v>6.33</v>
+        <v>6.02</v>
       </c>
       <c r="P286" s="17" t="n">
-        <v>30.28</v>
+        <v>30.34</v>
       </c>
       <c r="Q286" s="17" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="R286" s="17" t="inlineStr">
         <is>
@@ -36019,35 +35919,35 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1153.83</v>
+        <v>1098.51</v>
       </c>
       <c r="H287" s="17" t="n">
-        <v>57.1</v>
+        <v>57.19</v>
       </c>
       <c r="I287" s="17" t="n">
-        <v>229.14</v>
+        <v>229.3</v>
       </c>
       <c r="J287" s="18" t="n">
-        <v>19261088790</v>
+        <v>19284488790</v>
       </c>
       <c r="K287" s="18" t="n">
-        <v>3602499109.9335</v>
+        <v>3608177747.2335</v>
       </c>
       <c r="L287" s="18" t="n">
-        <v>14457877126.12892</v>
+        <v>14468089988.04707</v>
       </c>
       <c r="M287" s="17" t="n">
-        <v>20.21</v>
+        <v>19.21</v>
       </c>
       <c r="N287" s="17" t="n"/>
       <c r="O287" s="17" t="n">
-        <v>5.04</v>
+        <v>4.79</v>
       </c>
       <c r="P287" s="17" t="n">
-        <v>27.75</v>
+        <v>27.78</v>
       </c>
       <c r="Q287" s="17" t="n">
-        <v>3.78</v>
+        <v>3.59</v>
       </c>
       <c r="R287" s="17" t="inlineStr">
         <is>
@@ -36355,7 +36255,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15T23:41:33+09:00</t>
+          <t>2026-08-22T07:18:18+09:00</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>34297</v>
+        <v>34859</v>
       </c>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n">
@@ -815,11 +815,9 @@
         <v>37.73</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>15.31</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>12.69</v>
-      </c>
+        <v>14.82</v>
+      </c>
+      <c r="H5" s="10" t="n"/>
       <c r="I5" s="10" t="n"/>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="9" t="n">
@@ -847,10 +845,10 @@
         <v>5.72</v>
       </c>
       <c r="U5" s="10" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="V5" s="10" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="W5" s="10" t="n"/>
       <c r="X5" s="11" t="n">
@@ -866,7 +864,7 @@
         <v>18.82</v>
       </c>
       <c r="AB5" s="12" t="n">
-        <v>31.14</v>
+        <v>30.98</v>
       </c>
       <c r="AC5" s="12" t="n">
         <v>27.39</v>
@@ -885,10 +883,10 @@
         <v>3.04</v>
       </c>
       <c r="AI5" s="10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AJ5" s="10" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AK5" s="10" t="n"/>
     </row>
@@ -899,7 +897,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>18614</v>
+        <v>19709</v>
       </c>
       <c r="C6" s="9" t="n"/>
       <c r="D6" s="9" t="n">
@@ -914,9 +912,7 @@
       <c r="G6" s="10" t="n">
         <v>13.78</v>
       </c>
-      <c r="H6" s="10" t="n">
-        <v>13.14</v>
-      </c>
+      <c r="H6" s="10" t="n"/>
       <c r="I6" s="10" t="n"/>
       <c r="J6" s="9" t="n"/>
       <c r="K6" s="9" t="n">
@@ -947,7 +943,7 @@
         <v>3.29</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="W6" s="10" t="n"/>
       <c r="X6" s="11" t="n">
@@ -982,10 +978,10 @@
         <v>2.72</v>
       </c>
       <c r="AI6" s="10" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AJ6" s="10" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AK6" s="10" t="n"/>
     </row>
@@ -996,7 +992,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>12449</v>
+        <v>13163</v>
       </c>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
@@ -1007,11 +1003,9 @@
         <v>37.73</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>19.47</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>11.91</v>
-      </c>
+        <v>19.95</v>
+      </c>
+      <c r="H7" s="10" t="n"/>
       <c r="I7" s="10" t="n"/>
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="9" t="n">
@@ -1039,10 +1033,10 @@
         <v>4.96</v>
       </c>
       <c r="U7" s="10" t="n">
-        <v>3.47</v>
+        <v>3.54</v>
       </c>
       <c r="V7" s="10" t="n">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="W7" s="10" t="n"/>
       <c r="X7" s="11" t="n">
@@ -1058,10 +1052,10 @@
         <v>13.74</v>
       </c>
       <c r="AB7" s="12" t="n">
-        <v>20.28</v>
+        <v>20.18</v>
       </c>
       <c r="AC7" s="12" t="n">
-        <v>24.6</v>
+        <v>24.78</v>
       </c>
       <c r="AD7" s="12" t="n"/>
       <c r="AE7" s="9" t="n">
@@ -1077,10 +1071,10 @@
         <v>1.93</v>
       </c>
       <c r="AI7" s="10" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AJ7" s="10" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" s="10" t="n"/>
     </row>
@@ -1091,7 +1085,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>17781</v>
+        <v>18223</v>
       </c>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n">
@@ -1104,11 +1098,9 @@
         <v>13.27</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>5.88</v>
-      </c>
+        <v>6.4</v>
+      </c>
+      <c r="H8" s="10" t="n"/>
       <c r="I8" s="10" t="n"/>
       <c r="J8" s="9" t="n">
         <v>40.3</v>
@@ -1138,10 +1130,10 @@
         <v>2.17</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W8" s="10" t="n"/>
       <c r="X8" s="11" t="n">
@@ -1157,10 +1149,10 @@
         <v>17.78</v>
       </c>
       <c r="AB8" s="12" t="n">
-        <v>26.62</v>
+        <v>27.18</v>
       </c>
       <c r="AC8" s="12" t="n">
-        <v>23.41</v>
+        <v>23.63</v>
       </c>
       <c r="AD8" s="12" t="n"/>
       <c r="AE8" s="9" t="n">
@@ -1176,10 +1168,10 @@
         <v>0.96</v>
       </c>
       <c r="AI8" s="10" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="AJ8" s="10" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="AK8" s="10" t="n"/>
     </row>
@@ -1190,7 +1182,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
@@ -1199,11 +1191,9 @@
         <v>10.3</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>6.4</v>
-      </c>
+        <v>6.17</v>
+      </c>
+      <c r="H9" s="10" t="n"/>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="9" t="n"/>
@@ -1221,10 +1211,10 @@
         <v>2.35</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="V9" s="10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W9" s="10" t="n"/>
       <c r="X9" s="11" t="n">
@@ -1253,10 +1243,10 @@
         <v>2.09</v>
       </c>
       <c r="AI9" s="10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AJ9" s="10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK9" s="10" t="n"/>
     </row>
@@ -1267,7 +1257,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1104</v>
+        <v>1126</v>
       </c>
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="9" t="n"/>
@@ -1278,7 +1268,7 @@
         <v>36.95</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="H10" s="10" t="n"/>
       <c r="I10" s="10" t="n"/>
@@ -1308,7 +1298,7 @@
         <v>2.84</v>
       </c>
       <c r="U10" s="10" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="V10" s="10" t="n"/>
       <c r="W10" s="10" t="n"/>
@@ -1352,7 +1342,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>6395</v>
+        <v>7202</v>
       </c>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
@@ -1363,11 +1353,9 @@
         <v>32.18</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>20.91</v>
-      </c>
+        <v>28.12</v>
+      </c>
+      <c r="H11" s="10" t="n"/>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="9" t="n"/>
@@ -1389,10 +1377,10 @@
         <v>10.52</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>9.06</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="V11" s="10" t="n">
-        <v>7.12</v>
+        <v>7.99</v>
       </c>
       <c r="W11" s="10" t="n"/>
       <c r="X11" s="11" t="n">
@@ -1408,10 +1396,10 @@
         <v>33.73</v>
       </c>
       <c r="AB11" s="12" t="n">
-        <v>38.43</v>
+        <v>38.53</v>
       </c>
       <c r="AC11" s="12" t="n">
-        <v>37.49</v>
+        <v>37.64</v>
       </c>
       <c r="AD11" s="12" t="n"/>
       <c r="AE11" s="9" t="n"/>
@@ -1423,10 +1411,10 @@
         <v>4.38</v>
       </c>
       <c r="AI11" s="10" t="n">
-        <v>3.73</v>
+        <v>4.26</v>
       </c>
       <c r="AJ11" s="10" t="n">
-        <v>3.31</v>
+        <v>3.7</v>
       </c>
       <c r="AK11" s="10" t="n"/>
     </row>
@@ -1437,7 +1425,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>1216</v>
+        <v>1309</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>14.21</v>
@@ -1452,11 +1440,9 @@
         <v>18.39</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>14.04</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>9.130000000000001</v>
-      </c>
+        <v>13.93</v>
+      </c>
+      <c r="H12" s="10" t="n"/>
       <c r="I12" s="10" t="n"/>
       <c r="J12" s="9" t="n">
         <v>11.7</v>
@@ -1486,10 +1472,10 @@
         <v>6.21</v>
       </c>
       <c r="U12" s="10" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="W12" s="10" t="n"/>
       <c r="X12" s="11" t="n">
@@ -1524,10 +1510,10 @@
         <v>7.54</v>
       </c>
       <c r="AI12" s="10" t="n">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="AK12" s="10" t="n"/>
     </row>
@@ -1538,7 +1524,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>2654</v>
+        <v>2926</v>
       </c>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
@@ -1549,11 +1535,9 @@
         <v>20.62</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>19.32</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>13.07</v>
-      </c>
+        <v>20.27</v>
+      </c>
+      <c r="H13" s="10" t="n"/>
       <c r="I13" s="10" t="n"/>
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="9" t="n">
@@ -1581,10 +1565,10 @@
         <v>6.44</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>5.1</v>
+        <v>5.32</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>3.53</v>
+        <v>3.85</v>
       </c>
       <c r="W13" s="10" t="n"/>
       <c r="X13" s="11" t="n">
@@ -1600,10 +1584,10 @@
         <v>36.6</v>
       </c>
       <c r="AB13" s="12" t="n">
-        <v>30.6</v>
+        <v>30.33</v>
       </c>
       <c r="AC13" s="12" t="n">
-        <v>31.24</v>
+        <v>32.03</v>
       </c>
       <c r="AD13" s="12" t="n"/>
       <c r="AE13" s="9" t="n">
@@ -1619,10 +1603,10 @@
         <v>2.61</v>
       </c>
       <c r="AI13" s="10" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AJ13" s="10" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AK13" s="10" t="n"/>
     </row>
@@ -1633,7 +1617,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>819</v>
+        <v>914</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>23.46</v>
@@ -1646,11 +1630,9 @@
         <v>14.78</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>8</v>
-      </c>
+        <v>10.91</v>
+      </c>
+      <c r="H14" s="10" t="n"/>
       <c r="I14" s="10" t="n"/>
       <c r="J14" s="9" t="n">
         <v>11.21</v>
@@ -1680,10 +1662,10 @@
         <v>2.59</v>
       </c>
       <c r="U14" s="10" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="W14" s="10" t="n"/>
       <c r="X14" s="11" t="n">
@@ -1718,10 +1700,10 @@
         <v>1.65</v>
       </c>
       <c r="AI14" s="10" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="AJ14" s="10" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AK14" s="10" t="n"/>
     </row>
@@ -1732,7 +1714,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>37.11</v>
@@ -1747,11 +1729,9 @@
         <v>13.58</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>5.76</v>
-      </c>
+        <v>6.55</v>
+      </c>
+      <c r="H15" s="10" t="n"/>
       <c r="I15" s="10" t="n"/>
       <c r="J15" s="9" t="n">
         <v>15.59</v>
@@ -1781,10 +1761,10 @@
         <v>2.93</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="V15" s="10" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="W15" s="10" t="n"/>
       <c r="X15" s="11" t="n">
@@ -1819,10 +1799,10 @@
         <v>1.02</v>
       </c>
       <c r="AI15" s="10" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="AJ15" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="AK15" s="10" t="n"/>
     </row>
@@ -1840,7 +1820,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>5241</v>
+        <v>5211</v>
       </c>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="9" t="n"/>
@@ -1881,7 +1861,7 @@
         <v>5.43</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="V17" s="10" t="n">
         <v>3.12</v>
@@ -1948,9 +1928,7 @@
       <c r="G18" s="15" t="n">
         <v>13.78</v>
       </c>
-      <c r="H18" s="15" t="n">
-        <v>10.52</v>
-      </c>
+      <c r="H18" s="15" t="n"/>
       <c r="I18" s="15" t="n"/>
       <c r="J18" s="15" t="n">
         <v>15.59</v>
@@ -1983,7 +1961,7 @@
         <v>3.29</v>
       </c>
       <c r="V18" s="15" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="W18" s="15" t="n"/>
       <c r="X18" s="16" t="n">
@@ -1999,10 +1977,10 @@
         <v>22.59</v>
       </c>
       <c r="AB18" s="16" t="n">
-        <v>26.62</v>
+        <v>27.18</v>
       </c>
       <c r="AC18" s="16" t="n">
-        <v>24.01</v>
+        <v>24.2</v>
       </c>
       <c r="AD18" s="16" t="n"/>
       <c r="AE18" s="15" t="n">
@@ -2018,10 +1996,10 @@
         <v>2.09</v>
       </c>
       <c r="AI18" s="15" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AJ18" s="15" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AK18" s="15" t="n"/>
     </row>
@@ -2071,7 +2049,7 @@
         <v>5.43</v>
       </c>
       <c r="U19" s="15" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="V19" s="15" t="n">
         <v>3.12</v>
@@ -2138,9 +2116,7 @@
       <c r="G20" s="15" t="n">
         <v>13.78</v>
       </c>
-      <c r="H20" s="15" t="n">
-        <v>10.52</v>
-      </c>
+      <c r="H20" s="15" t="n"/>
       <c r="I20" s="15" t="n"/>
       <c r="J20" s="15" t="n">
         <v>27.95</v>
@@ -2170,10 +2146,10 @@
         <v>5.2</v>
       </c>
       <c r="U20" s="15" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="V20" s="15" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="W20" s="15" t="n"/>
       <c r="X20" s="16" t="n">
@@ -2189,10 +2165,10 @@
         <v>20.95</v>
       </c>
       <c r="AB20" s="16" t="n">
-        <v>26.54</v>
+        <v>26.82</v>
       </c>
       <c r="AC20" s="16" t="n">
-        <v>23.41</v>
+        <v>23.63</v>
       </c>
       <c r="AD20" s="16" t="n"/>
       <c r="AE20" s="15" t="n">
@@ -2211,7 +2187,7 @@
         <v>1.4</v>
       </c>
       <c r="AJ20" s="15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK20" s="15" t="n"/>
     </row>
@@ -2272,7 +2248,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>9143</v>
+        <v>9431</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>41.88</v>
@@ -2287,11 +2263,9 @@
         <v>59.99</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>52.22</v>
-      </c>
-      <c r="H24" s="10" t="n">
-        <v>28.53</v>
-      </c>
+        <v>53.78</v>
+      </c>
+      <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="9" t="n">
         <v>14.66</v>
@@ -2321,10 +2295,10 @@
         <v>6.09</v>
       </c>
       <c r="U24" s="10" t="n">
-        <v>6.44</v>
+        <v>6.36</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>5.47</v>
+        <v>5.6</v>
       </c>
       <c r="W24" s="10" t="n"/>
       <c r="X24" s="11" t="n">
@@ -2340,7 +2314,7 @@
         <v>10.51</v>
       </c>
       <c r="AB24" s="12" t="n">
-        <v>13</v>
+        <v>12.47</v>
       </c>
       <c r="AC24" s="12" t="n">
         <v>20.59</v>
@@ -2359,10 +2333,10 @@
         <v>3.02</v>
       </c>
       <c r="AI24" s="10" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AJ24" s="10" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AK24" s="10" t="n"/>
     </row>
@@ -2373,7 +2347,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>40276</v>
+        <v>43271</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>19.31</v>
@@ -2388,11 +2362,9 @@
         <v>34.46</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>26.05</v>
-      </c>
-      <c r="H25" s="10" t="n">
-        <v>18.65</v>
-      </c>
+        <v>25.83</v>
+      </c>
+      <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="9" t="n">
         <v>7.97</v>
@@ -2422,10 +2394,10 @@
         <v>5</v>
       </c>
       <c r="U25" s="10" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="V25" s="10" t="n">
-        <v>3.94</v>
+        <v>4.19</v>
       </c>
       <c r="W25" s="10" t="n"/>
       <c r="X25" s="11" t="n">
@@ -2441,10 +2413,10 @@
         <v>19.14</v>
       </c>
       <c r="AB25" s="12" t="n">
-        <v>21.47</v>
+        <v>21.39</v>
       </c>
       <c r="AC25" s="12" t="n">
-        <v>23.14</v>
+        <v>23.29</v>
       </c>
       <c r="AD25" s="12" t="n"/>
       <c r="AE25" s="9" t="n">
@@ -2460,10 +2432,10 @@
         <v>1.81</v>
       </c>
       <c r="AI25" s="10" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AJ25" s="10" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AK25" s="10" t="n"/>
     </row>
@@ -2474,7 +2446,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>10954</v>
+        <v>11656</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>16.34</v>
@@ -2489,11 +2461,9 @@
         <v>36.3</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>48.09</v>
-      </c>
-      <c r="H26" s="10" t="n">
-        <v>28.81</v>
-      </c>
+        <v>44.85</v>
+      </c>
+      <c r="H26" s="10" t="n"/>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="9" t="n">
         <v>9.449999999999999</v>
@@ -2523,10 +2493,10 @@
         <v>6.43</v>
       </c>
       <c r="U26" s="10" t="n">
-        <v>10.03</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="V26" s="10" t="n">
-        <v>7.15</v>
+        <v>7.56</v>
       </c>
       <c r="W26" s="10" t="n"/>
       <c r="X26" s="11" t="n">
@@ -2561,10 +2531,10 @@
         <v>2.14</v>
       </c>
       <c r="AI26" s="10" t="n">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="AJ26" s="10" t="n">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="AK26" s="10" t="n"/>
     </row>
@@ -2575,7 +2545,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>9485</v>
+        <v>10303</v>
       </c>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n">
@@ -2588,11 +2558,9 @@
         <v>41.99</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>97.16</v>
-      </c>
-      <c r="H27" s="10" t="n">
-        <v>30.18</v>
-      </c>
+        <v>102.89</v>
+      </c>
+      <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="9" t="n">
         <v>13.88</v>
@@ -2625,7 +2593,7 @@
         <v>2.59</v>
       </c>
       <c r="V27" s="10" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="11" t="n">
@@ -2641,7 +2609,7 @@
         <v>6.6</v>
       </c>
       <c r="AB27" s="12" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AC27" s="12" t="n">
         <v>8.65</v>
@@ -2660,10 +2628,10 @@
         <v>2.78</v>
       </c>
       <c r="AI27" s="10" t="n">
-        <v>2.94</v>
+        <v>3.17</v>
       </c>
       <c r="AJ27" s="10" t="n">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="AK27" s="10" t="n"/>
     </row>
@@ -2674,7 +2642,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>10245</v>
+        <v>11036</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>15.67</v>
@@ -2689,11 +2657,9 @@
         <v>26.64</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>16.73</v>
-      </c>
-      <c r="H28" s="10" t="n">
-        <v>11.19</v>
-      </c>
+        <v>16.96</v>
+      </c>
+      <c r="H28" s="10" t="n"/>
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="9" t="n">
         <v>20.45</v>
@@ -2723,10 +2689,10 @@
         <v>6.66</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="V28" s="10" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="W28" s="10" t="n"/>
       <c r="X28" s="11" t="n">
@@ -2761,10 +2727,10 @@
         <v>3.51</v>
       </c>
       <c r="AI28" s="10" t="n">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="AJ28" s="10" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AK28" s="10" t="n"/>
     </row>
@@ -2782,7 +2748,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>129058</v>
+        <v>129122</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>21.56</v>
@@ -2797,10 +2763,10 @@
         <v>22.08</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>18.5</v>
+        <v>18.51</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>17.24</v>
+        <v>17.23</v>
       </c>
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="9" t="n">
@@ -2831,7 +2797,7 @@
         <v>16.48</v>
       </c>
       <c r="U30" s="10" t="n">
-        <v>12.67</v>
+        <v>12.68</v>
       </c>
       <c r="V30" s="10" t="n">
         <v>9.279999999999999</v>
@@ -2853,7 +2819,7 @@
         <v>82.53</v>
       </c>
       <c r="AC30" s="12" t="n">
-        <v>62.15</v>
+        <v>62.2</v>
       </c>
       <c r="AD30" s="12" t="n"/>
       <c r="AE30" s="9" t="n">
@@ -2883,7 +2849,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>78245</v>
+        <v>77469</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>17.07</v>
@@ -2898,10 +2864,10 @@
         <v>19.36</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>19.01</v>
+        <v>18.82</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>18.1</v>
+        <v>17.92</v>
       </c>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="9" t="n">
@@ -2932,10 +2898,10 @@
         <v>4.86</v>
       </c>
       <c r="U31" s="10" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="V31" s="10" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="W31" s="10" t="n"/>
       <c r="X31" s="11" t="n">
@@ -2970,10 +2936,10 @@
         <v>1.93</v>
       </c>
       <c r="AI31" s="10" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AJ31" s="10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AK31" s="10" t="n"/>
     </row>
@@ -2984,7 +2950,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>103908</v>
+        <v>102564</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>20.08</v>
@@ -2999,10 +2965,10 @@
         <v>21.62</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>22.61</v>
+        <v>22.31</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>20.67</v>
+        <v>20.4</v>
       </c>
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="9" t="n">
@@ -3033,10 +2999,10 @@
         <v>3.55</v>
       </c>
       <c r="U32" s="10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="V32" s="10" t="n">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="W32" s="10" t="n"/>
       <c r="X32" s="11" t="n">
@@ -3071,10 +3037,10 @@
         <v>1.73</v>
       </c>
       <c r="AI32" s="10" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AJ32" s="10" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AK32" s="10" t="n"/>
     </row>
@@ -3085,7 +3051,7 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>281760</v>
+        <v>284176</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>28.47</v>
@@ -3100,10 +3066,10 @@
         <v>36.57</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>28.98</v>
+        <v>29.23</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>26.72</v>
+        <v>26.95</v>
       </c>
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="9" t="n">
@@ -3134,10 +3100,10 @@
         <v>3.77</v>
       </c>
       <c r="U33" s="10" t="n">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="V33" s="10" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="W33" s="10" t="n"/>
       <c r="X33" s="11" t="n">
@@ -3172,10 +3138,10 @@
         <v>2.78</v>
       </c>
       <c r="AI33" s="10" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="AJ33" s="10" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AK33" s="10" t="n"/>
     </row>
@@ -3186,7 +3152,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>11702</v>
+        <v>11545</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>15.9</v>
@@ -3201,10 +3167,10 @@
         <v>22.06</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>16.09</v>
+        <v>15.89</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>14.31</v>
+        <v>14.12</v>
       </c>
       <c r="I34" s="10" t="n"/>
       <c r="J34" s="9" t="n">
@@ -3235,10 +3201,10 @@
         <v>2.63</v>
       </c>
       <c r="U34" s="10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V34" s="10" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="W34" s="10" t="n"/>
       <c r="X34" s="11" t="n">
@@ -3254,7 +3220,7 @@
         <v>12.42</v>
       </c>
       <c r="AB34" s="12" t="n">
-        <v>13.68</v>
+        <v>13.66</v>
       </c>
       <c r="AC34" s="12" t="n">
         <v>14.01</v>
@@ -3273,10 +3239,10 @@
         <v>1.07</v>
       </c>
       <c r="AI34" s="10" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="AJ34" s="10" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AK34" s="10" t="n"/>
     </row>
@@ -3294,7 +3260,7 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>62969</v>
+        <v>62437</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>17.03</v>
@@ -3398,7 +3364,7 @@
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>84937</v>
+        <v>810</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>16.56</v>
@@ -3412,12 +3378,8 @@
       <c r="F38" s="9" t="n">
         <v>24.33</v>
       </c>
-      <c r="G38" s="10" t="n">
-        <v>25.35</v>
-      </c>
-      <c r="H38" s="10" t="n">
-        <v>22.21</v>
-      </c>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
       <c r="I38" s="10" t="n"/>
       <c r="J38" s="9" t="n">
         <v>9.84</v>
@@ -3447,10 +3409,10 @@
         <v>4.26</v>
       </c>
       <c r="U38" s="10" t="n">
-        <v>4.8</v>
+        <v>0.05</v>
       </c>
       <c r="V38" s="10" t="n">
-        <v>4.35</v>
+        <v>0.04</v>
       </c>
       <c r="W38" s="10" t="n"/>
       <c r="X38" s="11" t="n">
@@ -3485,10 +3447,10 @@
         <v>1.77</v>
       </c>
       <c r="AI38" s="10" t="n">
-        <v>1.87</v>
+        <v>0.02</v>
       </c>
       <c r="AJ38" s="10" t="n">
-        <v>1.71</v>
+        <v>0.02</v>
       </c>
       <c r="AK38" s="10" t="n"/>
     </row>
@@ -3506,7 +3468,7 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>37895</v>
+        <v>35342</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>5</v>
@@ -3551,10 +3513,10 @@
         <v>2.97</v>
       </c>
       <c r="U40" s="10" t="n">
-        <v>3.09</v>
+        <v>2.91</v>
       </c>
       <c r="V40" s="10" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="W40" s="10" t="n"/>
       <c r="X40" s="11" t="n">
@@ -3570,10 +3532,10 @@
         <v>13.2</v>
       </c>
       <c r="AB40" s="12" t="n">
-        <v>13.64</v>
+        <v>13.7</v>
       </c>
       <c r="AC40" s="12" t="n">
-        <v>14.87</v>
+        <v>14.91</v>
       </c>
       <c r="AD40" s="12" t="n"/>
       <c r="AE40" s="9" t="n">
@@ -3589,10 +3551,10 @@
         <v>1.45</v>
       </c>
       <c r="AI40" s="10" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AJ40" s="10" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AK40" s="10" t="n"/>
     </row>
@@ -3610,7 +3572,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>37248</v>
+        <v>35910</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>24.79</v>
@@ -3655,10 +3617,10 @@
         <v>6.69</v>
       </c>
       <c r="U42" s="10" t="n">
-        <v>7.05</v>
+        <v>6.89</v>
       </c>
       <c r="V42" s="10" t="n">
-        <v>6.04</v>
+        <v>5.89</v>
       </c>
       <c r="W42" s="10" t="n"/>
       <c r="X42" s="11" t="n">
@@ -3693,10 +3655,10 @@
         <v>3.66</v>
       </c>
       <c r="AI42" s="10" t="n">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="AJ42" s="10" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AK42" s="10" t="n"/>
     </row>
@@ -3720,11 +3682,9 @@
         <v>36.3</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>48.09</v>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>28.53</v>
-      </c>
+        <v>44.85</v>
+      </c>
+      <c r="H43" s="15" t="n"/>
       <c r="I43" s="15" t="n"/>
       <c r="J43" s="15" t="n">
         <v>13.88</v>
@@ -3754,10 +3714,10 @@
         <v>6.09</v>
       </c>
       <c r="U43" s="15" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="V43" s="15" t="n">
-        <v>3.94</v>
+        <v>4.19</v>
       </c>
       <c r="W43" s="15" t="n"/>
       <c r="X43" s="16" t="n">
@@ -3773,10 +3733,10 @@
         <v>19.14</v>
       </c>
       <c r="AB43" s="16" t="n">
-        <v>21.47</v>
+        <v>21.39</v>
       </c>
       <c r="AC43" s="16" t="n">
-        <v>23.14</v>
+        <v>23.29</v>
       </c>
       <c r="AD43" s="16" t="n"/>
       <c r="AE43" s="15" t="n">
@@ -3792,10 +3752,10 @@
         <v>2.78</v>
       </c>
       <c r="AI43" s="15" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AJ43" s="15" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AK43" s="15" t="n"/>
     </row>
@@ -3819,10 +3779,10 @@
         <v>22.06</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>19.01</v>
+        <v>18.82</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>18.1</v>
+        <v>17.92</v>
       </c>
       <c r="I44" s="15" t="n"/>
       <c r="J44" s="15" t="n">
@@ -3853,10 +3813,10 @@
         <v>3.77</v>
       </c>
       <c r="U44" s="15" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="V44" s="15" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="W44" s="15" t="n"/>
       <c r="X44" s="16" t="n">
@@ -3891,10 +3851,10 @@
         <v>1.73</v>
       </c>
       <c r="AI44" s="15" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AJ44" s="15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AK44" s="15" t="n"/>
     </row>
@@ -4012,12 +3972,8 @@
       <c r="F46" s="15" t="n">
         <v>24.33</v>
       </c>
-      <c r="G46" s="15" t="n">
-        <v>25.35</v>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>22.21</v>
-      </c>
+      <c r="G46" s="15" t="n"/>
+      <c r="H46" s="15" t="n"/>
       <c r="I46" s="15" t="n"/>
       <c r="J46" s="15" t="n">
         <v>9.84</v>
@@ -4047,10 +4003,10 @@
         <v>4.26</v>
       </c>
       <c r="U46" s="15" t="n">
-        <v>4.8</v>
+        <v>0.05</v>
       </c>
       <c r="V46" s="15" t="n">
-        <v>4.35</v>
+        <v>0.04</v>
       </c>
       <c r="W46" s="15" t="n"/>
       <c r="X46" s="16" t="n">
@@ -4085,10 +4041,10 @@
         <v>1.77</v>
       </c>
       <c r="AI46" s="15" t="n">
-        <v>1.87</v>
+        <v>0.02</v>
       </c>
       <c r="AJ46" s="15" t="n">
-        <v>1.71</v>
+        <v>0.02</v>
       </c>
       <c r="AK46" s="15" t="n"/>
     </row>
@@ -4142,10 +4098,10 @@
         <v>2.97</v>
       </c>
       <c r="U47" s="15" t="n">
-        <v>3.09</v>
+        <v>2.91</v>
       </c>
       <c r="V47" s="15" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="W47" s="15" t="n"/>
       <c r="X47" s="16" t="n">
@@ -4161,10 +4117,10 @@
         <v>13.2</v>
       </c>
       <c r="AB47" s="16" t="n">
-        <v>13.64</v>
+        <v>13.7</v>
       </c>
       <c r="AC47" s="16" t="n">
-        <v>14.87</v>
+        <v>14.91</v>
       </c>
       <c r="AD47" s="16" t="n"/>
       <c r="AE47" s="15" t="n">
@@ -4180,10 +4136,10 @@
         <v>1.45</v>
       </c>
       <c r="AI47" s="15" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AJ47" s="15" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AK47" s="15" t="n"/>
     </row>
@@ -4237,10 +4193,10 @@
         <v>6.69</v>
       </c>
       <c r="U48" s="15" t="n">
-        <v>7.05</v>
+        <v>6.89</v>
       </c>
       <c r="V48" s="15" t="n">
-        <v>6.04</v>
+        <v>5.89</v>
       </c>
       <c r="W48" s="15" t="n"/>
       <c r="X48" s="16" t="n">
@@ -4275,10 +4231,10 @@
         <v>3.66</v>
       </c>
       <c r="AI48" s="15" t="n">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="AJ48" s="15" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AK48" s="15" t="n"/>
     </row>
@@ -4302,10 +4258,10 @@
         <v>30.55</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>25.35</v>
+        <v>24.07</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>20.67</v>
+        <v>17.92</v>
       </c>
       <c r="I49" s="15" t="n"/>
       <c r="J49" s="15" t="n">
@@ -4336,10 +4292,10 @@
         <v>4.93</v>
       </c>
       <c r="U49" s="15" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="V49" s="15" t="n">
-        <v>3.83</v>
+        <v>3.59</v>
       </c>
       <c r="W49" s="15" t="n"/>
       <c r="X49" s="16" t="n">
@@ -4374,10 +4330,10 @@
         <v>2.04</v>
       </c>
       <c r="AI49" s="15" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AJ49" s="15" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AK49" s="15" t="n"/>
     </row>
@@ -4438,7 +4394,7 @@
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>3998</v>
+        <v>4738</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>10.61</v>
@@ -4453,11 +4409,9 @@
         <v>47.5</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>9.92</v>
-      </c>
-      <c r="H53" s="10" t="n">
-        <v>7.78</v>
-      </c>
+        <v>11.11</v>
+      </c>
+      <c r="H53" s="10" t="n"/>
       <c r="I53" s="10" t="n"/>
       <c r="J53" s="9" t="n">
         <v>7.18</v>
@@ -4487,10 +4441,10 @@
         <v>2.61</v>
       </c>
       <c r="U53" s="10" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="V53" s="10" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="W53" s="10" t="n"/>
       <c r="X53" s="11" t="n">
@@ -4525,10 +4479,10 @@
         <v>1.25</v>
       </c>
       <c r="AI53" s="10" t="n">
-        <v>0.59</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AJ53" s="10" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="AK53" s="10" t="n"/>
     </row>
@@ -4539,59 +4493,57 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>3998</v>
+        <v>4390</v>
       </c>
       <c r="C54" s="9" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>7.35</v>
+        <v>0.01</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>13.73</v>
+        <v>0.01</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="H54" s="10" t="n">
-        <v>8.74</v>
-      </c>
+        <v>10.75</v>
+      </c>
+      <c r="H54" s="10" t="n"/>
       <c r="I54" s="10" t="n"/>
       <c r="J54" s="9" t="n">
-        <v>3.59</v>
+        <v>0.68</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>3.14</v>
+        <v>0.01</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>3.61</v>
+        <v>0.16</v>
       </c>
       <c r="M54" s="9" t="n">
-        <v>5.3</v>
+        <v>-0.28</v>
       </c>
       <c r="N54" s="10" t="n"/>
       <c r="O54" s="10" t="n"/>
       <c r="P54" s="10" t="n"/>
       <c r="Q54" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="R54" s="9" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="S54" s="9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="T54" s="9" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="U54" s="10" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="W54" s="10" t="n"/>
       <c r="X54" s="11" t="n">
@@ -4614,22 +4566,22 @@
       </c>
       <c r="AD54" s="12" t="n"/>
       <c r="AE54" s="9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AF54" s="9" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="AG54" s="9" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="AH54" s="9" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="AI54" s="10" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="AJ54" s="10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="AK54" s="10" t="n"/>
     </row>
@@ -4640,7 +4592,7 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>7.23</v>
@@ -4721,7 +4673,7 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>5.78</v>
@@ -4735,12 +4687,8 @@
       <c r="F56" s="9" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="G56" s="10" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="H56" s="10" t="n">
-        <v>5.66</v>
-      </c>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
       <c r="I56" s="10" t="n"/>
       <c r="J56" s="9" t="n">
         <v>3.96</v>
@@ -4770,10 +4718,10 @@
         <v>0.92</v>
       </c>
       <c r="U56" s="10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="V56" s="10" t="n">
         <v>0.73</v>
-      </c>
-      <c r="V56" s="10" t="n">
-        <v>0.66</v>
       </c>
       <c r="W56" s="10" t="n"/>
       <c r="X56" s="11" t="n">
@@ -4808,10 +4756,10 @@
         <v>0.59</v>
       </c>
       <c r="AI56" s="10" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AJ56" s="10" t="n">
         <v>0.46</v>
-      </c>
-      <c r="AJ56" s="10" t="n">
-        <v>0.42</v>
       </c>
       <c r="AK56" s="10" t="n"/>
     </row>
@@ -4822,7 +4770,7 @@
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>7.57</v>
@@ -4907,7 +4855,7 @@
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>5.71</v>
@@ -4999,7 +4947,7 @@
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>385211</v>
+        <v>372346</v>
       </c>
       <c r="C60" s="9" t="n">
         <v>18.45</v>
@@ -5014,10 +4962,10 @@
         <v>30</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>30.32</v>
+        <v>29.31</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>25.65</v>
+        <v>24.79</v>
       </c>
       <c r="I60" s="10" t="n"/>
       <c r="J60" s="9" t="n">
@@ -5048,10 +4996,10 @@
         <v>12.5</v>
       </c>
       <c r="U60" s="10" t="n">
-        <v>12.54</v>
+        <v>12.12</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>9.210000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W60" s="10" t="n"/>
       <c r="X60" s="11" t="n">
@@ -5086,10 +5034,10 @@
         <v>3.94</v>
       </c>
       <c r="AI60" s="10" t="n">
-        <v>4.87</v>
+        <v>4.7</v>
       </c>
       <c r="AJ60" s="10" t="n">
-        <v>4.38</v>
+        <v>4.24</v>
       </c>
       <c r="AK60" s="10" t="n"/>
     </row>
@@ -5100,7 +5048,7 @@
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>175045</v>
+        <v>170411</v>
       </c>
       <c r="C61" s="9" t="n">
         <v>16.58</v>
@@ -5115,10 +5063,10 @@
         <v>24.83</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>36.08</v>
+        <v>34.77</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>28.85</v>
+        <v>28.07</v>
       </c>
       <c r="I61" s="10" t="n"/>
       <c r="J61" s="9" t="n">
@@ -5149,10 +5097,10 @@
         <v>4.81</v>
       </c>
       <c r="U61" s="10" t="n">
-        <v>6.03</v>
+        <v>5.86</v>
       </c>
       <c r="V61" s="10" t="n">
-        <v>5.33</v>
+        <v>5.17</v>
       </c>
       <c r="W61" s="10" t="n"/>
       <c r="X61" s="11" t="n">
@@ -5168,10 +5116,10 @@
         <v>20.61</v>
       </c>
       <c r="AB61" s="12" t="n">
-        <v>17.65</v>
+        <v>17.81</v>
       </c>
       <c r="AC61" s="12" t="n">
-        <v>19.61</v>
+        <v>19.57</v>
       </c>
       <c r="AD61" s="12" t="n"/>
       <c r="AE61" s="9" t="n">
@@ -5187,10 +5135,10 @@
         <v>2.79</v>
       </c>
       <c r="AI61" s="10" t="n">
-        <v>4.02</v>
+        <v>4.14</v>
       </c>
       <c r="AJ61" s="10" t="n">
-        <v>3.89</v>
+        <v>3.83</v>
       </c>
       <c r="AK61" s="10" t="n"/>
     </row>
@@ -5201,7 +5149,7 @@
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>14743</v>
+        <v>14507</v>
       </c>
       <c r="C62" s="9" t="n">
         <v>10.64</v>
@@ -5216,10 +5164,10 @@
         <v>22.45</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>26.27</v>
+        <v>25.85</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>17.29</v>
+        <v>17.02</v>
       </c>
       <c r="I62" s="10" t="n"/>
       <c r="J62" s="9" t="n">
@@ -5250,10 +5198,10 @@
         <v>1.48</v>
       </c>
       <c r="U62" s="10" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V62" s="10" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="W62" s="10" t="n"/>
       <c r="X62" s="11" t="n">
@@ -5288,10 +5236,10 @@
         <v>0.63</v>
       </c>
       <c r="AI62" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AJ62" s="10" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="AK62" s="10" t="n"/>
     </row>
@@ -5302,7 +5250,7 @@
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>69312</v>
+        <v>65005</v>
       </c>
       <c r="C63" s="9" t="n">
         <v>11.71</v>
@@ -5317,10 +5265,10 @@
         <v>20.48</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>22.31</v>
+        <v>20.92</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>19.21</v>
+        <v>18.02</v>
       </c>
       <c r="I63" s="10" t="n"/>
       <c r="J63" s="9" t="n">
@@ -5351,10 +5299,10 @@
         <v>5.69</v>
       </c>
       <c r="U63" s="10" t="n">
-        <v>6.02</v>
+        <v>5.65</v>
       </c>
       <c r="V63" s="10" t="n">
-        <v>4.79</v>
+        <v>4.49</v>
       </c>
       <c r="W63" s="10" t="n"/>
       <c r="X63" s="11" t="n">
@@ -5389,10 +5337,10 @@
         <v>3.17</v>
       </c>
       <c r="AI63" s="10" t="n">
-        <v>3.91</v>
+        <v>3.66</v>
       </c>
       <c r="AJ63" s="10" t="n">
-        <v>3.59</v>
+        <v>3.37</v>
       </c>
       <c r="AK63" s="10" t="n"/>
     </row>
@@ -5410,7 +5358,7 @@
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>40074</v>
+        <v>41853</v>
       </c>
       <c r="C65" s="9" t="n"/>
       <c r="D65" s="9" t="n">
@@ -5425,12 +5373,8 @@
       <c r="G65" s="10" t="n">
         <v>14.4</v>
       </c>
-      <c r="H65" s="10" t="n">
-        <v>16.32</v>
-      </c>
-      <c r="I65" s="10" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="10" t="n"/>
       <c r="J65" s="9" t="n"/>
       <c r="K65" s="9" t="n">
         <v>5.96</v>
@@ -5460,10 +5404,10 @@
         <v>1.54</v>
       </c>
       <c r="V65" s="10" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="W65" s="10" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="X65" s="11" t="n"/>
       <c r="Y65" s="11" t="n">
@@ -5498,10 +5442,10 @@
         <v>1.31</v>
       </c>
       <c r="AJ65" s="10" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AK65" s="10" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="66">
@@ -5511,7 +5455,7 @@
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>7558</v>
+        <v>7736</v>
       </c>
       <c r="C66" s="9" t="n"/>
       <c r="D66" s="9" t="n">
@@ -5526,12 +5470,8 @@
       <c r="G66" s="10" t="n">
         <v>15.32</v>
       </c>
-      <c r="H66" s="10" t="n">
-        <v>13.42</v>
-      </c>
-      <c r="I66" s="10" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="n"/>
       <c r="J66" s="9" t="n"/>
       <c r="K66" s="9" t="n">
         <v>5.66</v>
@@ -5561,10 +5501,10 @@
         <v>1.25</v>
       </c>
       <c r="V66" s="10" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="W66" s="10" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X66" s="11" t="n"/>
       <c r="Y66" s="11" t="n">
@@ -5580,10 +5520,10 @@
         <v>8.56</v>
       </c>
       <c r="AC66" s="12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="AD66" s="12" t="n">
-        <v>10.68</v>
+        <v>10.74</v>
       </c>
       <c r="AE66" s="9" t="n"/>
       <c r="AF66" s="9" t="n">
@@ -5599,10 +5539,10 @@
         <v>0.8</v>
       </c>
       <c r="AJ66" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="AK66" s="10" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="67">
@@ -5619,7 +5559,7 @@
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>73570</v>
+        <v>73844</v>
       </c>
       <c r="C68" s="9" t="n">
         <v>11.71</v>
@@ -5664,10 +5604,10 @@
         <v>3.37</v>
       </c>
       <c r="U68" s="10" t="n">
-        <v>3.47</v>
+        <v>3.52</v>
       </c>
       <c r="V68" s="10" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="W68" s="10" t="n"/>
       <c r="X68" s="11" t="n">
@@ -5702,10 +5642,10 @@
         <v>1.26</v>
       </c>
       <c r="AI68" s="10" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AJ68" s="10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK68" s="10" t="n"/>
     </row>
@@ -5723,7 +5663,7 @@
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>25756</v>
+        <v>26125</v>
       </c>
       <c r="C70" s="9" t="n">
         <v>31.28</v>
@@ -5737,12 +5677,8 @@
       <c r="F70" s="9" t="n">
         <v>23.11</v>
       </c>
-      <c r="G70" s="10" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="H70" s="10" t="n">
-        <v>12.43</v>
-      </c>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
       <c r="I70" s="10" t="n"/>
       <c r="J70" s="9" t="n">
         <v>18.39</v>
@@ -5772,10 +5708,10 @@
         <v>2.2</v>
       </c>
       <c r="U70" s="10" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V70" s="10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W70" s="10" t="n"/>
       <c r="X70" s="11" t="n">
@@ -5810,10 +5746,10 @@
         <v>2.17</v>
       </c>
       <c r="AI70" s="10" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AJ70" s="10" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="AK70" s="10" t="n"/>
     </row>
@@ -5824,7 +5760,7 @@
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>14026</v>
+        <v>13850</v>
       </c>
       <c r="C71" s="9" t="n">
         <v>13.89</v>
@@ -5838,12 +5774,8 @@
       <c r="F71" s="9" t="n">
         <v>20.71</v>
       </c>
-      <c r="G71" s="10" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="H71" s="10" t="n">
-        <v>8.56</v>
-      </c>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
       <c r="I71" s="10" t="n"/>
       <c r="J71" s="9" t="n">
         <v>7.78</v>
@@ -5873,10 +5805,10 @@
         <v>2.25</v>
       </c>
       <c r="U71" s="10" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V71" s="10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W71" s="10" t="n"/>
       <c r="X71" s="11" t="n">
@@ -5892,10 +5824,10 @@
         <v>10.96</v>
       </c>
       <c r="AB71" s="12" t="n">
-        <v>13.77</v>
+        <v>13.38</v>
       </c>
       <c r="AC71" s="12" t="n">
-        <v>15.67</v>
+        <v>15.49</v>
       </c>
       <c r="AD71" s="12" t="n"/>
       <c r="AE71" s="9" t="n">
@@ -5911,10 +5843,10 @@
         <v>1.35</v>
       </c>
       <c r="AI71" s="10" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AJ71" s="10" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="AK71" s="10" t="n"/>
     </row>
@@ -5929,32 +5861,30 @@
         <v>6.51</v>
       </c>
       <c r="D72" s="15" t="n">
-        <v>6.27</v>
+        <v>6</v>
       </c>
       <c r="E72" s="15" t="n">
-        <v>7.35</v>
+        <v>5.58</v>
       </c>
       <c r="F72" s="15" t="n">
-        <v>8.390000000000001</v>
+        <v>5.89</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>9.92</v>
-      </c>
-      <c r="H72" s="15" t="n">
-        <v>7.78</v>
-      </c>
+        <v>10.93</v>
+      </c>
+      <c r="H72" s="15" t="n"/>
       <c r="I72" s="15" t="n"/>
       <c r="J72" s="15" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="K72" s="15" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="L72" s="15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M72" s="15" t="n">
         <v>3.77</v>
-      </c>
-      <c r="K72" s="15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L72" s="15" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="M72" s="15" t="n">
-        <v>5.07</v>
       </c>
       <c r="N72" s="15" t="n"/>
       <c r="O72" s="15" t="n"/>
@@ -5963,19 +5893,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="R72" s="15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S72" s="15" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="T72" s="15" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="U72" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="V72" s="15" t="n">
         <v>0.73</v>
-      </c>
-      <c r="S72" s="15" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="T72" s="15" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="U72" s="15" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="V72" s="15" t="n">
-        <v>0.6899999999999999</v>
       </c>
       <c r="W72" s="15" t="n"/>
       <c r="X72" s="16" t="n">
@@ -5998,22 +5928,22 @@
       </c>
       <c r="AD72" s="16" t="n"/>
       <c r="AE72" s="15" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="AF72" s="15" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="AG72" s="15" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="AH72" s="15" t="n">
-        <v>0.53</v>
+        <v>0.43</v>
       </c>
       <c r="AI72" s="15" t="n">
-        <v>0.58</v>
+        <v>0.52</v>
       </c>
       <c r="AJ72" s="15" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="AK72" s="15" t="n"/>
     </row>
@@ -6037,10 +5967,10 @@
         <v>23.64</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>28.3</v>
+        <v>27.58</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>22.43</v>
+        <v>21.41</v>
       </c>
       <c r="I73" s="15" t="n"/>
       <c r="J73" s="15" t="n">
@@ -6071,10 +6001,10 @@
         <v>5.25</v>
       </c>
       <c r="U73" s="15" t="n">
-        <v>6.03</v>
+        <v>5.76</v>
       </c>
       <c r="V73" s="15" t="n">
-        <v>5.06</v>
+        <v>4.83</v>
       </c>
       <c r="W73" s="15" t="n"/>
       <c r="X73" s="16" t="n">
@@ -6090,10 +6020,10 @@
         <v>24.48</v>
       </c>
       <c r="AB73" s="16" t="n">
-        <v>23.99</v>
+        <v>24.07</v>
       </c>
       <c r="AC73" s="16" t="n">
-        <v>23.7</v>
+        <v>23.68</v>
       </c>
       <c r="AD73" s="16" t="n"/>
       <c r="AE73" s="15" t="n">
@@ -6109,10 +6039,10 @@
         <v>2.98</v>
       </c>
       <c r="AI73" s="15" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="AJ73" s="15" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="AK73" s="15" t="n"/>
     </row>
@@ -6136,12 +6066,8 @@
       <c r="G74" s="15" t="n">
         <v>14.86</v>
       </c>
-      <c r="H74" s="15" t="n">
-        <v>14.87</v>
-      </c>
-      <c r="I74" s="15" t="n">
-        <v>13.35</v>
-      </c>
+      <c r="H74" s="15" t="n"/>
+      <c r="I74" s="15" t="n"/>
       <c r="J74" s="15" t="n"/>
       <c r="K74" s="15" t="n">
         <v>5.81</v>
@@ -6171,10 +6097,10 @@
         <v>1.4</v>
       </c>
       <c r="V74" s="15" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="W74" s="15" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="X74" s="16" t="n"/>
       <c r="Y74" s="16" t="n">
@@ -6190,10 +6116,10 @@
         <v>9.91</v>
       </c>
       <c r="AC74" s="16" t="n">
-        <v>10.24</v>
+        <v>10.26</v>
       </c>
       <c r="AD74" s="16" t="n">
-        <v>10.84</v>
+        <v>10.87</v>
       </c>
       <c r="AE74" s="15" t="n"/>
       <c r="AF74" s="15" t="n">
@@ -6209,10 +6135,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ74" s="15" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK74" s="15" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="75">
@@ -6265,10 +6191,10 @@
         <v>3.37</v>
       </c>
       <c r="U75" s="15" t="n">
-        <v>3.47</v>
+        <v>3.52</v>
       </c>
       <c r="V75" s="15" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="W75" s="15" t="n"/>
       <c r="X75" s="16" t="n">
@@ -6303,10 +6229,10 @@
         <v>1.26</v>
       </c>
       <c r="AI75" s="15" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AJ75" s="15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK75" s="15" t="n"/>
     </row>
@@ -6329,12 +6255,8 @@
       <c r="F76" s="15" t="n">
         <v>21.91</v>
       </c>
-      <c r="G76" s="15" t="n">
-        <v>13.44</v>
-      </c>
-      <c r="H76" s="15" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="G76" s="15" t="n"/>
+      <c r="H76" s="15" t="n"/>
       <c r="I76" s="15" t="n"/>
       <c r="J76" s="15" t="n">
         <v>13.09</v>
@@ -6364,7 +6286,7 @@
         <v>2.23</v>
       </c>
       <c r="U76" s="15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V76" s="15" t="n">
         <v>1.54</v>
@@ -6383,10 +6305,10 @@
         <v>10.73</v>
       </c>
       <c r="AB76" s="16" t="n">
-        <v>12.85</v>
+        <v>12.66</v>
       </c>
       <c r="AC76" s="16" t="n">
-        <v>15.25</v>
+        <v>15.16</v>
       </c>
       <c r="AD76" s="16" t="n"/>
       <c r="AE76" s="15" t="n">
@@ -6402,10 +6324,10 @@
         <v>1.76</v>
       </c>
       <c r="AI76" s="15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AJ76" s="15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK76" s="15" t="n"/>
     </row>
@@ -6429,14 +6351,12 @@
         <v>18.97</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>15.32</v>
+        <v>18.12</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>13.42</v>
-      </c>
-      <c r="I77" s="15" t="n">
-        <v>13.35</v>
-      </c>
+        <v>21.41</v>
+      </c>
+      <c r="I77" s="15" t="n"/>
       <c r="J77" s="15" t="n">
         <v>7.18</v>
       </c>
@@ -6467,13 +6387,13 @@
         <v>1.48</v>
       </c>
       <c r="U77" s="15" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V77" s="15" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="W77" s="15" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="X77" s="16" t="n">
         <v>15.47</v>
@@ -6488,13 +6408,13 @@
         <v>10.49</v>
       </c>
       <c r="AB77" s="16" t="n">
-        <v>12.85</v>
+        <v>12.66</v>
       </c>
       <c r="AC77" s="16" t="n">
-        <v>15.25</v>
+        <v>15.16</v>
       </c>
       <c r="AD77" s="16" t="n">
-        <v>10.84</v>
+        <v>10.87</v>
       </c>
       <c r="AE77" s="15" t="n">
         <v>0.64</v>
@@ -6512,10 +6432,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ77" s="15" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AK77" s="15" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
     </row>
   </sheetData>
@@ -6638,7 +6558,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34297</v>
+        <v>34859</v>
       </c>
       <c r="F2" s="9" t="n"/>
       <c r="G2" s="9" t="n">
@@ -6651,11 +6571,9 @@
         <v>37.73</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>15.31</v>
-      </c>
-      <c r="K2" s="9" t="n">
-        <v>12.69</v>
-      </c>
+        <v>14.82</v>
+      </c>
+      <c r="K2" s="9" t="n"/>
       <c r="L2" s="9" t="n"/>
     </row>
     <row r="3">
@@ -6680,7 +6598,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>18614</v>
+        <v>19709</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n">
@@ -6695,9 +6613,7 @@
       <c r="J3" s="9" t="n">
         <v>13.78</v>
       </c>
-      <c r="K3" s="9" t="n">
-        <v>13.14</v>
-      </c>
+      <c r="K3" s="9" t="n"/>
       <c r="L3" s="9" t="n"/>
     </row>
     <row r="4">
@@ -6722,7 +6638,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>12449</v>
+        <v>13163</v>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n"/>
@@ -6733,11 +6649,9 @@
         <v>37.73</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>19.47</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>11.91</v>
-      </c>
+        <v>19.95</v>
+      </c>
+      <c r="K4" s="9" t="n"/>
       <c r="L4" s="9" t="n"/>
     </row>
     <row r="5">
@@ -6762,7 +6676,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>17781</v>
+        <v>18223</v>
       </c>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n">
@@ -6775,11 +6689,9 @@
         <v>13.27</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="K5" s="9" t="n">
-        <v>5.88</v>
-      </c>
+        <v>6.4</v>
+      </c>
+      <c r="K5" s="9" t="n"/>
       <c r="L5" s="9" t="n"/>
     </row>
     <row r="6">
@@ -6804,7 +6716,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -6813,11 +6725,9 @@
         <v>10.3</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>6.4</v>
-      </c>
+        <v>6.17</v>
+      </c>
+      <c r="K6" s="9" t="n"/>
       <c r="L6" s="9" t="n"/>
     </row>
     <row r="7">
@@ -6842,7 +6752,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1104</v>
+        <v>1126</v>
       </c>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
@@ -6853,7 +6763,7 @@
         <v>36.95</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -6880,7 +6790,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5241</v>
+        <v>5211</v>
       </c>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="9" t="n"/>
@@ -6916,7 +6826,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6395</v>
+        <v>7202</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -6927,11 +6837,9 @@
         <v>32.18</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="K9" s="9" t="n">
-        <v>20.91</v>
-      </c>
+        <v>28.12</v>
+      </c>
+      <c r="K9" s="9" t="n"/>
       <c r="L9" s="9" t="n"/>
     </row>
     <row r="10">
@@ -6956,7 +6864,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1216</v>
+        <v>1309</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>14.21</v>
@@ -6971,11 +6879,9 @@
         <v>18.39</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>14.04</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>9.130000000000001</v>
-      </c>
+        <v>13.93</v>
+      </c>
+      <c r="K10" s="9" t="n"/>
       <c r="L10" s="9" t="n"/>
     </row>
     <row r="11">
@@ -7000,7 +6906,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2654</v>
+        <v>2926</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
@@ -7011,11 +6917,9 @@
         <v>20.62</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>19.32</v>
-      </c>
-      <c r="K11" s="9" t="n">
-        <v>13.07</v>
-      </c>
+        <v>20.27</v>
+      </c>
+      <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n"/>
     </row>
     <row r="12">
@@ -7040,7 +6944,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>819</v>
+        <v>914</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>23.46</v>
@@ -7053,11 +6957,9 @@
         <v>14.78</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>10.26</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>8</v>
-      </c>
+        <v>10.91</v>
+      </c>
+      <c r="K12" s="9" t="n"/>
       <c r="L12" s="9" t="n"/>
     </row>
     <row r="13">
@@ -7082,7 +6984,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>37.11</v>
@@ -7097,11 +6999,9 @@
         <v>13.58</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>6.23</v>
-      </c>
-      <c r="K13" s="9" t="n">
-        <v>5.76</v>
-      </c>
+        <v>6.55</v>
+      </c>
+      <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
     </row>
     <row r="14">
@@ -7126,7 +7026,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9143</v>
+        <v>9431</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>41.88</v>
@@ -7141,11 +7041,9 @@
         <v>59.99</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>52.22</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>28.53</v>
-      </c>
+        <v>53.78</v>
+      </c>
+      <c r="K14" s="9" t="n"/>
       <c r="L14" s="9" t="n"/>
     </row>
     <row r="15">
@@ -7170,7 +7068,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>40276</v>
+        <v>43271</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>19.31</v>
@@ -7185,11 +7083,9 @@
         <v>34.46</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>26.05</v>
-      </c>
-      <c r="K15" s="9" t="n">
-        <v>18.65</v>
-      </c>
+        <v>25.83</v>
+      </c>
+      <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
     </row>
     <row r="16">
@@ -7214,7 +7110,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>10954</v>
+        <v>11656</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>16.34</v>
@@ -7229,11 +7125,9 @@
         <v>36.3</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>48.09</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>28.81</v>
-      </c>
+        <v>44.85</v>
+      </c>
+      <c r="K16" s="9" t="n"/>
       <c r="L16" s="9" t="n"/>
     </row>
     <row r="17">
@@ -7258,7 +7152,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9485</v>
+        <v>10303</v>
       </c>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n">
@@ -7271,11 +7165,9 @@
         <v>41.99</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>97.16</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <v>30.18</v>
-      </c>
+        <v>102.89</v>
+      </c>
+      <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
     </row>
     <row r="18">
@@ -7300,7 +7192,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10245</v>
+        <v>11036</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>15.67</v>
@@ -7315,11 +7207,9 @@
         <v>26.64</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>16.73</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <v>11.19</v>
-      </c>
+        <v>16.96</v>
+      </c>
+      <c r="K18" s="9" t="n"/>
       <c r="L18" s="9" t="n"/>
     </row>
     <row r="19">
@@ -7344,7 +7234,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>129058</v>
+        <v>129122</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>21.56</v>
@@ -7359,10 +7249,10 @@
         <v>22.08</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>18.5</v>
+        <v>18.51</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>17.24</v>
+        <v>17.23</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -7388,7 +7278,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>78245</v>
+        <v>77469</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>17.07</v>
@@ -7403,10 +7293,10 @@
         <v>19.36</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>19.01</v>
+        <v>18.82</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>18.1</v>
+        <v>17.92</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -7432,7 +7322,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>103908</v>
+        <v>102564</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>20.08</v>
@@ -7447,10 +7337,10 @@
         <v>21.62</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>22.61</v>
+        <v>22.31</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>20.67</v>
+        <v>20.4</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -7476,7 +7366,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>281760</v>
+        <v>284176</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>28.47</v>
@@ -7491,10 +7381,10 @@
         <v>36.57</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>28.98</v>
+        <v>29.23</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>26.72</v>
+        <v>26.95</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -7520,7 +7410,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11702</v>
+        <v>11545</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>15.9</v>
@@ -7535,10 +7425,10 @@
         <v>22.06</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>16.09</v>
+        <v>15.89</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>14.31</v>
+        <v>14.12</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -7564,7 +7454,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>62969</v>
+        <v>62437</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>17.03</v>
@@ -7604,7 +7494,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>84937</v>
+        <v>810</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>16.56</v>
@@ -7618,12 +7508,8 @@
       <c r="I25" s="9" t="n">
         <v>24.33</v>
       </c>
-      <c r="J25" s="9" t="n">
-        <v>25.35</v>
-      </c>
-      <c r="K25" s="9" t="n">
-        <v>22.21</v>
-      </c>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
     </row>
     <row r="26">
@@ -7648,7 +7534,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>37895</v>
+        <v>35342</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>5</v>
@@ -7688,7 +7574,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>37248</v>
+        <v>35910</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>24.79</v>
@@ -7728,7 +7614,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3998</v>
+        <v>4738</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>10.61</v>
@@ -7743,11 +7629,9 @@
         <v>47.5</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>9.92</v>
-      </c>
-      <c r="K28" s="9" t="n">
-        <v>7.78</v>
-      </c>
+        <v>11.11</v>
+      </c>
+      <c r="K28" s="9" t="n"/>
       <c r="L28" s="9" t="n"/>
     </row>
     <row r="29">
@@ -7772,26 +7656,24 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>3998</v>
+        <v>4390</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>7.35</v>
+        <v>0.01</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>13.73</v>
+        <v>0.01</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="K29" s="9" t="n">
-        <v>8.74</v>
-      </c>
+        <v>10.75</v>
+      </c>
+      <c r="K29" s="9" t="n"/>
       <c r="L29" s="9" t="n"/>
     </row>
     <row r="30">
@@ -7816,7 +7698,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>7.23</v>
@@ -7852,7 +7734,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>385211</v>
+        <v>372346</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>18.45</v>
@@ -7867,10 +7749,10 @@
         <v>30</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>30.32</v>
+        <v>29.31</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>25.65</v>
+        <v>24.79</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -7896,7 +7778,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>175045</v>
+        <v>170411</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>16.58</v>
@@ -7911,10 +7793,10 @@
         <v>24.83</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>36.08</v>
+        <v>34.77</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>28.85</v>
+        <v>28.07</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -7940,7 +7822,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>14743</v>
+        <v>14507</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>10.64</v>
@@ -7955,10 +7837,10 @@
         <v>22.45</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>26.27</v>
+        <v>25.85</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>17.29</v>
+        <v>17.02</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -7984,7 +7866,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>40074</v>
+        <v>41853</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -7999,12 +7881,8 @@
       <c r="J34" s="9" t="n">
         <v>14.4</v>
       </c>
-      <c r="K34" s="9" t="n">
-        <v>16.32</v>
-      </c>
-      <c r="L34" s="9" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" s="9" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -8028,7 +7906,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7558</v>
+        <v>7736</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -8043,12 +7921,8 @@
       <c r="J35" s="9" t="n">
         <v>15.32</v>
       </c>
-      <c r="K35" s="9" t="n">
-        <v>13.42</v>
-      </c>
-      <c r="L35" s="9" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="9" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -8072,7 +7946,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>73570</v>
+        <v>73844</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>11.71</v>
@@ -8112,7 +7986,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>25756</v>
+        <v>26125</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>31.28</v>
@@ -8126,12 +8000,8 @@
       <c r="I37" s="9" t="n">
         <v>23.11</v>
       </c>
-      <c r="J37" s="9" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>12.43</v>
-      </c>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="9" t="n"/>
       <c r="L37" s="9" t="n"/>
     </row>
     <row r="38">
@@ -8156,7 +8026,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14026</v>
+        <v>13850</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>13.89</v>
@@ -8170,12 +8040,8 @@
       <c r="I38" s="9" t="n">
         <v>20.71</v>
       </c>
-      <c r="J38" s="9" t="n">
-        <v>10.77</v>
-      </c>
-      <c r="K38" s="9" t="n">
-        <v>8.56</v>
-      </c>
+      <c r="J38" s="9" t="n"/>
+      <c r="K38" s="9" t="n"/>
       <c r="L38" s="9" t="n"/>
     </row>
     <row r="39">
@@ -8200,7 +8066,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>5.78</v>
@@ -8214,12 +8080,8 @@
       <c r="I39" s="9" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="J39" s="9" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <v>5.66</v>
-      </c>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="9" t="n"/>
       <c r="L39" s="9" t="n"/>
     </row>
     <row r="40">
@@ -8244,7 +8106,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>7.57</v>
@@ -8284,7 +8146,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>5.71</v>
@@ -8324,7 +8186,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>69312</v>
+        <v>65005</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>11.71</v>
@@ -8339,10 +8201,10 @@
         <v>20.48</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>22.31</v>
+        <v>20.92</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>19.21</v>
+        <v>18.02</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -8458,7 +8320,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34297</v>
+        <v>34859</v>
       </c>
       <c r="F2" s="9" t="n"/>
       <c r="G2" s="9" t="n">
@@ -8496,7 +8358,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>18614</v>
+        <v>19709</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n">
@@ -8534,7 +8396,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>12449</v>
+        <v>13163</v>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n">
@@ -8572,7 +8434,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>17781</v>
+        <v>18223</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>40.3</v>
@@ -8612,7 +8474,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -8646,7 +8508,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1104</v>
+        <v>1126</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>87.52</v>
@@ -8684,7 +8546,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5241</v>
+        <v>5211</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>991.9299999999999</v>
@@ -8724,7 +8586,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6395</v>
+        <v>7202</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -8760,7 +8622,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1216</v>
+        <v>1309</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>11.7</v>
@@ -8800,7 +8662,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2654</v>
+        <v>2926</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -8838,7 +8700,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>819</v>
+        <v>914</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>11.21</v>
@@ -8878,7 +8740,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>15.59</v>
@@ -8918,7 +8780,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9143</v>
+        <v>9431</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>14.66</v>
@@ -8958,7 +8820,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>40276</v>
+        <v>43271</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>7.97</v>
@@ -8998,7 +8860,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>10954</v>
+        <v>11656</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>9.449999999999999</v>
@@ -9038,7 +8900,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9485</v>
+        <v>10303</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>13.88</v>
@@ -9078,7 +8940,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10245</v>
+        <v>11036</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>20.45</v>
@@ -9118,7 +8980,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>129058</v>
+        <v>129122</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>15.68</v>
@@ -9158,7 +9020,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>78245</v>
+        <v>77469</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>12.31</v>
@@ -9198,7 +9060,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>103908</v>
+        <v>102564</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>14.87</v>
@@ -9238,7 +9100,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>281760</v>
+        <v>284176</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>15.21</v>
@@ -9278,7 +9140,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11702</v>
+        <v>11545</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>10.08</v>
@@ -9318,7 +9180,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>62969</v>
+        <v>62437</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>8.5</v>
@@ -9358,7 +9220,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>84937</v>
+        <v>810</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>9.84</v>
@@ -9398,7 +9260,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>37895</v>
+        <v>35342</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>4.69</v>
@@ -9438,7 +9300,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>37248</v>
+        <v>35910</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>11.71</v>
@@ -9478,7 +9340,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3998</v>
+        <v>4738</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>7.18</v>
@@ -9518,19 +9380,19 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>3998</v>
+        <v>4390</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>3.59</v>
+        <v>0.68</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>3.14</v>
+        <v>0.01</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>3.61</v>
+        <v>0.16</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>5.3</v>
+        <v>-0.28</v>
       </c>
       <c r="J29" s="9" t="n"/>
       <c r="K29" s="9" t="n"/>
@@ -9558,7 +9420,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>6.74</v>
@@ -9598,7 +9460,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>385211</v>
+        <v>372346</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>13.46</v>
@@ -9638,7 +9500,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>175045</v>
+        <v>170411</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>13.71</v>
@@ -9678,7 +9540,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>14743</v>
+        <v>14507</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>10.23</v>
@@ -9718,7 +9580,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>40074</v>
+        <v>41853</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -9758,7 +9620,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7558</v>
+        <v>7736</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -9798,7 +9660,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>73570</v>
+        <v>73844</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>7.78</v>
@@ -9838,7 +9700,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>25756</v>
+        <v>26125</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>18.39</v>
@@ -9878,7 +9740,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14026</v>
+        <v>13850</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>7.78</v>
@@ -9918,7 +9780,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>3.96</v>
@@ -9958,7 +9820,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>2.92</v>
@@ -9998,7 +9860,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>3</v>
@@ -10038,7 +9900,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>69312</v>
+        <v>65005</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>6.73</v>
@@ -10168,7 +10030,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34297</v>
+        <v>34859</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>1.95</v>
@@ -10183,10 +10045,10 @@
         <v>5.72</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -10212,7 +10074,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>18614</v>
+        <v>19709</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>2.73</v>
@@ -10230,7 +10092,7 @@
         <v>3.29</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -10256,7 +10118,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>12449</v>
+        <v>13163</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>1.21</v>
@@ -10271,10 +10133,10 @@
         <v>4.96</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>3.47</v>
+        <v>3.54</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -10300,7 +10162,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>17781</v>
+        <v>18223</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.51</v>
@@ -10315,10 +10177,10 @@
         <v>2.17</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -10344,7 +10206,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -10353,10 +10215,10 @@
         <v>2.35</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -10382,7 +10244,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1104</v>
+        <v>1126</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.85</v>
@@ -10397,7 +10259,7 @@
         <v>2.84</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -10424,7 +10286,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5241</v>
+        <v>5211</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>1.54</v>
@@ -10439,7 +10301,7 @@
         <v>5.43</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>3.12</v>
@@ -10468,7 +10330,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6395</v>
+        <v>7202</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -10479,10 +10341,10 @@
         <v>10.52</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>9.06</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>7.12</v>
+        <v>7.99</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -10508,7 +10370,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1216</v>
+        <v>1309</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1.05</v>
@@ -10523,10 +10385,10 @@
         <v>6.21</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -10552,7 +10414,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2654</v>
+        <v>2926</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>2.39</v>
@@ -10567,10 +10429,10 @@
         <v>6.44</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>5.1</v>
+        <v>5.32</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>3.53</v>
+        <v>3.85</v>
       </c>
       <c r="L11" s="9" t="n"/>
     </row>
@@ -10596,7 +10458,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>819</v>
+        <v>914</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>1.18</v>
@@ -10611,10 +10473,10 @@
         <v>2.59</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="L12" s="9" t="n"/>
     </row>
@@ -10640,7 +10502,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>2.1</v>
@@ -10655,10 +10517,10 @@
         <v>2.93</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="L13" s="9" t="n"/>
     </row>
@@ -10684,7 +10546,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9143</v>
+        <v>9431</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>3.47</v>
@@ -10699,10 +10561,10 @@
         <v>6.09</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>6.44</v>
+        <v>6.36</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>5.47</v>
+        <v>5.6</v>
       </c>
       <c r="L14" s="9" t="n"/>
     </row>
@@ -10728,7 +10590,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>40276</v>
+        <v>43271</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>1.32</v>
@@ -10743,10 +10605,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>3.94</v>
+        <v>4.19</v>
       </c>
       <c r="L15" s="9" t="n"/>
     </row>
@@ -10772,7 +10634,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>10954</v>
+        <v>11656</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>2.15</v>
@@ -10787,10 +10649,10 @@
         <v>6.43</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>10.03</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>7.15</v>
+        <v>7.56</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -10816,7 +10678,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9485</v>
+        <v>10303</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.99</v>
@@ -10834,7 +10696,7 @@
         <v>2.59</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -10860,7 +10722,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10245</v>
+        <v>11036</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>2.04</v>
@@ -10875,10 +10737,10 @@
         <v>6.66</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="L18" s="9" t="n"/>
     </row>
@@ -10904,7 +10766,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>129058</v>
+        <v>129122</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>13.34</v>
@@ -10919,7 +10781,7 @@
         <v>16.48</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>12.67</v>
+        <v>12.68</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>9.279999999999999</v>
@@ -10948,7 +10810,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>78245</v>
+        <v>77469</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>5.46</v>
@@ -10963,10 +10825,10 @@
         <v>4.86</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -10992,7 +10854,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>103908</v>
+        <v>102564</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>3.67</v>
@@ -11007,10 +10869,10 @@
         <v>3.55</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -11036,7 +10898,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>281760</v>
+        <v>284176</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>2.04</v>
@@ -11051,10 +10913,10 @@
         <v>3.77</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -11080,7 +10942,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11702</v>
+        <v>11545</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>2.64</v>
@@ -11095,10 +10957,10 @@
         <v>2.63</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -11124,7 +10986,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>62969</v>
+        <v>62437</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>2.86</v>
@@ -11168,7 +11030,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>84937</v>
+        <v>810</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>2.35</v>
@@ -11183,10 +11045,10 @@
         <v>4.26</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>4.8</v>
+        <v>0.05</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>4.35</v>
+        <v>0.04</v>
       </c>
       <c r="L25" s="9" t="n"/>
     </row>
@@ -11212,7 +11074,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>37895</v>
+        <v>35342</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.65</v>
@@ -11227,10 +11089,10 @@
         <v>2.97</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>3.09</v>
+        <v>2.91</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -11256,7 +11118,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>37248</v>
+        <v>35910</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1.85</v>
@@ -11271,10 +11133,10 @@
         <v>6.69</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>7.05</v>
+        <v>6.89</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>6.04</v>
+        <v>5.89</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -11300,7 +11162,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3998</v>
+        <v>4738</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -11315,10 +11177,10 @@
         <v>2.61</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -11344,25 +11206,25 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>3998</v>
+        <v>4390</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -11388,7 +11250,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -11428,7 +11290,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>385211</v>
+        <v>372346</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>7.79</v>
@@ -11443,10 +11305,10 @@
         <v>12.5</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>12.54</v>
+        <v>12.12</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>9.210000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -11472,7 +11334,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>175045</v>
+        <v>170411</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>5.84</v>
@@ -11487,10 +11349,10 @@
         <v>4.81</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>6.03</v>
+        <v>5.86</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>5.33</v>
+        <v>5.17</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -11516,7 +11378,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>14743</v>
+        <v>14507</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>3.12</v>
@@ -11531,10 +11393,10 @@
         <v>1.48</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -11560,7 +11422,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>40074</v>
+        <v>41853</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -11576,10 +11438,10 @@
         <v>1.54</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="35">
@@ -11604,7 +11466,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7558</v>
+        <v>7736</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -11620,10 +11482,10 @@
         <v>1.25</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="36">
@@ -11648,7 +11510,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>73570</v>
+        <v>73844</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>2.36</v>
@@ -11663,10 +11525,10 @@
         <v>3.37</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>3.47</v>
+        <v>3.52</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="L36" s="9" t="n"/>
     </row>
@@ -11692,7 +11554,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>25756</v>
+        <v>26125</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>2.06</v>
@@ -11707,10 +11569,10 @@
         <v>2.2</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -11736,7 +11598,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14026</v>
+        <v>13850</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>1.12</v>
@@ -11751,10 +11613,10 @@
         <v>2.25</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -11780,7 +11642,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>1.25</v>
@@ -11795,10 +11657,10 @@
         <v>0.92</v>
       </c>
       <c r="J39" s="9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K39" s="9" t="n">
         <v>0.73</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <v>0.66</v>
       </c>
       <c r="L39" s="9" t="n"/>
     </row>
@@ -11824,7 +11686,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.5600000000000001</v>
@@ -11864,7 +11726,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.88</v>
@@ -11904,7 +11766,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>69312</v>
+        <v>65005</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>3.49</v>
@@ -11919,10 +11781,10 @@
         <v>5.69</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>6.02</v>
+        <v>5.65</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>4.79</v>
+        <v>4.49</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -12038,7 +11900,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34297</v>
+        <v>34859</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>-6.66</v>
@@ -12053,7 +11915,7 @@
         <v>18.82</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>31.14</v>
+        <v>30.98</v>
       </c>
       <c r="K2" s="11" t="n">
         <v>27.39</v>
@@ -12082,7 +11944,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>18614</v>
+        <v>19709</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>-234.21</v>
@@ -12126,7 +11988,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>12449</v>
+        <v>13163</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>-17.23</v>
@@ -12141,10 +12003,10 @@
         <v>13.74</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>20.28</v>
+        <v>20.18</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>24.6</v>
+        <v>24.78</v>
       </c>
       <c r="L4" s="11" t="n"/>
     </row>
@@ -12170,7 +12032,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>17781</v>
+        <v>18223</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>-2.23</v>
@@ -12185,10 +12047,10 @@
         <v>17.78</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>26.62</v>
+        <v>27.18</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>23.41</v>
+        <v>23.63</v>
       </c>
       <c r="L5" s="11" t="n"/>
     </row>
@@ -12214,7 +12076,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>-7.73</v>
@@ -12258,7 +12120,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1104</v>
+        <v>1126</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>-13.03</v>
@@ -12300,7 +12162,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5241</v>
+        <v>5211</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>-52.75</v>
@@ -12344,7 +12206,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6395</v>
+        <v>7202</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>57.58</v>
@@ -12359,10 +12221,10 @@
         <v>33.73</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>38.43</v>
+        <v>38.53</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>37.49</v>
+        <v>37.64</v>
       </c>
       <c r="L9" s="11" t="n"/>
     </row>
@@ -12388,7 +12250,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1216</v>
+        <v>1309</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>7.36</v>
@@ -12432,7 +12294,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2654</v>
+        <v>2926</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>-18.17</v>
@@ -12447,10 +12309,10 @@
         <v>36.6</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>30.6</v>
+        <v>30.33</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>31.24</v>
+        <v>32.03</v>
       </c>
       <c r="L11" s="11" t="n"/>
     </row>
@@ -12476,7 +12338,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>819</v>
+        <v>914</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>5.01</v>
@@ -12520,7 +12382,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>5.67</v>
@@ -12564,7 +12426,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9143</v>
+        <v>9431</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>8.300000000000001</v>
@@ -12579,7 +12441,7 @@
         <v>10.51</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>13</v>
+        <v>12.47</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>20.59</v>
@@ -12608,7 +12470,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>40276</v>
+        <v>43271</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>6.84</v>
@@ -12623,10 +12485,10 @@
         <v>19.14</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>21.47</v>
+        <v>21.39</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>23.14</v>
+        <v>23.29</v>
       </c>
       <c r="L15" s="11" t="n"/>
     </row>
@@ -12652,7 +12514,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>10954</v>
+        <v>11656</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>13.15</v>
@@ -12696,7 +12558,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9485</v>
+        <v>10303</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>-3.83</v>
@@ -12711,7 +12573,7 @@
         <v>6.6</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="K17" s="11" t="n">
         <v>8.65</v>
@@ -12740,7 +12602,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10245</v>
+        <v>11036</v>
       </c>
       <c r="F18" s="11" t="n">
         <v>13.01</v>
@@ -12784,7 +12646,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>129058</v>
+        <v>129122</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>61.86</v>
@@ -12802,7 +12664,7 @@
         <v>82.53</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>62.15</v>
+        <v>62.2</v>
       </c>
       <c r="L19" s="11" t="n"/>
     </row>
@@ -12828,7 +12690,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>78245</v>
+        <v>77469</v>
       </c>
       <c r="F20" s="11" t="n">
         <v>31.97</v>
@@ -12872,7 +12734,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>103908</v>
+        <v>102564</v>
       </c>
       <c r="F21" s="11" t="n">
         <v>18.26</v>
@@ -12916,7 +12778,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>281760</v>
+        <v>284176</v>
       </c>
       <c r="F22" s="11" t="n">
         <v>7.16</v>
@@ -12960,7 +12822,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11702</v>
+        <v>11545</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>16.6</v>
@@ -12975,7 +12837,7 @@
         <v>12.42</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>13.68</v>
+        <v>13.66</v>
       </c>
       <c r="K23" s="11" t="n">
         <v>14.01</v>
@@ -13004,7 +12866,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>62969</v>
+        <v>62437</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>16.81</v>
@@ -13048,7 +12910,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>84937</v>
+        <v>810</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>14.19</v>
@@ -13092,7 +12954,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>37895</v>
+        <v>35342</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>12.91</v>
@@ -13107,10 +12969,10 @@
         <v>13.2</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>13.64</v>
+        <v>13.7</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>14.87</v>
+        <v>14.91</v>
       </c>
       <c r="L26" s="11" t="n"/>
     </row>
@@ -13136,7 +12998,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>37248</v>
+        <v>35910</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>7.44</v>
@@ -13180,7 +13042,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3998</v>
+        <v>4738</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>7.62</v>
@@ -13224,7 +13086,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>3998</v>
+        <v>4390</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>12.82</v>
@@ -13268,7 +13130,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="F30" s="11" t="n">
         <v>11.21</v>
@@ -13308,7 +13170,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>385211</v>
+        <v>372346</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>42.25</v>
@@ -13352,7 +13214,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>175045</v>
+        <v>170411</v>
       </c>
       <c r="F32" s="11" t="n">
         <v>35.19</v>
@@ -13367,10 +13229,10 @@
         <v>20.61</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>17.65</v>
+        <v>17.81</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>19.61</v>
+        <v>19.57</v>
       </c>
       <c r="L32" s="11" t="n"/>
     </row>
@@ -13396,7 +13258,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>14743</v>
+        <v>14507</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>29.29</v>
@@ -13440,7 +13302,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>40074</v>
+        <v>41853</v>
       </c>
       <c r="F34" s="11" t="n"/>
       <c r="G34" s="11" t="n">
@@ -13484,7 +13346,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7558</v>
+        <v>7736</v>
       </c>
       <c r="F35" s="11" t="n"/>
       <c r="G35" s="11" t="n">
@@ -13500,10 +13362,10 @@
         <v>8.56</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>9.699999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="L35" s="11" t="n">
-        <v>10.68</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="36">
@@ -13528,7 +13390,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>73570</v>
+        <v>73844</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>20.11</v>
@@ -13572,7 +13434,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>25756</v>
+        <v>26125</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>6.6</v>
@@ -13616,7 +13478,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14026</v>
+        <v>13850</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>8.1</v>
@@ -13631,10 +13493,10 @@
         <v>10.96</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>13.77</v>
+        <v>13.38</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>15.67</v>
+        <v>15.49</v>
       </c>
       <c r="L38" s="11" t="n"/>
     </row>
@@ -13660,7 +13522,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="F39" s="11" t="n">
         <v>21.69</v>
@@ -13704,7 +13566,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>7.43</v>
@@ -13744,7 +13606,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>15.47</v>
@@ -13784,7 +13646,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>69312</v>
+        <v>65005</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>29.81</v>
@@ -13918,7 +13780,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34297</v>
+        <v>34859</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>1.14</v>
@@ -13933,10 +13795,10 @@
         <v>3.04</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -13962,7 +13824,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>18614</v>
+        <v>19709</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>0.42</v>
@@ -13977,10 +13839,10 @@
         <v>2.72</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -14006,7 +13868,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>12449</v>
+        <v>13163</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>0.73</v>
@@ -14021,10 +13883,10 @@
         <v>1.93</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -14050,7 +13912,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>17781</v>
+        <v>18223</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.29</v>
@@ -14065,10 +13927,10 @@
         <v>0.96</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -14094,7 +13956,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -14103,10 +13965,10 @@
         <v>2.09</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -14132,7 +13994,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1104</v>
+        <v>1126</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.18</v>
@@ -14172,7 +14034,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5241</v>
+        <v>5211</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.12</v>
@@ -14216,7 +14078,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6395</v>
+        <v>7202</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -14227,10 +14089,10 @@
         <v>4.38</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>3.73</v>
+        <v>4.26</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>3.31</v>
+        <v>3.7</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -14256,7 +14118,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1216</v>
+        <v>1309</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1.13</v>
@@ -14271,10 +14133,10 @@
         <v>7.54</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -14300,7 +14162,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2654</v>
+        <v>2926</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -14315,10 +14177,10 @@
         <v>2.61</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="L11" s="9" t="n"/>
     </row>
@@ -14344,7 +14206,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>819</v>
+        <v>914</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>1.29</v>
@@ -14359,10 +14221,10 @@
         <v>1.65</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="L12" s="9" t="n"/>
     </row>
@@ -14388,7 +14250,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.72</v>
@@ -14403,10 +14265,10 @@
         <v>1.02</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="L13" s="9" t="n"/>
     </row>
@@ -14432,7 +14294,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9143</v>
+        <v>9431</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>1.78</v>
@@ -14447,10 +14309,10 @@
         <v>3.02</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="L14" s="9" t="n"/>
     </row>
@@ -14476,7 +14338,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>40276</v>
+        <v>43271</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.53</v>
@@ -14491,10 +14353,10 @@
         <v>1.81</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="L15" s="9" t="n"/>
     </row>
@@ -14520,7 +14382,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>10954</v>
+        <v>11656</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.9</v>
@@ -14535,10 +14397,10 @@
         <v>2.14</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -14564,7 +14426,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9485</v>
+        <v>10303</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.9</v>
@@ -14579,10 +14441,10 @@
         <v>2.78</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>2.94</v>
+        <v>3.17</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -14608,7 +14470,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10245</v>
+        <v>11036</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.98</v>
@@ -14623,10 +14485,10 @@
         <v>3.51</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="L18" s="9" t="n"/>
     </row>
@@ -14652,7 +14514,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>129058</v>
+        <v>129122</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>1.87</v>
@@ -14696,7 +14558,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>78245</v>
+        <v>77469</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>2.28</v>
@@ -14711,10 +14573,10 @@
         <v>1.93</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -14740,7 +14602,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>103908</v>
+        <v>102564</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>1.73</v>
@@ -14755,10 +14617,10 @@
         <v>1.73</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -14784,7 +14646,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>281760</v>
+        <v>284176</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>2.21</v>
@@ -14799,10 +14661,10 @@
         <v>2.78</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -14828,7 +14690,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11702</v>
+        <v>11545</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.86</v>
@@ -14843,10 +14705,10 @@
         <v>1.07</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -14872,7 +14734,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>62969</v>
+        <v>62437</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>1.26</v>
@@ -14916,7 +14778,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>84937</v>
+        <v>810</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>1.24</v>
@@ -14931,10 +14793,10 @@
         <v>1.77</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1.87</v>
+        <v>0.02</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1.71</v>
+        <v>0.02</v>
       </c>
       <c r="L25" s="9" t="n"/>
     </row>
@@ -14960,7 +14822,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>37895</v>
+        <v>35342</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.32</v>
@@ -14975,10 +14837,10 @@
         <v>1.45</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -15004,7 +14866,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>37248</v>
+        <v>35910</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1.3</v>
@@ -15019,10 +14881,10 @@
         <v>3.66</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -15048,7 +14910,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3998</v>
+        <v>4738</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.34</v>
@@ -15063,10 +14925,10 @@
         <v>1.25</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.59</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -15092,25 +14954,25 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>3998</v>
+        <v>4390</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -15136,7 +14998,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.19</v>
@@ -15176,7 +15038,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>385211</v>
+        <v>372346</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>2.08</v>
@@ -15191,10 +15053,10 @@
         <v>3.94</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>4.87</v>
+        <v>4.7</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>4.38</v>
+        <v>4.24</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -15220,7 +15082,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>175045</v>
+        <v>170411</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>2.31</v>
@@ -15235,10 +15097,10 @@
         <v>2.79</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>4.02</v>
+        <v>4.14</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>3.89</v>
+        <v>3.83</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -15264,7 +15126,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>14743</v>
+        <v>14507</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.92</v>
@@ -15279,10 +15141,10 @@
         <v>0.63</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -15308,7 +15170,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>40074</v>
+        <v>41853</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -15324,10 +15186,10 @@
         <v>1.31</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="35">
@@ -15352,7 +15214,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7558</v>
+        <v>7736</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -15368,10 +15230,10 @@
         <v>0.8</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="36">
@@ -15396,7 +15258,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>73570</v>
+        <v>73844</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -15411,10 +15273,10 @@
         <v>1.26</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="L36" s="9" t="n"/>
     </row>
@@ -15440,7 +15302,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>25756</v>
+        <v>26125</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1.66</v>
@@ -15455,10 +15317,10 @@
         <v>2.17</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -15484,7 +15346,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14026</v>
+        <v>13850</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.64</v>
@@ -15499,10 +15361,10 @@
         <v>1.35</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -15528,7 +15390,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.49</v>
@@ -15543,10 +15405,10 @@
         <v>0.59</v>
       </c>
       <c r="J39" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K39" s="9" t="n">
         <v>0.46</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <v>0.42</v>
       </c>
       <c r="L39" s="9" t="n"/>
     </row>
@@ -15572,7 +15434,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.32</v>
@@ -15612,7 +15474,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.5</v>
@@ -15652,7 +15514,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>69312</v>
+        <v>65005</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>2.12</v>
@@ -15667,10 +15529,10 @@
         <v>3.17</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>3.91</v>
+        <v>3.66</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>3.59</v>
+        <v>3.37</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -16133,9 +15995,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G6" s="17" t="n">
-        <v>453000</v>
-      </c>
+      <c r="G6" s="17" t="n"/>
       <c r="H6" s="17" t="n">
         <v>31175.2</v>
       </c>
@@ -16152,17 +16012,17 @@
         <v>12097690124766.46</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>15.31</v>
+        <v>14.82</v>
       </c>
       <c r="N6" s="17" t="n"/>
       <c r="O6" s="17" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="P6" s="17" t="n">
-        <v>31.14</v>
+        <v>30.98</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R6" s="17" t="inlineStr">
         <is>
@@ -16206,9 +16066,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G7" s="17" t="n">
-        <v>453000</v>
-      </c>
+      <c r="G7" s="17" t="n"/>
       <c r="H7" s="17" t="n">
         <v>35696.77</v>
       </c>
@@ -16224,18 +16082,16 @@
       <c r="L7" s="18" t="n">
         <v>15253493850623.39</v>
       </c>
-      <c r="M7" s="17" t="n">
-        <v>12.69</v>
-      </c>
+      <c r="M7" s="17" t="n"/>
       <c r="N7" s="17" t="n"/>
       <c r="O7" s="17" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="P7" s="17" t="n">
         <v>27.39</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R7" s="17" t="inlineStr">
         <is>
@@ -16628,9 +16484,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G13" s="17" t="n">
-        <v>84200</v>
-      </c>
+      <c r="G13" s="17" t="n"/>
       <c r="H13" s="17" t="n">
         <v>6366.76</v>
       </c>
@@ -16657,7 +16511,7 @@
         <v>27.32</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="R13" s="17" t="inlineStr">
         <is>
@@ -16701,9 +16555,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G14" s="17" t="n">
-        <v>84200</v>
-      </c>
+      <c r="G14" s="17" t="n"/>
       <c r="H14" s="17" t="n">
         <v>6407.04</v>
       </c>
@@ -16719,18 +16571,16 @@
       <c r="L14" s="18" t="n">
         <v>10084109156939.35</v>
       </c>
-      <c r="M14" s="17" t="n">
-        <v>13.14</v>
-      </c>
+      <c r="M14" s="17" t="n"/>
       <c r="N14" s="17" t="n"/>
       <c r="O14" s="17" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="P14" s="17" t="n">
         <v>21.57</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="R14" s="17" t="inlineStr">
         <is>
@@ -17121,36 +16971,34 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G20" s="17" t="n">
-        <v>20200</v>
-      </c>
+      <c r="G20" s="17" t="n"/>
       <c r="H20" s="17" t="n">
-        <v>1190.4</v>
+        <v>1187.67</v>
       </c>
       <c r="I20" s="17" t="n">
-        <v>6047.79</v>
+        <v>6045.06</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>12883875960000</v>
+        <v>12893142220000</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>1016780057301.109</v>
+        <v>1014448739155.678</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>5165719366941.109</v>
+        <v>5163388048795.679</v>
       </c>
       <c r="M20" s="17" t="n">
-        <v>19.47</v>
+        <v>19.95</v>
       </c>
       <c r="N20" s="17" t="n"/>
       <c r="O20" s="17" t="n">
-        <v>3.47</v>
+        <v>3.54</v>
       </c>
       <c r="P20" s="17" t="n">
-        <v>20.28</v>
+        <v>20.18</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="R20" s="17" t="inlineStr">
         <is>
@@ -17194,36 +17042,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G21" s="17" t="n">
-        <v>20200</v>
-      </c>
+      <c r="G21" s="17" t="n"/>
       <c r="H21" s="17" t="n">
-        <v>1696.49</v>
+        <v>1710.15</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>7744.28</v>
+        <v>7755.21</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>14766844080000</v>
+        <v>14782416070000</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>1449061141256.545</v>
+        <v>1460728238033.814</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>6614780508197.654</v>
-      </c>
-      <c r="M21" s="17" t="n">
-        <v>11.91</v>
-      </c>
+        <v>6624116286829.493</v>
+      </c>
+      <c r="M21" s="17" t="n"/>
       <c r="N21" s="17" t="n"/>
       <c r="O21" s="17" t="n">
-        <v>2.61</v>
+        <v>2.73</v>
       </c>
       <c r="P21" s="17" t="n">
-        <v>24.6</v>
+        <v>24.78</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="R21" s="17" t="inlineStr">
         <is>
@@ -17618,36 +17462,34 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G27" s="17" t="n">
-        <v>348500</v>
-      </c>
+      <c r="G27" s="17" t="n"/>
       <c r="H27" s="17" t="n">
-        <v>50792.88</v>
+        <v>51760.25</v>
       </c>
       <c r="I27" s="17" t="n">
-        <v>229197.94</v>
+        <v>229984.8</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>34862870089999</v>
+        <v>34925797590000</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>3591799715834.4</v>
+        <v>3660207210316.02</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>16207647634859.7</v>
+        <v>16263290290871.05</v>
       </c>
       <c r="M27" s="17" t="n">
-        <v>6.67</v>
+        <v>6.4</v>
       </c>
       <c r="N27" s="17" t="n"/>
       <c r="O27" s="17" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="P27" s="17" t="n">
-        <v>26.62</v>
+        <v>27.18</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="R27" s="17" t="inlineStr">
         <is>
@@ -17691,36 +17533,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G28" s="17" t="n">
-        <v>348500</v>
-      </c>
+      <c r="G28" s="17" t="n"/>
       <c r="H28" s="17" t="n">
-        <v>59289.32</v>
+        <v>60133.68</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>277423.87</v>
+        <v>278897.54</v>
       </c>
       <c r="J28" s="18" t="n">
-        <v>37449280420000</v>
+        <v>37512995060000</v>
       </c>
       <c r="K28" s="18" t="n">
-        <v>4192622326751.6</v>
+        <v>4252331214596.92</v>
       </c>
       <c r="L28" s="18" t="n">
-        <v>19617926635439.45</v>
-      </c>
-      <c r="M28" s="17" t="n">
-        <v>5.88</v>
-      </c>
+        <v>19722136500824.19</v>
+      </c>
+      <c r="M28" s="17" t="n"/>
       <c r="N28" s="17" t="n"/>
       <c r="O28" s="17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P28" s="17" t="n">
-        <v>23.41</v>
+        <v>23.63</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="R28" s="17" t="inlineStr">
         <is>
@@ -18087,9 +17925,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G34" s="17" t="n">
-        <v>49050</v>
-      </c>
+      <c r="G34" s="17" t="n"/>
       <c r="H34" s="17" t="n">
         <v>7317.5</v>
       </c>
@@ -18106,17 +17942,17 @@
         <v>1363491609003.722</v>
       </c>
       <c r="M34" s="17" t="n">
-        <v>6.35</v>
+        <v>6.17</v>
       </c>
       <c r="N34" s="17" t="n"/>
       <c r="O34" s="17" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="P34" s="17" t="n">
         <v>24.95</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
@@ -18160,9 +17996,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G35" s="17" t="n">
-        <v>49050</v>
-      </c>
+      <c r="G35" s="17" t="n"/>
       <c r="H35" s="17" t="n">
         <v>7666.2</v>
       </c>
@@ -18178,18 +18012,16 @@
       <c r="L35" s="18" t="n">
         <v>1647518204706.319</v>
       </c>
-      <c r="M35" s="17" t="n">
-        <v>6.4</v>
-      </c>
+      <c r="M35" s="17" t="n"/>
       <c r="N35" s="17" t="n"/>
       <c r="O35" s="17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P35" s="17" t="n">
         <v>19.48</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
@@ -18580,9 +18412,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G41" s="17" t="n">
-        <v>16940</v>
-      </c>
+      <c r="G41" s="17" t="n"/>
       <c r="H41" s="17" t="n"/>
       <c r="I41" s="17" t="n"/>
       <c r="J41" s="18" t="n">
@@ -18591,11 +18421,11 @@
       <c r="K41" s="18" t="n"/>
       <c r="L41" s="18" t="n"/>
       <c r="M41" s="17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="N41" s="17" t="n"/>
       <c r="O41" s="17" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="P41" s="17" t="n">
         <v>24.85</v>
@@ -18643,9 +18473,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G42" s="17" t="n">
-        <v>16940</v>
-      </c>
+      <c r="G42" s="17" t="n"/>
       <c r="H42" s="17" t="n"/>
       <c r="I42" s="17" t="n"/>
       <c r="J42" s="18" t="n">
@@ -19068,7 +18896,7 @@
       <c r="M48" s="17" t="n"/>
       <c r="N48" s="17" t="n"/>
       <c r="O48" s="17" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="P48" s="17" t="n">
         <v>16.62</v>
@@ -19520,36 +19348,34 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G55" s="17" t="n">
-        <v>197700</v>
-      </c>
+      <c r="G55" s="17" t="n"/>
       <c r="H55" s="17" t="n">
-        <v>7956.2</v>
+        <v>7767.72</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>22672.63</v>
+        <v>22571.32</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>2373493190000</v>
+        <v>2323641630000</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>356687067527</v>
+        <v>348237212674.865</v>
       </c>
       <c r="L55" s="18" t="n">
-        <v>1016444154255.762</v>
+        <v>1011902357272.74</v>
       </c>
       <c r="M55" s="17" t="n">
-        <v>25.9</v>
+        <v>28.12</v>
       </c>
       <c r="N55" s="17" t="n"/>
       <c r="O55" s="17" t="n">
-        <v>9.06</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="P55" s="17" t="n">
-        <v>38.43</v>
+        <v>38.53</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>3.73</v>
+        <v>4.26</v>
       </c>
       <c r="R55" s="17" t="inlineStr">
         <is>
@@ -19593,14 +19419,12 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G56" s="17" t="n">
-        <v>197700</v>
-      </c>
+      <c r="G56" s="17" t="n"/>
       <c r="H56" s="17" t="n">
         <v>9452.709999999999</v>
       </c>
       <c r="I56" s="17" t="n">
-        <v>27753.46</v>
+        <v>27652.15</v>
       </c>
       <c r="J56" s="18" t="n">
         <v>2676693990000</v>
@@ -19609,20 +19433,18 @@
         <v>423777698330.52</v>
       </c>
       <c r="L56" s="18" t="n">
-        <v>1244224667108.417</v>
-      </c>
-      <c r="M56" s="17" t="n">
-        <v>20.91</v>
-      </c>
+        <v>1239682870125.395</v>
+      </c>
+      <c r="M56" s="17" t="n"/>
       <c r="N56" s="17" t="n"/>
       <c r="O56" s="17" t="n">
-        <v>7.12</v>
+        <v>7.99</v>
       </c>
       <c r="P56" s="17" t="n">
-        <v>37.49</v>
+        <v>37.64</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>3.31</v>
+        <v>3.7</v>
       </c>
       <c r="R56" s="17" t="inlineStr">
         <is>
@@ -20019,9 +19841,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G62" s="17" t="n">
-        <v>49700</v>
-      </c>
+      <c r="G62" s="17" t="n"/>
       <c r="H62" s="17" t="n">
         <v>3930.5</v>
       </c>
@@ -20038,17 +19858,17 @@
         <v>622240560926.5</v>
       </c>
       <c r="M62" s="17" t="n">
-        <v>14.04</v>
+        <v>13.93</v>
       </c>
       <c r="N62" s="17" t="n"/>
       <c r="O62" s="17" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="P62" s="17" t="n">
         <v>26.46</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>2.77</v>
+        <v>2.96</v>
       </c>
       <c r="R62" s="17" t="inlineStr">
         <is>
@@ -20092,9 +19912,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G63" s="17" t="n">
-        <v>49700</v>
-      </c>
+      <c r="G63" s="17" t="n"/>
       <c r="H63" s="17" t="n">
         <v>5446</v>
       </c>
@@ -20110,18 +19928,16 @@
       <c r="L63" s="18" t="n">
         <v>806976902884.5</v>
       </c>
-      <c r="M63" s="17" t="n">
-        <v>9.130000000000001</v>
-      </c>
+      <c r="M63" s="17" t="n"/>
       <c r="N63" s="17" t="n"/>
       <c r="O63" s="17" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="P63" s="17" t="n">
         <v>25.85</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="R63" s="17" t="inlineStr">
         <is>
@@ -20512,36 +20328,34 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G69" s="17" t="n">
-        <v>44100</v>
-      </c>
+      <c r="G69" s="17" t="n"/>
       <c r="H69" s="17" t="n">
-        <v>2444.6</v>
+        <v>2412.78</v>
       </c>
       <c r="I69" s="17" t="n">
-        <v>9110.459999999999</v>
+        <v>9078.639999999999</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>1609432900000</v>
+        <v>1610128790000</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>203942129601.428</v>
+        <v>201287095264.946</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>760045029521.428</v>
+        <v>757389995184.946</v>
       </c>
       <c r="M69" s="17" t="n">
-        <v>19.32</v>
+        <v>20.27</v>
       </c>
       <c r="N69" s="17" t="n"/>
       <c r="O69" s="17" t="n">
-        <v>5.1</v>
+        <v>5.32</v>
       </c>
       <c r="P69" s="17" t="n">
-        <v>30.6</v>
+        <v>30.33</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="R69" s="17" t="inlineStr">
         <is>
@@ -20585,36 +20399,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G70" s="17" t="n">
-        <v>44100</v>
-      </c>
+      <c r="G70" s="17" t="n"/>
       <c r="H70" s="17" t="n">
-        <v>3373.17</v>
+        <v>3462.71</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>12483.63</v>
+        <v>12541.35</v>
       </c>
       <c r="J70" s="18" t="n">
-        <v>2119123930000</v>
+        <v>2147608440000</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>281408236591.6845</v>
+        <v>288878801372.204</v>
       </c>
       <c r="L70" s="18" t="n">
-        <v>1041453266113.113</v>
-      </c>
-      <c r="M70" s="17" t="n">
-        <v>13.07</v>
-      </c>
+        <v>1046268796557.15</v>
+      </c>
+      <c r="M70" s="17" t="n"/>
       <c r="N70" s="17" t="n"/>
       <c r="O70" s="17" t="n">
-        <v>3.53</v>
+        <v>3.85</v>
       </c>
       <c r="P70" s="17" t="n">
-        <v>31.24</v>
+        <v>32.03</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="R70" s="17" t="inlineStr">
         <is>
@@ -21009,9 +20819,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G76" s="17" t="n">
-        <v>22550</v>
-      </c>
+      <c r="G76" s="17" t="n"/>
       <c r="H76" s="17" t="n">
         <v>2393.79</v>
       </c>
@@ -21028,17 +20836,17 @@
         <v>681678021001.8715</v>
       </c>
       <c r="M76" s="17" t="n">
-        <v>10.26</v>
+        <v>10.91</v>
       </c>
       <c r="N76" s="17" t="n"/>
       <c r="O76" s="17" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="P76" s="17" t="n">
         <v>18.75</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="R76" s="17" t="inlineStr">
         <is>
@@ -21082,9 +20890,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G77" s="17" t="n">
-        <v>22550</v>
-      </c>
+      <c r="G77" s="17" t="n"/>
       <c r="H77" s="17" t="n">
         <v>2818.93</v>
       </c>
@@ -21100,18 +20906,16 @@
       <c r="L77" s="18" t="n">
         <v>801213744014.1482</v>
       </c>
-      <c r="M77" s="17" t="n">
-        <v>8</v>
-      </c>
+      <c r="M77" s="17" t="n"/>
       <c r="N77" s="17" t="n"/>
       <c r="O77" s="17" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="P77" s="17" t="n">
         <v>19.15</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="R77" s="17" t="inlineStr">
         <is>
@@ -21508,9 +21312,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G83" s="17" t="n">
-        <v>16700</v>
-      </c>
+      <c r="G83" s="17" t="n"/>
       <c r="H83" s="17" t="n">
         <v>2442</v>
       </c>
@@ -21527,17 +21329,17 @@
         <v>331992443278</v>
       </c>
       <c r="M83" s="17" t="n">
-        <v>6.23</v>
+        <v>6.55</v>
       </c>
       <c r="N83" s="17" t="n"/>
       <c r="O83" s="17" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="P83" s="17" t="n">
         <v>28.53</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="R83" s="17" t="inlineStr">
         <is>
@@ -21581,9 +21383,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G84" s="17" t="n">
-        <v>16700</v>
-      </c>
+      <c r="G84" s="17" t="n"/>
       <c r="H84" s="17" t="n">
         <v>2901</v>
       </c>
@@ -21599,18 +21399,16 @@
       <c r="L84" s="18" t="n">
         <v>418828450507</v>
       </c>
-      <c r="M84" s="17" t="n">
-        <v>5.76</v>
-      </c>
+      <c r="M84" s="17" t="n"/>
       <c r="N84" s="17" t="n"/>
       <c r="O84" s="17" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="P84" s="17" t="n">
         <v>23.13</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="R84" s="17" t="inlineStr">
         <is>
@@ -22007,9 +21805,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G90" s="17" t="n">
-        <v>130000</v>
-      </c>
+      <c r="G90" s="17" t="n"/>
       <c r="H90" s="17" t="n">
         <v>2345.72</v>
       </c>
@@ -22026,17 +21822,17 @@
         <v>1995963043226.628</v>
       </c>
       <c r="M90" s="17" t="n">
-        <v>52.22</v>
+        <v>53.78</v>
       </c>
       <c r="N90" s="17" t="n"/>
       <c r="O90" s="17" t="n">
-        <v>6.44</v>
+        <v>6.36</v>
       </c>
       <c r="P90" s="17" t="n">
-        <v>13</v>
+        <v>12.47</v>
       </c>
       <c r="Q90" s="17" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R90" s="17" t="inlineStr">
         <is>
@@ -22080,9 +21876,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G91" s="17" t="n">
-        <v>130000</v>
-      </c>
+      <c r="G91" s="17" t="n"/>
       <c r="H91" s="17" t="n">
         <v>4555.93</v>
       </c>
@@ -22098,18 +21892,16 @@
       <c r="L91" s="18" t="n">
         <v>2317972672631.471</v>
       </c>
-      <c r="M91" s="17" t="n">
-        <v>28.53</v>
-      </c>
+      <c r="M91" s="17" t="n"/>
       <c r="N91" s="17" t="n"/>
       <c r="O91" s="17" t="n">
-        <v>5.47</v>
+        <v>5.6</v>
       </c>
       <c r="P91" s="17" t="n">
         <v>20.59</v>
       </c>
       <c r="Q91" s="17" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="R91" s="17" t="inlineStr">
         <is>
@@ -22506,36 +22298,34 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G97" s="17" t="n">
-        <v>1085000</v>
-      </c>
+      <c r="G97" s="17" t="n"/>
       <c r="H97" s="17" t="n">
-        <v>47228.97</v>
+        <v>47335.29</v>
       </c>
       <c r="I97" s="17" t="n">
-        <v>227325.61</v>
+        <v>227413.59</v>
       </c>
       <c r="J97" s="18" t="n">
-        <v>32235043260000</v>
+        <v>32193561600000</v>
       </c>
       <c r="K97" s="18" t="n">
-        <v>2429873419334.724</v>
+        <v>2435343300128.52</v>
       </c>
       <c r="L97" s="18" t="n">
-        <v>11695627022499.48</v>
+        <v>11700153348856.35</v>
       </c>
       <c r="M97" s="17" t="n">
-        <v>26.05</v>
+        <v>25.83</v>
       </c>
       <c r="N97" s="17" t="n"/>
       <c r="O97" s="17" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="P97" s="17" t="n">
-        <v>21.47</v>
+        <v>21.39</v>
       </c>
       <c r="Q97" s="17" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="R97" s="17" t="inlineStr">
         <is>
@@ -22579,36 +22369,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G98" s="17" t="n">
-        <v>1085000</v>
-      </c>
+      <c r="G98" s="17" t="n"/>
       <c r="H98" s="17" t="n">
-        <v>58167.58</v>
+        <v>58607.21</v>
       </c>
       <c r="I98" s="17" t="n">
-        <v>275459.28</v>
+        <v>275911.06</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>34513976160000</v>
+        <v>34591903430000</v>
       </c>
       <c r="K98" s="18" t="n">
-        <v>2992651491893.04</v>
+        <v>3015270179805.42</v>
       </c>
       <c r="L98" s="18" t="n">
-        <v>14172046132040.97</v>
-      </c>
-      <c r="M98" s="17" t="n">
-        <v>18.65</v>
-      </c>
+        <v>14195289422645.33</v>
+      </c>
+      <c r="M98" s="17" t="n"/>
       <c r="N98" s="17" t="n"/>
       <c r="O98" s="17" t="n">
-        <v>3.94</v>
+        <v>4.19</v>
       </c>
       <c r="P98" s="17" t="n">
-        <v>23.14</v>
+        <v>23.29</v>
       </c>
       <c r="Q98" s="17" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="R98" s="17" t="inlineStr">
         <is>
@@ -23005,9 +22791,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G104" s="17" t="n">
-        <v>695000</v>
-      </c>
+      <c r="G104" s="17" t="n"/>
       <c r="H104" s="17" t="n">
         <v>16754.84</v>
       </c>
@@ -23024,17 +22808,17 @@
         <v>1713760610815.525</v>
       </c>
       <c r="M104" s="17" t="n">
-        <v>48.09</v>
+        <v>44.85</v>
       </c>
       <c r="N104" s="17" t="n"/>
       <c r="O104" s="17" t="n">
-        <v>10.03</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="P104" s="17" t="n">
         <v>22.68</v>
       </c>
       <c r="Q104" s="17" t="n">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="R104" s="17" t="inlineStr">
         <is>
@@ -23078,9 +22862,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G105" s="17" t="n">
-        <v>695000</v>
-      </c>
+      <c r="G105" s="17" t="n"/>
       <c r="H105" s="17" t="n">
         <v>24122.73</v>
       </c>
@@ -23096,18 +22878,16 @@
       <c r="L105" s="18" t="n">
         <v>2122160071223.144</v>
       </c>
-      <c r="M105" s="17" t="n">
-        <v>28.81</v>
-      </c>
+      <c r="M105" s="17" t="n"/>
       <c r="N105" s="17" t="n"/>
       <c r="O105" s="17" t="n">
-        <v>7.15</v>
+        <v>7.56</v>
       </c>
       <c r="P105" s="17" t="n">
         <v>27.48</v>
       </c>
       <c r="Q105" s="17" t="n">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="R105" s="17" t="inlineStr">
         <is>
@@ -23502,9 +23282,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G111" s="17" t="n">
-        <v>70300</v>
-      </c>
+      <c r="G111" s="17" t="n"/>
       <c r="H111" s="17" t="n">
         <v>790.5</v>
       </c>
@@ -23521,17 +23299,17 @@
         <v>4924009921049.891</v>
       </c>
       <c r="M111" s="17" t="n">
-        <v>97.16</v>
+        <v>102.89</v>
       </c>
       <c r="N111" s="17" t="n"/>
       <c r="O111" s="17" t="n">
         <v>2.59</v>
       </c>
       <c r="P111" s="17" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q111" s="17" t="n">
-        <v>2.94</v>
+        <v>3.17</v>
       </c>
       <c r="R111" s="17" t="inlineStr">
         <is>
@@ -23575,9 +23353,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G112" s="17" t="n">
-        <v>70300</v>
-      </c>
+      <c r="G112" s="17" t="n"/>
       <c r="H112" s="17" t="n">
         <v>2329</v>
       </c>
@@ -23593,18 +23369,16 @@
       <c r="L112" s="18" t="n">
         <v>5144333066583.118</v>
       </c>
-      <c r="M112" s="17" t="n">
-        <v>30.18</v>
-      </c>
+      <c r="M112" s="17" t="n"/>
       <c r="N112" s="17" t="n"/>
       <c r="O112" s="17" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="P112" s="17" t="n">
         <v>8.65</v>
       </c>
       <c r="Q112" s="17" t="n">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="R112" s="17" t="inlineStr">
         <is>
@@ -24001,9 +23775,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G118" s="17" t="n">
-        <v>130100</v>
-      </c>
+      <c r="G118" s="17" t="n"/>
       <c r="H118" s="17" t="n">
         <v>8113.99</v>
       </c>
@@ -24020,17 +23792,17 @@
         <v>3892781692167.539</v>
       </c>
       <c r="M118" s="17" t="n">
-        <v>16.73</v>
+        <v>16.96</v>
       </c>
       <c r="N118" s="17" t="n"/>
       <c r="O118" s="17" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P118" s="17" t="n">
         <v>25.69</v>
       </c>
       <c r="Q118" s="17" t="n">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="R118" s="17" t="inlineStr">
         <is>
@@ -24074,9 +23846,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G119" s="17" t="n">
-        <v>130100</v>
-      </c>
+      <c r="G119" s="17" t="n"/>
       <c r="H119" s="17" t="n">
         <v>11630.63</v>
       </c>
@@ -24092,18 +23862,16 @@
       <c r="L119" s="18" t="n">
         <v>5059227604140.619</v>
       </c>
-      <c r="M119" s="17" t="n">
-        <v>11.19</v>
-      </c>
+      <c r="M119" s="17" t="n"/>
       <c r="N119" s="17" t="n"/>
       <c r="O119" s="17" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="P119" s="17" t="n">
         <v>28.36</v>
       </c>
       <c r="Q119" s="17" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="R119" s="17" t="inlineStr">
         <is>
@@ -24501,7 +24269,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>563.5700000000001</v>
+        <v>563.85</v>
       </c>
       <c r="H125" s="17" t="n">
         <v>30.46</v>
@@ -24519,11 +24287,11 @@
         <v>10186173464.337</v>
       </c>
       <c r="M125" s="17" t="n">
-        <v>18.5</v>
+        <v>18.51</v>
       </c>
       <c r="N125" s="17" t="n"/>
       <c r="O125" s="17" t="n">
-        <v>12.67</v>
+        <v>12.68</v>
       </c>
       <c r="P125" s="17" t="n">
         <v>82.53</v>
@@ -24574,32 +24342,32 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>563.5700000000001</v>
+        <v>563.85</v>
       </c>
       <c r="H126" s="17" t="n">
-        <v>32.69</v>
+        <v>32.72</v>
       </c>
       <c r="I126" s="17" t="n">
-        <v>60.72</v>
+        <v>60.73</v>
       </c>
       <c r="J126" s="18" t="n">
-        <v>85308175580</v>
+        <v>85415234360</v>
       </c>
       <c r="K126" s="18" t="n">
-        <v>7485538259.999999</v>
+        <v>7493415860.000001</v>
       </c>
       <c r="L126" s="18" t="n">
-        <v>13904240318.079</v>
+        <v>13908153121.999</v>
       </c>
       <c r="M126" s="17" t="n">
-        <v>17.24</v>
+        <v>17.23</v>
       </c>
       <c r="N126" s="17" t="n"/>
       <c r="O126" s="17" t="n">
         <v>9.279999999999999</v>
       </c>
       <c r="P126" s="17" t="n">
-        <v>62.15</v>
+        <v>62.2</v>
       </c>
       <c r="Q126" s="17" t="n">
         <v>1.51</v>
@@ -25000,7 +24768,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>551.03</v>
+        <v>545.5700000000001</v>
       </c>
       <c r="H132" s="17" t="n">
         <v>28.99</v>
@@ -25018,17 +24786,17 @@
         <v>19560796522.68309</v>
       </c>
       <c r="M132" s="17" t="n">
-        <v>19.01</v>
+        <v>18.82</v>
       </c>
       <c r="N132" s="17" t="n"/>
       <c r="O132" s="17" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="P132" s="17" t="n">
         <v>22.72</v>
       </c>
       <c r="Q132" s="17" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R132" s="17" t="inlineStr">
         <is>
@@ -25073,7 +24841,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>551.03</v>
+        <v>545.5700000000001</v>
       </c>
       <c r="H133" s="17" t="n">
         <v>30.44</v>
@@ -25091,17 +24859,17 @@
         <v>22591656618.88455</v>
       </c>
       <c r="M133" s="17" t="n">
-        <v>18.1</v>
+        <v>17.92</v>
       </c>
       <c r="N133" s="17" t="n"/>
       <c r="O133" s="17" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="P133" s="17" t="n">
         <v>20.51</v>
       </c>
       <c r="Q133" s="17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R133" s="17" t="inlineStr">
         <is>
@@ -25499,7 +25267,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>384.29</v>
+        <v>379.32</v>
       </c>
       <c r="H139" s="17" t="n">
         <v>17</v>
@@ -25517,17 +25285,17 @@
         <v>28486442015.57588</v>
       </c>
       <c r="M139" s="17" t="n">
-        <v>22.61</v>
+        <v>22.31</v>
       </c>
       <c r="N139" s="17" t="n"/>
       <c r="O139" s="17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P139" s="17" t="n">
         <v>16.99</v>
       </c>
       <c r="Q139" s="17" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R139" s="17" t="inlineStr">
         <is>
@@ -25572,7 +25340,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>384.29</v>
+        <v>379.32</v>
       </c>
       <c r="H140" s="17" t="n">
         <v>18.59</v>
@@ -25590,17 +25358,17 @@
         <v>31619750267.15752</v>
       </c>
       <c r="M140" s="17" t="n">
-        <v>20.67</v>
+        <v>20.4</v>
       </c>
       <c r="N140" s="17" t="n"/>
       <c r="O140" s="17" t="n">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="P140" s="17" t="n">
         <v>16.73</v>
       </c>
       <c r="Q140" s="17" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R140" s="17" t="inlineStr">
         <is>
@@ -25998,7 +25766,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>209.91</v>
+        <v>211.71</v>
       </c>
       <c r="H146" s="17" t="n">
         <v>7.24</v>
@@ -26016,17 +25784,17 @@
         <v>70225512519.7807</v>
       </c>
       <c r="M146" s="17" t="n">
-        <v>28.98</v>
+        <v>29.23</v>
       </c>
       <c r="N146" s="17" t="n"/>
       <c r="O146" s="17" t="n">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="P146" s="17" t="n">
         <v>14.35</v>
       </c>
       <c r="Q146" s="17" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="R146" s="17" t="inlineStr">
         <is>
@@ -26071,7 +25839,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>209.91</v>
+        <v>211.71</v>
       </c>
       <c r="H147" s="17" t="n">
         <v>7.86</v>
@@ -26089,17 +25857,17 @@
         <v>75627625676.04219</v>
       </c>
       <c r="M147" s="17" t="n">
-        <v>26.72</v>
+        <v>26.95</v>
       </c>
       <c r="N147" s="17" t="n"/>
       <c r="O147" s="17" t="n">
-        <v>3.73</v>
+        <v>3.76</v>
       </c>
       <c r="P147" s="17" t="n">
         <v>14.46</v>
       </c>
       <c r="Q147" s="17" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="R147" s="17" t="inlineStr">
         <is>
@@ -26497,35 +26265,35 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>298.2</v>
+        <v>294.21</v>
       </c>
       <c r="H153" s="17" t="n">
-        <v>18.54</v>
+        <v>18.51</v>
       </c>
       <c r="I153" s="17" t="n">
-        <v>141.75</v>
+        <v>141.74</v>
       </c>
       <c r="J153" s="18" t="n">
-        <v>13331155060</v>
+        <v>13351488390</v>
       </c>
       <c r="K153" s="18" t="n">
-        <v>727415869.43103</v>
+        <v>726463869.9860101</v>
       </c>
       <c r="L153" s="18" t="n">
-        <v>5562550865.578766</v>
+        <v>5561910169.971308</v>
       </c>
       <c r="M153" s="17" t="n">
-        <v>16.09</v>
+        <v>15.89</v>
       </c>
       <c r="N153" s="17" t="n"/>
       <c r="O153" s="17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="P153" s="17" t="n">
-        <v>13.68</v>
+        <v>13.66</v>
       </c>
       <c r="Q153" s="17" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="R153" s="17" t="inlineStr">
         <is>
@@ -26570,35 +26338,35 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>298.2</v>
+        <v>294.21</v>
       </c>
       <c r="H154" s="17" t="n">
-        <v>20.84</v>
+        <v>20.83</v>
       </c>
       <c r="I154" s="17" t="n">
-        <v>155.77</v>
+        <v>155.76</v>
       </c>
       <c r="J154" s="18" t="n">
-        <v>14177225420</v>
+        <v>14198392090</v>
       </c>
       <c r="K154" s="18" t="n">
-        <v>817658824.2423899</v>
+        <v>817587797.0785199</v>
       </c>
       <c r="L154" s="18" t="n">
-        <v>6112835237.940718</v>
+        <v>6112146741.053395</v>
       </c>
       <c r="M154" s="17" t="n">
-        <v>14.31</v>
+        <v>14.12</v>
       </c>
       <c r="N154" s="17" t="n"/>
       <c r="O154" s="17" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="P154" s="17" t="n">
         <v>14.01</v>
       </c>
       <c r="Q154" s="17" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R154" s="17" t="inlineStr">
         <is>
@@ -27486,9 +27254,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G167" s="17" t="n">
-        <v>21.26</v>
-      </c>
+      <c r="G167" s="17" t="n"/>
       <c r="H167" s="17" t="n">
         <v>0.84</v>
       </c>
@@ -27504,18 +27270,16 @@
       <c r="L167" s="18" t="n">
         <v>12962308973.02548</v>
       </c>
-      <c r="M167" s="17" t="n">
-        <v>25.35</v>
-      </c>
+      <c r="M167" s="17" t="n"/>
       <c r="N167" s="17" t="n"/>
       <c r="O167" s="17" t="n">
-        <v>4.8</v>
+        <v>0.05</v>
       </c>
       <c r="P167" s="17" t="n">
         <v>19.84</v>
       </c>
       <c r="Q167" s="17" t="n">
-        <v>1.87</v>
+        <v>0.02</v>
       </c>
       <c r="R167" s="17" t="inlineStr">
         <is>
@@ -27559,9 +27323,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G168" s="17" t="n">
-        <v>21.26</v>
-      </c>
+      <c r="G168" s="17" t="n"/>
       <c r="H168" s="17" t="n">
         <v>0.96</v>
       </c>
@@ -27577,18 +27339,16 @@
       <c r="L168" s="18" t="n">
         <v>14307031242.83625</v>
       </c>
-      <c r="M168" s="17" t="n">
-        <v>22.21</v>
-      </c>
+      <c r="M168" s="17" t="n"/>
       <c r="N168" s="17" t="n"/>
       <c r="O168" s="17" t="n">
-        <v>4.35</v>
+        <v>0.04</v>
       </c>
       <c r="P168" s="17" t="n">
         <v>20.55</v>
       </c>
       <c r="Q168" s="17" t="n">
-        <v>1.71</v>
+        <v>0.02</v>
       </c>
       <c r="R168" s="17" t="inlineStr">
         <is>
@@ -27987,30 +27747,30 @@
       </c>
       <c r="G174" s="17" t="n"/>
       <c r="H174" s="17" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="I174" s="17" t="n">
-        <v>18.17</v>
+        <v>18.18</v>
       </c>
       <c r="J174" s="18" t="n">
         <v>22326243840</v>
       </c>
       <c r="K174" s="18" t="n">
-        <v>1367525003.82017</v>
+        <v>1373438681.59342</v>
       </c>
       <c r="L174" s="18" t="n">
-        <v>10485951180.08664</v>
+        <v>10489955331.3069</v>
       </c>
       <c r="M174" s="17" t="n"/>
       <c r="N174" s="17" t="n"/>
       <c r="O174" s="17" t="n">
-        <v>3.09</v>
+        <v>2.91</v>
       </c>
       <c r="P174" s="17" t="n">
-        <v>13.64</v>
+        <v>13.7</v>
       </c>
       <c r="Q174" s="17" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="R174" s="17" t="inlineStr">
         <is>
@@ -28059,27 +27819,27 @@
         <v>2.85</v>
       </c>
       <c r="I175" s="17" t="n">
-        <v>20.1</v>
+        <v>20.11</v>
       </c>
       <c r="J175" s="18" t="n">
         <v>24744432810</v>
       </c>
       <c r="K175" s="18" t="n">
-        <v>1641435019.39365</v>
+        <v>1647019838.98829</v>
       </c>
       <c r="L175" s="18" t="n">
-        <v>11597366831.71808</v>
+        <v>11605152464.28588</v>
       </c>
       <c r="M175" s="17" t="n"/>
       <c r="N175" s="17" t="n"/>
       <c r="O175" s="17" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="P175" s="17" t="n">
-        <v>14.87</v>
+        <v>14.91</v>
       </c>
       <c r="Q175" s="17" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="R175" s="17" t="inlineStr">
         <is>
@@ -28495,13 +28255,13 @@
       <c r="M181" s="17" t="n"/>
       <c r="N181" s="17" t="n"/>
       <c r="O181" s="17" t="n">
-        <v>7.05</v>
+        <v>6.89</v>
       </c>
       <c r="P181" s="17" t="n">
         <v>17.22</v>
       </c>
       <c r="Q181" s="17" t="n">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="R181" s="17" t="inlineStr">
         <is>
@@ -28564,13 +28324,13 @@
       <c r="M182" s="17" t="n"/>
       <c r="N182" s="17" t="n"/>
       <c r="O182" s="17" t="n">
-        <v>6.04</v>
+        <v>5.89</v>
       </c>
       <c r="P182" s="17" t="n">
         <v>18.67</v>
       </c>
       <c r="Q182" s="17" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="R182" s="17" t="inlineStr">
         <is>
@@ -28967,9 +28727,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G188" s="17" t="n">
-        <v>115500</v>
-      </c>
+      <c r="G188" s="17" t="n"/>
       <c r="H188" s="17" t="n">
         <v>13470</v>
       </c>
@@ -28986,17 +28744,17 @@
         <v>2419672871894.003</v>
       </c>
       <c r="M188" s="17" t="n">
-        <v>9.92</v>
+        <v>11.11</v>
       </c>
       <c r="N188" s="17" t="n"/>
       <c r="O188" s="17" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="P188" s="17" t="n">
         <v>16.32</v>
       </c>
       <c r="Q188" s="17" t="n">
-        <v>0.59</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R188" s="17" t="inlineStr">
         <is>
@@ -29040,9 +28798,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G189" s="17" t="n">
-        <v>115500</v>
-      </c>
+      <c r="G189" s="17" t="n"/>
       <c r="H189" s="17" t="n">
         <v>14842.75</v>
       </c>
@@ -29058,18 +28814,16 @@
       <c r="L189" s="18" t="n">
         <v>3096745015201.536</v>
       </c>
-      <c r="M189" s="17" t="n">
-        <v>7.78</v>
-      </c>
+      <c r="M189" s="17" t="n"/>
       <c r="N189" s="17" t="n"/>
       <c r="O189" s="17" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="P189" s="17" t="n">
         <v>25.82</v>
       </c>
       <c r="Q189" s="17" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="R189" s="17" t="inlineStr">
         <is>
@@ -29185,19 +28939,19 @@
         <v>5024387667000</v>
       </c>
       <c r="M191" s="7" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="N191" s="7" t="n">
-        <v>3.59</v>
+        <v>0.68</v>
       </c>
       <c r="O191" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="P191" s="7" t="n">
         <v>12.82</v>
       </c>
       <c r="Q191" s="7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="R191" s="7" t="inlineStr">
         <is>
@@ -29260,19 +29014,19 @@
         <v>5954812811000</v>
       </c>
       <c r="M192" s="7" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="N192" s="7" t="n">
-        <v>3.14</v>
+        <v>0.01</v>
       </c>
       <c r="O192" s="7" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="P192" s="7" t="n">
         <v>16.79</v>
       </c>
       <c r="Q192" s="7" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="R192" s="7" t="inlineStr">
         <is>
@@ -29335,19 +29089,19 @@
         <v>6894504330000</v>
       </c>
       <c r="M193" s="7" t="n">
-        <v>7.35</v>
+        <v>0.01</v>
       </c>
       <c r="N193" s="7" t="n">
-        <v>3.61</v>
+        <v>0.16</v>
       </c>
       <c r="O193" s="7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="P193" s="7" t="n">
         <v>8.77</v>
       </c>
       <c r="Q193" s="7" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="R193" s="7" t="inlineStr">
         <is>
@@ -29410,19 +29164,19 @@
         <v>7191120447000</v>
       </c>
       <c r="M194" s="7" t="n">
-        <v>13.73</v>
+        <v>0.01</v>
       </c>
       <c r="N194" s="7" t="n">
-        <v>5.3</v>
+        <v>-0.28</v>
       </c>
       <c r="O194" s="7" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="P194" s="7" t="n">
         <v>5.71</v>
       </c>
       <c r="Q194" s="7" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="R194" s="7" t="inlineStr">
         <is>
@@ -29466,9 +29220,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G195" s="17" t="n">
-        <v>57900</v>
-      </c>
+      <c r="G195" s="17" t="n"/>
       <c r="H195" s="17" t="n">
         <v>6179.71</v>
       </c>
@@ -29485,17 +29237,17 @@
         <v>7589662196632.624</v>
       </c>
       <c r="M195" s="17" t="n">
-        <v>10.02</v>
+        <v>10.75</v>
       </c>
       <c r="N195" s="17" t="n"/>
       <c r="O195" s="17" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="P195" s="17" t="n">
         <v>7.52</v>
       </c>
       <c r="Q195" s="17" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="R195" s="17" t="inlineStr">
         <is>
@@ -29539,9 +29291,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G196" s="17" t="n">
-        <v>57900</v>
-      </c>
+      <c r="G196" s="17" t="n"/>
       <c r="H196" s="17" t="n">
         <v>6625.59</v>
       </c>
@@ -29557,18 +29307,16 @@
       <c r="L196" s="18" t="n">
         <v>8016959738234.411</v>
       </c>
-      <c r="M196" s="17" t="n">
-        <v>8.74</v>
-      </c>
+      <c r="M196" s="17" t="n"/>
       <c r="N196" s="17" t="n"/>
       <c r="O196" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="P196" s="17" t="n">
         <v>8.130000000000001</v>
       </c>
       <c r="Q196" s="17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="R196" s="17" t="inlineStr">
         <is>
@@ -29961,9 +29709,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G202" s="17" t="n">
-        <v>7550</v>
-      </c>
+      <c r="G202" s="17" t="n"/>
       <c r="H202" s="17" t="n"/>
       <c r="I202" s="17" t="n"/>
       <c r="J202" s="18" t="n">
@@ -30018,9 +29764,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G203" s="17" t="n">
-        <v>7550</v>
-      </c>
+      <c r="G203" s="17" t="n"/>
       <c r="H203" s="17" t="n"/>
       <c r="I203" s="17" t="n"/>
       <c r="J203" s="18" t="n">
@@ -30429,7 +30173,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>827.9</v>
+        <v>800.25</v>
       </c>
       <c r="H209" s="17" t="n">
         <v>27.3</v>
@@ -30447,17 +30191,17 @@
         <v>30718072169.32038</v>
       </c>
       <c r="M209" s="17" t="n">
-        <v>30.32</v>
+        <v>29.31</v>
       </c>
       <c r="N209" s="17" t="n"/>
       <c r="O209" s="17" t="n">
-        <v>12.54</v>
+        <v>12.12</v>
       </c>
       <c r="P209" s="17" t="n">
         <v>48.83</v>
       </c>
       <c r="Q209" s="17" t="n">
-        <v>4.87</v>
+        <v>4.7</v>
       </c>
       <c r="R209" s="17" t="inlineStr">
         <is>
@@ -30502,7 +30246,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>827.9</v>
+        <v>800.25</v>
       </c>
       <c r="H210" s="17" t="n">
         <v>32.28</v>
@@ -30520,17 +30264,17 @@
         <v>41831388012.75748</v>
       </c>
       <c r="M210" s="17" t="n">
-        <v>25.65</v>
+        <v>24.79</v>
       </c>
       <c r="N210" s="17" t="n"/>
       <c r="O210" s="17" t="n">
-        <v>9.210000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="P210" s="17" t="n">
         <v>41.41</v>
       </c>
       <c r="Q210" s="17" t="n">
-        <v>4.38</v>
+        <v>4.24</v>
       </c>
       <c r="R210" s="17" t="inlineStr">
         <is>
@@ -30928,35 +30672,35 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>647.47</v>
+        <v>630.33</v>
       </c>
       <c r="H216" s="17" t="n">
-        <v>17.95</v>
+        <v>18.13</v>
       </c>
       <c r="I216" s="17" t="n">
-        <v>107.34</v>
+        <v>107.58</v>
       </c>
       <c r="J216" s="18" t="n">
-        <v>43507800000</v>
+        <v>41142734290</v>
       </c>
       <c r="K216" s="18" t="n">
-        <v>4851716081.676801</v>
+        <v>4900495700.254</v>
       </c>
       <c r="L216" s="18" t="n">
-        <v>29020651108.09325</v>
+        <v>29085337051.0126</v>
       </c>
       <c r="M216" s="17" t="n">
-        <v>36.08</v>
+        <v>34.77</v>
       </c>
       <c r="N216" s="17" t="n"/>
       <c r="O216" s="17" t="n">
-        <v>6.03</v>
+        <v>5.86</v>
       </c>
       <c r="P216" s="17" t="n">
-        <v>17.65</v>
+        <v>17.81</v>
       </c>
       <c r="Q216" s="17" t="n">
-        <v>4.02</v>
+        <v>4.14</v>
       </c>
       <c r="R216" s="17" t="inlineStr">
         <is>
@@ -31001,35 +30745,35 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>647.47</v>
+        <v>630.33</v>
       </c>
       <c r="H217" s="17" t="n">
-        <v>22.44</v>
+        <v>22.45</v>
       </c>
       <c r="I217" s="17" t="n">
-        <v>121.55</v>
+        <v>121.95</v>
       </c>
       <c r="J217" s="18" t="n">
-        <v>44949674000</v>
+        <v>44542211380</v>
       </c>
       <c r="K217" s="18" t="n">
-        <v>6066618671.988</v>
+        <v>6070538776.568</v>
       </c>
       <c r="L217" s="18" t="n">
-        <v>32860214065.59445</v>
+        <v>32969267638.85003</v>
       </c>
       <c r="M217" s="17" t="n">
-        <v>28.85</v>
+        <v>28.07</v>
       </c>
       <c r="N217" s="17" t="n"/>
       <c r="O217" s="17" t="n">
-        <v>5.33</v>
+        <v>5.17</v>
       </c>
       <c r="P217" s="17" t="n">
-        <v>19.61</v>
+        <v>19.57</v>
       </c>
       <c r="Q217" s="17" t="n">
-        <v>3.89</v>
+        <v>3.83</v>
       </c>
       <c r="R217" s="17" t="inlineStr">
         <is>
@@ -31427,7 +31171,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>11.87</v>
+        <v>11.68</v>
       </c>
       <c r="H223" s="17" t="n">
         <v>0.45</v>
@@ -31445,17 +31189,17 @@
         <v>8066736165.96809</v>
       </c>
       <c r="M223" s="17" t="n">
-        <v>26.27</v>
+        <v>25.85</v>
       </c>
       <c r="N223" s="17" t="n"/>
       <c r="O223" s="17" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="P223" s="17" t="n">
         <v>7.11</v>
       </c>
       <c r="Q223" s="17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="R223" s="17" t="inlineStr">
         <is>
@@ -31500,7 +31244,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>11.87</v>
+        <v>11.68</v>
       </c>
       <c r="H224" s="17" t="n">
         <v>0.6899999999999999</v>
@@ -31518,17 +31262,17 @@
         <v>8578215933.122852</v>
       </c>
       <c r="M224" s="17" t="n">
-        <v>17.29</v>
+        <v>17.02</v>
       </c>
       <c r="N224" s="17" t="n"/>
       <c r="O224" s="17" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="P224" s="17" t="n">
         <v>10.24</v>
       </c>
       <c r="Q224" s="17" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="R224" s="17" t="inlineStr">
         <is>
@@ -31925,9 +31669,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G230" s="17" t="n">
-        <v>7065</v>
-      </c>
+      <c r="G230" s="17" t="n"/>
       <c r="H230" s="17" t="n">
         <v>432.91</v>
       </c>
@@ -31943,18 +31685,16 @@
       <c r="L230" s="18" t="n">
         <v>3721807683261.386</v>
       </c>
-      <c r="M230" s="17" t="n">
-        <v>16.32</v>
-      </c>
+      <c r="M230" s="17" t="n"/>
       <c r="N230" s="17" t="n"/>
       <c r="O230" s="17" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="P230" s="17" t="n">
         <v>10.79</v>
       </c>
       <c r="Q230" s="17" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="R230" s="17" t="inlineStr">
         <is>
@@ -31998,9 +31738,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G231" s="17" t="n">
-        <v>7065</v>
-      </c>
+      <c r="G231" s="17" t="n"/>
       <c r="H231" s="17" t="n">
         <v>468.02</v>
       </c>
@@ -32016,18 +31754,16 @@
       <c r="L231" s="18" t="n">
         <v>3949963559227.447</v>
       </c>
-      <c r="M231" s="17" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="M231" s="17" t="n"/>
       <c r="N231" s="17" t="n"/>
       <c r="O231" s="17" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="P231" s="17" t="n">
         <v>10.99</v>
       </c>
       <c r="Q231" s="17" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="R231" s="17" t="inlineStr">
         <is>
@@ -32424,36 +32160,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G237" s="17" t="n">
-        <v>5644</v>
-      </c>
+      <c r="G237" s="17" t="n"/>
       <c r="H237" s="17" t="n">
-        <v>420.47</v>
+        <v>421.59</v>
       </c>
       <c r="I237" s="17" t="n">
-        <v>4437.99</v>
+        <v>4438.54</v>
       </c>
       <c r="J237" s="18" t="n">
         <v>1474454185460</v>
       </c>
       <c r="K237" s="18" t="n">
-        <v>89448496253.70444</v>
+        <v>89687492473.17276</v>
       </c>
       <c r="L237" s="18" t="n">
-        <v>944120991059.0703</v>
-      </c>
-      <c r="M237" s="17" t="n">
-        <v>13.42</v>
-      </c>
+        <v>944238433801.3171</v>
+      </c>
+      <c r="M237" s="17" t="n"/>
       <c r="N237" s="17" t="n"/>
       <c r="O237" s="17" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="P237" s="17" t="n">
-        <v>9.699999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="Q237" s="17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="R237" s="17" t="inlineStr">
         <is>
@@ -32497,36 +32229,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G238" s="17" t="n">
-        <v>5644</v>
-      </c>
+      <c r="G238" s="17" t="n"/>
       <c r="H238" s="17" t="n">
-        <v>486.57</v>
+        <v>489.47</v>
       </c>
       <c r="I238" s="17" t="n">
-        <v>4677.09</v>
+        <v>4679.07</v>
       </c>
       <c r="J238" s="18" t="n">
-        <v>1513554307950</v>
+        <v>1515254307950</v>
       </c>
       <c r="K238" s="18" t="n">
-        <v>103509976594.0072</v>
+        <v>104128493976.6275</v>
       </c>
       <c r="L238" s="18" t="n">
-        <v>994985793557.3655</v>
-      </c>
-      <c r="M238" s="17" t="n">
-        <v>11.6</v>
-      </c>
+        <v>995407175741.4319</v>
+      </c>
+      <c r="M238" s="17" t="n"/>
       <c r="N238" s="17" t="n"/>
       <c r="O238" s="17" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P238" s="17" t="n">
-        <v>10.68</v>
+        <v>10.74</v>
       </c>
       <c r="Q238" s="17" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="R238" s="17" t="inlineStr">
         <is>
@@ -32942,13 +32670,13 @@
       <c r="M244" s="17" t="n"/>
       <c r="N244" s="17" t="n"/>
       <c r="O244" s="17" t="n">
-        <v>3.47</v>
+        <v>3.52</v>
       </c>
       <c r="P244" s="17" t="n">
         <v>23.17</v>
       </c>
       <c r="Q244" s="17" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R244" s="17" t="inlineStr">
         <is>
@@ -33011,13 +32739,13 @@
       <c r="M245" s="17" t="n"/>
       <c r="N245" s="17" t="n"/>
       <c r="O245" s="17" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="P245" s="17" t="n">
         <v>24.14</v>
       </c>
       <c r="Q245" s="17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="R245" s="17" t="inlineStr">
         <is>
@@ -33414,9 +33142,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G251" s="17" t="n">
-        <v>18.8</v>
-      </c>
+      <c r="G251" s="17" t="n"/>
       <c r="H251" s="17" t="n">
         <v>1.17</v>
       </c>
@@ -33432,18 +33158,16 @@
       <c r="L251" s="18" t="n">
         <v>91594511352.27213</v>
       </c>
-      <c r="M251" s="17" t="n">
-        <v>16.1</v>
-      </c>
+      <c r="M251" s="17" t="n"/>
       <c r="N251" s="17" t="n"/>
       <c r="O251" s="17" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="P251" s="17" t="n">
         <v>11.93</v>
       </c>
       <c r="Q251" s="17" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="R251" s="17" t="inlineStr">
         <is>
@@ -33487,9 +33211,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G252" s="17" t="n">
-        <v>18.8</v>
-      </c>
+      <c r="G252" s="17" t="n"/>
       <c r="H252" s="17" t="n">
         <v>1.51</v>
       </c>
@@ -33505,18 +33227,16 @@
       <c r="L252" s="18" t="n">
         <v>95821703524.881</v>
       </c>
-      <c r="M252" s="17" t="n">
-        <v>12.43</v>
-      </c>
+      <c r="M252" s="17" t="n"/>
       <c r="N252" s="17" t="n"/>
       <c r="O252" s="17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="P252" s="17" t="n">
         <v>14.84</v>
       </c>
       <c r="Q252" s="17" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R252" s="17" t="inlineStr">
         <is>
@@ -33913,36 +33633,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G258" s="17" t="n">
-        <v>8.01</v>
-      </c>
+      <c r="G258" s="17" t="n"/>
       <c r="H258" s="17" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="I258" s="17" t="n">
-        <v>5.65</v>
+        <v>5.64</v>
       </c>
       <c r="J258" s="18" t="n">
-        <v>114719395190</v>
+        <v>114720037870</v>
       </c>
       <c r="K258" s="18" t="n">
-        <v>8739275278.16556</v>
+        <v>8480709883.56156</v>
       </c>
       <c r="L258" s="18" t="n">
-        <v>66454955184.60375</v>
-      </c>
-      <c r="M258" s="17" t="n">
-        <v>10.77</v>
-      </c>
+        <v>66277605180.44487</v>
+      </c>
+      <c r="M258" s="17" t="n"/>
       <c r="N258" s="17" t="n"/>
       <c r="O258" s="17" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P258" s="17" t="n">
-        <v>13.77</v>
+        <v>13.38</v>
       </c>
       <c r="Q258" s="17" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="R258" s="17" t="inlineStr">
         <is>
@@ -33986,36 +33702,32 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G259" s="17" t="n">
-        <v>8.01</v>
-      </c>
+      <c r="G259" s="17" t="n"/>
       <c r="H259" s="17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="I259" s="17" t="n">
-        <v>6.3</v>
+        <v>6.27</v>
       </c>
       <c r="J259" s="18" t="n">
-        <v>131129395490</v>
+        <v>131296032459</v>
       </c>
       <c r="K259" s="18" t="n">
-        <v>11003367897.09804</v>
+        <v>10838826282.35004</v>
       </c>
       <c r="L259" s="18" t="n">
-        <v>74002165225.2233</v>
-      </c>
-      <c r="M259" s="17" t="n">
-        <v>8.56</v>
-      </c>
+        <v>73711956127.50876</v>
+      </c>
+      <c r="M259" s="17" t="n"/>
       <c r="N259" s="17" t="n"/>
       <c r="O259" s="17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P259" s="17" t="n">
-        <v>15.67</v>
+        <v>15.49</v>
       </c>
       <c r="Q259" s="17" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="R259" s="17" t="inlineStr">
         <is>
@@ -34412,14 +34124,12 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G265" s="17" t="n">
-        <v>11900</v>
-      </c>
+      <c r="G265" s="17" t="n"/>
       <c r="H265" s="17" t="n">
         <v>1728</v>
       </c>
       <c r="I265" s="17" t="n">
-        <v>16230.44</v>
+        <v>16225.08</v>
       </c>
       <c r="J265" s="18" t="n">
         <v>518900000000</v>
@@ -34428,20 +34138,18 @@
         <v>35036039808</v>
       </c>
       <c r="L265" s="18" t="n">
-        <v>329080086593.1232</v>
-      </c>
-      <c r="M265" s="17" t="n">
-        <v>6.89</v>
-      </c>
+        <v>328971474869.7184</v>
+      </c>
+      <c r="M265" s="17" t="n"/>
       <c r="N265" s="17" t="n"/>
       <c r="O265" s="17" t="n">
-        <v>0.73</v>
+        <v>0.82</v>
       </c>
       <c r="P265" s="17" t="n">
         <v>11.18</v>
       </c>
       <c r="Q265" s="17" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="R265" s="17" t="inlineStr">
         <is>
@@ -34485,14 +34193,12 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G266" s="17" t="n">
-        <v>11900</v>
-      </c>
+      <c r="G266" s="17" t="n"/>
       <c r="H266" s="17" t="n">
         <v>2102</v>
       </c>
       <c r="I266" s="17" t="n">
-        <v>18123.08</v>
+        <v>18111.21</v>
       </c>
       <c r="J266" s="18" t="n">
         <v>579800000000</v>
@@ -34501,20 +34207,18 @@
         <v>42619071572</v>
       </c>
       <c r="L266" s="18" t="n">
-        <v>367454298636.552</v>
-      </c>
-      <c r="M266" s="17" t="n">
-        <v>5.66</v>
-      </c>
+        <v>367213567791.274</v>
+      </c>
+      <c r="M266" s="17" t="n"/>
       <c r="N266" s="17" t="n"/>
       <c r="O266" s="17" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="P266" s="17" t="n">
         <v>12.24</v>
       </c>
       <c r="Q266" s="17" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="R266" s="17" t="inlineStr">
         <is>
@@ -34911,9 +34615,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G272" s="17" t="n">
-        <v>11280</v>
-      </c>
+      <c r="G272" s="17" t="n"/>
       <c r="H272" s="17" t="n"/>
       <c r="I272" s="17" t="n"/>
       <c r="J272" s="18" t="n">
@@ -34968,9 +34670,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G273" s="17" t="n">
-        <v>11280</v>
-      </c>
+      <c r="G273" s="17" t="n"/>
       <c r="H273" s="17" t="n"/>
       <c r="I273" s="17" t="n"/>
       <c r="J273" s="18" t="n">
@@ -35378,9 +35078,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G279" s="17" t="n">
-        <v>6070</v>
-      </c>
+      <c r="G279" s="17" t="n"/>
       <c r="H279" s="17" t="n"/>
       <c r="I279" s="17" t="n"/>
       <c r="J279" s="18" t="n">
@@ -35435,9 +35133,7 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G280" s="17" t="n">
-        <v>6070</v>
-      </c>
+      <c r="G280" s="17" t="n"/>
       <c r="H280" s="17" t="n"/>
       <c r="I280" s="17" t="n"/>
       <c r="J280" s="18" t="n">
@@ -35846,7 +35542,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1098.51</v>
+        <v>1030.25</v>
       </c>
       <c r="H286" s="17" t="n">
         <v>49.24</v>
@@ -35864,17 +35560,17 @@
         <v>11512631631.36988</v>
       </c>
       <c r="M286" s="17" t="n">
-        <v>22.31</v>
+        <v>20.92</v>
       </c>
       <c r="N286" s="17" t="n"/>
       <c r="O286" s="17" t="n">
-        <v>6.02</v>
+        <v>5.65</v>
       </c>
       <c r="P286" s="17" t="n">
         <v>30.34</v>
       </c>
       <c r="Q286" s="17" t="n">
-        <v>3.91</v>
+        <v>3.66</v>
       </c>
       <c r="R286" s="17" t="inlineStr">
         <is>
@@ -35919,7 +35615,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1098.51</v>
+        <v>1030.25</v>
       </c>
       <c r="H287" s="17" t="n">
         <v>57.19</v>
@@ -35937,17 +35633,17 @@
         <v>14468089988.04707</v>
       </c>
       <c r="M287" s="17" t="n">
-        <v>19.21</v>
+        <v>18.02</v>
       </c>
       <c r="N287" s="17" t="n"/>
       <c r="O287" s="17" t="n">
-        <v>4.79</v>
+        <v>4.49</v>
       </c>
       <c r="P287" s="17" t="n">
         <v>27.78</v>
       </c>
       <c r="Q287" s="17" t="n">
-        <v>3.59</v>
+        <v>3.37</v>
       </c>
       <c r="R287" s="17" t="inlineStr">
         <is>
@@ -36255,7 +35951,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-22T07:18:18+09:00</t>
+          <t>2026-08-29T12:28:39+09:00</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>34859</v>
+        <v>34029</v>
       </c>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n">
@@ -815,9 +815,11 @@
         <v>37.73</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>14.82</v>
-      </c>
-      <c r="H5" s="10" t="n"/>
+        <v>14.11</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>12.23</v>
+      </c>
       <c r="I5" s="10" t="n"/>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="9" t="n">
@@ -845,10 +847,10 @@
         <v>5.72</v>
       </c>
       <c r="U5" s="10" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="V5" s="10" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="W5" s="10" t="n"/>
       <c r="X5" s="11" t="n">
@@ -883,10 +885,10 @@
         <v>3.04</v>
       </c>
       <c r="AI5" s="10" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AJ5" s="10" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AK5" s="10" t="n"/>
     </row>
@@ -897,7 +899,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>19709</v>
+        <v>19759</v>
       </c>
       <c r="C6" s="9" t="n"/>
       <c r="D6" s="9" t="n">
@@ -910,9 +912,11 @@
         <v>27.94</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>13.78</v>
-      </c>
-      <c r="H6" s="10" t="n"/>
+        <v>13.46</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>13.55</v>
+      </c>
       <c r="I6" s="10" t="n"/>
       <c r="J6" s="9" t="n"/>
       <c r="K6" s="9" t="n">
@@ -940,10 +944,10 @@
         <v>5.64</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="W6" s="10" t="n"/>
       <c r="X6" s="11" t="n">
@@ -978,10 +982,10 @@
         <v>2.72</v>
       </c>
       <c r="AI6" s="10" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AJ6" s="10" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AK6" s="10" t="n"/>
     </row>
@@ -992,7 +996,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>13163</v>
+        <v>13580</v>
       </c>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
@@ -1003,9 +1007,11 @@
         <v>37.73</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>19.95</v>
-      </c>
-      <c r="H7" s="10" t="n"/>
+        <v>20.37</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>12.56</v>
+      </c>
       <c r="I7" s="10" t="n"/>
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="9" t="n">
@@ -1033,10 +1039,10 @@
         <v>4.96</v>
       </c>
       <c r="U7" s="10" t="n">
-        <v>3.54</v>
+        <v>3.61</v>
       </c>
       <c r="V7" s="10" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="W7" s="10" t="n"/>
       <c r="X7" s="11" t="n">
@@ -1055,7 +1061,7 @@
         <v>20.18</v>
       </c>
       <c r="AC7" s="12" t="n">
-        <v>24.78</v>
+        <v>24.71</v>
       </c>
       <c r="AD7" s="12" t="n"/>
       <c r="AE7" s="9" t="n">
@@ -1071,10 +1077,10 @@
         <v>1.93</v>
       </c>
       <c r="AI7" s="10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AJ7" s="10" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" s="10" t="n"/>
     </row>
@@ -1085,7 +1091,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>18223</v>
+        <v>18309</v>
       </c>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n">
@@ -1098,9 +1104,11 @@
         <v>13.27</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H8" s="10" t="n"/>
+        <v>6.21</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>5.8</v>
+      </c>
       <c r="I8" s="10" t="n"/>
       <c r="J8" s="9" t="n">
         <v>40.3</v>
@@ -1130,10 +1138,10 @@
         <v>2.17</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W8" s="10" t="n"/>
       <c r="X8" s="11" t="n">
@@ -1168,10 +1176,10 @@
         <v>0.96</v>
       </c>
       <c r="AI8" s="10" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="AJ8" s="10" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="AK8" s="10" t="n"/>
     </row>
@@ -1182,7 +1190,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1357</v>
+        <v>1334</v>
       </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
@@ -1191,9 +1199,11 @@
         <v>10.3</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="H9" s="10" t="n"/>
+        <v>5.87</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>6.12</v>
+      </c>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="9" t="n"/>
@@ -1211,10 +1221,10 @@
         <v>2.35</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="V9" s="10" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="W9" s="10" t="n"/>
       <c r="X9" s="11" t="n">
@@ -1243,10 +1253,10 @@
         <v>2.09</v>
       </c>
       <c r="AI9" s="10" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AJ9" s="10" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK9" s="10" t="n"/>
     </row>
@@ -1257,7 +1267,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1126</v>
+        <v>1081</v>
       </c>
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="9" t="n"/>
@@ -1268,7 +1278,7 @@
         <v>36.95</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>8.56</v>
+        <v>8.02</v>
       </c>
       <c r="H10" s="10" t="n"/>
       <c r="I10" s="10" t="n"/>
@@ -1298,7 +1308,7 @@
         <v>2.84</v>
       </c>
       <c r="U10" s="10" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="V10" s="10" t="n"/>
       <c r="W10" s="10" t="n"/>
@@ -1342,7 +1352,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>7202</v>
+        <v>7011</v>
       </c>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
@@ -1353,9 +1363,11 @@
         <v>32.18</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>28.12</v>
-      </c>
-      <c r="H11" s="10" t="n"/>
+        <v>26.15</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>22.27</v>
+      </c>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="9" t="n"/>
@@ -1377,10 +1389,10 @@
         <v>10.52</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>9.869999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="V11" s="10" t="n">
-        <v>7.99</v>
+        <v>7.61</v>
       </c>
       <c r="W11" s="10" t="n"/>
       <c r="X11" s="11" t="n">
@@ -1411,10 +1423,10 @@
         <v>4.38</v>
       </c>
       <c r="AI11" s="10" t="n">
-        <v>4.26</v>
+        <v>4.06</v>
       </c>
       <c r="AJ11" s="10" t="n">
-        <v>3.7</v>
+        <v>3.53</v>
       </c>
       <c r="AK11" s="10" t="n"/>
     </row>
@@ -1425,7 +1437,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>1309</v>
+        <v>1265</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>14.21</v>
@@ -1440,9 +1452,11 @@
         <v>18.39</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>13.93</v>
-      </c>
-      <c r="H12" s="10" t="n"/>
+        <v>12.99</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>9.220000000000001</v>
+      </c>
       <c r="I12" s="10" t="n"/>
       <c r="J12" s="9" t="n">
         <v>11.7</v>
@@ -1472,10 +1486,10 @@
         <v>6.21</v>
       </c>
       <c r="U12" s="10" t="n">
-        <v>3.69</v>
+        <v>3.44</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="W12" s="10" t="n"/>
       <c r="X12" s="11" t="n">
@@ -1510,10 +1524,10 @@
         <v>7.54</v>
       </c>
       <c r="AI12" s="10" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="AK12" s="10" t="n"/>
     </row>
@@ -1524,7 +1538,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>2926</v>
+        <v>2826</v>
       </c>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
@@ -1535,9 +1549,11 @@
         <v>20.62</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>20.27</v>
-      </c>
-      <c r="H13" s="10" t="n"/>
+        <v>19.15</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>13.17</v>
+      </c>
       <c r="I13" s="10" t="n"/>
       <c r="J13" s="9" t="n"/>
       <c r="K13" s="9" t="n">
@@ -1565,10 +1581,10 @@
         <v>6.44</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>5.32</v>
+        <v>5.03</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>3.85</v>
+        <v>3.64</v>
       </c>
       <c r="W13" s="10" t="n"/>
       <c r="X13" s="11" t="n">
@@ -1603,10 +1619,10 @@
         <v>2.61</v>
       </c>
       <c r="AI13" s="10" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AJ13" s="10" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AK13" s="10" t="n"/>
     </row>
@@ -1617,7 +1633,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>914</v>
+        <v>844</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>23.46</v>
@@ -1630,9 +1646,11 @@
         <v>14.78</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>10.91</v>
-      </c>
-      <c r="H14" s="10" t="n"/>
+        <v>9.869999999999999</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>8</v>
+      </c>
       <c r="I14" s="10" t="n"/>
       <c r="J14" s="9" t="n">
         <v>11.21</v>
@@ -1662,10 +1680,10 @@
         <v>2.59</v>
       </c>
       <c r="U14" s="10" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="W14" s="10" t="n"/>
       <c r="X14" s="11" t="n">
@@ -1681,7 +1699,7 @@
         <v>19.3</v>
       </c>
       <c r="AB14" s="12" t="n">
-        <v>18.75</v>
+        <v>18.45</v>
       </c>
       <c r="AC14" s="12" t="n">
         <v>19.15</v>
@@ -1700,10 +1718,10 @@
         <v>1.65</v>
       </c>
       <c r="AI14" s="10" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AJ14" s="10" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AK14" s="10" t="n"/>
     </row>
@@ -1714,7 +1732,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>37.11</v>
@@ -1729,9 +1747,11 @@
         <v>13.58</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="H15" s="10" t="n"/>
+        <v>5.92</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>5.92</v>
+      </c>
       <c r="I15" s="10" t="n"/>
       <c r="J15" s="9" t="n">
         <v>15.59</v>
@@ -1761,10 +1781,10 @@
         <v>2.93</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="V15" s="10" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="W15" s="10" t="n"/>
       <c r="X15" s="11" t="n">
@@ -1780,7 +1800,7 @@
         <v>24.23</v>
       </c>
       <c r="AB15" s="12" t="n">
-        <v>28.53</v>
+        <v>29.46</v>
       </c>
       <c r="AC15" s="12" t="n">
         <v>23.13</v>
@@ -1799,10 +1819,10 @@
         <v>1.02</v>
       </c>
       <c r="AI15" s="10" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AJ15" s="10" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="AK15" s="10" t="n"/>
     </row>
@@ -1820,7 +1840,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>5211</v>
+        <v>5099</v>
       </c>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="9" t="n"/>
@@ -1861,10 +1881,10 @@
         <v>5.43</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="V17" s="10" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="W17" s="10" t="n"/>
       <c r="X17" s="11" t="n">
@@ -1899,10 +1919,10 @@
         <v>0.61</v>
       </c>
       <c r="AI17" s="10" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="AJ17" s="10" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="AK17" s="10" t="n"/>
     </row>
@@ -1926,9 +1946,11 @@
         <v>20.62</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>13.78</v>
-      </c>
-      <c r="H18" s="15" t="n"/>
+        <v>12.99</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>10.73</v>
+      </c>
       <c r="I18" s="15" t="n"/>
       <c r="J18" s="15" t="n">
         <v>15.59</v>
@@ -1958,10 +1980,10 @@
         <v>4.96</v>
       </c>
       <c r="U18" s="15" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="V18" s="15" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="W18" s="15" t="n"/>
       <c r="X18" s="16" t="n">
@@ -1980,7 +2002,7 @@
         <v>27.18</v>
       </c>
       <c r="AC18" s="16" t="n">
-        <v>24.2</v>
+        <v>24.17</v>
       </c>
       <c r="AD18" s="16" t="n"/>
       <c r="AE18" s="15" t="n">
@@ -1996,10 +2018,10 @@
         <v>2.09</v>
       </c>
       <c r="AI18" s="15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AJ18" s="15" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AK18" s="15" t="n"/>
     </row>
@@ -2049,10 +2071,10 @@
         <v>5.43</v>
       </c>
       <c r="U19" s="15" t="n">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="V19" s="15" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="W19" s="15" t="n"/>
       <c r="X19" s="16" t="n">
@@ -2087,10 +2109,10 @@
         <v>0.61</v>
       </c>
       <c r="AI19" s="15" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="AJ19" s="15" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="AK19" s="15" t="n"/>
     </row>
@@ -2114,9 +2136,11 @@
         <v>24.28</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>13.78</v>
-      </c>
-      <c r="H20" s="15" t="n"/>
+        <v>12.99</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>10.73</v>
+      </c>
       <c r="I20" s="15" t="n"/>
       <c r="J20" s="15" t="n">
         <v>27.95</v>
@@ -2146,10 +2170,10 @@
         <v>5.2</v>
       </c>
       <c r="U20" s="15" t="n">
-        <v>3.42</v>
+        <v>3.33</v>
       </c>
       <c r="V20" s="15" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="W20" s="15" t="n"/>
       <c r="X20" s="16" t="n">
@@ -2184,10 +2208,10 @@
         <v>2.01</v>
       </c>
       <c r="AI20" s="15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AJ20" s="15" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK20" s="15" t="n"/>
     </row>
@@ -2248,7 +2272,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>9431</v>
+        <v>9161</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>41.88</v>
@@ -2263,9 +2287,11 @@
         <v>59.99</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="H24" s="10" t="n"/>
+        <v>50.51</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>27.77</v>
+      </c>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="9" t="n">
         <v>14.66</v>
@@ -2295,10 +2321,10 @@
         <v>6.09</v>
       </c>
       <c r="U24" s="10" t="n">
-        <v>6.36</v>
+        <v>5.98</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>5.6</v>
+        <v>5.32</v>
       </c>
       <c r="W24" s="10" t="n"/>
       <c r="X24" s="11" t="n">
@@ -2333,10 +2359,10 @@
         <v>3.02</v>
       </c>
       <c r="AI24" s="10" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AJ24" s="10" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AK24" s="10" t="n"/>
     </row>
@@ -2347,7 +2373,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>43271</v>
+        <v>40326</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>19.31</v>
@@ -2362,9 +2388,11 @@
         <v>34.46</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>25.83</v>
-      </c>
-      <c r="H25" s="10" t="n"/>
+        <v>23.22</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>17.78</v>
+      </c>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="9" t="n">
         <v>7.97</v>
@@ -2394,10 +2422,10 @@
         <v>5</v>
       </c>
       <c r="U25" s="10" t="n">
-        <v>5</v>
+        <v>4.52</v>
       </c>
       <c r="V25" s="10" t="n">
-        <v>4.19</v>
+        <v>3.81</v>
       </c>
       <c r="W25" s="10" t="n"/>
       <c r="X25" s="11" t="n">
@@ -2413,10 +2441,10 @@
         <v>19.14</v>
       </c>
       <c r="AB25" s="12" t="n">
-        <v>21.39</v>
+        <v>21.52</v>
       </c>
       <c r="AC25" s="12" t="n">
-        <v>23.29</v>
+        <v>23.48</v>
       </c>
       <c r="AD25" s="12" t="n"/>
       <c r="AE25" s="9" t="n">
@@ -2432,10 +2460,10 @@
         <v>1.81</v>
       </c>
       <c r="AI25" s="10" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AJ25" s="10" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AK25" s="10" t="n"/>
     </row>
@@ -2446,7 +2474,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>11656</v>
+        <v>10582</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>16.34</v>
@@ -2461,9 +2489,11 @@
         <v>36.3</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>44.85</v>
-      </c>
-      <c r="H26" s="10" t="n"/>
+        <v>40.64</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>27.03</v>
+      </c>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="9" t="n">
         <v>9.449999999999999</v>
@@ -2493,10 +2523,10 @@
         <v>6.43</v>
       </c>
       <c r="U26" s="10" t="n">
-        <v>9.359999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="V26" s="10" t="n">
-        <v>7.56</v>
+        <v>6.71</v>
       </c>
       <c r="W26" s="10" t="n"/>
       <c r="X26" s="11" t="n">
@@ -2531,10 +2561,10 @@
         <v>2.14</v>
       </c>
       <c r="AI26" s="10" t="n">
-        <v>3.11</v>
+        <v>2.76</v>
       </c>
       <c r="AJ26" s="10" t="n">
-        <v>2.61</v>
+        <v>2.32</v>
       </c>
       <c r="AK26" s="10" t="n"/>
     </row>
@@ -2545,7 +2575,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>10303</v>
+        <v>9558</v>
       </c>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n">
@@ -2558,9 +2588,11 @@
         <v>41.99</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>102.89</v>
-      </c>
-      <c r="H27" s="10" t="n"/>
+        <v>92.31</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>29.54</v>
+      </c>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="9" t="n">
         <v>13.88</v>
@@ -2590,10 +2622,10 @@
         <v>2.1</v>
       </c>
       <c r="U27" s="10" t="n">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="V27" s="10" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="11" t="n">
@@ -2628,10 +2660,10 @@
         <v>2.78</v>
       </c>
       <c r="AI27" s="10" t="n">
-        <v>3.17</v>
+        <v>2.88</v>
       </c>
       <c r="AJ27" s="10" t="n">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="AK27" s="10" t="n"/>
     </row>
@@ -2642,7 +2674,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>11036</v>
+        <v>10282</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>15.67</v>
@@ -2657,9 +2689,11 @@
         <v>26.64</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>16.96</v>
-      </c>
-      <c r="H28" s="10" t="n"/>
+        <v>15.41</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>11.21</v>
+      </c>
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="9" t="n">
         <v>20.45</v>
@@ -2689,10 +2723,10 @@
         <v>6.66</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="V28" s="10" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="W28" s="10" t="n"/>
       <c r="X28" s="11" t="n">
@@ -2708,10 +2742,10 @@
         <v>30.05</v>
       </c>
       <c r="AB28" s="12" t="n">
-        <v>25.69</v>
+        <v>25.7</v>
       </c>
       <c r="AC28" s="12" t="n">
-        <v>28.36</v>
+        <v>27.68</v>
       </c>
       <c r="AD28" s="12" t="n"/>
       <c r="AE28" s="9" t="n">
@@ -2727,10 +2761,10 @@
         <v>3.51</v>
       </c>
       <c r="AI28" s="10" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="AJ28" s="10" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AK28" s="10" t="n"/>
     </row>
@@ -2748,7 +2782,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>129122</v>
+        <v>120289</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>21.56</v>
@@ -2763,10 +2797,10 @@
         <v>22.08</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>18.51</v>
+        <v>17.24</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>17.23</v>
+        <v>16.05</v>
       </c>
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="9" t="n">
@@ -2797,10 +2831,10 @@
         <v>16.48</v>
       </c>
       <c r="U30" s="10" t="n">
-        <v>12.68</v>
+        <v>11.81</v>
       </c>
       <c r="V30" s="10" t="n">
-        <v>9.279999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="W30" s="10" t="n"/>
       <c r="X30" s="11" t="n">
@@ -2835,10 +2869,10 @@
         <v>1.48</v>
       </c>
       <c r="AI30" s="10" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="AJ30" s="10" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AK30" s="10" t="n"/>
     </row>
@@ -2849,7 +2883,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>77469</v>
+        <v>73126</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>17.07</v>
@@ -2864,10 +2898,10 @@
         <v>19.36</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>18.82</v>
+        <v>17.76</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>17.92</v>
+        <v>16.92</v>
       </c>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="9" t="n">
@@ -2898,10 +2932,10 @@
         <v>4.86</v>
       </c>
       <c r="U31" s="10" t="n">
-        <v>3.96</v>
+        <v>3.74</v>
       </c>
       <c r="V31" s="10" t="n">
-        <v>3.43</v>
+        <v>3.24</v>
       </c>
       <c r="W31" s="10" t="n"/>
       <c r="X31" s="11" t="n">
@@ -2936,10 +2970,10 @@
         <v>1.93</v>
       </c>
       <c r="AI31" s="10" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AJ31" s="10" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AK31" s="10" t="n"/>
     </row>
@@ -2950,7 +2984,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>102564</v>
+        <v>97175</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>20.08</v>
@@ -2965,10 +2999,10 @@
         <v>21.62</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>22.31</v>
+        <v>21.14</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>20.4</v>
+        <v>19.33</v>
       </c>
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="9" t="n">
@@ -2999,10 +3033,10 @@
         <v>3.55</v>
       </c>
       <c r="U32" s="10" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="V32" s="10" t="n">
-        <v>3.24</v>
+        <v>3.07</v>
       </c>
       <c r="W32" s="10" t="n"/>
       <c r="X32" s="11" t="n">
@@ -3037,10 +3071,10 @@
         <v>1.73</v>
       </c>
       <c r="AI32" s="10" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AJ32" s="10" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AK32" s="10" t="n"/>
     </row>
@@ -3051,7 +3085,7 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>284176</v>
+        <v>269518</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>28.47</v>
@@ -3066,10 +3100,10 @@
         <v>36.57</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>29.23</v>
+        <v>27.72</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>26.95</v>
+        <v>25.56</v>
       </c>
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="9" t="n">
@@ -3100,10 +3134,10 @@
         <v>3.77</v>
       </c>
       <c r="U33" s="10" t="n">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="V33" s="10" t="n">
-        <v>3.76</v>
+        <v>3.56</v>
       </c>
       <c r="W33" s="10" t="n"/>
       <c r="X33" s="11" t="n">
@@ -3138,10 +3172,10 @@
         <v>2.78</v>
       </c>
       <c r="AI33" s="10" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="AJ33" s="10" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="AK33" s="10" t="n"/>
     </row>
@@ -3152,7 +3186,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>11545</v>
+        <v>11220</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>15.9</v>
@@ -3167,10 +3201,10 @@
         <v>22.06</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>15.89</v>
+        <v>15.45</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>14.12</v>
+        <v>13.72</v>
       </c>
       <c r="I34" s="10" t="n"/>
       <c r="J34" s="9" t="n">
@@ -3201,10 +3235,10 @@
         <v>2.63</v>
       </c>
       <c r="U34" s="10" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V34" s="10" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="W34" s="10" t="n"/>
       <c r="X34" s="11" t="n">
@@ -3239,10 +3273,10 @@
         <v>1.07</v>
       </c>
       <c r="AI34" s="10" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="AJ34" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AK34" s="10" t="n"/>
     </row>
@@ -3260,7 +3294,7 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>62437</v>
+        <v>56078</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>17.03</v>
@@ -3305,10 +3339,10 @@
         <v>14.29</v>
       </c>
       <c r="U36" s="10" t="n">
-        <v>9.039999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>7.35</v>
+        <v>6.57</v>
       </c>
       <c r="W36" s="10" t="n"/>
       <c r="X36" s="11" t="n">
@@ -3324,10 +3358,10 @@
         <v>15.36</v>
       </c>
       <c r="AB36" s="12" t="n">
-        <v>31.06</v>
+        <v>31.14</v>
       </c>
       <c r="AC36" s="12" t="n">
-        <v>36.92</v>
+        <v>37.01</v>
       </c>
       <c r="AD36" s="12" t="n"/>
       <c r="AE36" s="9" t="n">
@@ -3343,10 +3377,10 @@
         <v>7.21</v>
       </c>
       <c r="AI36" s="10" t="n">
-        <v>3.86</v>
+        <v>3.46</v>
       </c>
       <c r="AJ36" s="10" t="n">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="AK36" s="10" t="n"/>
     </row>
@@ -3364,7 +3398,7 @@
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>810</v>
+        <v>775</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>16.56</v>
@@ -3409,7 +3443,7 @@
         <v>4.26</v>
       </c>
       <c r="U38" s="10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="V38" s="10" t="n">
         <v>0.04</v>
@@ -3468,7 +3502,7 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>35342</v>
+        <v>33829</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>5</v>
@@ -3513,10 +3547,10 @@
         <v>2.97</v>
       </c>
       <c r="U40" s="10" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="V40" s="10" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="W40" s="10" t="n"/>
       <c r="X40" s="11" t="n">
@@ -3551,10 +3585,10 @@
         <v>1.45</v>
       </c>
       <c r="AI40" s="10" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AJ40" s="10" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK40" s="10" t="n"/>
     </row>
@@ -3572,7 +3606,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>35910</v>
+        <v>33190</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>24.79</v>
@@ -3617,10 +3651,10 @@
         <v>6.69</v>
       </c>
       <c r="U42" s="10" t="n">
-        <v>6.89</v>
+        <v>6.35</v>
       </c>
       <c r="V42" s="10" t="n">
-        <v>5.89</v>
+        <v>5.43</v>
       </c>
       <c r="W42" s="10" t="n"/>
       <c r="X42" s="11" t="n">
@@ -3636,10 +3670,10 @@
         <v>16.02</v>
       </c>
       <c r="AB42" s="12" t="n">
-        <v>17.22</v>
+        <v>17.2</v>
       </c>
       <c r="AC42" s="12" t="n">
-        <v>18.67</v>
+        <v>18.63</v>
       </c>
       <c r="AD42" s="12" t="n"/>
       <c r="AE42" s="9" t="n">
@@ -3655,10 +3689,10 @@
         <v>3.66</v>
       </c>
       <c r="AI42" s="10" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="AJ42" s="10" t="n">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="AK42" s="10" t="n"/>
     </row>
@@ -3682,9 +3716,11 @@
         <v>36.3</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>44.85</v>
-      </c>
-      <c r="H43" s="15" t="n"/>
+        <v>40.64</v>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>27.03</v>
+      </c>
       <c r="I43" s="15" t="n"/>
       <c r="J43" s="15" t="n">
         <v>13.88</v>
@@ -3714,10 +3750,10 @@
         <v>6.09</v>
       </c>
       <c r="U43" s="15" t="n">
-        <v>5</v>
+        <v>4.52</v>
       </c>
       <c r="V43" s="15" t="n">
-        <v>4.19</v>
+        <v>3.81</v>
       </c>
       <c r="W43" s="15" t="n"/>
       <c r="X43" s="16" t="n">
@@ -3733,10 +3769,10 @@
         <v>19.14</v>
       </c>
       <c r="AB43" s="16" t="n">
-        <v>21.39</v>
+        <v>21.52</v>
       </c>
       <c r="AC43" s="16" t="n">
-        <v>23.29</v>
+        <v>23.48</v>
       </c>
       <c r="AD43" s="16" t="n"/>
       <c r="AE43" s="15" t="n">
@@ -3752,10 +3788,10 @@
         <v>2.78</v>
       </c>
       <c r="AI43" s="15" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AJ43" s="15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AK43" s="15" t="n"/>
     </row>
@@ -3779,10 +3815,10 @@
         <v>22.06</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>18.82</v>
+        <v>17.76</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>17.92</v>
+        <v>16.92</v>
       </c>
       <c r="I44" s="15" t="n"/>
       <c r="J44" s="15" t="n">
@@ -3813,10 +3849,10 @@
         <v>3.77</v>
       </c>
       <c r="U44" s="15" t="n">
-        <v>3.96</v>
+        <v>3.74</v>
       </c>
       <c r="V44" s="15" t="n">
-        <v>3.43</v>
+        <v>3.24</v>
       </c>
       <c r="W44" s="15" t="n"/>
       <c r="X44" s="16" t="n">
@@ -3851,10 +3887,10 @@
         <v>1.73</v>
       </c>
       <c r="AI44" s="15" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AJ44" s="15" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AK44" s="15" t="n"/>
     </row>
@@ -3908,10 +3944,10 @@
         <v>14.29</v>
       </c>
       <c r="U45" s="15" t="n">
-        <v>9.039999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="V45" s="15" t="n">
-        <v>7.35</v>
+        <v>6.57</v>
       </c>
       <c r="W45" s="15" t="n"/>
       <c r="X45" s="16" t="n">
@@ -3927,10 +3963,10 @@
         <v>15.36</v>
       </c>
       <c r="AB45" s="16" t="n">
-        <v>31.06</v>
+        <v>31.14</v>
       </c>
       <c r="AC45" s="16" t="n">
-        <v>36.92</v>
+        <v>37.01</v>
       </c>
       <c r="AD45" s="16" t="n"/>
       <c r="AE45" s="15" t="n">
@@ -3946,10 +3982,10 @@
         <v>7.21</v>
       </c>
       <c r="AI45" s="15" t="n">
-        <v>3.86</v>
+        <v>3.46</v>
       </c>
       <c r="AJ45" s="15" t="n">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="AK45" s="15" t="n"/>
     </row>
@@ -4003,7 +4039,7 @@
         <v>4.26</v>
       </c>
       <c r="U46" s="15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="V46" s="15" t="n">
         <v>0.04</v>
@@ -4098,10 +4134,10 @@
         <v>2.97</v>
       </c>
       <c r="U47" s="15" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="V47" s="15" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="W47" s="15" t="n"/>
       <c r="X47" s="16" t="n">
@@ -4136,10 +4172,10 @@
         <v>1.45</v>
       </c>
       <c r="AI47" s="15" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AJ47" s="15" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK47" s="15" t="n"/>
     </row>
@@ -4193,10 +4229,10 @@
         <v>6.69</v>
       </c>
       <c r="U48" s="15" t="n">
-        <v>6.89</v>
+        <v>6.35</v>
       </c>
       <c r="V48" s="15" t="n">
-        <v>5.89</v>
+        <v>5.43</v>
       </c>
       <c r="W48" s="15" t="n"/>
       <c r="X48" s="16" t="n">
@@ -4212,10 +4248,10 @@
         <v>16.02</v>
       </c>
       <c r="AB48" s="16" t="n">
-        <v>17.22</v>
+        <v>17.2</v>
       </c>
       <c r="AC48" s="16" t="n">
-        <v>18.67</v>
+        <v>18.63</v>
       </c>
       <c r="AD48" s="16" t="n"/>
       <c r="AE48" s="15" t="n">
@@ -4231,10 +4267,10 @@
         <v>3.66</v>
       </c>
       <c r="AI48" s="15" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="AJ48" s="15" t="n">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="AK48" s="15" t="n"/>
     </row>
@@ -4258,10 +4294,10 @@
         <v>30.55</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>24.07</v>
+        <v>22.18</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>17.92</v>
+        <v>18.55</v>
       </c>
       <c r="I49" s="15" t="n"/>
       <c r="J49" s="15" t="n">
@@ -4292,10 +4328,10 @@
         <v>4.93</v>
       </c>
       <c r="U49" s="15" t="n">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="V49" s="15" t="n">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="W49" s="15" t="n"/>
       <c r="X49" s="16" t="n">
@@ -4311,7 +4347,7 @@
         <v>16.82</v>
       </c>
       <c r="AB49" s="16" t="n">
-        <v>18.53</v>
+        <v>18.52</v>
       </c>
       <c r="AC49" s="16" t="n">
         <v>20.53</v>
@@ -4330,10 +4366,10 @@
         <v>2.04</v>
       </c>
       <c r="AI49" s="15" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="AJ49" s="15" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AK49" s="15" t="n"/>
     </row>
@@ -4394,7 +4430,7 @@
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>4738</v>
+        <v>4990</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>10.61</v>
@@ -4409,9 +4445,11 @@
         <v>47.5</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="H53" s="10" t="n"/>
+        <v>11.01</v>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>9.43</v>
+      </c>
       <c r="I53" s="10" t="n"/>
       <c r="J53" s="9" t="n">
         <v>7.18</v>
@@ -4441,10 +4479,10 @@
         <v>2.61</v>
       </c>
       <c r="U53" s="10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="V53" s="10" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="W53" s="10" t="n"/>
       <c r="X53" s="11" t="n">
@@ -4479,10 +4517,10 @@
         <v>1.25</v>
       </c>
       <c r="AI53" s="10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="AJ53" s="10" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="AK53" s="10" t="n"/>
     </row>
@@ -4493,57 +4531,59 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>4390</v>
+        <v>4466</v>
       </c>
       <c r="C54" s="9" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>0.01</v>
+        <v>7.35</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>0.01</v>
+        <v>13.73</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="H54" s="10" t="n"/>
+        <v>10.7</v>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v>9.48</v>
+      </c>
       <c r="I54" s="10" t="n"/>
       <c r="J54" s="9" t="n">
-        <v>0.68</v>
+        <v>3.59</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.01</v>
+        <v>3.14</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0.16</v>
+        <v>3.61</v>
       </c>
       <c r="M54" s="9" t="n">
-        <v>-0.28</v>
+        <v>5.3</v>
       </c>
       <c r="N54" s="10" t="n"/>
       <c r="O54" s="10" t="n"/>
       <c r="P54" s="10" t="n"/>
       <c r="Q54" s="9" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R54" s="9" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="S54" s="9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="T54" s="9" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="U54" s="10" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="W54" s="10" t="n"/>
       <c r="X54" s="11" t="n">
@@ -4566,22 +4606,22 @@
       </c>
       <c r="AD54" s="12" t="n"/>
       <c r="AE54" s="9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AF54" s="9" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AG54" s="9" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AH54" s="9" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AI54" s="10" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AJ54" s="10" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="AK54" s="10" t="n"/>
     </row>
@@ -4592,7 +4632,7 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>7.23</v>
@@ -4673,7 +4713,7 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>5.78</v>
@@ -4687,8 +4727,12 @@
       <c r="F56" s="9" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="G56" s="10" t="n"/>
-      <c r="H56" s="10" t="n"/>
+      <c r="G56" s="10" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>6.27</v>
+      </c>
       <c r="I56" s="10" t="n"/>
       <c r="J56" s="9" t="n">
         <v>3.96</v>
@@ -4718,7 +4762,7 @@
         <v>0.92</v>
       </c>
       <c r="U56" s="10" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="V56" s="10" t="n">
         <v>0.73</v>
@@ -4756,7 +4800,7 @@
         <v>0.59</v>
       </c>
       <c r="AI56" s="10" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="AJ56" s="10" t="n">
         <v>0.46</v>
@@ -4770,7 +4814,7 @@
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>7.57</v>
@@ -4855,7 +4899,7 @@
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>5.71</v>
@@ -4947,7 +4991,7 @@
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>372346</v>
+        <v>378716</v>
       </c>
       <c r="C60" s="9" t="n">
         <v>18.45</v>
@@ -4962,10 +5006,10 @@
         <v>30</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>29.31</v>
+        <v>29.94</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>24.79</v>
+        <v>25.14</v>
       </c>
       <c r="I60" s="10" t="n"/>
       <c r="J60" s="9" t="n">
@@ -4996,10 +5040,10 @@
         <v>12.5</v>
       </c>
       <c r="U60" s="10" t="n">
-        <v>12.12</v>
+        <v>12.35</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>8.9</v>
+        <v>9.06</v>
       </c>
       <c r="W60" s="10" t="n"/>
       <c r="X60" s="11" t="n">
@@ -5015,10 +5059,10 @@
         <v>43.54</v>
       </c>
       <c r="AB60" s="12" t="n">
-        <v>48.83</v>
+        <v>48.66</v>
       </c>
       <c r="AC60" s="12" t="n">
-        <v>41.41</v>
+        <v>41.56</v>
       </c>
       <c r="AD60" s="12" t="n"/>
       <c r="AE60" s="9" t="n">
@@ -5034,10 +5078,10 @@
         <v>3.94</v>
       </c>
       <c r="AI60" s="10" t="n">
-        <v>4.7</v>
+        <v>4.78</v>
       </c>
       <c r="AJ60" s="10" t="n">
-        <v>4.24</v>
+        <v>4.3</v>
       </c>
       <c r="AK60" s="10" t="n"/>
     </row>
@@ -5048,7 +5092,7 @@
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>170411</v>
+        <v>187497</v>
       </c>
       <c r="C61" s="9" t="n">
         <v>16.58</v>
@@ -5063,10 +5107,10 @@
         <v>24.83</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>34.77</v>
+        <v>38.25</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>28.07</v>
+        <v>30.59</v>
       </c>
       <c r="I61" s="10" t="n"/>
       <c r="J61" s="9" t="n">
@@ -5097,10 +5141,10 @@
         <v>4.81</v>
       </c>
       <c r="U61" s="10" t="n">
-        <v>5.86</v>
+        <v>6.45</v>
       </c>
       <c r="V61" s="10" t="n">
-        <v>5.17</v>
+        <v>5.68</v>
       </c>
       <c r="W61" s="10" t="n"/>
       <c r="X61" s="11" t="n">
@@ -5119,7 +5163,7 @@
         <v>17.81</v>
       </c>
       <c r="AC61" s="12" t="n">
-        <v>19.57</v>
+        <v>19.74</v>
       </c>
       <c r="AD61" s="12" t="n"/>
       <c r="AE61" s="9" t="n">
@@ -5135,10 +5179,10 @@
         <v>2.79</v>
       </c>
       <c r="AI61" s="10" t="n">
-        <v>4.14</v>
+        <v>4.56</v>
       </c>
       <c r="AJ61" s="10" t="n">
-        <v>3.83</v>
+        <v>4.21</v>
       </c>
       <c r="AK61" s="10" t="n"/>
     </row>
@@ -5149,7 +5193,7 @@
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>14507</v>
+        <v>17886</v>
       </c>
       <c r="C62" s="9" t="n">
         <v>10.64</v>
@@ -5164,10 +5208,10 @@
         <v>22.45</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>25.85</v>
+        <v>31.88</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>17.02</v>
+        <v>21.02</v>
       </c>
       <c r="I62" s="10" t="n"/>
       <c r="J62" s="9" t="n">
@@ -5198,10 +5242,10 @@
         <v>1.48</v>
       </c>
       <c r="U62" s="10" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="V62" s="10" t="n">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="W62" s="10" t="n"/>
       <c r="X62" s="11" t="n">
@@ -5217,10 +5261,10 @@
         <v>6.63</v>
       </c>
       <c r="AB62" s="12" t="n">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="AC62" s="12" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
       <c r="AD62" s="12" t="n"/>
       <c r="AE62" s="9" t="n">
@@ -5236,10 +5280,10 @@
         <v>0.63</v>
       </c>
       <c r="AI62" s="10" t="n">
-        <v>0.79</v>
+        <v>0.98</v>
       </c>
       <c r="AJ62" s="10" t="n">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AK62" s="10" t="n"/>
     </row>
@@ -5250,7 +5294,7 @@
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>65005</v>
+        <v>63718</v>
       </c>
       <c r="C63" s="9" t="n">
         <v>11.71</v>
@@ -5265,10 +5309,10 @@
         <v>20.48</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>20.92</v>
+        <v>20.51</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>18.02</v>
+        <v>17.66</v>
       </c>
       <c r="I63" s="10" t="n"/>
       <c r="J63" s="9" t="n">
@@ -5299,10 +5343,10 @@
         <v>5.69</v>
       </c>
       <c r="U63" s="10" t="n">
-        <v>5.65</v>
+        <v>5.53</v>
       </c>
       <c r="V63" s="10" t="n">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
       <c r="W63" s="10" t="n"/>
       <c r="X63" s="11" t="n">
@@ -5337,10 +5381,10 @@
         <v>3.17</v>
       </c>
       <c r="AI63" s="10" t="n">
-        <v>3.66</v>
+        <v>3.59</v>
       </c>
       <c r="AJ63" s="10" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="AK63" s="10" t="n"/>
     </row>
@@ -5358,7 +5402,7 @@
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>41853</v>
+        <v>43220</v>
       </c>
       <c r="C65" s="9" t="n"/>
       <c r="D65" s="9" t="n">
@@ -5373,8 +5417,12 @@
       <c r="G65" s="10" t="n">
         <v>14.4</v>
       </c>
-      <c r="H65" s="10" t="n"/>
-      <c r="I65" s="10" t="n"/>
+      <c r="H65" s="10" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="I65" s="10" t="n">
+        <v>13.49</v>
+      </c>
       <c r="J65" s="9" t="n"/>
       <c r="K65" s="9" t="n">
         <v>5.96</v>
@@ -5407,7 +5455,7 @@
         <v>1.8</v>
       </c>
       <c r="W65" s="10" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X65" s="11" t="n"/>
       <c r="Y65" s="11" t="n">
@@ -5423,10 +5471,10 @@
         <v>11.26</v>
       </c>
       <c r="AC65" s="12" t="n">
-        <v>10.79</v>
+        <v>11.97</v>
       </c>
       <c r="AD65" s="12" t="n">
-        <v>10.99</v>
+        <v>12.9</v>
       </c>
       <c r="AE65" s="9" t="n"/>
       <c r="AF65" s="9" t="n">
@@ -5455,7 +5503,7 @@
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>7736</v>
+        <v>8139</v>
       </c>
       <c r="C66" s="9" t="n"/>
       <c r="D66" s="9" t="n">
@@ -5470,8 +5518,12 @@
       <c r="G66" s="10" t="n">
         <v>15.32</v>
       </c>
-      <c r="H66" s="10" t="n"/>
-      <c r="I66" s="10" t="n"/>
+      <c r="H66" s="10" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="I66" s="10" t="n">
+        <v>12.21</v>
+      </c>
       <c r="J66" s="9" t="n"/>
       <c r="K66" s="9" t="n">
         <v>5.66</v>
@@ -5501,10 +5553,10 @@
         <v>1.25</v>
       </c>
       <c r="V66" s="10" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W66" s="10" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="X66" s="11" t="n"/>
       <c r="Y66" s="11" t="n">
@@ -5539,10 +5591,10 @@
         <v>0.8</v>
       </c>
       <c r="AJ66" s="10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AK66" s="10" t="n">
         <v>0.84</v>
-      </c>
-      <c r="AK66" s="10" t="n">
-        <v>0.82</v>
       </c>
     </row>
     <row r="67">
@@ -5559,7 +5611,7 @@
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>73844</v>
+        <v>74085</v>
       </c>
       <c r="C68" s="9" t="n">
         <v>11.71</v>
@@ -5623,10 +5675,10 @@
         <v>18.5</v>
       </c>
       <c r="AB68" s="12" t="n">
-        <v>23.17</v>
+        <v>23.11</v>
       </c>
       <c r="AC68" s="12" t="n">
-        <v>24.14</v>
+        <v>24.11</v>
       </c>
       <c r="AD68" s="12" t="n"/>
       <c r="AE68" s="9" t="n">
@@ -5663,7 +5715,7 @@
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>26125</v>
+        <v>27442</v>
       </c>
       <c r="C70" s="9" t="n">
         <v>31.28</v>
@@ -5677,8 +5729,12 @@
       <c r="F70" s="9" t="n">
         <v>23.11</v>
       </c>
-      <c r="G70" s="10" t="n"/>
-      <c r="H70" s="10" t="n"/>
+      <c r="G70" s="10" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="H70" s="10" t="n">
+        <v>13.15</v>
+      </c>
       <c r="I70" s="10" t="n"/>
       <c r="J70" s="9" t="n">
         <v>18.39</v>
@@ -5711,7 +5767,7 @@
         <v>1.92</v>
       </c>
       <c r="V70" s="10" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="W70" s="10" t="n"/>
       <c r="X70" s="11" t="n">
@@ -5727,10 +5783,10 @@
         <v>10.49</v>
       </c>
       <c r="AB70" s="12" t="n">
-        <v>11.93</v>
+        <v>11.97</v>
       </c>
       <c r="AC70" s="12" t="n">
-        <v>14.84</v>
+        <v>13.89</v>
       </c>
       <c r="AD70" s="12" t="n"/>
       <c r="AE70" s="9" t="n">
@@ -5746,10 +5802,10 @@
         <v>2.17</v>
       </c>
       <c r="AI70" s="10" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AJ70" s="10" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AK70" s="10" t="n"/>
     </row>
@@ -5760,7 +5816,7 @@
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>13850</v>
+        <v>14276</v>
       </c>
       <c r="C71" s="9" t="n">
         <v>13.89</v>
@@ -5774,8 +5830,12 @@
       <c r="F71" s="9" t="n">
         <v>20.71</v>
       </c>
-      <c r="G71" s="10" t="n"/>
-      <c r="H71" s="10" t="n"/>
+      <c r="G71" s="10" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="H71" s="10" t="n">
+        <v>8.83</v>
+      </c>
       <c r="I71" s="10" t="n"/>
       <c r="J71" s="9" t="n">
         <v>7.78</v>
@@ -5805,10 +5865,10 @@
         <v>2.25</v>
       </c>
       <c r="U71" s="10" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="V71" s="10" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="W71" s="10" t="n"/>
       <c r="X71" s="11" t="n">
@@ -5824,10 +5884,10 @@
         <v>10.96</v>
       </c>
       <c r="AB71" s="12" t="n">
-        <v>13.38</v>
+        <v>13.73</v>
       </c>
       <c r="AC71" s="12" t="n">
-        <v>15.49</v>
+        <v>16.74</v>
       </c>
       <c r="AD71" s="12" t="n"/>
       <c r="AE71" s="9" t="n">
@@ -5843,10 +5903,10 @@
         <v>1.35</v>
       </c>
       <c r="AI71" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="AJ71" s="10" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="AK71" s="10" t="n"/>
     </row>
@@ -5861,30 +5921,32 @@
         <v>6.51</v>
       </c>
       <c r="D72" s="15" t="n">
-        <v>6</v>
+        <v>6.27</v>
       </c>
       <c r="E72" s="15" t="n">
-        <v>5.58</v>
+        <v>7.35</v>
       </c>
       <c r="F72" s="15" t="n">
-        <v>5.89</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>10.93</v>
-      </c>
-      <c r="H72" s="15" t="n"/>
+        <v>10.7</v>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>9.43</v>
+      </c>
       <c r="I72" s="15" t="n"/>
       <c r="J72" s="15" t="n">
-        <v>3.48</v>
+        <v>3.77</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>3.03</v>
+        <v>3.35</v>
       </c>
       <c r="L72" s="15" t="n">
-        <v>2.65</v>
+        <v>3.56</v>
       </c>
       <c r="M72" s="15" t="n">
-        <v>3.77</v>
+        <v>5.07</v>
       </c>
       <c r="N72" s="15" t="n"/>
       <c r="O72" s="15" t="n"/>
@@ -5893,19 +5955,19 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="R72" s="15" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="S72" s="15" t="n">
-        <v>0.46</v>
+        <v>0.55</v>
       </c>
       <c r="T72" s="15" t="n">
-        <v>0.52</v>
+        <v>0.66</v>
       </c>
       <c r="U72" s="15" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="V72" s="15" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="W72" s="15" t="n"/>
       <c r="X72" s="16" t="n">
@@ -5928,22 +5990,22 @@
       </c>
       <c r="AD72" s="16" t="n"/>
       <c r="AE72" s="15" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="AF72" s="15" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="AG72" s="15" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="AH72" s="15" t="n">
-        <v>0.43</v>
+        <v>0.53</v>
       </c>
       <c r="AI72" s="15" t="n">
-        <v>0.52</v>
+        <v>0.63</v>
       </c>
       <c r="AJ72" s="15" t="n">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="AK72" s="15" t="n"/>
     </row>
@@ -5967,10 +6029,10 @@
         <v>23.64</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>27.58</v>
+        <v>30.91</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>21.41</v>
+        <v>23.08</v>
       </c>
       <c r="I73" s="15" t="n"/>
       <c r="J73" s="15" t="n">
@@ -6001,10 +6063,10 @@
         <v>5.25</v>
       </c>
       <c r="U73" s="15" t="n">
-        <v>5.76</v>
+        <v>5.99</v>
       </c>
       <c r="V73" s="15" t="n">
-        <v>4.83</v>
+        <v>5.04</v>
       </c>
       <c r="W73" s="15" t="n"/>
       <c r="X73" s="16" t="n">
@@ -6023,7 +6085,7 @@
         <v>24.07</v>
       </c>
       <c r="AC73" s="16" t="n">
-        <v>23.68</v>
+        <v>23.76</v>
       </c>
       <c r="AD73" s="16" t="n"/>
       <c r="AE73" s="15" t="n">
@@ -6039,10 +6101,10 @@
         <v>2.98</v>
       </c>
       <c r="AI73" s="15" t="n">
-        <v>3.9</v>
+        <v>4.07</v>
       </c>
       <c r="AJ73" s="15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AK73" s="15" t="n"/>
     </row>
@@ -6066,8 +6128,12 @@
       <c r="G74" s="15" t="n">
         <v>14.86</v>
       </c>
-      <c r="H74" s="15" t="n"/>
-      <c r="I74" s="15" t="n"/>
+      <c r="H74" s="15" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="I74" s="15" t="n">
+        <v>12.85</v>
+      </c>
       <c r="J74" s="15" t="n"/>
       <c r="K74" s="15" t="n">
         <v>5.81</v>
@@ -6097,10 +6163,10 @@
         <v>1.4</v>
       </c>
       <c r="V74" s="15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W74" s="15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X74" s="16" t="n"/>
       <c r="Y74" s="16" t="n">
@@ -6116,10 +6182,10 @@
         <v>9.91</v>
       </c>
       <c r="AC74" s="16" t="n">
-        <v>10.26</v>
+        <v>10.85</v>
       </c>
       <c r="AD74" s="16" t="n">
-        <v>10.87</v>
+        <v>11.82</v>
       </c>
       <c r="AE74" s="15" t="n"/>
       <c r="AF74" s="15" t="n">
@@ -6135,10 +6201,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ74" s="15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK74" s="15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="75">
@@ -6210,10 +6276,10 @@
         <v>18.5</v>
       </c>
       <c r="AB75" s="16" t="n">
-        <v>23.17</v>
+        <v>23.11</v>
       </c>
       <c r="AC75" s="16" t="n">
-        <v>24.14</v>
+        <v>24.11</v>
       </c>
       <c r="AD75" s="16" t="n"/>
       <c r="AE75" s="15" t="n">
@@ -6255,8 +6321,12 @@
       <c r="F76" s="15" t="n">
         <v>21.91</v>
       </c>
-      <c r="G76" s="15" t="n"/>
-      <c r="H76" s="15" t="n"/>
+      <c r="G76" s="15" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="H76" s="15" t="n">
+        <v>10.99</v>
+      </c>
       <c r="I76" s="15" t="n"/>
       <c r="J76" s="15" t="n">
         <v>13.09</v>
@@ -6286,10 +6356,10 @@
         <v>2.23</v>
       </c>
       <c r="U76" s="15" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="V76" s="15" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="W76" s="15" t="n"/>
       <c r="X76" s="16" t="n">
@@ -6305,10 +6375,10 @@
         <v>10.73</v>
       </c>
       <c r="AB76" s="16" t="n">
-        <v>12.66</v>
+        <v>12.85</v>
       </c>
       <c r="AC76" s="16" t="n">
-        <v>15.16</v>
+        <v>15.31</v>
       </c>
       <c r="AD76" s="16" t="n"/>
       <c r="AE76" s="15" t="n">
@@ -6324,10 +6394,10 @@
         <v>1.76</v>
       </c>
       <c r="AI76" s="15" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AJ76" s="15" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK76" s="15" t="n"/>
     </row>
@@ -6351,12 +6421,14 @@
         <v>18.97</v>
       </c>
       <c r="G77" s="15" t="n">
-        <v>18.12</v>
+        <v>15.32</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>21.41</v>
-      </c>
-      <c r="I77" s="15" t="n"/>
+        <v>14.18</v>
+      </c>
+      <c r="I77" s="15" t="n">
+        <v>12.85</v>
+      </c>
       <c r="J77" s="15" t="n">
         <v>7.18</v>
       </c>
@@ -6387,13 +6459,13 @@
         <v>1.48</v>
       </c>
       <c r="U77" s="15" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="V77" s="15" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="W77" s="15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X77" s="16" t="n">
         <v>15.47</v>
@@ -6408,13 +6480,13 @@
         <v>10.49</v>
       </c>
       <c r="AB77" s="16" t="n">
-        <v>12.66</v>
+        <v>12.85</v>
       </c>
       <c r="AC77" s="16" t="n">
-        <v>15.16</v>
+        <v>15.31</v>
       </c>
       <c r="AD77" s="16" t="n">
-        <v>10.87</v>
+        <v>11.82</v>
       </c>
       <c r="AE77" s="15" t="n">
         <v>0.64</v>
@@ -6429,13 +6501,13 @@
         <v>0.97</v>
       </c>
       <c r="AI77" s="15" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AJ77" s="15" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AK77" s="15" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>
@@ -6558,7 +6630,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34859</v>
+        <v>34029</v>
       </c>
       <c r="F2" s="9" t="n"/>
       <c r="G2" s="9" t="n">
@@ -6571,9 +6643,11 @@
         <v>37.73</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>14.82</v>
-      </c>
-      <c r="K2" s="9" t="n"/>
+        <v>14.11</v>
+      </c>
+      <c r="K2" s="9" t="n">
+        <v>12.23</v>
+      </c>
       <c r="L2" s="9" t="n"/>
     </row>
     <row r="3">
@@ -6598,7 +6672,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19709</v>
+        <v>19759</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n">
@@ -6611,9 +6685,11 @@
         <v>27.94</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>13.78</v>
-      </c>
-      <c r="K3" s="9" t="n"/>
+        <v>13.46</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>13.55</v>
+      </c>
       <c r="L3" s="9" t="n"/>
     </row>
     <row r="4">
@@ -6638,7 +6714,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13163</v>
+        <v>13580</v>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n"/>
@@ -6649,9 +6725,11 @@
         <v>37.73</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>19.95</v>
-      </c>
-      <c r="K4" s="9" t="n"/>
+        <v>20.37</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>12.56</v>
+      </c>
       <c r="L4" s="9" t="n"/>
     </row>
     <row r="5">
@@ -6676,7 +6754,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>18223</v>
+        <v>18309</v>
       </c>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n">
@@ -6689,9 +6767,11 @@
         <v>13.27</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K5" s="9" t="n"/>
+        <v>6.21</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>5.8</v>
+      </c>
       <c r="L5" s="9" t="n"/>
     </row>
     <row r="6">
@@ -6716,7 +6796,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1357</v>
+        <v>1334</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -6725,9 +6805,11 @@
         <v>10.3</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="K6" s="9" t="n"/>
+        <v>5.87</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>6.12</v>
+      </c>
       <c r="L6" s="9" t="n"/>
     </row>
     <row r="7">
@@ -6752,7 +6834,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1126</v>
+        <v>1081</v>
       </c>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
@@ -6763,7 +6845,7 @@
         <v>36.95</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>8.56</v>
+        <v>8.02</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -6790,7 +6872,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5211</v>
+        <v>5099</v>
       </c>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="9" t="n"/>
@@ -6826,7 +6908,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7202</v>
+        <v>7011</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -6837,9 +6919,11 @@
         <v>32.18</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>28.12</v>
-      </c>
-      <c r="K9" s="9" t="n"/>
+        <v>26.15</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>22.27</v>
+      </c>
       <c r="L9" s="9" t="n"/>
     </row>
     <row r="10">
@@ -6864,7 +6948,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1309</v>
+        <v>1265</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>14.21</v>
@@ -6879,9 +6963,11 @@
         <v>18.39</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>13.93</v>
-      </c>
-      <c r="K10" s="9" t="n"/>
+        <v>12.99</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>9.220000000000001</v>
+      </c>
       <c r="L10" s="9" t="n"/>
     </row>
     <row r="11">
@@ -6906,7 +6992,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2926</v>
+        <v>2826</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
@@ -6917,9 +7003,11 @@
         <v>20.62</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>20.27</v>
-      </c>
-      <c r="K11" s="9" t="n"/>
+        <v>19.15</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>13.17</v>
+      </c>
       <c r="L11" s="9" t="n"/>
     </row>
     <row r="12">
@@ -6944,7 +7032,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>914</v>
+        <v>844</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>23.46</v>
@@ -6957,9 +7045,11 @@
         <v>14.78</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>10.91</v>
-      </c>
-      <c r="K12" s="9" t="n"/>
+        <v>9.869999999999999</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>8</v>
+      </c>
       <c r="L12" s="9" t="n"/>
     </row>
     <row r="13">
@@ -6984,7 +7074,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>37.11</v>
@@ -6999,9 +7089,11 @@
         <v>13.58</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="K13" s="9" t="n"/>
+        <v>5.92</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>5.92</v>
+      </c>
       <c r="L13" s="9" t="n"/>
     </row>
     <row r="14">
@@ -7026,7 +7118,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9431</v>
+        <v>9161</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>41.88</v>
@@ -7041,9 +7133,11 @@
         <v>59.99</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>53.78</v>
-      </c>
-      <c r="K14" s="9" t="n"/>
+        <v>50.51</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>27.77</v>
+      </c>
       <c r="L14" s="9" t="n"/>
     </row>
     <row r="15">
@@ -7068,7 +7162,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>43271</v>
+        <v>40326</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>19.31</v>
@@ -7083,9 +7177,11 @@
         <v>34.46</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>25.83</v>
-      </c>
-      <c r="K15" s="9" t="n"/>
+        <v>23.22</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>17.78</v>
+      </c>
       <c r="L15" s="9" t="n"/>
     </row>
     <row r="16">
@@ -7110,7 +7206,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>11656</v>
+        <v>10582</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>16.34</v>
@@ -7125,9 +7221,11 @@
         <v>36.3</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>44.85</v>
-      </c>
-      <c r="K16" s="9" t="n"/>
+        <v>40.64</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>27.03</v>
+      </c>
       <c r="L16" s="9" t="n"/>
     </row>
     <row r="17">
@@ -7152,7 +7250,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10303</v>
+        <v>9558</v>
       </c>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n">
@@ -7165,9 +7263,11 @@
         <v>41.99</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>102.89</v>
-      </c>
-      <c r="K17" s="9" t="n"/>
+        <v>92.31</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>29.54</v>
+      </c>
       <c r="L17" s="9" t="n"/>
     </row>
     <row r="18">
@@ -7192,7 +7292,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>11036</v>
+        <v>10282</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>15.67</v>
@@ -7207,9 +7307,11 @@
         <v>26.64</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>16.96</v>
-      </c>
-      <c r="K18" s="9" t="n"/>
+        <v>15.41</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>11.21</v>
+      </c>
       <c r="L18" s="9" t="n"/>
     </row>
     <row r="19">
@@ -7234,7 +7336,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>129122</v>
+        <v>120289</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>21.56</v>
@@ -7249,10 +7351,10 @@
         <v>22.08</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>18.51</v>
+        <v>17.24</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>17.23</v>
+        <v>16.05</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -7278,7 +7380,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>77469</v>
+        <v>73126</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>17.07</v>
@@ -7293,10 +7395,10 @@
         <v>19.36</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>18.82</v>
+        <v>17.76</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>17.92</v>
+        <v>16.92</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -7322,7 +7424,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>102564</v>
+        <v>97175</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>20.08</v>
@@ -7337,10 +7439,10 @@
         <v>21.62</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>22.31</v>
+        <v>21.14</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>20.4</v>
+        <v>19.33</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -7366,7 +7468,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>284176</v>
+        <v>269518</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>28.47</v>
@@ -7381,10 +7483,10 @@
         <v>36.57</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>29.23</v>
+        <v>27.72</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>26.95</v>
+        <v>25.56</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -7410,7 +7512,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11545</v>
+        <v>11220</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>15.9</v>
@@ -7425,10 +7527,10 @@
         <v>22.06</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>15.89</v>
+        <v>15.45</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>14.12</v>
+        <v>13.72</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -7454,7 +7556,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>62437</v>
+        <v>56078</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>17.03</v>
@@ -7494,7 +7596,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>810</v>
+        <v>775</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>16.56</v>
@@ -7534,7 +7636,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>35342</v>
+        <v>33829</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>5</v>
@@ -7574,7 +7676,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>35910</v>
+        <v>33190</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>24.79</v>
@@ -7614,7 +7716,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4738</v>
+        <v>4990</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>10.61</v>
@@ -7629,9 +7731,11 @@
         <v>47.5</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="K28" s="9" t="n"/>
+        <v>11.01</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>9.43</v>
+      </c>
       <c r="L28" s="9" t="n"/>
     </row>
     <row r="29">
@@ -7656,24 +7760,26 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4390</v>
+        <v>4466</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.01</v>
+        <v>7.35</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0.01</v>
+        <v>13.73</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="K29" s="9" t="n"/>
+        <v>10.7</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>9.48</v>
+      </c>
       <c r="L29" s="9" t="n"/>
     </row>
     <row r="30">
@@ -7698,7 +7804,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>7.23</v>
@@ -7734,7 +7840,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>372346</v>
+        <v>378716</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>18.45</v>
@@ -7749,10 +7855,10 @@
         <v>30</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>29.31</v>
+        <v>29.94</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>24.79</v>
+        <v>25.14</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -7778,7 +7884,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>170411</v>
+        <v>187497</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>16.58</v>
@@ -7793,10 +7899,10 @@
         <v>24.83</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>34.77</v>
+        <v>38.25</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>28.07</v>
+        <v>30.59</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -7822,7 +7928,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>14507</v>
+        <v>17886</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>10.64</v>
@@ -7837,10 +7943,10 @@
         <v>22.45</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>25.85</v>
+        <v>31.88</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>17.02</v>
+        <v>21.02</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -7866,7 +7972,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41853</v>
+        <v>43220</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -7881,8 +7987,12 @@
       <c r="J34" s="9" t="n">
         <v>14.4</v>
       </c>
-      <c r="K34" s="9" t="n"/>
-      <c r="L34" s="9" t="n"/>
+      <c r="K34" s="9" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="L34" s="9" t="n">
+        <v>13.49</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -7906,7 +8016,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7736</v>
+        <v>8139</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -7921,8 +8031,12 @@
       <c r="J35" s="9" t="n">
         <v>15.32</v>
       </c>
-      <c r="K35" s="9" t="n"/>
-      <c r="L35" s="9" t="n"/>
+      <c r="K35" s="9" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>12.21</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -7946,7 +8060,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>73844</v>
+        <v>74085</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>11.71</v>
@@ -7986,7 +8100,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>26125</v>
+        <v>27442</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>31.28</v>
@@ -8000,8 +8114,12 @@
       <c r="I37" s="9" t="n">
         <v>23.11</v>
       </c>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="9" t="n"/>
+      <c r="J37" s="9" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>13.15</v>
+      </c>
       <c r="L37" s="9" t="n"/>
     </row>
     <row r="38">
@@ -8026,7 +8144,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>13850</v>
+        <v>14276</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>13.89</v>
@@ -8040,8 +8158,12 @@
       <c r="I38" s="9" t="n">
         <v>20.71</v>
       </c>
-      <c r="J38" s="9" t="n"/>
-      <c r="K38" s="9" t="n"/>
+      <c r="J38" s="9" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>8.83</v>
+      </c>
       <c r="L38" s="9" t="n"/>
     </row>
     <row r="39">
@@ -8066,7 +8188,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>5.78</v>
@@ -8080,8 +8202,12 @@
       <c r="I39" s="9" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
+      <c r="J39" s="9" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>6.27</v>
+      </c>
       <c r="L39" s="9" t="n"/>
     </row>
     <row r="40">
@@ -8106,7 +8232,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>7.57</v>
@@ -8146,7 +8272,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>5.71</v>
@@ -8186,7 +8312,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>65005</v>
+        <v>63718</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>11.71</v>
@@ -8201,10 +8327,10 @@
         <v>20.48</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>20.92</v>
+        <v>20.51</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>18.02</v>
+        <v>17.66</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -8320,7 +8446,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34859</v>
+        <v>34029</v>
       </c>
       <c r="F2" s="9" t="n"/>
       <c r="G2" s="9" t="n">
@@ -8358,7 +8484,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19709</v>
+        <v>19759</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n">
@@ -8396,7 +8522,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13163</v>
+        <v>13580</v>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n">
@@ -8434,7 +8560,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>18223</v>
+        <v>18309</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>40.3</v>
@@ -8474,7 +8600,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1357</v>
+        <v>1334</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -8508,7 +8634,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1126</v>
+        <v>1081</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>87.52</v>
@@ -8546,7 +8672,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5211</v>
+        <v>5099</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>991.9299999999999</v>
@@ -8586,7 +8712,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7202</v>
+        <v>7011</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -8622,7 +8748,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1309</v>
+        <v>1265</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>11.7</v>
@@ -8662,7 +8788,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2926</v>
+        <v>2826</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -8700,7 +8826,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>914</v>
+        <v>844</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>11.21</v>
@@ -8740,7 +8866,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>15.59</v>
@@ -8780,7 +8906,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9431</v>
+        <v>9161</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>14.66</v>
@@ -8820,7 +8946,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>43271</v>
+        <v>40326</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>7.97</v>
@@ -8860,7 +8986,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>11656</v>
+        <v>10582</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>9.449999999999999</v>
@@ -8900,7 +9026,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10303</v>
+        <v>9558</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>13.88</v>
@@ -8940,7 +9066,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>11036</v>
+        <v>10282</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>20.45</v>
@@ -8980,7 +9106,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>129122</v>
+        <v>120289</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>15.68</v>
@@ -9020,7 +9146,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>77469</v>
+        <v>73126</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>12.31</v>
@@ -9060,7 +9186,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>102564</v>
+        <v>97175</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>14.87</v>
@@ -9100,7 +9226,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>284176</v>
+        <v>269518</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>15.21</v>
@@ -9140,7 +9266,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11545</v>
+        <v>11220</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>10.08</v>
@@ -9180,7 +9306,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>62437</v>
+        <v>56078</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>8.5</v>
@@ -9220,7 +9346,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>810</v>
+        <v>775</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>9.84</v>
@@ -9260,7 +9386,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>35342</v>
+        <v>33829</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>4.69</v>
@@ -9300,7 +9426,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>35910</v>
+        <v>33190</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>11.71</v>
@@ -9340,7 +9466,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4738</v>
+        <v>4990</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>7.18</v>
@@ -9380,19 +9506,19 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4390</v>
+        <v>4466</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0.68</v>
+        <v>3.59</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0.01</v>
+        <v>3.14</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.16</v>
+        <v>3.61</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>-0.28</v>
+        <v>5.3</v>
       </c>
       <c r="J29" s="9" t="n"/>
       <c r="K29" s="9" t="n"/>
@@ -9420,7 +9546,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>6.74</v>
@@ -9460,7 +9586,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>372346</v>
+        <v>378716</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>13.46</v>
@@ -9500,7 +9626,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>170411</v>
+        <v>187497</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>13.71</v>
@@ -9540,7 +9666,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>14507</v>
+        <v>17886</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>10.23</v>
@@ -9580,7 +9706,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41853</v>
+        <v>43220</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -9620,7 +9746,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7736</v>
+        <v>8139</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -9660,7 +9786,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>73844</v>
+        <v>74085</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>7.78</v>
@@ -9700,7 +9826,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>26125</v>
+        <v>27442</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>18.39</v>
@@ -9740,7 +9866,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>13850</v>
+        <v>14276</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>7.78</v>
@@ -9780,7 +9906,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>3.96</v>
@@ -9820,7 +9946,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>2.92</v>
@@ -9860,7 +9986,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>3</v>
@@ -9900,7 +10026,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>65005</v>
+        <v>63718</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>6.73</v>
@@ -10030,7 +10156,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34859</v>
+        <v>34029</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>1.95</v>
@@ -10045,10 +10171,10 @@
         <v>5.72</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -10074,7 +10200,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19709</v>
+        <v>19759</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>2.73</v>
@@ -10089,10 +10215,10 @@
         <v>5.64</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -10118,7 +10244,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13163</v>
+        <v>13580</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>1.21</v>
@@ -10133,10 +10259,10 @@
         <v>4.96</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>3.54</v>
+        <v>3.61</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -10162,7 +10288,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>18223</v>
+        <v>18309</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.51</v>
@@ -10177,10 +10303,10 @@
         <v>2.17</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -10206,7 +10332,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1357</v>
+        <v>1334</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -10215,10 +10341,10 @@
         <v>2.35</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -10244,7 +10370,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1126</v>
+        <v>1081</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.85</v>
@@ -10259,7 +10385,7 @@
         <v>2.84</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -10286,7 +10412,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5211</v>
+        <v>5099</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>1.54</v>
@@ -10301,10 +10427,10 @@
         <v>5.43</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="L8" s="9" t="n"/>
     </row>
@@ -10330,7 +10456,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7202</v>
+        <v>7011</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -10341,10 +10467,10 @@
         <v>10.52</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>9.869999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>7.99</v>
+        <v>7.61</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -10370,7 +10496,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1309</v>
+        <v>1265</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1.05</v>
@@ -10385,10 +10511,10 @@
         <v>6.21</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>3.69</v>
+        <v>3.44</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -10414,7 +10540,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2926</v>
+        <v>2826</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>2.39</v>
@@ -10429,10 +10555,10 @@
         <v>6.44</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>5.32</v>
+        <v>5.03</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>3.85</v>
+        <v>3.64</v>
       </c>
       <c r="L11" s="9" t="n"/>
     </row>
@@ -10458,7 +10584,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>914</v>
+        <v>844</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>1.18</v>
@@ -10473,10 +10599,10 @@
         <v>2.59</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="L12" s="9" t="n"/>
     </row>
@@ -10502,7 +10628,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>2.1</v>
@@ -10517,10 +10643,10 @@
         <v>2.93</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="L13" s="9" t="n"/>
     </row>
@@ -10546,7 +10672,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9431</v>
+        <v>9161</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>3.47</v>
@@ -10561,10 +10687,10 @@
         <v>6.09</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>6.36</v>
+        <v>5.98</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>5.6</v>
+        <v>5.32</v>
       </c>
       <c r="L14" s="9" t="n"/>
     </row>
@@ -10590,7 +10716,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>43271</v>
+        <v>40326</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>1.32</v>
@@ -10605,10 +10731,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>5</v>
+        <v>4.52</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>4.19</v>
+        <v>3.81</v>
       </c>
       <c r="L15" s="9" t="n"/>
     </row>
@@ -10634,7 +10760,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>11656</v>
+        <v>10582</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>2.15</v>
@@ -10649,10 +10775,10 @@
         <v>6.43</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>9.359999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>7.56</v>
+        <v>6.71</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -10678,7 +10804,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10303</v>
+        <v>9558</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.99</v>
@@ -10693,10 +10819,10 @@
         <v>2.1</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -10722,7 +10848,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>11036</v>
+        <v>10282</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>2.04</v>
@@ -10737,10 +10863,10 @@
         <v>6.66</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="L18" s="9" t="n"/>
     </row>
@@ -10766,7 +10892,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>129122</v>
+        <v>120289</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>13.34</v>
@@ -10781,10 +10907,10 @@
         <v>16.48</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>12.68</v>
+        <v>11.81</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>9.279999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -10810,7 +10936,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>77469</v>
+        <v>73126</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>5.46</v>
@@ -10825,10 +10951,10 @@
         <v>4.86</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>3.96</v>
+        <v>3.74</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>3.43</v>
+        <v>3.24</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -10854,7 +10980,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>102564</v>
+        <v>97175</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>3.67</v>
@@ -10869,10 +10995,10 @@
         <v>3.55</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>3.24</v>
+        <v>3.07</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -10898,7 +11024,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>284176</v>
+        <v>269518</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>2.04</v>
@@ -10913,10 +11039,10 @@
         <v>3.77</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>3.76</v>
+        <v>3.56</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -10942,7 +11068,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11545</v>
+        <v>11220</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>2.64</v>
@@ -10957,10 +11083,10 @@
         <v>2.63</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -10986,7 +11112,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>62437</v>
+        <v>56078</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>2.86</v>
@@ -11001,10 +11127,10 @@
         <v>14.29</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>9.039999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>7.35</v>
+        <v>6.57</v>
       </c>
       <c r="L24" s="9" t="n"/>
     </row>
@@ -11030,7 +11156,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>810</v>
+        <v>775</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>2.35</v>
@@ -11045,7 +11171,7 @@
         <v>4.26</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0.04</v>
@@ -11074,7 +11200,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>35342</v>
+        <v>33829</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.65</v>
@@ -11089,10 +11215,10 @@
         <v>2.97</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -11118,7 +11244,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>35910</v>
+        <v>33190</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1.85</v>
@@ -11133,10 +11259,10 @@
         <v>6.69</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>6.89</v>
+        <v>6.35</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>5.89</v>
+        <v>5.43</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -11162,7 +11288,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4738</v>
+        <v>4990</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -11177,10 +11303,10 @@
         <v>2.61</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -11206,25 +11332,25 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4390</v>
+        <v>4466</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -11250,7 +11376,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -11290,7 +11416,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>372346</v>
+        <v>378716</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>7.79</v>
@@ -11305,10 +11431,10 @@
         <v>12.5</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>12.12</v>
+        <v>12.35</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>8.9</v>
+        <v>9.06</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -11334,7 +11460,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>170411</v>
+        <v>187497</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>5.84</v>
@@ -11349,10 +11475,10 @@
         <v>4.81</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>5.86</v>
+        <v>6.45</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>5.17</v>
+        <v>5.68</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -11378,7 +11504,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>14507</v>
+        <v>17886</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>3.12</v>
@@ -11393,10 +11519,10 @@
         <v>1.48</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -11422,7 +11548,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41853</v>
+        <v>43220</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -11441,7 +11567,7 @@
         <v>1.8</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="35">
@@ -11466,7 +11592,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7736</v>
+        <v>8139</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -11482,10 +11608,10 @@
         <v>1.25</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="36">
@@ -11510,7 +11636,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>73844</v>
+        <v>74085</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>2.36</v>
@@ -11554,7 +11680,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>26125</v>
+        <v>27442</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>2.06</v>
@@ -11572,7 +11698,7 @@
         <v>1.92</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -11598,7 +11724,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>13850</v>
+        <v>14276</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>1.12</v>
@@ -11613,10 +11739,10 @@
         <v>2.25</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -11642,7 +11768,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>1.25</v>
@@ -11657,7 +11783,7 @@
         <v>0.92</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>0.73</v>
@@ -11686,7 +11812,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.5600000000000001</v>
@@ -11726,7 +11852,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.88</v>
@@ -11766,7 +11892,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>65005</v>
+        <v>63718</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>3.49</v>
@@ -11781,10 +11907,10 @@
         <v>5.69</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>5.65</v>
+        <v>5.53</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -11900,7 +12026,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34859</v>
+        <v>34029</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>-6.66</v>
@@ -11944,7 +12070,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19709</v>
+        <v>19759</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>-234.21</v>
@@ -11988,7 +12114,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13163</v>
+        <v>13580</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>-17.23</v>
@@ -12006,7 +12132,7 @@
         <v>20.18</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>24.78</v>
+        <v>24.71</v>
       </c>
       <c r="L4" s="11" t="n"/>
     </row>
@@ -12032,7 +12158,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>18223</v>
+        <v>18309</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>-2.23</v>
@@ -12076,7 +12202,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1357</v>
+        <v>1334</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>-7.73</v>
@@ -12120,7 +12246,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1126</v>
+        <v>1081</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>-13.03</v>
@@ -12162,7 +12288,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5211</v>
+        <v>5099</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>-52.75</v>
@@ -12206,7 +12332,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7202</v>
+        <v>7011</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>57.58</v>
@@ -12250,7 +12376,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1309</v>
+        <v>1265</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>7.36</v>
@@ -12294,7 +12420,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2926</v>
+        <v>2826</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>-18.17</v>
@@ -12338,7 +12464,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>914</v>
+        <v>844</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>5.01</v>
@@ -12353,7 +12479,7 @@
         <v>19.3</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>18.75</v>
+        <v>18.45</v>
       </c>
       <c r="K12" s="11" t="n">
         <v>19.15</v>
@@ -12382,7 +12508,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>5.67</v>
@@ -12397,7 +12523,7 @@
         <v>24.23</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>28.53</v>
+        <v>29.46</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>23.13</v>
@@ -12426,7 +12552,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9431</v>
+        <v>9161</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>8.300000000000001</v>
@@ -12470,7 +12596,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>43271</v>
+        <v>40326</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>6.84</v>
@@ -12485,10 +12611,10 @@
         <v>19.14</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>21.39</v>
+        <v>21.52</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>23.29</v>
+        <v>23.48</v>
       </c>
       <c r="L15" s="11" t="n"/>
     </row>
@@ -12514,7 +12640,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>11656</v>
+        <v>10582</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>13.15</v>
@@ -12558,7 +12684,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10303</v>
+        <v>9558</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>-3.83</v>
@@ -12602,7 +12728,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>11036</v>
+        <v>10282</v>
       </c>
       <c r="F18" s="11" t="n">
         <v>13.01</v>
@@ -12617,10 +12743,10 @@
         <v>30.05</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>25.69</v>
+        <v>25.7</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>28.36</v>
+        <v>27.68</v>
       </c>
       <c r="L18" s="11" t="n"/>
     </row>
@@ -12646,7 +12772,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>129122</v>
+        <v>120289</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>61.86</v>
@@ -12690,7 +12816,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>77469</v>
+        <v>73126</v>
       </c>
       <c r="F20" s="11" t="n">
         <v>31.97</v>
@@ -12734,7 +12860,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>102564</v>
+        <v>97175</v>
       </c>
       <c r="F21" s="11" t="n">
         <v>18.26</v>
@@ -12778,7 +12904,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>284176</v>
+        <v>269518</v>
       </c>
       <c r="F22" s="11" t="n">
         <v>7.16</v>
@@ -12822,7 +12948,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11545</v>
+        <v>11220</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>16.6</v>
@@ -12866,7 +12992,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>62437</v>
+        <v>56078</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>16.81</v>
@@ -12881,10 +13007,10 @@
         <v>15.36</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>31.06</v>
+        <v>31.14</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>36.92</v>
+        <v>37.01</v>
       </c>
       <c r="L24" s="11" t="n"/>
     </row>
@@ -12910,7 +13036,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>810</v>
+        <v>775</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>14.19</v>
@@ -12954,7 +13080,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>35342</v>
+        <v>33829</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>12.91</v>
@@ -12998,7 +13124,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>35910</v>
+        <v>33190</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>7.44</v>
@@ -13013,10 +13139,10 @@
         <v>16.02</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>17.22</v>
+        <v>17.2</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>18.67</v>
+        <v>18.63</v>
       </c>
       <c r="L27" s="11" t="n"/>
     </row>
@@ -13042,7 +13168,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4738</v>
+        <v>4990</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>7.62</v>
@@ -13086,7 +13212,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4390</v>
+        <v>4466</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>12.82</v>
@@ -13130,7 +13256,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F30" s="11" t="n">
         <v>11.21</v>
@@ -13170,7 +13296,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>372346</v>
+        <v>378716</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>42.25</v>
@@ -13185,10 +13311,10 @@
         <v>43.54</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>48.83</v>
+        <v>48.66</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>41.41</v>
+        <v>41.56</v>
       </c>
       <c r="L31" s="11" t="n"/>
     </row>
@@ -13214,7 +13340,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>170411</v>
+        <v>187497</v>
       </c>
       <c r="F32" s="11" t="n">
         <v>35.19</v>
@@ -13232,7 +13358,7 @@
         <v>17.81</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>19.57</v>
+        <v>19.74</v>
       </c>
       <c r="L32" s="11" t="n"/>
     </row>
@@ -13258,7 +13384,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>14507</v>
+        <v>17886</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>29.29</v>
@@ -13273,10 +13399,10 @@
         <v>6.63</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
       <c r="L33" s="11" t="n"/>
     </row>
@@ -13302,7 +13428,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41853</v>
+        <v>43220</v>
       </c>
       <c r="F34" s="11" t="n"/>
       <c r="G34" s="11" t="n">
@@ -13318,10 +13444,10 @@
         <v>11.26</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>10.79</v>
+        <v>11.97</v>
       </c>
       <c r="L34" s="11" t="n">
-        <v>10.99</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="35">
@@ -13346,7 +13472,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7736</v>
+        <v>8139</v>
       </c>
       <c r="F35" s="11" t="n"/>
       <c r="G35" s="11" t="n">
@@ -13390,7 +13516,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>73844</v>
+        <v>74085</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>20.11</v>
@@ -13405,10 +13531,10 @@
         <v>18.5</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>23.17</v>
+        <v>23.11</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>24.14</v>
+        <v>24.11</v>
       </c>
       <c r="L36" s="11" t="n"/>
     </row>
@@ -13434,7 +13560,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>26125</v>
+        <v>27442</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>6.6</v>
@@ -13449,10 +13575,10 @@
         <v>10.49</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>11.93</v>
+        <v>11.97</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>14.84</v>
+        <v>13.89</v>
       </c>
       <c r="L37" s="11" t="n"/>
     </row>
@@ -13478,7 +13604,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>13850</v>
+        <v>14276</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>8.1</v>
@@ -13493,10 +13619,10 @@
         <v>10.96</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>13.38</v>
+        <v>13.73</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>15.49</v>
+        <v>16.74</v>
       </c>
       <c r="L38" s="11" t="n"/>
     </row>
@@ -13522,7 +13648,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F39" s="11" t="n">
         <v>21.69</v>
@@ -13566,7 +13692,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>7.43</v>
@@ -13606,7 +13732,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>15.47</v>
@@ -13646,7 +13772,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>65005</v>
+        <v>63718</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>29.81</v>
@@ -13780,7 +13906,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34859</v>
+        <v>34029</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>1.14</v>
@@ -13795,10 +13921,10 @@
         <v>3.04</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -13824,7 +13950,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19709</v>
+        <v>19759</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>0.42</v>
@@ -13839,10 +13965,10 @@
         <v>2.72</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -13868,7 +13994,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13163</v>
+        <v>13580</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>0.73</v>
@@ -13883,10 +14009,10 @@
         <v>1.93</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="L4" s="9" t="n"/>
     </row>
@@ -13912,7 +14038,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>18223</v>
+        <v>18309</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.29</v>
@@ -13927,10 +14053,10 @@
         <v>0.96</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -13956,7 +14082,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1357</v>
+        <v>1334</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -13965,10 +14091,10 @@
         <v>2.09</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -13994,7 +14120,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1126</v>
+        <v>1081</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.18</v>
@@ -14034,7 +14160,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5211</v>
+        <v>5099</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.12</v>
@@ -14049,10 +14175,10 @@
         <v>0.61</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="L8" s="9" t="n"/>
     </row>
@@ -14078,7 +14204,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7202</v>
+        <v>7011</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -14089,10 +14215,10 @@
         <v>4.38</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>4.26</v>
+        <v>4.06</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>3.7</v>
+        <v>3.53</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -14118,7 +14244,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1309</v>
+        <v>1265</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1.13</v>
@@ -14133,10 +14259,10 @@
         <v>7.54</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -14162,7 +14288,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2926</v>
+        <v>2826</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -14177,10 +14303,10 @@
         <v>2.61</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="L11" s="9" t="n"/>
     </row>
@@ -14206,7 +14332,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>914</v>
+        <v>844</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>1.29</v>
@@ -14221,10 +14347,10 @@
         <v>1.65</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="L12" s="9" t="n"/>
     </row>
@@ -14250,7 +14376,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.72</v>
@@ -14265,10 +14391,10 @@
         <v>1.02</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="L13" s="9" t="n"/>
     </row>
@@ -14294,7 +14420,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9431</v>
+        <v>9161</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>1.78</v>
@@ -14309,10 +14435,10 @@
         <v>3.02</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="L14" s="9" t="n"/>
     </row>
@@ -14338,7 +14464,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>43271</v>
+        <v>40326</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.53</v>
@@ -14353,10 +14479,10 @@
         <v>1.81</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="L15" s="9" t="n"/>
     </row>
@@ -14382,7 +14508,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>11656</v>
+        <v>10582</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.9</v>
@@ -14397,10 +14523,10 @@
         <v>2.14</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>3.11</v>
+        <v>2.76</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>2.61</v>
+        <v>2.32</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -14426,7 +14552,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10303</v>
+        <v>9558</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.9</v>
@@ -14441,10 +14567,10 @@
         <v>2.78</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>3.17</v>
+        <v>2.88</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -14470,7 +14596,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>11036</v>
+        <v>10282</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.98</v>
@@ -14485,10 +14611,10 @@
         <v>3.51</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="L18" s="9" t="n"/>
     </row>
@@ -14514,7 +14640,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>129122</v>
+        <v>120289</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>1.87</v>
@@ -14529,10 +14655,10 @@
         <v>1.48</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -14558,7 +14684,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>77469</v>
+        <v>73126</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>2.28</v>
@@ -14573,10 +14699,10 @@
         <v>1.93</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -14602,7 +14728,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>102564</v>
+        <v>97175</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>1.73</v>
@@ -14617,10 +14743,10 @@
         <v>1.73</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -14646,7 +14772,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>284176</v>
+        <v>269518</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>2.21</v>
@@ -14661,10 +14787,10 @@
         <v>2.78</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -14690,7 +14816,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11545</v>
+        <v>11220</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.86</v>
@@ -14705,10 +14831,10 @@
         <v>1.07</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -14734,7 +14860,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>62437</v>
+        <v>56078</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>1.26</v>
@@ -14749,10 +14875,10 @@
         <v>7.21</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>3.86</v>
+        <v>3.46</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="L24" s="9" t="n"/>
     </row>
@@ -14778,7 +14904,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>810</v>
+        <v>775</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>1.24</v>
@@ -14822,7 +14948,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>35342</v>
+        <v>33829</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.32</v>
@@ -14837,10 +14963,10 @@
         <v>1.45</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -14866,7 +14992,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>35910</v>
+        <v>33190</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1.3</v>
@@ -14881,10 +15007,10 @@
         <v>3.66</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -14910,7 +15036,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4738</v>
+        <v>4990</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.34</v>
@@ -14925,10 +15051,10 @@
         <v>1.25</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -14954,25 +15080,25 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4390</v>
+        <v>4466</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -14998,7 +15124,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.19</v>
@@ -15038,7 +15164,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>372346</v>
+        <v>378716</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>2.08</v>
@@ -15053,10 +15179,10 @@
         <v>3.94</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>4.7</v>
+        <v>4.78</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>4.24</v>
+        <v>4.3</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -15082,7 +15208,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>170411</v>
+        <v>187497</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>2.31</v>
@@ -15097,10 +15223,10 @@
         <v>2.79</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>4.14</v>
+        <v>4.56</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>3.83</v>
+        <v>4.21</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -15126,7 +15252,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>14507</v>
+        <v>17886</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.92</v>
@@ -15141,10 +15267,10 @@
         <v>0.63</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.79</v>
+        <v>0.98</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -15170,7 +15296,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>41853</v>
+        <v>43220</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -15214,7 +15340,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>7736</v>
+        <v>8139</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -15230,10 +15356,10 @@
         <v>0.8</v>
       </c>
       <c r="K35" s="9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L35" s="9" t="n">
         <v>0.84</v>
-      </c>
-      <c r="L35" s="9" t="n">
-        <v>0.82</v>
       </c>
     </row>
     <row r="36">
@@ -15258,7 +15384,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>73844</v>
+        <v>74085</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -15302,7 +15428,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>26125</v>
+        <v>27442</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1.66</v>
@@ -15317,10 +15443,10 @@
         <v>2.17</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -15346,7 +15472,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>13850</v>
+        <v>14276</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.64</v>
@@ -15361,10 +15487,10 @@
         <v>1.35</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -15390,7 +15516,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.49</v>
@@ -15405,7 +15531,7 @@
         <v>0.59</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>0.46</v>
@@ -15434,7 +15560,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.32</v>
@@ -15474,7 +15600,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.5</v>
@@ -15514,7 +15640,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>65005</v>
+        <v>63718</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>2.12</v>
@@ -15529,10 +15655,10 @@
         <v>3.17</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>3.66</v>
+        <v>3.59</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -15995,7 +16121,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G6" s="17" t="n"/>
+      <c r="G6" s="17" t="n">
+        <v>436500</v>
+      </c>
       <c r="H6" s="17" t="n">
         <v>31175.2</v>
       </c>
@@ -16012,17 +16140,17 @@
         <v>12097690124766.46</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>14.82</v>
+        <v>14.11</v>
       </c>
       <c r="N6" s="17" t="n"/>
       <c r="O6" s="17" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="P6" s="17" t="n">
         <v>30.98</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="R6" s="17" t="inlineStr">
         <is>
@@ -16066,7 +16194,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G7" s="17" t="n"/>
+      <c r="G7" s="17" t="n">
+        <v>436500</v>
+      </c>
       <c r="H7" s="17" t="n">
         <v>35696.77</v>
       </c>
@@ -16082,16 +16212,18 @@
       <c r="L7" s="18" t="n">
         <v>15253493850623.39</v>
       </c>
-      <c r="M7" s="17" t="n"/>
+      <c r="M7" s="17" t="n">
+        <v>12.23</v>
+      </c>
       <c r="N7" s="17" t="n"/>
       <c r="O7" s="17" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="P7" s="17" t="n">
         <v>27.39</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="R7" s="17" t="inlineStr">
         <is>
@@ -16484,7 +16616,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G13" s="17" t="n"/>
+      <c r="G13" s="17" t="n">
+        <v>86800</v>
+      </c>
       <c r="H13" s="17" t="n">
         <v>6366.76</v>
       </c>
@@ -16501,17 +16635,17 @@
         <v>8121009511148.494</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>13.78</v>
+        <v>13.46</v>
       </c>
       <c r="N13" s="17" t="n"/>
       <c r="O13" s="17" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="P13" s="17" t="n">
         <v>27.32</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="R13" s="17" t="inlineStr">
         <is>
@@ -16555,7 +16689,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G14" s="17" t="n"/>
+      <c r="G14" s="17" t="n">
+        <v>86800</v>
+      </c>
       <c r="H14" s="17" t="n">
         <v>6407.04</v>
       </c>
@@ -16571,16 +16707,18 @@
       <c r="L14" s="18" t="n">
         <v>10084109156939.35</v>
       </c>
-      <c r="M14" s="17" t="n"/>
+      <c r="M14" s="17" t="n">
+        <v>13.55</v>
+      </c>
       <c r="N14" s="17" t="n"/>
       <c r="O14" s="17" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="P14" s="17" t="n">
         <v>21.57</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="R14" s="17" t="inlineStr">
         <is>
@@ -16971,34 +17109,36 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G20" s="17" t="n"/>
+      <c r="G20" s="17" t="n">
+        <v>21400</v>
+      </c>
       <c r="H20" s="17" t="n">
-        <v>1187.67</v>
+        <v>1183.96</v>
       </c>
       <c r="I20" s="17" t="n">
-        <v>6045.06</v>
+        <v>6041.35</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>12893142220000</v>
+        <v>12886285050000</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>1014448739155.678</v>
+        <v>1011283343129.024</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>5163388048795.679</v>
+        <v>5160222652769.023</v>
       </c>
       <c r="M20" s="17" t="n">
-        <v>19.95</v>
+        <v>20.37</v>
       </c>
       <c r="N20" s="17" t="n"/>
       <c r="O20" s="17" t="n">
-        <v>3.54</v>
+        <v>3.61</v>
       </c>
       <c r="P20" s="17" t="n">
         <v>20.18</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R20" s="17" t="inlineStr">
         <is>
@@ -17042,32 +17182,36 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G21" s="17" t="n"/>
+      <c r="G21" s="17" t="n">
+        <v>21400</v>
+      </c>
       <c r="H21" s="17" t="n">
-        <v>1710.15</v>
+        <v>1703.54</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>7755.21</v>
+        <v>7744.89</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>14782416070000</v>
+        <v>14798025900000</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>1460728238033.814</v>
+        <v>1455080851728.347</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>6624116286829.493</v>
-      </c>
-      <c r="M21" s="17" t="n"/>
+        <v>6615303504497.371</v>
+      </c>
+      <c r="M21" s="17" t="n">
+        <v>12.56</v>
+      </c>
       <c r="N21" s="17" t="n"/>
       <c r="O21" s="17" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="P21" s="17" t="n">
-        <v>24.78</v>
+        <v>24.71</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="R21" s="17" t="inlineStr">
         <is>
@@ -17462,7 +17606,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G27" s="17" t="n"/>
+      <c r="G27" s="17" t="n">
+        <v>348500</v>
+      </c>
       <c r="H27" s="17" t="n">
         <v>51760.25</v>
       </c>
@@ -17479,17 +17625,17 @@
         <v>16263290290871.05</v>
       </c>
       <c r="M27" s="17" t="n">
-        <v>6.4</v>
+        <v>6.21</v>
       </c>
       <c r="N27" s="17" t="n"/>
       <c r="O27" s="17" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="P27" s="17" t="n">
         <v>27.18</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="R27" s="17" t="inlineStr">
         <is>
@@ -17533,7 +17679,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G28" s="17" t="n"/>
+      <c r="G28" s="17" t="n">
+        <v>348500</v>
+      </c>
       <c r="H28" s="17" t="n">
         <v>60133.68</v>
       </c>
@@ -17549,16 +17697,18 @@
       <c r="L28" s="18" t="n">
         <v>19722136500824.19</v>
       </c>
-      <c r="M28" s="17" t="n"/>
+      <c r="M28" s="17" t="n">
+        <v>5.8</v>
+      </c>
       <c r="N28" s="17" t="n"/>
       <c r="O28" s="17" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P28" s="17" t="n">
         <v>23.63</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="R28" s="17" t="inlineStr">
         <is>
@@ -17925,7 +18075,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G34" s="17" t="n"/>
+      <c r="G34" s="17" t="n">
+        <v>46950</v>
+      </c>
       <c r="H34" s="17" t="n">
         <v>7317.5</v>
       </c>
@@ -17942,17 +18094,17 @@
         <v>1363491609003.722</v>
       </c>
       <c r="M34" s="17" t="n">
-        <v>6.17</v>
+        <v>5.87</v>
       </c>
       <c r="N34" s="17" t="n"/>
       <c r="O34" s="17" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="P34" s="17" t="n">
         <v>24.95</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
@@ -17996,7 +18148,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G35" s="17" t="n"/>
+      <c r="G35" s="17" t="n">
+        <v>46950</v>
+      </c>
       <c r="H35" s="17" t="n">
         <v>7666.2</v>
       </c>
@@ -18012,16 +18166,18 @@
       <c r="L35" s="18" t="n">
         <v>1647518204706.319</v>
       </c>
-      <c r="M35" s="17" t="n"/>
+      <c r="M35" s="17" t="n">
+        <v>6.12</v>
+      </c>
       <c r="N35" s="17" t="n"/>
       <c r="O35" s="17" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="P35" s="17" t="n">
         <v>19.48</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
@@ -18412,7 +18568,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G41" s="17" t="n"/>
+      <c r="G41" s="17" t="n">
+        <v>16110</v>
+      </c>
       <c r="H41" s="17" t="n"/>
       <c r="I41" s="17" t="n"/>
       <c r="J41" s="18" t="n">
@@ -18421,11 +18579,11 @@
       <c r="K41" s="18" t="n"/>
       <c r="L41" s="18" t="n"/>
       <c r="M41" s="17" t="n">
-        <v>8.56</v>
+        <v>8.02</v>
       </c>
       <c r="N41" s="17" t="n"/>
       <c r="O41" s="17" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="P41" s="17" t="n">
         <v>24.85</v>
@@ -18473,7 +18631,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G42" s="17" t="n"/>
+      <c r="G42" s="17" t="n">
+        <v>16110</v>
+      </c>
       <c r="H42" s="17" t="n"/>
       <c r="I42" s="17" t="n"/>
       <c r="J42" s="18" t="n">
@@ -18896,13 +19056,13 @@
       <c r="M48" s="17" t="n"/>
       <c r="N48" s="17" t="n"/>
       <c r="O48" s="17" t="n">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="P48" s="17" t="n">
         <v>16.62</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -18965,13 +19125,13 @@
       <c r="M49" s="17" t="n"/>
       <c r="N49" s="17" t="n"/>
       <c r="O49" s="17" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="P49" s="17" t="n">
         <v>20</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
@@ -19348,7 +19508,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G55" s="17" t="n"/>
+      <c r="G55" s="17" t="n">
+        <v>210500</v>
+      </c>
       <c r="H55" s="17" t="n">
         <v>7767.72</v>
       </c>
@@ -19365,17 +19527,17 @@
         <v>1011902357272.74</v>
       </c>
       <c r="M55" s="17" t="n">
-        <v>28.12</v>
+        <v>26.15</v>
       </c>
       <c r="N55" s="17" t="n"/>
       <c r="O55" s="17" t="n">
-        <v>9.869999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="P55" s="17" t="n">
         <v>38.53</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>4.26</v>
+        <v>4.06</v>
       </c>
       <c r="R55" s="17" t="inlineStr">
         <is>
@@ -19419,7 +19581,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G56" s="17" t="n"/>
+      <c r="G56" s="17" t="n">
+        <v>210500</v>
+      </c>
       <c r="H56" s="17" t="n">
         <v>9452.709999999999</v>
       </c>
@@ -19435,16 +19599,18 @@
       <c r="L56" s="18" t="n">
         <v>1239682870125.395</v>
       </c>
-      <c r="M56" s="17" t="n"/>
+      <c r="M56" s="17" t="n">
+        <v>22.27</v>
+      </c>
       <c r="N56" s="17" t="n"/>
       <c r="O56" s="17" t="n">
-        <v>7.99</v>
+        <v>7.61</v>
       </c>
       <c r="P56" s="17" t="n">
         <v>37.64</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>3.7</v>
+        <v>3.53</v>
       </c>
       <c r="R56" s="17" t="inlineStr">
         <is>
@@ -19841,7 +20007,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G62" s="17" t="n"/>
+      <c r="G62" s="17" t="n">
+        <v>50200</v>
+      </c>
       <c r="H62" s="17" t="n">
         <v>3930.5</v>
       </c>
@@ -19858,17 +20026,17 @@
         <v>622240560926.5</v>
       </c>
       <c r="M62" s="17" t="n">
-        <v>13.93</v>
+        <v>12.99</v>
       </c>
       <c r="N62" s="17" t="n"/>
       <c r="O62" s="17" t="n">
-        <v>3.69</v>
+        <v>3.44</v>
       </c>
       <c r="P62" s="17" t="n">
         <v>26.46</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="R62" s="17" t="inlineStr">
         <is>
@@ -19912,7 +20080,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G63" s="17" t="n"/>
+      <c r="G63" s="17" t="n">
+        <v>50200</v>
+      </c>
       <c r="H63" s="17" t="n">
         <v>5446</v>
       </c>
@@ -19928,16 +20098,18 @@
       <c r="L63" s="18" t="n">
         <v>806976902884.5</v>
       </c>
-      <c r="M63" s="17" t="n"/>
+      <c r="M63" s="17" t="n">
+        <v>9.220000000000001</v>
+      </c>
       <c r="N63" s="17" t="n"/>
       <c r="O63" s="17" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="P63" s="17" t="n">
         <v>25.85</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="R63" s="17" t="inlineStr">
         <is>
@@ -20328,7 +20500,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G69" s="17" t="n"/>
+      <c r="G69" s="17" t="n">
+        <v>45600</v>
+      </c>
       <c r="H69" s="17" t="n">
         <v>2412.78</v>
       </c>
@@ -20345,17 +20519,17 @@
         <v>757389995184.946</v>
       </c>
       <c r="M69" s="17" t="n">
-        <v>20.27</v>
+        <v>19.15</v>
       </c>
       <c r="N69" s="17" t="n"/>
       <c r="O69" s="17" t="n">
-        <v>5.32</v>
+        <v>5.03</v>
       </c>
       <c r="P69" s="17" t="n">
         <v>30.33</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="R69" s="17" t="inlineStr">
         <is>
@@ -20399,7 +20573,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G70" s="17" t="n"/>
+      <c r="G70" s="17" t="n">
+        <v>45600</v>
+      </c>
       <c r="H70" s="17" t="n">
         <v>3462.71</v>
       </c>
@@ -20415,16 +20591,18 @@
       <c r="L70" s="18" t="n">
         <v>1046268796557.15</v>
       </c>
-      <c r="M70" s="17" t="n"/>
+      <c r="M70" s="17" t="n">
+        <v>13.17</v>
+      </c>
       <c r="N70" s="17" t="n"/>
       <c r="O70" s="17" t="n">
-        <v>3.85</v>
+        <v>3.64</v>
       </c>
       <c r="P70" s="17" t="n">
         <v>32.03</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="R70" s="17" t="inlineStr">
         <is>
@@ -20819,7 +20997,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G76" s="17" t="n"/>
+      <c r="G76" s="17" t="n">
+        <v>22550</v>
+      </c>
       <c r="H76" s="17" t="n">
         <v>2393.79</v>
       </c>
@@ -20836,17 +21016,17 @@
         <v>681678021001.8715</v>
       </c>
       <c r="M76" s="17" t="n">
-        <v>10.91</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="N76" s="17" t="n"/>
       <c r="O76" s="17" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="P76" s="17" t="n">
-        <v>18.75</v>
+        <v>18.45</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="R76" s="17" t="inlineStr">
         <is>
@@ -20890,7 +21070,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G77" s="17" t="n"/>
+      <c r="G77" s="17" t="n">
+        <v>22550</v>
+      </c>
       <c r="H77" s="17" t="n">
         <v>2818.93</v>
       </c>
@@ -20906,16 +21088,18 @@
       <c r="L77" s="18" t="n">
         <v>801213744014.1482</v>
       </c>
-      <c r="M77" s="17" t="n"/>
+      <c r="M77" s="17" t="n">
+        <v>8</v>
+      </c>
       <c r="N77" s="17" t="n"/>
       <c r="O77" s="17" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="P77" s="17" t="n">
         <v>19.15</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="R77" s="17" t="inlineStr">
         <is>
@@ -21312,7 +21496,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G83" s="17" t="n"/>
+      <c r="G83" s="17" t="n">
+        <v>17160</v>
+      </c>
       <c r="H83" s="17" t="n">
         <v>2442</v>
       </c>
@@ -21329,17 +21515,17 @@
         <v>331992443278</v>
       </c>
       <c r="M83" s="17" t="n">
-        <v>6.55</v>
+        <v>5.92</v>
       </c>
       <c r="N83" s="17" t="n"/>
       <c r="O83" s="17" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="P83" s="17" t="n">
-        <v>28.53</v>
+        <v>29.46</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="R83" s="17" t="inlineStr">
         <is>
@@ -21383,7 +21569,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G84" s="17" t="n"/>
+      <c r="G84" s="17" t="n">
+        <v>17160</v>
+      </c>
       <c r="H84" s="17" t="n">
         <v>2901</v>
       </c>
@@ -21399,16 +21587,18 @@
       <c r="L84" s="18" t="n">
         <v>418828450507</v>
       </c>
-      <c r="M84" s="17" t="n"/>
+      <c r="M84" s="17" t="n">
+        <v>5.92</v>
+      </c>
       <c r="N84" s="17" t="n"/>
       <c r="O84" s="17" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="P84" s="17" t="n">
         <v>23.13</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="R84" s="17" t="inlineStr">
         <is>
@@ -21805,7 +21995,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G90" s="17" t="n"/>
+      <c r="G90" s="17" t="n">
+        <v>126500</v>
+      </c>
       <c r="H90" s="17" t="n">
         <v>2345.72</v>
       </c>
@@ -21822,17 +22014,17 @@
         <v>1995963043226.628</v>
       </c>
       <c r="M90" s="17" t="n">
-        <v>53.78</v>
+        <v>50.51</v>
       </c>
       <c r="N90" s="17" t="n"/>
       <c r="O90" s="17" t="n">
-        <v>6.36</v>
+        <v>5.98</v>
       </c>
       <c r="P90" s="17" t="n">
         <v>12.47</v>
       </c>
       <c r="Q90" s="17" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R90" s="17" t="inlineStr">
         <is>
@@ -21876,7 +22068,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G91" s="17" t="n"/>
+      <c r="G91" s="17" t="n">
+        <v>126500</v>
+      </c>
       <c r="H91" s="17" t="n">
         <v>4555.93</v>
       </c>
@@ -21892,16 +22086,18 @@
       <c r="L91" s="18" t="n">
         <v>2317972672631.471</v>
       </c>
-      <c r="M91" s="17" t="n"/>
+      <c r="M91" s="17" t="n">
+        <v>27.77</v>
+      </c>
       <c r="N91" s="17" t="n"/>
       <c r="O91" s="17" t="n">
-        <v>5.6</v>
+        <v>5.32</v>
       </c>
       <c r="P91" s="17" t="n">
         <v>20.59</v>
       </c>
       <c r="Q91" s="17" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="R91" s="17" t="inlineStr">
         <is>
@@ -22298,34 +22494,36 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G97" s="17" t="n"/>
+      <c r="G97" s="17" t="n">
+        <v>1055000</v>
+      </c>
       <c r="H97" s="17" t="n">
-        <v>47335.29</v>
+        <v>48183.27</v>
       </c>
       <c r="I97" s="17" t="n">
-        <v>227413.59</v>
+        <v>228115.29</v>
       </c>
       <c r="J97" s="18" t="n">
-        <v>32193561600000</v>
+        <v>32193552050000</v>
       </c>
       <c r="K97" s="18" t="n">
-        <v>2435343300128.52</v>
+        <v>2478970997723.124</v>
       </c>
       <c r="L97" s="18" t="n">
-        <v>11700153348856.35</v>
+        <v>11736255268615.88</v>
       </c>
       <c r="M97" s="17" t="n">
-        <v>25.83</v>
+        <v>23.22</v>
       </c>
       <c r="N97" s="17" t="n"/>
       <c r="O97" s="17" t="n">
-        <v>5</v>
+        <v>4.52</v>
       </c>
       <c r="P97" s="17" t="n">
-        <v>21.39</v>
+        <v>21.52</v>
       </c>
       <c r="Q97" s="17" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="R97" s="17" t="inlineStr">
         <is>
@@ -22369,32 +22567,36 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G98" s="17" t="n"/>
+      <c r="G98" s="17" t="n">
+        <v>1055000</v>
+      </c>
       <c r="H98" s="17" t="n">
-        <v>58607.21</v>
+        <v>59324.66</v>
       </c>
       <c r="I98" s="17" t="n">
-        <v>275911.06</v>
+        <v>277206.44</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>34591903430000</v>
+        <v>34591886820000</v>
       </c>
       <c r="K98" s="18" t="n">
-        <v>3015270179805.42</v>
+        <v>3052181649716.928</v>
       </c>
       <c r="L98" s="18" t="n">
-        <v>14195289422645.33</v>
-      </c>
-      <c r="M98" s="17" t="n"/>
+        <v>14261935583756.64</v>
+      </c>
+      <c r="M98" s="17" t="n">
+        <v>17.78</v>
+      </c>
       <c r="N98" s="17" t="n"/>
       <c r="O98" s="17" t="n">
-        <v>4.19</v>
+        <v>3.81</v>
       </c>
       <c r="P98" s="17" t="n">
-        <v>23.29</v>
+        <v>23.48</v>
       </c>
       <c r="Q98" s="17" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="R98" s="17" t="inlineStr">
         <is>
@@ -22791,7 +22993,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G104" s="17" t="n"/>
+      <c r="G104" s="17" t="n">
+        <v>652000</v>
+      </c>
       <c r="H104" s="17" t="n">
         <v>16754.84</v>
       </c>
@@ -22808,17 +23012,17 @@
         <v>1713760610815.525</v>
       </c>
       <c r="M104" s="17" t="n">
-        <v>44.85</v>
+        <v>40.64</v>
       </c>
       <c r="N104" s="17" t="n"/>
       <c r="O104" s="17" t="n">
-        <v>9.359999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="P104" s="17" t="n">
         <v>22.68</v>
       </c>
       <c r="Q104" s="17" t="n">
-        <v>3.11</v>
+        <v>2.76</v>
       </c>
       <c r="R104" s="17" t="inlineStr">
         <is>
@@ -22862,7 +23066,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G105" s="17" t="n"/>
+      <c r="G105" s="17" t="n">
+        <v>652000</v>
+      </c>
       <c r="H105" s="17" t="n">
         <v>24122.73</v>
       </c>
@@ -22878,16 +23084,18 @@
       <c r="L105" s="18" t="n">
         <v>2122160071223.144</v>
       </c>
-      <c r="M105" s="17" t="n"/>
+      <c r="M105" s="17" t="n">
+        <v>27.03</v>
+      </c>
       <c r="N105" s="17" t="n"/>
       <c r="O105" s="17" t="n">
-        <v>7.56</v>
+        <v>6.71</v>
       </c>
       <c r="P105" s="17" t="n">
         <v>27.48</v>
       </c>
       <c r="Q105" s="17" t="n">
-        <v>2.61</v>
+        <v>2.32</v>
       </c>
       <c r="R105" s="17" t="inlineStr">
         <is>
@@ -23282,7 +23490,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G111" s="17" t="n"/>
+      <c r="G111" s="17" t="n">
+        <v>68800</v>
+      </c>
       <c r="H111" s="17" t="n">
         <v>790.5</v>
       </c>
@@ -23299,17 +23509,17 @@
         <v>4924009921049.891</v>
       </c>
       <c r="M111" s="17" t="n">
-        <v>102.89</v>
+        <v>92.31</v>
       </c>
       <c r="N111" s="17" t="n"/>
       <c r="O111" s="17" t="n">
-        <v>2.59</v>
+        <v>2.32</v>
       </c>
       <c r="P111" s="17" t="n">
         <v>2.7</v>
       </c>
       <c r="Q111" s="17" t="n">
-        <v>3.17</v>
+        <v>2.88</v>
       </c>
       <c r="R111" s="17" t="inlineStr">
         <is>
@@ -23353,7 +23563,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G112" s="17" t="n"/>
+      <c r="G112" s="17" t="n">
+        <v>68800</v>
+      </c>
       <c r="H112" s="17" t="n">
         <v>2329</v>
       </c>
@@ -23369,16 +23581,18 @@
       <c r="L112" s="18" t="n">
         <v>5144333066583.118</v>
       </c>
-      <c r="M112" s="17" t="n"/>
+      <c r="M112" s="17" t="n">
+        <v>29.54</v>
+      </c>
       <c r="N112" s="17" t="n"/>
       <c r="O112" s="17" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="P112" s="17" t="n">
         <v>8.65</v>
       </c>
       <c r="Q112" s="17" t="n">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="R112" s="17" t="inlineStr">
         <is>
@@ -23775,7 +23989,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G118" s="17" t="n"/>
+      <c r="G118" s="17" t="n">
+        <v>126800</v>
+      </c>
       <c r="H118" s="17" t="n">
         <v>8113.99</v>
       </c>
@@ -23792,17 +24008,17 @@
         <v>3892781692167.539</v>
       </c>
       <c r="M118" s="17" t="n">
-        <v>16.96</v>
+        <v>15.41</v>
       </c>
       <c r="N118" s="17" t="n"/>
       <c r="O118" s="17" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P118" s="17" t="n">
-        <v>25.69</v>
+        <v>25.7</v>
       </c>
       <c r="Q118" s="17" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="R118" s="17" t="inlineStr">
         <is>
@@ -23846,32 +24062,36 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G119" s="17" t="n"/>
+      <c r="G119" s="17" t="n">
+        <v>126800</v>
+      </c>
       <c r="H119" s="17" t="n">
-        <v>11630.63</v>
+        <v>11310.84</v>
       </c>
       <c r="I119" s="17" t="n">
-        <v>46354.42</v>
+        <v>46060.57</v>
       </c>
       <c r="J119" s="18" t="n">
-        <v>8253101590000</v>
+        <v>8139996120000</v>
       </c>
       <c r="K119" s="18" t="n">
-        <v>1269393736376.883</v>
+        <v>1234491449925.292</v>
       </c>
       <c r="L119" s="18" t="n">
-        <v>5059227604140.619</v>
-      </c>
-      <c r="M119" s="17" t="n"/>
+        <v>5027155892910.839</v>
+      </c>
+      <c r="M119" s="17" t="n">
+        <v>11.21</v>
+      </c>
       <c r="N119" s="17" t="n"/>
       <c r="O119" s="17" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P119" s="17" t="n">
-        <v>28.36</v>
+        <v>27.68</v>
       </c>
       <c r="Q119" s="17" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="R119" s="17" t="inlineStr">
         <is>
@@ -24269,7 +24489,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>563.85</v>
+        <v>525.28</v>
       </c>
       <c r="H125" s="17" t="n">
         <v>30.46</v>
@@ -24287,17 +24507,17 @@
         <v>10186173464.337</v>
       </c>
       <c r="M125" s="17" t="n">
-        <v>18.51</v>
+        <v>17.24</v>
       </c>
       <c r="N125" s="17" t="n"/>
       <c r="O125" s="17" t="n">
-        <v>12.68</v>
+        <v>11.81</v>
       </c>
       <c r="P125" s="17" t="n">
         <v>82.53</v>
       </c>
       <c r="Q125" s="17" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="R125" s="17" t="inlineStr">
         <is>
@@ -24342,7 +24562,7 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>563.85</v>
+        <v>525.28</v>
       </c>
       <c r="H126" s="17" t="n">
         <v>32.72</v>
@@ -24360,17 +24580,17 @@
         <v>13908153121.999</v>
       </c>
       <c r="M126" s="17" t="n">
-        <v>17.23</v>
+        <v>16.05</v>
       </c>
       <c r="N126" s="17" t="n"/>
       <c r="O126" s="17" t="n">
-        <v>9.279999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="P126" s="17" t="n">
         <v>62.2</v>
       </c>
       <c r="Q126" s="17" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="R126" s="17" t="inlineStr">
         <is>
@@ -24768,7 +24988,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>545.5700000000001</v>
+        <v>514.98</v>
       </c>
       <c r="H132" s="17" t="n">
         <v>28.99</v>
@@ -24786,17 +25006,17 @@
         <v>19560796522.68309</v>
       </c>
       <c r="M132" s="17" t="n">
-        <v>18.82</v>
+        <v>17.76</v>
       </c>
       <c r="N132" s="17" t="n"/>
       <c r="O132" s="17" t="n">
-        <v>3.96</v>
+        <v>3.74</v>
       </c>
       <c r="P132" s="17" t="n">
         <v>22.72</v>
       </c>
       <c r="Q132" s="17" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="R132" s="17" t="inlineStr">
         <is>
@@ -24841,7 +25061,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>545.5700000000001</v>
+        <v>514.98</v>
       </c>
       <c r="H133" s="17" t="n">
         <v>30.44</v>
@@ -24859,17 +25079,17 @@
         <v>22591656618.88455</v>
       </c>
       <c r="M133" s="17" t="n">
-        <v>17.92</v>
+        <v>16.92</v>
       </c>
       <c r="N133" s="17" t="n"/>
       <c r="O133" s="17" t="n">
-        <v>3.43</v>
+        <v>3.24</v>
       </c>
       <c r="P133" s="17" t="n">
         <v>20.51</v>
       </c>
       <c r="Q133" s="17" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="R133" s="17" t="inlineStr">
         <is>
@@ -25267,7 +25487,7 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>379.32</v>
+        <v>359.39</v>
       </c>
       <c r="H139" s="17" t="n">
         <v>17</v>
@@ -25285,17 +25505,17 @@
         <v>28486442015.57588</v>
       </c>
       <c r="M139" s="17" t="n">
-        <v>22.31</v>
+        <v>21.14</v>
       </c>
       <c r="N139" s="17" t="n"/>
       <c r="O139" s="17" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="P139" s="17" t="n">
         <v>16.99</v>
       </c>
       <c r="Q139" s="17" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="R139" s="17" t="inlineStr">
         <is>
@@ -25340,7 +25560,7 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>379.32</v>
+        <v>359.39</v>
       </c>
       <c r="H140" s="17" t="n">
         <v>18.59</v>
@@ -25358,17 +25578,17 @@
         <v>31619750267.15752</v>
       </c>
       <c r="M140" s="17" t="n">
-        <v>20.4</v>
+        <v>19.33</v>
       </c>
       <c r="N140" s="17" t="n"/>
       <c r="O140" s="17" t="n">
-        <v>3.24</v>
+        <v>3.07</v>
       </c>
       <c r="P140" s="17" t="n">
         <v>16.73</v>
       </c>
       <c r="Q140" s="17" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="R140" s="17" t="inlineStr">
         <is>
@@ -25766,7 +25986,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>211.71</v>
+        <v>200.79</v>
       </c>
       <c r="H146" s="17" t="n">
         <v>7.24</v>
@@ -25784,17 +26004,17 @@
         <v>70225512519.7807</v>
       </c>
       <c r="M146" s="17" t="n">
-        <v>29.23</v>
+        <v>27.72</v>
       </c>
       <c r="N146" s="17" t="n"/>
       <c r="O146" s="17" t="n">
-        <v>4.05</v>
+        <v>3.84</v>
       </c>
       <c r="P146" s="17" t="n">
         <v>14.35</v>
       </c>
       <c r="Q146" s="17" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="R146" s="17" t="inlineStr">
         <is>
@@ -25839,7 +26059,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>211.71</v>
+        <v>200.79</v>
       </c>
       <c r="H147" s="17" t="n">
         <v>7.86</v>
@@ -25857,17 +26077,17 @@
         <v>75627625676.04219</v>
       </c>
       <c r="M147" s="17" t="n">
-        <v>26.95</v>
+        <v>25.56</v>
       </c>
       <c r="N147" s="17" t="n"/>
       <c r="O147" s="17" t="n">
-        <v>3.76</v>
+        <v>3.56</v>
       </c>
       <c r="P147" s="17" t="n">
         <v>14.46</v>
       </c>
       <c r="Q147" s="17" t="n">
-        <v>2.75</v>
+        <v>2.61</v>
       </c>
       <c r="R147" s="17" t="inlineStr">
         <is>
@@ -26265,7 +26485,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>294.21</v>
+        <v>285.93</v>
       </c>
       <c r="H153" s="17" t="n">
         <v>18.51</v>
@@ -26283,17 +26503,17 @@
         <v>5561910169.971308</v>
       </c>
       <c r="M153" s="17" t="n">
-        <v>15.89</v>
+        <v>15.45</v>
       </c>
       <c r="N153" s="17" t="n"/>
       <c r="O153" s="17" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="P153" s="17" t="n">
         <v>13.66</v>
       </c>
       <c r="Q153" s="17" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="R153" s="17" t="inlineStr">
         <is>
@@ -26338,7 +26558,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>294.21</v>
+        <v>285.93</v>
       </c>
       <c r="H154" s="17" t="n">
         <v>20.83</v>
@@ -26356,17 +26576,17 @@
         <v>6112146741.053395</v>
       </c>
       <c r="M154" s="17" t="n">
-        <v>14.12</v>
+        <v>13.72</v>
       </c>
       <c r="N154" s="17" t="n"/>
       <c r="O154" s="17" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="P154" s="17" t="n">
         <v>14.01</v>
       </c>
       <c r="Q154" s="17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="R154" s="17" t="inlineStr">
         <is>
@@ -26765,30 +26985,30 @@
       </c>
       <c r="G160" s="17" t="n"/>
       <c r="H160" s="17" t="n">
-        <v>37.14</v>
+        <v>37.24</v>
       </c>
       <c r="I160" s="17" t="n">
-        <v>129.97</v>
+        <v>130.03</v>
       </c>
       <c r="J160" s="18" t="n">
-        <v>13968855280</v>
+        <v>13961205280</v>
       </c>
       <c r="K160" s="18" t="n">
-        <v>1704045312.3356</v>
+        <v>1708828409.7131</v>
       </c>
       <c r="L160" s="18" t="n">
-        <v>5963050116.0019</v>
+        <v>5965722432.506709</v>
       </c>
       <c r="M160" s="17" t="n"/>
       <c r="N160" s="17" t="n"/>
       <c r="O160" s="17" t="n">
-        <v>9.039999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="P160" s="17" t="n">
-        <v>31.06</v>
+        <v>31.14</v>
       </c>
       <c r="Q160" s="17" t="n">
-        <v>3.86</v>
+        <v>3.46</v>
       </c>
       <c r="R160" s="17" t="inlineStr">
         <is>
@@ -26834,30 +27054,30 @@
       </c>
       <c r="G161" s="17" t="n"/>
       <c r="H161" s="17" t="n">
-        <v>53.51</v>
+        <v>53.68</v>
       </c>
       <c r="I161" s="17" t="n">
-        <v>159.86</v>
+        <v>160.02</v>
       </c>
       <c r="J161" s="18" t="n">
-        <v>18732966500</v>
+        <v>18701268180</v>
       </c>
       <c r="K161" s="18" t="n">
-        <v>2455049410.7009</v>
+        <v>2462837715.5434</v>
       </c>
       <c r="L161" s="18" t="n">
-        <v>7334686221.760492</v>
+        <v>7341709864.180807</v>
       </c>
       <c r="M161" s="17" t="n"/>
       <c r="N161" s="17" t="n"/>
       <c r="O161" s="17" t="n">
-        <v>7.35</v>
+        <v>6.57</v>
       </c>
       <c r="P161" s="17" t="n">
-        <v>36.92</v>
+        <v>37.01</v>
       </c>
       <c r="Q161" s="17" t="n">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="R161" s="17" t="inlineStr">
         <is>
@@ -27273,7 +27493,7 @@
       <c r="M167" s="17" t="n"/>
       <c r="N167" s="17" t="n"/>
       <c r="O167" s="17" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="P167" s="17" t="n">
         <v>19.84</v>
@@ -27764,13 +27984,13 @@
       <c r="M174" s="17" t="n"/>
       <c r="N174" s="17" t="n"/>
       <c r="O174" s="17" t="n">
-        <v>2.91</v>
+        <v>2.78</v>
       </c>
       <c r="P174" s="17" t="n">
         <v>13.7</v>
       </c>
       <c r="Q174" s="17" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="R174" s="17" t="inlineStr">
         <is>
@@ -27833,13 +28053,13 @@
       <c r="M175" s="17" t="n"/>
       <c r="N175" s="17" t="n"/>
       <c r="O175" s="17" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="P175" s="17" t="n">
         <v>14.91</v>
       </c>
       <c r="Q175" s="17" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="R175" s="17" t="inlineStr">
         <is>
@@ -28238,30 +28458,30 @@
       </c>
       <c r="G181" s="17" t="n"/>
       <c r="H181" s="17" t="n">
-        <v>14.91</v>
+        <v>14.9</v>
       </c>
       <c r="I181" s="17" t="n">
-        <v>92.83</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="J181" s="18" t="n">
-        <v>97802372670</v>
+        <v>97824460000</v>
       </c>
       <c r="K181" s="18" t="n">
-        <v>8036815422.23196</v>
+        <v>8030719972.51368</v>
       </c>
       <c r="L181" s="18" t="n">
-        <v>50027452520.55033</v>
+        <v>50022377449.11489</v>
       </c>
       <c r="M181" s="17" t="n"/>
       <c r="N181" s="17" t="n"/>
       <c r="O181" s="17" t="n">
-        <v>6.89</v>
+        <v>6.35</v>
       </c>
       <c r="P181" s="17" t="n">
-        <v>17.22</v>
+        <v>17.2</v>
       </c>
       <c r="Q181" s="17" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="R181" s="17" t="inlineStr">
         <is>
@@ -28307,30 +28527,30 @@
       </c>
       <c r="G182" s="17" t="n"/>
       <c r="H182" s="17" t="n">
-        <v>18.79</v>
+        <v>18.74</v>
       </c>
       <c r="I182" s="17" t="n">
-        <v>108.47</v>
+        <v>108.42</v>
       </c>
       <c r="J182" s="18" t="n">
-        <v>118735855860</v>
+        <v>118685164060</v>
       </c>
       <c r="K182" s="18" t="n">
-        <v>10125145598.65764</v>
+        <v>10100122457.1528</v>
       </c>
       <c r="L182" s="18" t="n">
-        <v>58457648745.99268</v>
+        <v>58431739406.94032</v>
       </c>
       <c r="M182" s="17" t="n"/>
       <c r="N182" s="17" t="n"/>
       <c r="O182" s="17" t="n">
-        <v>5.89</v>
+        <v>5.43</v>
       </c>
       <c r="P182" s="17" t="n">
-        <v>18.67</v>
+        <v>18.63</v>
       </c>
       <c r="Q182" s="17" t="n">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="R182" s="17" t="inlineStr">
         <is>
@@ -28727,7 +28947,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G188" s="17" t="n"/>
+      <c r="G188" s="17" t="n">
+        <v>140000</v>
+      </c>
       <c r="H188" s="17" t="n">
         <v>13470</v>
       </c>
@@ -28744,17 +28966,17 @@
         <v>2419672871894.003</v>
       </c>
       <c r="M188" s="17" t="n">
-        <v>11.11</v>
+        <v>11.01</v>
       </c>
       <c r="N188" s="17" t="n"/>
       <c r="O188" s="17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P188" s="17" t="n">
         <v>16.32</v>
       </c>
       <c r="Q188" s="17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="R188" s="17" t="inlineStr">
         <is>
@@ -28798,7 +29020,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G189" s="17" t="n"/>
+      <c r="G189" s="17" t="n">
+        <v>140000</v>
+      </c>
       <c r="H189" s="17" t="n">
         <v>14842.75</v>
       </c>
@@ -28814,16 +29038,18 @@
       <c r="L189" s="18" t="n">
         <v>3096745015201.536</v>
       </c>
-      <c r="M189" s="17" t="n"/>
+      <c r="M189" s="17" t="n">
+        <v>9.43</v>
+      </c>
       <c r="N189" s="17" t="n"/>
       <c r="O189" s="17" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="P189" s="17" t="n">
         <v>25.82</v>
       </c>
       <c r="Q189" s="17" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="R189" s="17" t="inlineStr">
         <is>
@@ -28939,19 +29165,19 @@
         <v>5024387667000</v>
       </c>
       <c r="M191" s="7" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="N191" s="7" t="n">
-        <v>0.68</v>
+        <v>3.59</v>
       </c>
       <c r="O191" s="7" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P191" s="7" t="n">
         <v>12.82</v>
       </c>
       <c r="Q191" s="7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R191" s="7" t="inlineStr">
         <is>
@@ -29014,19 +29240,19 @@
         <v>5954812811000</v>
       </c>
       <c r="M192" s="7" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="N192" s="7" t="n">
-        <v>0.01</v>
+        <v>3.14</v>
       </c>
       <c r="O192" s="7" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="P192" s="7" t="n">
         <v>16.79</v>
       </c>
       <c r="Q192" s="7" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="R192" s="7" t="inlineStr">
         <is>
@@ -29089,19 +29315,19 @@
         <v>6894504330000</v>
       </c>
       <c r="M193" s="7" t="n">
-        <v>0.01</v>
+        <v>7.35</v>
       </c>
       <c r="N193" s="7" t="n">
-        <v>0.16</v>
+        <v>3.61</v>
       </c>
       <c r="O193" s="7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="P193" s="7" t="n">
         <v>8.77</v>
       </c>
       <c r="Q193" s="7" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="R193" s="7" t="inlineStr">
         <is>
@@ -29164,19 +29390,19 @@
         <v>7191120447000</v>
       </c>
       <c r="M194" s="7" t="n">
-        <v>0.01</v>
+        <v>13.73</v>
       </c>
       <c r="N194" s="7" t="n">
-        <v>-0.28</v>
+        <v>5.3</v>
       </c>
       <c r="O194" s="7" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="P194" s="7" t="n">
         <v>5.71</v>
       </c>
       <c r="Q194" s="7" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="R194" s="7" t="inlineStr">
         <is>
@@ -29220,7 +29446,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G195" s="17" t="n"/>
+      <c r="G195" s="17" t="n">
+        <v>62800</v>
+      </c>
       <c r="H195" s="17" t="n">
         <v>6179.71</v>
       </c>
@@ -29237,17 +29465,17 @@
         <v>7589662196632.624</v>
       </c>
       <c r="M195" s="17" t="n">
-        <v>10.75</v>
+        <v>10.7</v>
       </c>
       <c r="N195" s="17" t="n"/>
       <c r="O195" s="17" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="P195" s="17" t="n">
         <v>7.52</v>
       </c>
       <c r="Q195" s="17" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="R195" s="17" t="inlineStr">
         <is>
@@ -29291,7 +29519,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G196" s="17" t="n"/>
+      <c r="G196" s="17" t="n">
+        <v>62800</v>
+      </c>
       <c r="H196" s="17" t="n">
         <v>6625.59</v>
       </c>
@@ -29307,16 +29537,18 @@
       <c r="L196" s="18" t="n">
         <v>8016959738234.411</v>
       </c>
-      <c r="M196" s="17" t="n"/>
+      <c r="M196" s="17" t="n">
+        <v>9.48</v>
+      </c>
       <c r="N196" s="17" t="n"/>
       <c r="O196" s="17" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="P196" s="17" t="n">
         <v>8.130000000000001</v>
       </c>
       <c r="Q196" s="17" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="R196" s="17" t="inlineStr">
         <is>
@@ -29709,7 +29941,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G202" s="17" t="n"/>
+      <c r="G202" s="17" t="n">
+        <v>8400</v>
+      </c>
       <c r="H202" s="17" t="n"/>
       <c r="I202" s="17" t="n"/>
       <c r="J202" s="18" t="n">
@@ -29764,7 +29998,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G203" s="17" t="n"/>
+      <c r="G203" s="17" t="n">
+        <v>8400</v>
+      </c>
       <c r="H203" s="17" t="n"/>
       <c r="I203" s="17" t="n"/>
       <c r="J203" s="18" t="n">
@@ -30173,35 +30409,35 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>800.25</v>
+        <v>813.9400000000001</v>
       </c>
       <c r="H209" s="17" t="n">
-        <v>27.3</v>
+        <v>27.19</v>
       </c>
       <c r="I209" s="17" t="n">
-        <v>66.02</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="J209" s="18" t="n">
-        <v>79160595630</v>
+        <v>79153079140</v>
       </c>
       <c r="K209" s="18" t="n">
-        <v>12704517055.44044</v>
+        <v>12649566621.53124</v>
       </c>
       <c r="L209" s="18" t="n">
-        <v>30718072169.32038</v>
+        <v>30677414343.27097</v>
       </c>
       <c r="M209" s="17" t="n">
-        <v>29.31</v>
+        <v>29.94</v>
       </c>
       <c r="N209" s="17" t="n"/>
       <c r="O209" s="17" t="n">
-        <v>12.12</v>
+        <v>12.35</v>
       </c>
       <c r="P209" s="17" t="n">
-        <v>48.83</v>
+        <v>48.66</v>
       </c>
       <c r="Q209" s="17" t="n">
-        <v>4.7</v>
+        <v>4.78</v>
       </c>
       <c r="R209" s="17" t="inlineStr">
         <is>
@@ -30246,35 +30482,35 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>800.25</v>
+        <v>813.9400000000001</v>
       </c>
       <c r="H210" s="17" t="n">
-        <v>32.28</v>
+        <v>32.38</v>
       </c>
       <c r="I210" s="17" t="n">
-        <v>89.90000000000001</v>
+        <v>89.89</v>
       </c>
       <c r="J210" s="18" t="n">
-        <v>87860975330</v>
+        <v>88053195170</v>
       </c>
       <c r="K210" s="18" t="n">
-        <v>15020024116.01176</v>
+        <v>15064766145.85688</v>
       </c>
       <c r="L210" s="18" t="n">
-        <v>41831388012.75748</v>
+        <v>41823834814.59047</v>
       </c>
       <c r="M210" s="17" t="n">
-        <v>24.79</v>
+        <v>25.14</v>
       </c>
       <c r="N210" s="17" t="n"/>
       <c r="O210" s="17" t="n">
-        <v>8.9</v>
+        <v>9.06</v>
       </c>
       <c r="P210" s="17" t="n">
-        <v>41.41</v>
+        <v>41.56</v>
       </c>
       <c r="Q210" s="17" t="n">
-        <v>4.24</v>
+        <v>4.3</v>
       </c>
       <c r="R210" s="17" t="inlineStr">
         <is>
@@ -30672,35 +30908,35 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>630.33</v>
+        <v>693.53</v>
       </c>
       <c r="H216" s="17" t="n">
         <v>18.13</v>
       </c>
       <c r="I216" s="17" t="n">
-        <v>107.58</v>
+        <v>107.59</v>
       </c>
       <c r="J216" s="18" t="n">
-        <v>41142734290</v>
+        <v>41117805710</v>
       </c>
       <c r="K216" s="18" t="n">
-        <v>4900495700.254</v>
+        <v>4902117812.493999</v>
       </c>
       <c r="L216" s="18" t="n">
-        <v>29085337051.0126</v>
+        <v>29086374878.3913</v>
       </c>
       <c r="M216" s="17" t="n">
-        <v>34.77</v>
+        <v>38.25</v>
       </c>
       <c r="N216" s="17" t="n"/>
       <c r="O216" s="17" t="n">
-        <v>5.86</v>
+        <v>6.45</v>
       </c>
       <c r="P216" s="17" t="n">
         <v>17.81</v>
       </c>
       <c r="Q216" s="17" t="n">
-        <v>4.14</v>
+        <v>4.56</v>
       </c>
       <c r="R216" s="17" t="inlineStr">
         <is>
@@ -30745,35 +30981,35 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>630.33</v>
+        <v>693.53</v>
       </c>
       <c r="H217" s="17" t="n">
-        <v>22.45</v>
+        <v>22.67</v>
       </c>
       <c r="I217" s="17" t="n">
-        <v>121.95</v>
+        <v>122.09</v>
       </c>
       <c r="J217" s="18" t="n">
-        <v>44542211380</v>
+        <v>44504854240</v>
       </c>
       <c r="K217" s="18" t="n">
-        <v>6070538776.568</v>
+        <v>6128726646.137199</v>
       </c>
       <c r="L217" s="18" t="n">
-        <v>32969267638.85003</v>
+        <v>33007534064.01535</v>
       </c>
       <c r="M217" s="17" t="n">
-        <v>28.07</v>
+        <v>30.59</v>
       </c>
       <c r="N217" s="17" t="n"/>
       <c r="O217" s="17" t="n">
-        <v>5.17</v>
+        <v>5.68</v>
       </c>
       <c r="P217" s="17" t="n">
-        <v>19.57</v>
+        <v>19.74</v>
       </c>
       <c r="Q217" s="17" t="n">
-        <v>3.83</v>
+        <v>4.21</v>
       </c>
       <c r="R217" s="17" t="inlineStr">
         <is>
@@ -31171,7 +31407,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>11.68</v>
+        <v>14.4</v>
       </c>
       <c r="H223" s="17" t="n">
         <v>0.45</v>
@@ -31180,26 +31416,26 @@
         <v>6.49</v>
       </c>
       <c r="J223" s="18" t="n">
-        <v>18250445930</v>
+        <v>18265234810</v>
       </c>
       <c r="K223" s="18" t="n">
-        <v>561226943.2801499</v>
+        <v>561090316.16106</v>
       </c>
       <c r="L223" s="18" t="n">
-        <v>8066736165.96809</v>
+        <v>8066654189.696636</v>
       </c>
       <c r="M223" s="17" t="n">
-        <v>25.85</v>
+        <v>31.88</v>
       </c>
       <c r="N223" s="17" t="n"/>
       <c r="O223" s="17" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="P223" s="17" t="n">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="Q223" s="17" t="n">
-        <v>0.79</v>
+        <v>0.98</v>
       </c>
       <c r="R223" s="17" t="inlineStr">
         <is>
@@ -31244,7 +31480,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>11.68</v>
+        <v>14.4</v>
       </c>
       <c r="H224" s="17" t="n">
         <v>0.6899999999999999</v>
@@ -31253,26 +31489,26 @@
         <v>6.91</v>
       </c>
       <c r="J224" s="18" t="n">
-        <v>19062563820</v>
+        <v>19047530490</v>
       </c>
       <c r="K224" s="18" t="n">
-        <v>852466278.59127</v>
+        <v>851013062.8700399</v>
       </c>
       <c r="L224" s="18" t="n">
-        <v>8578215933.122852</v>
+        <v>8577262027.41866</v>
       </c>
       <c r="M224" s="17" t="n">
-        <v>17.02</v>
+        <v>21.02</v>
       </c>
       <c r="N224" s="17" t="n"/>
       <c r="O224" s="17" t="n">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="P224" s="17" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
       <c r="Q224" s="17" t="n">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R224" s="17" t="inlineStr">
         <is>
@@ -31669,29 +31905,33 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G230" s="17" t="n"/>
+      <c r="G230" s="17" t="n">
+        <v>7493</v>
+      </c>
       <c r="H230" s="17" t="n">
-        <v>432.91</v>
+        <v>481.98</v>
       </c>
       <c r="I230" s="17" t="n">
-        <v>4130.3</v>
+        <v>4156.85</v>
       </c>
       <c r="J230" s="18" t="n">
-        <v>4334484533599</v>
+        <v>4351984533599</v>
       </c>
       <c r="K230" s="18" t="n">
-        <v>390091850394.128</v>
+        <v>434310577780.9013</v>
       </c>
       <c r="L230" s="18" t="n">
-        <v>3721807683261.386</v>
-      </c>
-      <c r="M230" s="17" t="n"/>
+        <v>3745730013893.256</v>
+      </c>
+      <c r="M230" s="17" t="n">
+        <v>15.55</v>
+      </c>
       <c r="N230" s="17" t="n"/>
       <c r="O230" s="17" t="n">
         <v>1.8</v>
       </c>
       <c r="P230" s="17" t="n">
-        <v>10.79</v>
+        <v>11.97</v>
       </c>
       <c r="Q230" s="17" t="n">
         <v>1.55</v>
@@ -31738,29 +31978,33 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G231" s="17" t="n"/>
+      <c r="G231" s="17" t="n">
+        <v>7493</v>
+      </c>
       <c r="H231" s="17" t="n">
-        <v>468.02</v>
+        <v>555.5</v>
       </c>
       <c r="I231" s="17" t="n">
-        <v>4383.5</v>
+        <v>4457.38</v>
       </c>
       <c r="J231" s="18" t="n">
-        <v>4472040978550</v>
+        <v>4490768251270</v>
       </c>
       <c r="K231" s="18" t="n">
-        <v>421729915712.8628</v>
+        <v>500563107286.091</v>
       </c>
       <c r="L231" s="18" t="n">
-        <v>3949963559227.447</v>
-      </c>
-      <c r="M231" s="17" t="n"/>
+        <v>4016534644923.769</v>
+      </c>
+      <c r="M231" s="17" t="n">
+        <v>13.49</v>
+      </c>
       <c r="N231" s="17" t="n"/>
       <c r="O231" s="17" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="P231" s="17" t="n">
-        <v>10.99</v>
+        <v>12.9</v>
       </c>
       <c r="Q231" s="17" t="n">
         <v>1.5</v>
@@ -32160,7 +32404,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G237" s="17" t="n"/>
+      <c r="G237" s="17" t="n">
+        <v>5977</v>
+      </c>
       <c r="H237" s="17" t="n">
         <v>421.59</v>
       </c>
@@ -32171,21 +32417,23 @@
         <v>1474454185460</v>
       </c>
       <c r="K237" s="18" t="n">
-        <v>89687492473.17276</v>
+        <v>89687739247.02324</v>
       </c>
       <c r="L237" s="18" t="n">
-        <v>944238433801.3171</v>
-      </c>
-      <c r="M237" s="17" t="n"/>
+        <v>944238555065.9872</v>
+      </c>
+      <c r="M237" s="17" t="n">
+        <v>14.18</v>
+      </c>
       <c r="N237" s="17" t="n"/>
       <c r="O237" s="17" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="P237" s="17" t="n">
         <v>9.73</v>
       </c>
       <c r="Q237" s="17" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="R237" s="17" t="inlineStr">
         <is>
@@ -32229,9 +32477,11 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G238" s="17" t="n"/>
+      <c r="G238" s="17" t="n">
+        <v>5977</v>
+      </c>
       <c r="H238" s="17" t="n">
-        <v>489.47</v>
+        <v>489.48</v>
       </c>
       <c r="I238" s="17" t="n">
         <v>4679.07</v>
@@ -32240,21 +32490,23 @@
         <v>1515254307950</v>
       </c>
       <c r="K238" s="18" t="n">
-        <v>104128493976.6275</v>
+        <v>104129595949.5115</v>
       </c>
       <c r="L238" s="18" t="n">
-        <v>995407175741.4319</v>
-      </c>
-      <c r="M238" s="17" t="n"/>
+        <v>995407838515.5771</v>
+      </c>
+      <c r="M238" s="17" t="n">
+        <v>12.21</v>
+      </c>
       <c r="N238" s="17" t="n"/>
       <c r="O238" s="17" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="P238" s="17" t="n">
         <v>10.74</v>
       </c>
       <c r="Q238" s="17" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="R238" s="17" t="inlineStr">
         <is>
@@ -32653,19 +32905,19 @@
       </c>
       <c r="G244" s="17" t="n"/>
       <c r="H244" s="17" t="n">
-        <v>21.62</v>
+        <v>21.56</v>
       </c>
       <c r="I244" s="17" t="n">
-        <v>98.92</v>
+        <v>98.89</v>
       </c>
       <c r="J244" s="18" t="n">
-        <v>497116610580</v>
+        <v>496510915310</v>
       </c>
       <c r="K244" s="18" t="n">
-        <v>43968724376.70679</v>
+        <v>43840637229.93564</v>
       </c>
       <c r="L244" s="18" t="n">
-        <v>201153210418.3217</v>
+        <v>201086912514.9956</v>
       </c>
       <c r="M244" s="17" t="n"/>
       <c r="N244" s="17" t="n"/>
@@ -32673,7 +32925,7 @@
         <v>3.52</v>
       </c>
       <c r="P244" s="17" t="n">
-        <v>23.17</v>
+        <v>23.11</v>
       </c>
       <c r="Q244" s="17" t="n">
         <v>1.43</v>
@@ -32722,19 +32974,19 @@
       </c>
       <c r="G245" s="17" t="n"/>
       <c r="H245" s="17" t="n">
-        <v>25.48</v>
+        <v>25.43</v>
       </c>
       <c r="I245" s="17" t="n">
-        <v>112.11</v>
+        <v>112.05</v>
       </c>
       <c r="J245" s="18" t="n">
-        <v>540390426950</v>
+        <v>540009724169</v>
       </c>
       <c r="K245" s="18" t="n">
-        <v>51803045889.77528</v>
+        <v>51713187642.18332</v>
       </c>
       <c r="L245" s="18" t="n">
-        <v>227966465416.778</v>
+        <v>227853656887.194</v>
       </c>
       <c r="M245" s="17" t="n"/>
       <c r="N245" s="17" t="n"/>
@@ -32742,7 +32994,7 @@
         <v>3.11</v>
       </c>
       <c r="P245" s="17" t="n">
-        <v>24.14</v>
+        <v>24.11</v>
       </c>
       <c r="Q245" s="17" t="n">
         <v>1.31</v>
@@ -33142,32 +33394,36 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G251" s="17" t="n"/>
+      <c r="G251" s="17" t="n">
+        <v>20</v>
+      </c>
       <c r="H251" s="17" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="I251" s="17" t="n">
-        <v>9.960000000000001</v>
+        <v>10.43</v>
       </c>
       <c r="J251" s="18" t="n">
-        <v>102780441360</v>
+        <v>103700366140</v>
       </c>
       <c r="K251" s="18" t="n">
-        <v>10734432079.84254</v>
+        <v>11027660771.33847</v>
       </c>
       <c r="L251" s="18" t="n">
-        <v>91594511352.27213</v>
-      </c>
-      <c r="M251" s="17" t="n"/>
+        <v>95898425041.84567</v>
+      </c>
+      <c r="M251" s="17" t="n">
+        <v>16.68</v>
+      </c>
       <c r="N251" s="17" t="n"/>
       <c r="O251" s="17" t="n">
         <v>1.92</v>
       </c>
       <c r="P251" s="17" t="n">
-        <v>11.93</v>
+        <v>11.97</v>
       </c>
       <c r="Q251" s="17" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="R251" s="17" t="inlineStr">
         <is>
@@ -33211,32 +33467,36 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G252" s="17" t="n"/>
+      <c r="G252" s="17" t="n">
+        <v>20</v>
+      </c>
       <c r="H252" s="17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I252" s="17" t="n">
-        <v>10.42</v>
+        <v>11.47</v>
       </c>
       <c r="J252" s="18" t="n">
-        <v>116607465970</v>
+        <v>117329033660</v>
       </c>
       <c r="K252" s="18" t="n">
-        <v>13905237409.89762</v>
+        <v>13989003900.31869</v>
       </c>
       <c r="L252" s="18" t="n">
-        <v>95821703524.881</v>
-      </c>
-      <c r="M252" s="17" t="n"/>
+        <v>105497679798.0244</v>
+      </c>
+      <c r="M252" s="17" t="n">
+        <v>13.15</v>
+      </c>
       <c r="N252" s="17" t="n"/>
       <c r="O252" s="17" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="P252" s="17" t="n">
-        <v>14.84</v>
+        <v>13.89</v>
       </c>
       <c r="Q252" s="17" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="R252" s="17" t="inlineStr">
         <is>
@@ -33633,32 +33893,36 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G258" s="17" t="n"/>
+      <c r="G258" s="17" t="n">
+        <v>8.140000000000001</v>
+      </c>
       <c r="H258" s="17" t="n">
         <v>0.72</v>
       </c>
       <c r="I258" s="17" t="n">
-        <v>5.64</v>
+        <v>5.37</v>
       </c>
       <c r="J258" s="18" t="n">
         <v>114720037870</v>
       </c>
       <c r="K258" s="18" t="n">
-        <v>8480709883.56156</v>
+        <v>8482472829.43386</v>
       </c>
       <c r="L258" s="18" t="n">
-        <v>66277605180.44487</v>
-      </c>
-      <c r="M258" s="17" t="n"/>
+        <v>63082618877.36219</v>
+      </c>
+      <c r="M258" s="17" t="n">
+        <v>11.28</v>
+      </c>
       <c r="N258" s="17" t="n"/>
       <c r="O258" s="17" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="P258" s="17" t="n">
-        <v>13.38</v>
+        <v>13.73</v>
       </c>
       <c r="Q258" s="17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="R258" s="17" t="inlineStr">
         <is>
@@ -33702,32 +33966,36 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G259" s="17" t="n"/>
+      <c r="G259" s="17" t="n">
+        <v>8.140000000000001</v>
+      </c>
       <c r="H259" s="17" t="n">
         <v>0.92</v>
       </c>
       <c r="I259" s="17" t="n">
-        <v>6.27</v>
+        <v>5.65</v>
       </c>
       <c r="J259" s="18" t="n">
         <v>131296032459</v>
       </c>
       <c r="K259" s="18" t="n">
-        <v>10838826282.35004</v>
+        <v>10839531460.69896</v>
       </c>
       <c r="L259" s="18" t="n">
-        <v>73711956127.50876</v>
-      </c>
-      <c r="M259" s="17" t="n"/>
+        <v>66433118377.05018</v>
+      </c>
+      <c r="M259" s="17" t="n">
+        <v>8.83</v>
+      </c>
       <c r="N259" s="17" t="n"/>
       <c r="O259" s="17" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="P259" s="17" t="n">
-        <v>15.49</v>
+        <v>16.74</v>
       </c>
       <c r="Q259" s="17" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="R259" s="17" t="inlineStr">
         <is>
@@ -34124,7 +34392,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G265" s="17" t="n"/>
+      <c r="G265" s="17" t="n">
+        <v>13180</v>
+      </c>
       <c r="H265" s="17" t="n">
         <v>1728</v>
       </c>
@@ -34140,16 +34410,18 @@
       <c r="L265" s="18" t="n">
         <v>328971474869.7184</v>
       </c>
-      <c r="M265" s="17" t="n"/>
+      <c r="M265" s="17" t="n">
+        <v>7.63</v>
+      </c>
       <c r="N265" s="17" t="n"/>
       <c r="O265" s="17" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P265" s="17" t="n">
         <v>11.18</v>
       </c>
       <c r="Q265" s="17" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="R265" s="17" t="inlineStr">
         <is>
@@ -34193,7 +34465,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G266" s="17" t="n"/>
+      <c r="G266" s="17" t="n">
+        <v>13180</v>
+      </c>
       <c r="H266" s="17" t="n">
         <v>2102</v>
       </c>
@@ -34209,7 +34483,9 @@
       <c r="L266" s="18" t="n">
         <v>367213567791.274</v>
       </c>
-      <c r="M266" s="17" t="n"/>
+      <c r="M266" s="17" t="n">
+        <v>6.27</v>
+      </c>
       <c r="N266" s="17" t="n"/>
       <c r="O266" s="17" t="n">
         <v>0.73</v>
@@ -34615,7 +34891,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G272" s="17" t="n"/>
+      <c r="G272" s="17" t="n">
+        <v>11540</v>
+      </c>
       <c r="H272" s="17" t="n"/>
       <c r="I272" s="17" t="n"/>
       <c r="J272" s="18" t="n">
@@ -34670,7 +34948,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G273" s="17" t="n"/>
+      <c r="G273" s="17" t="n">
+        <v>11540</v>
+      </c>
       <c r="H273" s="17" t="n"/>
       <c r="I273" s="17" t="n"/>
       <c r="J273" s="18" t="n">
@@ -35078,7 +35358,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G279" s="17" t="n"/>
+      <c r="G279" s="17" t="n">
+        <v>6520</v>
+      </c>
       <c r="H279" s="17" t="n"/>
       <c r="I279" s="17" t="n"/>
       <c r="J279" s="18" t="n">
@@ -35133,7 +35415,9 @@
           <t>컨센</t>
         </is>
       </c>
-      <c r="G280" s="17" t="n"/>
+      <c r="G280" s="17" t="n">
+        <v>6520</v>
+      </c>
       <c r="H280" s="17" t="n"/>
       <c r="I280" s="17" t="n"/>
       <c r="J280" s="18" t="n">
@@ -35542,7 +35826,7 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1030.25</v>
+        <v>1009.86</v>
       </c>
       <c r="H286" s="17" t="n">
         <v>49.24</v>
@@ -35560,17 +35844,17 @@
         <v>11512631631.36988</v>
       </c>
       <c r="M286" s="17" t="n">
-        <v>20.92</v>
+        <v>20.51</v>
       </c>
       <c r="N286" s="17" t="n"/>
       <c r="O286" s="17" t="n">
-        <v>5.65</v>
+        <v>5.53</v>
       </c>
       <c r="P286" s="17" t="n">
         <v>30.34</v>
       </c>
       <c r="Q286" s="17" t="n">
-        <v>3.66</v>
+        <v>3.59</v>
       </c>
       <c r="R286" s="17" t="inlineStr">
         <is>
@@ -35615,7 +35899,7 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1030.25</v>
+        <v>1009.86</v>
       </c>
       <c r="H287" s="17" t="n">
         <v>57.19</v>
@@ -35633,17 +35917,17 @@
         <v>14468089988.04707</v>
       </c>
       <c r="M287" s="17" t="n">
-        <v>18.02</v>
+        <v>17.66</v>
       </c>
       <c r="N287" s="17" t="n"/>
       <c r="O287" s="17" t="n">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
       <c r="P287" s="17" t="n">
         <v>27.78</v>
       </c>
       <c r="Q287" s="17" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="R287" s="17" t="inlineStr">
         <is>
@@ -35951,7 +36235,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-29T12:28:39+09:00</t>
+          <t>2026-09-05T08:38:22+09:00</t>
         </is>
       </c>
     </row>

--- a/telegram_research_dashboard/static/valuation_full.xlsx
+++ b/telegram_research_dashboard/static/valuation_full.xlsx
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>34029</v>
+        <v>37480</v>
       </c>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n">
@@ -815,10 +815,10 @@
         <v>37.73</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>14.11</v>
+        <v>15.36</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>12.23</v>
+        <v>13.42</v>
       </c>
       <c r="I5" s="10" t="n"/>
       <c r="J5" s="9" t="n"/>
@@ -847,10 +847,10 @@
         <v>5.72</v>
       </c>
       <c r="U5" s="10" t="n">
-        <v>3.95</v>
+        <v>4.15</v>
       </c>
       <c r="V5" s="10" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="W5" s="10" t="n"/>
       <c r="X5" s="11" t="n">
@@ -866,7 +866,7 @@
         <v>18.82</v>
       </c>
       <c r="AB5" s="12" t="n">
-        <v>30.98</v>
+        <v>30.52</v>
       </c>
       <c r="AC5" s="12" t="n">
         <v>27.39</v>
@@ -885,10 +885,10 @@
         <v>3.04</v>
       </c>
       <c r="AI5" s="10" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AJ5" s="10" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AK5" s="10" t="n"/>
     </row>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>19759</v>
+        <v>19558</v>
       </c>
       <c r="C6" s="9" t="n"/>
       <c r="D6" s="9" t="n">
@@ -912,10 +912,10 @@
         <v>27.94</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>13.46</v>
+        <v>13.87</v>
       </c>
       <c r="H6" s="10" t="n">
-        <v>13.55</v>
+        <v>13.31</v>
       </c>
       <c r="I6" s="10" t="n"/>
       <c r="J6" s="9" t="n"/>
@@ -944,10 +944,10 @@
         <v>5.64</v>
       </c>
       <c r="U6" s="10" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="V6" s="10" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="W6" s="10" t="n"/>
       <c r="X6" s="11" t="n">
@@ -963,10 +963,10 @@
         <v>22.59</v>
       </c>
       <c r="AB6" s="12" t="n">
-        <v>27.32</v>
+        <v>26.58</v>
       </c>
       <c r="AC6" s="12" t="n">
-        <v>21.57</v>
+        <v>21.78</v>
       </c>
       <c r="AD6" s="12" t="n"/>
       <c r="AE6" s="9" t="n">
@@ -982,10 +982,10 @@
         <v>2.72</v>
       </c>
       <c r="AI6" s="10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ6" s="10" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AJ6" s="10" t="n">
-        <v>1.7</v>
       </c>
       <c r="AK6" s="10" t="n"/>
     </row>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>13580</v>
+        <v>13630</v>
       </c>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
@@ -1007,7 +1007,7 @@
         <v>37.73</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>20.37</v>
+        <v>18.07</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>12.56</v>
@@ -1039,7 +1039,7 @@
         <v>4.96</v>
       </c>
       <c r="U7" s="10" t="n">
-        <v>3.61</v>
+        <v>3.54</v>
       </c>
       <c r="V7" s="10" t="n">
         <v>2.76</v>
@@ -1058,7 +1058,7 @@
         <v>13.74</v>
       </c>
       <c r="AB7" s="12" t="n">
-        <v>20.18</v>
+        <v>21.73</v>
       </c>
       <c r="AC7" s="12" t="n">
         <v>24.71</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>18309</v>
+        <v>19273</v>
       </c>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="9" t="n">
@@ -1104,10 +1104,10 @@
         <v>13.27</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>6.21</v>
+        <v>7.06</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>5.8</v>
+        <v>6.08</v>
       </c>
       <c r="I8" s="10" t="n"/>
       <c r="J8" s="9" t="n">
@@ -1138,10 +1138,10 @@
         <v>2.17</v>
       </c>
       <c r="U8" s="10" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="V8" s="10" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="W8" s="10" t="n"/>
       <c r="X8" s="11" t="n">
@@ -1157,7 +1157,7 @@
         <v>17.78</v>
       </c>
       <c r="AB8" s="12" t="n">
-        <v>27.18</v>
+        <v>24.77</v>
       </c>
       <c r="AC8" s="12" t="n">
         <v>23.63</v>
@@ -1176,10 +1176,10 @@
         <v>0.96</v>
       </c>
       <c r="AI8" s="10" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="AJ8" s="10" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AK8" s="10" t="n"/>
     </row>
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>1334</v>
+        <v>1349</v>
       </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
@@ -1199,10 +1199,10 @@
         <v>10.3</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>5.87</v>
+        <v>6.46</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>6.12</v>
+        <v>6.17</v>
       </c>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="9" t="n"/>
@@ -1221,10 +1221,10 @@
         <v>2.35</v>
       </c>
       <c r="U9" s="10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V9" s="10" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W9" s="10" t="n"/>
       <c r="X9" s="11" t="n">
@@ -1240,7 +1240,7 @@
         <v>32.19</v>
       </c>
       <c r="AB9" s="12" t="n">
-        <v>24.95</v>
+        <v>22.79</v>
       </c>
       <c r="AC9" s="12" t="n">
         <v>19.48</v>
@@ -1253,10 +1253,10 @@
         <v>2.09</v>
       </c>
       <c r="AI9" s="10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AJ9" s="10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK9" s="10" t="n"/>
     </row>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="9" t="n"/>
@@ -1277,9 +1277,7 @@
       <c r="F10" s="9" t="n">
         <v>36.95</v>
       </c>
-      <c r="G10" s="10" t="n">
-        <v>8.02</v>
-      </c>
+      <c r="G10" s="10" t="n"/>
       <c r="H10" s="10" t="n"/>
       <c r="I10" s="10" t="n"/>
       <c r="J10" s="9" t="n">
@@ -1307,9 +1305,7 @@
       <c r="T10" s="9" t="n">
         <v>2.84</v>
       </c>
-      <c r="U10" s="10" t="n">
-        <v>1.84</v>
-      </c>
+      <c r="U10" s="10" t="n"/>
       <c r="V10" s="10" t="n"/>
       <c r="W10" s="10" t="n"/>
       <c r="X10" s="11" t="n">
@@ -1324,9 +1320,7 @@
       <c r="AA10" s="11" t="n">
         <v>10.15</v>
       </c>
-      <c r="AB10" s="12" t="n">
-        <v>24.85</v>
-      </c>
+      <c r="AB10" s="12" t="n"/>
       <c r="AC10" s="12" t="n"/>
       <c r="AD10" s="12" t="n"/>
       <c r="AE10" s="9" t="n">
@@ -1352,7 +1346,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>7011</v>
+        <v>8257</v>
       </c>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
@@ -1363,10 +1357,10 @@
         <v>32.18</v>
       </c>
       <c r="G11" s="10" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="H11" s="10" t="n">
         <v>26.15</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>22.27</v>
       </c>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="9" t="n"/>
@@ -1389,10 +1383,10 @@
         <v>10.52</v>
       </c>
       <c r="U11" s="10" t="n">
-        <v>9.17</v>
+        <v>10.95</v>
       </c>
       <c r="V11" s="10" t="n">
-        <v>7.61</v>
+        <v>8.94</v>
       </c>
       <c r="W11" s="10" t="n"/>
       <c r="X11" s="11" t="n">
@@ -1408,7 +1402,7 @@
         <v>33.73</v>
       </c>
       <c r="AB11" s="12" t="n">
-        <v>38.53</v>
+        <v>37.81</v>
       </c>
       <c r="AC11" s="12" t="n">
         <v>37.64</v>
@@ -1423,10 +1417,10 @@
         <v>4.38</v>
       </c>
       <c r="AI11" s="10" t="n">
-        <v>4.06</v>
+        <v>4.77</v>
       </c>
       <c r="AJ11" s="10" t="n">
-        <v>3.53</v>
+        <v>4.14</v>
       </c>
       <c r="AK11" s="10" t="n"/>
     </row>
@@ -1437,7 +1431,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>1265</v>
+        <v>1328</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>14.21</v>
@@ -1452,10 +1446,10 @@
         <v>18.39</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>12.99</v>
+        <v>13.36</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>9.220000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I12" s="10" t="n"/>
       <c r="J12" s="9" t="n">
@@ -1486,10 +1480,10 @@
         <v>6.21</v>
       </c>
       <c r="U12" s="10" t="n">
-        <v>3.44</v>
+        <v>2.86</v>
       </c>
       <c r="V12" s="10" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="W12" s="10" t="n"/>
       <c r="X12" s="11" t="n">
@@ -1505,7 +1499,7 @@
         <v>41.36</v>
       </c>
       <c r="AB12" s="12" t="n">
-        <v>26.46</v>
+        <v>24</v>
       </c>
       <c r="AC12" s="12" t="n">
         <v>25.85</v>
@@ -1524,10 +1518,10 @@
         <v>7.54</v>
       </c>
       <c r="AI12" s="10" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="AJ12" s="10" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="AK12" s="10" t="n"/>
     </row>
@@ -1538,7 +1532,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>2826</v>
+        <v>3129</v>
       </c>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
@@ -1549,10 +1543,10 @@
         <v>20.62</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>19.15</v>
+        <v>22.04</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>13.17</v>
+        <v>14.44</v>
       </c>
       <c r="I13" s="10" t="n"/>
       <c r="J13" s="9" t="n"/>
@@ -1581,10 +1575,10 @@
         <v>6.44</v>
       </c>
       <c r="U13" s="10" t="n">
-        <v>5.03</v>
+        <v>5.62</v>
       </c>
       <c r="V13" s="10" t="n">
-        <v>3.64</v>
+        <v>4.05</v>
       </c>
       <c r="W13" s="10" t="n"/>
       <c r="X13" s="11" t="n">
@@ -1600,10 +1594,10 @@
         <v>36.6</v>
       </c>
       <c r="AB13" s="12" t="n">
-        <v>30.33</v>
+        <v>29.23</v>
       </c>
       <c r="AC13" s="12" t="n">
-        <v>32.03</v>
+        <v>32.59</v>
       </c>
       <c r="AD13" s="12" t="n"/>
       <c r="AE13" s="9" t="n">
@@ -1619,10 +1613,10 @@
         <v>2.61</v>
       </c>
       <c r="AI13" s="10" t="n">
-        <v>2.36</v>
+        <v>2.57</v>
       </c>
       <c r="AJ13" s="10" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AK13" s="10" t="n"/>
     </row>
@@ -1633,7 +1627,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>844</v>
+        <v>815</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>23.46</v>
@@ -1646,10 +1640,10 @@
         <v>14.78</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>9.869999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="I14" s="10" t="n"/>
       <c r="J14" s="9" t="n">
@@ -1680,10 +1674,10 @@
         <v>2.59</v>
       </c>
       <c r="U14" s="10" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="V14" s="10" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="W14" s="10" t="n"/>
       <c r="X14" s="11" t="n">
@@ -1699,7 +1693,7 @@
         <v>19.3</v>
       </c>
       <c r="AB14" s="12" t="n">
-        <v>18.45</v>
+        <v>19.11</v>
       </c>
       <c r="AC14" s="12" t="n">
         <v>19.15</v>
@@ -1718,10 +1712,10 @@
         <v>1.65</v>
       </c>
       <c r="AI14" s="10" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AJ14" s="10" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK14" s="10" t="n"/>
     </row>
@@ -1732,7 +1726,7 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>37.11</v>
@@ -1747,10 +1741,10 @@
         <v>13.58</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>5.92</v>
+        <v>6.88</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>5.92</v>
+        <v>5.79</v>
       </c>
       <c r="I15" s="10" t="n"/>
       <c r="J15" s="9" t="n">
@@ -1781,10 +1775,10 @@
         <v>2.93</v>
       </c>
       <c r="U15" s="10" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="V15" s="10" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W15" s="10" t="n"/>
       <c r="X15" s="11" t="n">
@@ -1800,7 +1794,7 @@
         <v>24.23</v>
       </c>
       <c r="AB15" s="12" t="n">
-        <v>29.46</v>
+        <v>24.74</v>
       </c>
       <c r="AC15" s="12" t="n">
         <v>23.13</v>
@@ -1819,10 +1813,10 @@
         <v>1.02</v>
       </c>
       <c r="AI15" s="10" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="AJ15" s="10" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="AK15" s="10" t="n"/>
     </row>
@@ -1840,7 +1834,7 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>5099</v>
+        <v>5195</v>
       </c>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="9" t="n"/>
@@ -1881,10 +1875,10 @@
         <v>5.43</v>
       </c>
       <c r="U17" s="10" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="V17" s="10" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="W17" s="10" t="n"/>
       <c r="X17" s="11" t="n">
@@ -1919,10 +1913,10 @@
         <v>0.61</v>
       </c>
       <c r="AI17" s="10" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="AJ17" s="10" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="AK17" s="10" t="n"/>
     </row>
@@ -1946,10 +1940,10 @@
         <v>20.62</v>
       </c>
       <c r="G18" s="15" t="n">
-        <v>12.99</v>
+        <v>13.61</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>10.73</v>
+        <v>11.1</v>
       </c>
       <c r="I18" s="15" t="n"/>
       <c r="J18" s="15" t="n">
@@ -1980,10 +1974,10 @@
         <v>4.96</v>
       </c>
       <c r="U18" s="15" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="V18" s="15" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="W18" s="15" t="n"/>
       <c r="X18" s="16" t="n">
@@ -1999,7 +1993,7 @@
         <v>22.59</v>
       </c>
       <c r="AB18" s="16" t="n">
-        <v>27.18</v>
+        <v>24.75</v>
       </c>
       <c r="AC18" s="16" t="n">
         <v>24.17</v>
@@ -2018,7 +2012,7 @@
         <v>2.09</v>
       </c>
       <c r="AI18" s="15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AJ18" s="15" t="n">
         <v>1.5</v>
@@ -2071,10 +2065,10 @@
         <v>5.43</v>
       </c>
       <c r="U19" s="15" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="V19" s="15" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="W19" s="15" t="n"/>
       <c r="X19" s="16" t="n">
@@ -2109,10 +2103,10 @@
         <v>0.61</v>
       </c>
       <c r="AI19" s="15" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="AJ19" s="15" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="AK19" s="15" t="n"/>
     </row>
@@ -2136,10 +2130,10 @@
         <v>24.28</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>12.99</v>
+        <v>13.61</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>10.73</v>
+        <v>11.1</v>
       </c>
       <c r="I20" s="15" t="n"/>
       <c r="J20" s="15" t="n">
@@ -2170,10 +2164,10 @@
         <v>5.2</v>
       </c>
       <c r="U20" s="15" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="V20" s="15" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="W20" s="15" t="n"/>
       <c r="X20" s="16" t="n">
@@ -2189,7 +2183,7 @@
         <v>20.95</v>
       </c>
       <c r="AB20" s="16" t="n">
-        <v>26.82</v>
+        <v>24.74</v>
       </c>
       <c r="AC20" s="16" t="n">
         <v>23.63</v>
@@ -2211,7 +2205,7 @@
         <v>1.42</v>
       </c>
       <c r="AJ20" s="15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK20" s="15" t="n"/>
     </row>
@@ -2272,7 +2266,7 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>9161</v>
+        <v>9485</v>
       </c>
       <c r="C24" s="9" t="n">
         <v>41.88</v>
@@ -2287,10 +2281,10 @@
         <v>59.99</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>50.51</v>
+        <v>55.63</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>27.77</v>
+        <v>28.85</v>
       </c>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="9" t="n">
@@ -2321,10 +2315,10 @@
         <v>6.09</v>
       </c>
       <c r="U24" s="10" t="n">
-        <v>5.98</v>
+        <v>6.37</v>
       </c>
       <c r="V24" s="10" t="n">
-        <v>5.32</v>
+        <v>5.49</v>
       </c>
       <c r="W24" s="10" t="n"/>
       <c r="X24" s="11" t="n">
@@ -2340,10 +2334,10 @@
         <v>10.51</v>
       </c>
       <c r="AB24" s="12" t="n">
-        <v>12.47</v>
+        <v>11.95</v>
       </c>
       <c r="AC24" s="12" t="n">
-        <v>20.59</v>
+        <v>20.45</v>
       </c>
       <c r="AD24" s="12" t="n"/>
       <c r="AE24" s="9" t="n">
@@ -2359,10 +2353,10 @@
         <v>3.02</v>
       </c>
       <c r="AI24" s="10" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AJ24" s="10" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AK24" s="10" t="n"/>
     </row>
@@ -2373,7 +2367,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>40326</v>
+        <v>41472</v>
       </c>
       <c r="C25" s="9" t="n">
         <v>19.31</v>
@@ -2388,10 +2382,10 @@
         <v>34.46</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>23.22</v>
+        <v>22.44</v>
       </c>
       <c r="H25" s="10" t="n">
-        <v>17.78</v>
+        <v>18.22</v>
       </c>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="9" t="n">
@@ -2422,10 +2416,10 @@
         <v>5</v>
       </c>
       <c r="U25" s="10" t="n">
-        <v>4.52</v>
+        <v>4.74</v>
       </c>
       <c r="V25" s="10" t="n">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="W25" s="10" t="n"/>
       <c r="X25" s="11" t="n">
@@ -2441,7 +2435,7 @@
         <v>19.14</v>
       </c>
       <c r="AB25" s="12" t="n">
-        <v>21.52</v>
+        <v>23.15</v>
       </c>
       <c r="AC25" s="12" t="n">
         <v>23.48</v>
@@ -2460,10 +2454,10 @@
         <v>1.81</v>
       </c>
       <c r="AI25" s="10" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AJ25" s="10" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AK25" s="10" t="n"/>
     </row>
@@ -2474,7 +2468,7 @@
         </is>
       </c>
       <c r="B26" s="8" t="n">
-        <v>10582</v>
+        <v>11044</v>
       </c>
       <c r="C26" s="9" t="n">
         <v>16.34</v>
@@ -2489,10 +2483,10 @@
         <v>36.3</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>40.64</v>
+        <v>40.52</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>27.03</v>
+        <v>28.13</v>
       </c>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="9" t="n">
@@ -2523,10 +2517,10 @@
         <v>6.43</v>
       </c>
       <c r="U26" s="10" t="n">
-        <v>8.48</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="V26" s="10" t="n">
-        <v>6.71</v>
+        <v>6.98</v>
       </c>
       <c r="W26" s="10" t="n"/>
       <c r="X26" s="11" t="n">
@@ -2542,10 +2536,10 @@
         <v>19.2</v>
       </c>
       <c r="AB26" s="12" t="n">
-        <v>22.68</v>
+        <v>23.25</v>
       </c>
       <c r="AC26" s="12" t="n">
-        <v>27.48</v>
+        <v>27.46</v>
       </c>
       <c r="AD26" s="12" t="n"/>
       <c r="AE26" s="9" t="n">
@@ -2561,10 +2555,10 @@
         <v>2.14</v>
       </c>
       <c r="AI26" s="10" t="n">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="AJ26" s="10" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AK26" s="10" t="n"/>
     </row>
@@ -2575,7 +2569,7 @@
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>9558</v>
+        <v>9886</v>
       </c>
       <c r="C27" s="9" t="n"/>
       <c r="D27" s="9" t="n">
@@ -2588,10 +2582,10 @@
         <v>41.99</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>92.31</v>
+        <v>89.69</v>
       </c>
       <c r="H27" s="10" t="n">
-        <v>29.54</v>
+        <v>30.44</v>
       </c>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="9" t="n">
@@ -2622,10 +2616,10 @@
         <v>2.1</v>
       </c>
       <c r="U27" s="10" t="n">
-        <v>2.32</v>
+        <v>2.69</v>
       </c>
       <c r="V27" s="10" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="11" t="n">
@@ -2641,7 +2635,7 @@
         <v>6.6</v>
       </c>
       <c r="AB27" s="12" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="AC27" s="12" t="n">
         <v>8.65</v>
@@ -2660,10 +2654,10 @@
         <v>2.78</v>
       </c>
       <c r="AI27" s="10" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AJ27" s="10" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="AK27" s="10" t="n"/>
     </row>
@@ -2674,7 +2668,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>10282</v>
+        <v>10100</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>15.67</v>
@@ -2689,10 +2683,10 @@
         <v>26.64</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>15.41</v>
+        <v>15.43</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>11.21</v>
+        <v>11.18</v>
       </c>
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="9" t="n">
@@ -2723,10 +2717,10 @@
         <v>6.66</v>
       </c>
       <c r="U28" s="10" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="V28" s="10" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="W28" s="10" t="n"/>
       <c r="X28" s="11" t="n">
@@ -2742,10 +2736,10 @@
         <v>30.05</v>
       </c>
       <c r="AB28" s="12" t="n">
-        <v>25.7</v>
+        <v>25.21</v>
       </c>
       <c r="AC28" s="12" t="n">
-        <v>27.68</v>
+        <v>27.27</v>
       </c>
       <c r="AD28" s="12" t="n"/>
       <c r="AE28" s="9" t="n">
@@ -2761,10 +2755,10 @@
         <v>3.51</v>
       </c>
       <c r="AI28" s="10" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AJ28" s="10" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AK28" s="10" t="n"/>
     </row>
@@ -2782,7 +2776,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>120289</v>
+        <v>120040</v>
       </c>
       <c r="C30" s="9" t="n">
         <v>21.56</v>
@@ -2797,10 +2791,10 @@
         <v>22.08</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>17.24</v>
+        <v>17.21</v>
       </c>
       <c r="H30" s="10" t="n">
-        <v>16.05</v>
+        <v>16.02</v>
       </c>
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="9" t="n">
@@ -2831,10 +2825,10 @@
         <v>16.48</v>
       </c>
       <c r="U30" s="10" t="n">
-        <v>11.81</v>
+        <v>11.79</v>
       </c>
       <c r="V30" s="10" t="n">
-        <v>8.65</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="W30" s="10" t="n"/>
       <c r="X30" s="11" t="n">
@@ -2850,10 +2844,10 @@
         <v>76.87</v>
       </c>
       <c r="AB30" s="12" t="n">
-        <v>82.53</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="AC30" s="12" t="n">
-        <v>62.2</v>
+        <v>62.21</v>
       </c>
       <c r="AD30" s="12" t="n"/>
       <c r="AE30" s="9" t="n">
@@ -2869,10 +2863,10 @@
         <v>1.48</v>
       </c>
       <c r="AI30" s="10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AJ30" s="10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AK30" s="10" t="n"/>
     </row>
@@ -2883,7 +2877,7 @@
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>73126</v>
+        <v>73692</v>
       </c>
       <c r="C31" s="9" t="n">
         <v>17.07</v>
@@ -2898,10 +2892,10 @@
         <v>19.36</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>17.76</v>
+        <v>17.9</v>
       </c>
       <c r="H31" s="10" t="n">
-        <v>16.92</v>
+        <v>17.05</v>
       </c>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="9" t="n">
@@ -2932,10 +2926,10 @@
         <v>4.86</v>
       </c>
       <c r="U31" s="10" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="V31" s="10" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="W31" s="10" t="n"/>
       <c r="X31" s="11" t="n">
@@ -2970,10 +2964,10 @@
         <v>1.93</v>
       </c>
       <c r="AI31" s="10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AJ31" s="10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AK31" s="10" t="n"/>
     </row>
@@ -2984,7 +2978,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>97175</v>
+        <v>96232</v>
       </c>
       <c r="C32" s="9" t="n">
         <v>20.08</v>
@@ -2999,10 +2993,10 @@
         <v>21.62</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>21.14</v>
+        <v>20.95</v>
       </c>
       <c r="H32" s="10" t="n">
-        <v>19.33</v>
+        <v>19.12</v>
       </c>
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="9" t="n">
@@ -3033,10 +3027,10 @@
         <v>3.55</v>
       </c>
       <c r="U32" s="10" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="V32" s="10" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="W32" s="10" t="n"/>
       <c r="X32" s="11" t="n">
@@ -3052,10 +3046,10 @@
         <v>17.66</v>
       </c>
       <c r="AB32" s="12" t="n">
-        <v>16.99</v>
+        <v>16.98</v>
       </c>
       <c r="AC32" s="12" t="n">
-        <v>16.73</v>
+        <v>16.75</v>
       </c>
       <c r="AD32" s="12" t="n"/>
       <c r="AE32" s="9" t="n">
@@ -3071,10 +3065,10 @@
         <v>1.73</v>
       </c>
       <c r="AI32" s="10" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AJ32" s="10" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AK32" s="10" t="n"/>
     </row>
@@ -3085,7 +3079,7 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>269518</v>
+        <v>265343</v>
       </c>
       <c r="C33" s="9" t="n">
         <v>28.47</v>
@@ -3100,10 +3094,10 @@
         <v>36.57</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>27.72</v>
+        <v>27.29</v>
       </c>
       <c r="H33" s="10" t="n">
-        <v>25.56</v>
+        <v>25.16</v>
       </c>
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="9" t="n">
@@ -3134,10 +3128,10 @@
         <v>3.77</v>
       </c>
       <c r="U33" s="10" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="V33" s="10" t="n">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="W33" s="10" t="n"/>
       <c r="X33" s="11" t="n">
@@ -3172,10 +3166,10 @@
         <v>2.78</v>
       </c>
       <c r="AI33" s="10" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="AJ33" s="10" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="AK33" s="10" t="n"/>
     </row>
@@ -3186,7 +3180,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>11220</v>
+        <v>10975</v>
       </c>
       <c r="C34" s="9" t="n">
         <v>15.9</v>
@@ -3201,10 +3195,10 @@
         <v>22.06</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>15.45</v>
+        <v>15.11</v>
       </c>
       <c r="H34" s="10" t="n">
-        <v>13.72</v>
+        <v>13.42</v>
       </c>
       <c r="I34" s="10" t="n"/>
       <c r="J34" s="9" t="n">
@@ -3235,10 +3229,10 @@
         <v>2.63</v>
       </c>
       <c r="U34" s="10" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="V34" s="10" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="W34" s="10" t="n"/>
       <c r="X34" s="11" t="n">
@@ -3273,10 +3267,10 @@
         <v>1.07</v>
       </c>
       <c r="AI34" s="10" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="AJ34" s="10" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="AK34" s="10" t="n"/>
     </row>
@@ -3294,7 +3288,7 @@
         </is>
       </c>
       <c r="B36" s="8" t="n">
-        <v>56078</v>
+        <v>53637</v>
       </c>
       <c r="C36" s="9" t="n">
         <v>17.03</v>
@@ -3339,10 +3333,10 @@
         <v>14.29</v>
       </c>
       <c r="U36" s="10" t="n">
-        <v>8.09</v>
+        <v>7.75</v>
       </c>
       <c r="V36" s="10" t="n">
-        <v>6.57</v>
+        <v>6.3</v>
       </c>
       <c r="W36" s="10" t="n"/>
       <c r="X36" s="11" t="n">
@@ -3358,10 +3352,10 @@
         <v>15.36</v>
       </c>
       <c r="AB36" s="12" t="n">
-        <v>31.14</v>
+        <v>31.17</v>
       </c>
       <c r="AC36" s="12" t="n">
-        <v>37.01</v>
+        <v>36.99</v>
       </c>
       <c r="AD36" s="12" t="n"/>
       <c r="AE36" s="9" t="n">
@@ -3377,10 +3371,10 @@
         <v>7.21</v>
       </c>
       <c r="AI36" s="10" t="n">
-        <v>3.46</v>
+        <v>3.31</v>
       </c>
       <c r="AJ36" s="10" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="AK36" s="10" t="n"/>
     </row>
@@ -3398,7 +3392,7 @@
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>775</v>
+        <v>752</v>
       </c>
       <c r="C38" s="9" t="n">
         <v>16.56</v>
@@ -3462,10 +3456,10 @@
         <v>17.62</v>
       </c>
       <c r="AB38" s="12" t="n">
-        <v>19.84</v>
+        <v>19.87</v>
       </c>
       <c r="AC38" s="12" t="n">
-        <v>20.55</v>
+        <v>20.57</v>
       </c>
       <c r="AD38" s="12" t="n"/>
       <c r="AE38" s="9" t="n">
@@ -3502,7 +3496,7 @@
         </is>
       </c>
       <c r="B40" s="8" t="n">
-        <v>33829</v>
+        <v>33466</v>
       </c>
       <c r="C40" s="9" t="n">
         <v>5</v>
@@ -3547,10 +3541,10 @@
         <v>2.97</v>
       </c>
       <c r="U40" s="10" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="V40" s="10" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="W40" s="10" t="n"/>
       <c r="X40" s="11" t="n">
@@ -3569,7 +3563,7 @@
         <v>13.7</v>
       </c>
       <c r="AC40" s="12" t="n">
-        <v>14.91</v>
+        <v>14.89</v>
       </c>
       <c r="AD40" s="12" t="n"/>
       <c r="AE40" s="9" t="n">
@@ -3585,10 +3579,10 @@
         <v>1.45</v>
       </c>
       <c r="AI40" s="10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AJ40" s="10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK40" s="10" t="n"/>
     </row>
@@ -3606,7 +3600,7 @@
         </is>
       </c>
       <c r="B42" s="8" t="n">
-        <v>33190</v>
+        <v>31792</v>
       </c>
       <c r="C42" s="9" t="n">
         <v>24.79</v>
@@ -3651,10 +3645,10 @@
         <v>6.69</v>
       </c>
       <c r="U42" s="10" t="n">
-        <v>6.35</v>
+        <v>6.16</v>
       </c>
       <c r="V42" s="10" t="n">
-        <v>5.43</v>
+        <v>5.26</v>
       </c>
       <c r="W42" s="10" t="n"/>
       <c r="X42" s="11" t="n">
@@ -3673,7 +3667,7 @@
         <v>17.2</v>
       </c>
       <c r="AC42" s="12" t="n">
-        <v>18.63</v>
+        <v>18.76</v>
       </c>
       <c r="AD42" s="12" t="n"/>
       <c r="AE42" s="9" t="n">
@@ -3689,10 +3683,10 @@
         <v>3.66</v>
       </c>
       <c r="AI42" s="10" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AJ42" s="10" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="AK42" s="10" t="n"/>
     </row>
@@ -3716,10 +3710,10 @@
         <v>36.3</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>40.64</v>
+        <v>40.52</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>27.03</v>
+        <v>28.13</v>
       </c>
       <c r="I43" s="15" t="n"/>
       <c r="J43" s="15" t="n">
@@ -3750,10 +3744,10 @@
         <v>6.09</v>
       </c>
       <c r="U43" s="15" t="n">
-        <v>4.52</v>
+        <v>4.74</v>
       </c>
       <c r="V43" s="15" t="n">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="W43" s="15" t="n"/>
       <c r="X43" s="16" t="n">
@@ -3769,7 +3763,7 @@
         <v>19.14</v>
       </c>
       <c r="AB43" s="16" t="n">
-        <v>21.52</v>
+        <v>23.15</v>
       </c>
       <c r="AC43" s="16" t="n">
         <v>23.48</v>
@@ -3788,10 +3782,10 @@
         <v>2.78</v>
       </c>
       <c r="AI43" s="15" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AJ43" s="15" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AK43" s="15" t="n"/>
     </row>
@@ -3815,10 +3809,10 @@
         <v>22.06</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>17.76</v>
+        <v>17.9</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>16.92</v>
+        <v>17.05</v>
       </c>
       <c r="I44" s="15" t="n"/>
       <c r="J44" s="15" t="n">
@@ -3849,10 +3843,10 @@
         <v>3.77</v>
       </c>
       <c r="U44" s="15" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="V44" s="15" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="W44" s="15" t="n"/>
       <c r="X44" s="16" t="n">
@@ -3868,10 +3862,10 @@
         <v>17.66</v>
       </c>
       <c r="AB44" s="16" t="n">
-        <v>16.99</v>
+        <v>16.98</v>
       </c>
       <c r="AC44" s="16" t="n">
-        <v>16.73</v>
+        <v>16.75</v>
       </c>
       <c r="AD44" s="16" t="n"/>
       <c r="AE44" s="15" t="n">
@@ -3887,10 +3881,10 @@
         <v>1.73</v>
       </c>
       <c r="AI44" s="15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AJ44" s="15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AK44" s="15" t="n"/>
     </row>
@@ -3944,10 +3938,10 @@
         <v>14.29</v>
       </c>
       <c r="U45" s="15" t="n">
-        <v>8.09</v>
+        <v>7.75</v>
       </c>
       <c r="V45" s="15" t="n">
-        <v>6.57</v>
+        <v>6.3</v>
       </c>
       <c r="W45" s="15" t="n"/>
       <c r="X45" s="16" t="n">
@@ -3963,10 +3957,10 @@
         <v>15.36</v>
       </c>
       <c r="AB45" s="16" t="n">
-        <v>31.14</v>
+        <v>31.17</v>
       </c>
       <c r="AC45" s="16" t="n">
-        <v>37.01</v>
+        <v>36.99</v>
       </c>
       <c r="AD45" s="16" t="n"/>
       <c r="AE45" s="15" t="n">
@@ -3982,10 +3976,10 @@
         <v>7.21</v>
       </c>
       <c r="AI45" s="15" t="n">
-        <v>3.46</v>
+        <v>3.31</v>
       </c>
       <c r="AJ45" s="15" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="AK45" s="15" t="n"/>
     </row>
@@ -4058,10 +4052,10 @@
         <v>17.62</v>
       </c>
       <c r="AB46" s="16" t="n">
-        <v>19.84</v>
+        <v>19.87</v>
       </c>
       <c r="AC46" s="16" t="n">
-        <v>20.55</v>
+        <v>20.57</v>
       </c>
       <c r="AD46" s="16" t="n"/>
       <c r="AE46" s="15" t="n">
@@ -4134,10 +4128,10 @@
         <v>2.97</v>
       </c>
       <c r="U47" s="15" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="V47" s="15" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="W47" s="15" t="n"/>
       <c r="X47" s="16" t="n">
@@ -4156,7 +4150,7 @@
         <v>13.7</v>
       </c>
       <c r="AC47" s="16" t="n">
-        <v>14.91</v>
+        <v>14.89</v>
       </c>
       <c r="AD47" s="16" t="n"/>
       <c r="AE47" s="15" t="n">
@@ -4172,10 +4166,10 @@
         <v>1.45</v>
       </c>
       <c r="AI47" s="15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AJ47" s="15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK47" s="15" t="n"/>
     </row>
@@ -4229,10 +4223,10 @@
         <v>6.69</v>
       </c>
       <c r="U48" s="15" t="n">
-        <v>6.35</v>
+        <v>6.16</v>
       </c>
       <c r="V48" s="15" t="n">
-        <v>5.43</v>
+        <v>5.26</v>
       </c>
       <c r="W48" s="15" t="n"/>
       <c r="X48" s="16" t="n">
@@ -4251,7 +4245,7 @@
         <v>17.2</v>
       </c>
       <c r="AC48" s="16" t="n">
-        <v>18.63</v>
+        <v>18.76</v>
       </c>
       <c r="AD48" s="16" t="n"/>
       <c r="AE48" s="15" t="n">
@@ -4267,10 +4261,10 @@
         <v>3.66</v>
       </c>
       <c r="AI48" s="15" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AJ48" s="15" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="AK48" s="15" t="n"/>
     </row>
@@ -4294,10 +4288,10 @@
         <v>30.55</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>22.18</v>
+        <v>21.7</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>18.55</v>
+        <v>18.67</v>
       </c>
       <c r="I49" s="15" t="n"/>
       <c r="J49" s="15" t="n">
@@ -4328,10 +4322,10 @@
         <v>4.93</v>
       </c>
       <c r="U49" s="15" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="V49" s="15" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="W49" s="15" t="n"/>
       <c r="X49" s="16" t="n">
@@ -4347,10 +4341,10 @@
         <v>16.82</v>
       </c>
       <c r="AB49" s="16" t="n">
-        <v>18.52</v>
+        <v>18.54</v>
       </c>
       <c r="AC49" s="16" t="n">
-        <v>20.53</v>
+        <v>20.48</v>
       </c>
       <c r="AD49" s="16" t="n"/>
       <c r="AE49" s="15" t="n">
@@ -4366,10 +4360,10 @@
         <v>2.04</v>
       </c>
       <c r="AI49" s="15" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AJ49" s="15" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AK49" s="15" t="n"/>
     </row>
@@ -4430,7 +4424,7 @@
         </is>
       </c>
       <c r="B53" s="8" t="n">
-        <v>4990</v>
+        <v>5097</v>
       </c>
       <c r="C53" s="9" t="n">
         <v>10.61</v>
@@ -4445,10 +4439,10 @@
         <v>47.5</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>11.01</v>
+        <v>10.58</v>
       </c>
       <c r="H53" s="10" t="n">
-        <v>9.43</v>
+        <v>9.6</v>
       </c>
       <c r="I53" s="10" t="n"/>
       <c r="J53" s="9" t="n">
@@ -4479,10 +4473,10 @@
         <v>2.61</v>
       </c>
       <c r="U53" s="10" t="n">
-        <v>1.18</v>
+        <v>2.83</v>
       </c>
       <c r="V53" s="10" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="W53" s="10" t="n"/>
       <c r="X53" s="11" t="n">
@@ -4498,7 +4492,7 @@
         <v>5.74</v>
       </c>
       <c r="AB53" s="12" t="n">
-        <v>16.32</v>
+        <v>30.59</v>
       </c>
       <c r="AC53" s="12" t="n">
         <v>25.82</v>
@@ -4517,10 +4511,10 @@
         <v>1.25</v>
       </c>
       <c r="AI53" s="10" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="AJ53" s="10" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AK53" s="10" t="n"/>
     </row>
@@ -4531,7 +4525,7 @@
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>4466</v>
+        <v>4397</v>
       </c>
       <c r="C54" s="9" t="n">
         <v>5.38</v>
@@ -4546,10 +4540,10 @@
         <v>13.73</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>10.7</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>9.48</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I54" s="10" t="n"/>
       <c r="J54" s="9" t="n">
@@ -4580,10 +4574,10 @@
         <v>0.77</v>
       </c>
       <c r="U54" s="10" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="V54" s="10" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="W54" s="10" t="n"/>
       <c r="X54" s="11" t="n">
@@ -4599,7 +4593,7 @@
         <v>5.71</v>
       </c>
       <c r="AB54" s="12" t="n">
-        <v>7.52</v>
+        <v>8</v>
       </c>
       <c r="AC54" s="12" t="n">
         <v>8.130000000000001</v>
@@ -4618,10 +4612,10 @@
         <v>0.63</v>
       </c>
       <c r="AI54" s="10" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="AJ54" s="10" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="AK54" s="10" t="n"/>
     </row>
@@ -4632,7 +4626,7 @@
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C55" s="9" t="n">
         <v>7.23</v>
@@ -4713,7 +4707,7 @@
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C56" s="9" t="n">
         <v>5.78</v>
@@ -4728,10 +4722,10 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>7.63</v>
+        <v>7.34</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>6.27</v>
+        <v>6.03</v>
       </c>
       <c r="I56" s="10" t="n"/>
       <c r="J56" s="9" t="n">
@@ -4762,10 +4756,10 @@
         <v>0.92</v>
       </c>
       <c r="U56" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="V56" s="10" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="W56" s="10" t="n"/>
       <c r="X56" s="11" t="n">
@@ -4800,10 +4794,10 @@
         <v>0.59</v>
       </c>
       <c r="AI56" s="10" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="AJ56" s="10" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="AK56" s="10" t="n"/>
     </row>
@@ -4814,7 +4808,7 @@
         </is>
       </c>
       <c r="B57" s="8" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>7.57</v>
@@ -4899,7 +4893,7 @@
         </is>
       </c>
       <c r="B58" s="8" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C58" s="9" t="n">
         <v>5.71</v>
@@ -4991,7 +4985,7 @@
         </is>
       </c>
       <c r="B60" s="8" t="n">
-        <v>378716</v>
+        <v>380870</v>
       </c>
       <c r="C60" s="9" t="n">
         <v>18.45</v>
@@ -5006,10 +5000,10 @@
         <v>30</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>29.94</v>
+        <v>30.11</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>25.14</v>
+        <v>25.28</v>
       </c>
       <c r="I60" s="10" t="n"/>
       <c r="J60" s="9" t="n">
@@ -5040,10 +5034,10 @@
         <v>12.5</v>
       </c>
       <c r="U60" s="10" t="n">
-        <v>12.35</v>
+        <v>12.42</v>
       </c>
       <c r="V60" s="10" t="n">
-        <v>9.06</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="W60" s="10" t="n"/>
       <c r="X60" s="11" t="n">
@@ -5078,10 +5072,10 @@
         <v>3.94</v>
       </c>
       <c r="AI60" s="10" t="n">
-        <v>4.78</v>
+        <v>4.81</v>
       </c>
       <c r="AJ60" s="10" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AK60" s="10" t="n"/>
     </row>
@@ -5092,7 +5086,7 @@
         </is>
       </c>
       <c r="B61" s="8" t="n">
-        <v>187497</v>
+        <v>182688</v>
       </c>
       <c r="C61" s="9" t="n">
         <v>16.58</v>
@@ -5107,10 +5101,10 @@
         <v>24.83</v>
       </c>
       <c r="G61" s="10" t="n">
-        <v>38.25</v>
+        <v>37.27</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>30.59</v>
+        <v>29.81</v>
       </c>
       <c r="I61" s="10" t="n"/>
       <c r="J61" s="9" t="n">
@@ -5141,10 +5135,10 @@
         <v>4.81</v>
       </c>
       <c r="U61" s="10" t="n">
-        <v>6.45</v>
+        <v>6.28</v>
       </c>
       <c r="V61" s="10" t="n">
-        <v>5.68</v>
+        <v>5.53</v>
       </c>
       <c r="W61" s="10" t="n"/>
       <c r="X61" s="11" t="n">
@@ -5179,10 +5173,10 @@
         <v>2.79</v>
       </c>
       <c r="AI61" s="10" t="n">
-        <v>4.56</v>
+        <v>4.44</v>
       </c>
       <c r="AJ61" s="10" t="n">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="AK61" s="10" t="n"/>
     </row>
@@ -5193,7 +5187,7 @@
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>17886</v>
+        <v>16867</v>
       </c>
       <c r="C62" s="9" t="n">
         <v>10.64</v>
@@ -5208,10 +5202,10 @@
         <v>22.45</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>31.88</v>
+        <v>30.06</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>21.02</v>
+        <v>19.82</v>
       </c>
       <c r="I62" s="10" t="n"/>
       <c r="J62" s="9" t="n">
@@ -5242,10 +5236,10 @@
         <v>1.48</v>
       </c>
       <c r="U62" s="10" t="n">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="V62" s="10" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="W62" s="10" t="n"/>
       <c r="X62" s="11" t="n">
@@ -5280,10 +5274,10 @@
         <v>0.63</v>
       </c>
       <c r="AI62" s="10" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="AJ62" s="10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="AK62" s="10" t="n"/>
     </row>
@@ -5294,7 +5288,7 @@
         </is>
       </c>
       <c r="B63" s="8" t="n">
-        <v>63718</v>
+        <v>62409</v>
       </c>
       <c r="C63" s="9" t="n">
         <v>11.71</v>
@@ -5309,10 +5303,10 @@
         <v>20.48</v>
       </c>
       <c r="G63" s="10" t="n">
-        <v>20.51</v>
+        <v>20.07</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>17.66</v>
+        <v>17.26</v>
       </c>
       <c r="I63" s="10" t="n"/>
       <c r="J63" s="9" t="n">
@@ -5343,10 +5337,10 @@
         <v>5.69</v>
       </c>
       <c r="U63" s="10" t="n">
-        <v>5.53</v>
+        <v>5.42</v>
       </c>
       <c r="V63" s="10" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="W63" s="10" t="n"/>
       <c r="X63" s="11" t="n">
@@ -5362,10 +5356,10 @@
         <v>28.36</v>
       </c>
       <c r="AB63" s="12" t="n">
-        <v>30.34</v>
+        <v>30.36</v>
       </c>
       <c r="AC63" s="12" t="n">
-        <v>27.78</v>
+        <v>27.82</v>
       </c>
       <c r="AD63" s="12" t="n"/>
       <c r="AE63" s="9" t="n">
@@ -5381,10 +5375,10 @@
         <v>3.17</v>
       </c>
       <c r="AI63" s="10" t="n">
-        <v>3.59</v>
+        <v>3.52</v>
       </c>
       <c r="AJ63" s="10" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="AK63" s="10" t="n"/>
     </row>
@@ -5402,7 +5396,7 @@
         </is>
       </c>
       <c r="B65" s="8" t="n">
-        <v>43220</v>
+        <v>41747</v>
       </c>
       <c r="C65" s="9" t="n"/>
       <c r="D65" s="9" t="n">
@@ -5418,10 +5412,10 @@
         <v>14.4</v>
       </c>
       <c r="H65" s="10" t="n">
-        <v>15.55</v>
+        <v>16.21</v>
       </c>
       <c r="I65" s="10" t="n">
-        <v>13.49</v>
+        <v>14.81</v>
       </c>
       <c r="J65" s="9" t="n"/>
       <c r="K65" s="9" t="n">
@@ -5452,10 +5446,10 @@
         <v>1.54</v>
       </c>
       <c r="V65" s="10" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="W65" s="10" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="X65" s="11" t="n"/>
       <c r="Y65" s="11" t="n">
@@ -5471,10 +5465,10 @@
         <v>11.26</v>
       </c>
       <c r="AC65" s="12" t="n">
-        <v>11.97</v>
+        <v>10.93</v>
       </c>
       <c r="AD65" s="12" t="n">
-        <v>12.9</v>
+        <v>11.27</v>
       </c>
       <c r="AE65" s="9" t="n"/>
       <c r="AF65" s="9" t="n">
@@ -5490,10 +5484,10 @@
         <v>1.31</v>
       </c>
       <c r="AJ65" s="10" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AK65" s="10" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="66">
@@ -5503,7 +5497,7 @@
         </is>
       </c>
       <c r="B66" s="8" t="n">
-        <v>8139</v>
+        <v>7804</v>
       </c>
       <c r="C66" s="9" t="n"/>
       <c r="D66" s="9" t="n">
@@ -5519,10 +5513,10 @@
         <v>15.32</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>14.18</v>
+        <v>13.35</v>
       </c>
       <c r="I66" s="10" t="n">
-        <v>12.21</v>
+        <v>11.41</v>
       </c>
       <c r="J66" s="9" t="n"/>
       <c r="K66" s="9" t="n">
@@ -5553,10 +5547,10 @@
         <v>1.25</v>
       </c>
       <c r="V66" s="10" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="W66" s="10" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="X66" s="11" t="n"/>
       <c r="Y66" s="11" t="n">
@@ -5575,7 +5569,7 @@
         <v>9.73</v>
       </c>
       <c r="AD66" s="12" t="n">
-        <v>10.74</v>
+        <v>10.82</v>
       </c>
       <c r="AE66" s="9" t="n"/>
       <c r="AF66" s="9" t="n">
@@ -5591,10 +5585,10 @@
         <v>0.8</v>
       </c>
       <c r="AJ66" s="10" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="AK66" s="10" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="67">
@@ -5611,7 +5605,7 @@
         </is>
       </c>
       <c r="B68" s="8" t="n">
-        <v>74085</v>
+        <v>71495</v>
       </c>
       <c r="C68" s="9" t="n">
         <v>11.71</v>
@@ -5656,10 +5650,10 @@
         <v>3.37</v>
       </c>
       <c r="U68" s="10" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="V68" s="10" t="n">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="W68" s="10" t="n"/>
       <c r="X68" s="11" t="n">
@@ -5678,7 +5672,7 @@
         <v>23.11</v>
       </c>
       <c r="AC68" s="12" t="n">
-        <v>24.11</v>
+        <v>24.12</v>
       </c>
       <c r="AD68" s="12" t="n"/>
       <c r="AE68" s="9" t="n">
@@ -5694,10 +5688,10 @@
         <v>1.26</v>
       </c>
       <c r="AI68" s="10" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AJ68" s="10" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK68" s="10" t="n"/>
     </row>
@@ -5715,7 +5709,7 @@
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>27442</v>
+        <v>27156</v>
       </c>
       <c r="C70" s="9" t="n">
         <v>31.28</v>
@@ -5730,10 +5724,10 @@
         <v>23.11</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>16.68</v>
+        <v>16.93</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>13.15</v>
+        <v>13.05</v>
       </c>
       <c r="I70" s="10" t="n"/>
       <c r="J70" s="9" t="n">
@@ -5764,10 +5758,10 @@
         <v>2.2</v>
       </c>
       <c r="U70" s="10" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V70" s="10" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W70" s="10" t="n"/>
       <c r="X70" s="11" t="n">
@@ -5783,10 +5777,10 @@
         <v>10.49</v>
       </c>
       <c r="AB70" s="12" t="n">
-        <v>11.97</v>
+        <v>11.67</v>
       </c>
       <c r="AC70" s="12" t="n">
-        <v>13.89</v>
+        <v>13.87</v>
       </c>
       <c r="AD70" s="12" t="n"/>
       <c r="AE70" s="9" t="n">
@@ -5802,10 +5796,10 @@
         <v>2.17</v>
       </c>
       <c r="AI70" s="10" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AJ70" s="10" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AK70" s="10" t="n"/>
     </row>
@@ -5816,7 +5810,7 @@
         </is>
       </c>
       <c r="B71" s="8" t="n">
-        <v>14276</v>
+        <v>14144</v>
       </c>
       <c r="C71" s="9" t="n">
         <v>13.89</v>
@@ -5831,10 +5825,10 @@
         <v>20.71</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>11.28</v>
+        <v>12.14</v>
       </c>
       <c r="H71" s="10" t="n">
-        <v>8.83</v>
+        <v>8.94</v>
       </c>
       <c r="I71" s="10" t="n"/>
       <c r="J71" s="9" t="n">
@@ -5865,10 +5859,10 @@
         <v>2.25</v>
       </c>
       <c r="U71" s="10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="V71" s="10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W71" s="10" t="n"/>
       <c r="X71" s="11" t="n">
@@ -5884,10 +5878,10 @@
         <v>10.96</v>
       </c>
       <c r="AB71" s="12" t="n">
-        <v>13.73</v>
+        <v>12.65</v>
       </c>
       <c r="AC71" s="12" t="n">
-        <v>16.74</v>
+        <v>16.42</v>
       </c>
       <c r="AD71" s="12" t="n"/>
       <c r="AE71" s="9" t="n">
@@ -5906,7 +5900,7 @@
         <v>0.83</v>
       </c>
       <c r="AJ71" s="10" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="AK71" s="10" t="n"/>
     </row>
@@ -5930,10 +5924,10 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G72" s="15" t="n">
-        <v>10.7</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>9.43</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I72" s="15" t="n"/>
       <c r="J72" s="15" t="n">
@@ -5964,10 +5958,10 @@
         <v>0.66</v>
       </c>
       <c r="U72" s="15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="V72" s="15" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="W72" s="15" t="n"/>
       <c r="X72" s="16" t="n">
@@ -6002,10 +5996,10 @@
         <v>0.53</v>
       </c>
       <c r="AI72" s="15" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="AJ72" s="15" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="AK72" s="15" t="n"/>
     </row>
@@ -6029,10 +6023,10 @@
         <v>23.64</v>
       </c>
       <c r="G73" s="15" t="n">
-        <v>30.91</v>
+        <v>30.09</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>23.08</v>
+        <v>22.55</v>
       </c>
       <c r="I73" s="15" t="n"/>
       <c r="J73" s="15" t="n">
@@ -6063,10 +6057,10 @@
         <v>5.25</v>
       </c>
       <c r="U73" s="15" t="n">
-        <v>5.99</v>
+        <v>5.85</v>
       </c>
       <c r="V73" s="15" t="n">
-        <v>5.04</v>
+        <v>4.92</v>
       </c>
       <c r="W73" s="15" t="n"/>
       <c r="X73" s="16" t="n">
@@ -6082,10 +6076,10 @@
         <v>24.48</v>
       </c>
       <c r="AB73" s="16" t="n">
-        <v>24.07</v>
+        <v>24.09</v>
       </c>
       <c r="AC73" s="16" t="n">
-        <v>23.76</v>
+        <v>23.78</v>
       </c>
       <c r="AD73" s="16" t="n"/>
       <c r="AE73" s="15" t="n">
@@ -6101,10 +6095,10 @@
         <v>2.98</v>
       </c>
       <c r="AI73" s="15" t="n">
-        <v>4.07</v>
+        <v>3.98</v>
       </c>
       <c r="AJ73" s="15" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="AK73" s="15" t="n"/>
     </row>
@@ -6129,10 +6123,10 @@
         <v>14.86</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>14.87</v>
+        <v>14.78</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>12.85</v>
+        <v>13.11</v>
       </c>
       <c r="J74" s="15" t="n"/>
       <c r="K74" s="15" t="n">
@@ -6163,10 +6157,10 @@
         <v>1.4</v>
       </c>
       <c r="V74" s="15" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="W74" s="15" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="X74" s="16" t="n"/>
       <c r="Y74" s="16" t="n">
@@ -6182,10 +6176,10 @@
         <v>9.91</v>
       </c>
       <c r="AC74" s="16" t="n">
-        <v>10.85</v>
+        <v>10.33</v>
       </c>
       <c r="AD74" s="16" t="n">
-        <v>11.82</v>
+        <v>11.04</v>
       </c>
       <c r="AE74" s="15" t="n"/>
       <c r="AF74" s="15" t="n">
@@ -6201,10 +6195,10 @@
         <v>1.06</v>
       </c>
       <c r="AJ74" s="15" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AK74" s="15" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="75">
@@ -6257,10 +6251,10 @@
         <v>3.37</v>
       </c>
       <c r="U75" s="15" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="V75" s="15" t="n">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="W75" s="15" t="n"/>
       <c r="X75" s="16" t="n">
@@ -6279,7 +6273,7 @@
         <v>23.11</v>
       </c>
       <c r="AC75" s="16" t="n">
-        <v>24.11</v>
+        <v>24.12</v>
       </c>
       <c r="AD75" s="16" t="n"/>
       <c r="AE75" s="15" t="n">
@@ -6295,10 +6289,10 @@
         <v>1.26</v>
       </c>
       <c r="AI75" s="15" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AJ75" s="15" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK75" s="15" t="n"/>
     </row>
@@ -6322,10 +6316,10 @@
         <v>21.91</v>
       </c>
       <c r="G76" s="15" t="n">
-        <v>13.98</v>
+        <v>14.54</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>10.99</v>
+        <v>11</v>
       </c>
       <c r="I76" s="15" t="n"/>
       <c r="J76" s="15" t="n">
@@ -6356,10 +6350,10 @@
         <v>2.23</v>
       </c>
       <c r="U76" s="15" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V76" s="15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W76" s="15" t="n"/>
       <c r="X76" s="16" t="n">
@@ -6375,10 +6369,10 @@
         <v>10.73</v>
       </c>
       <c r="AB76" s="16" t="n">
-        <v>12.85</v>
+        <v>12.16</v>
       </c>
       <c r="AC76" s="16" t="n">
-        <v>15.31</v>
+        <v>15.14</v>
       </c>
       <c r="AD76" s="16" t="n"/>
       <c r="AE76" s="15" t="n">
@@ -6394,10 +6388,10 @@
         <v>1.76</v>
       </c>
       <c r="AI76" s="15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AJ76" s="15" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK76" s="15" t="n"/>
     </row>
@@ -6424,10 +6418,10 @@
         <v>15.32</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>14.18</v>
+        <v>13.35</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>12.85</v>
+        <v>13.11</v>
       </c>
       <c r="J77" s="15" t="n">
         <v>7.18</v>
@@ -6459,13 +6453,13 @@
         <v>1.48</v>
       </c>
       <c r="U77" s="15" t="n">
-        <v>1.73</v>
+        <v>1.99</v>
       </c>
       <c r="V77" s="15" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="W77" s="15" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="X77" s="16" t="n">
         <v>15.47</v>
@@ -6480,13 +6474,13 @@
         <v>10.49</v>
       </c>
       <c r="AB77" s="16" t="n">
-        <v>12.85</v>
+        <v>12.16</v>
       </c>
       <c r="AC77" s="16" t="n">
-        <v>15.31</v>
+        <v>15.14</v>
       </c>
       <c r="AD77" s="16" t="n">
-        <v>11.82</v>
+        <v>11.04</v>
       </c>
       <c r="AE77" s="15" t="n">
         <v>0.64</v>
@@ -6501,13 +6495,13 @@
         <v>0.97</v>
       </c>
       <c r="AI77" s="15" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AJ77" s="15" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK77" s="15" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -6630,7 +6624,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34029</v>
+        <v>37480</v>
       </c>
       <c r="F2" s="9" t="n"/>
       <c r="G2" s="9" t="n">
@@ -6643,10 +6637,10 @@
         <v>37.73</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>14.11</v>
+        <v>15.36</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>12.23</v>
+        <v>13.42</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -6672,7 +6666,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19759</v>
+        <v>19558</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n">
@@ -6685,10 +6679,10 @@
         <v>27.94</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>13.46</v>
+        <v>13.87</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>13.55</v>
+        <v>13.31</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -6714,7 +6708,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13580</v>
+        <v>13630</v>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n"/>
@@ -6725,7 +6719,7 @@
         <v>37.73</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>20.37</v>
+        <v>18.07</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>12.56</v>
@@ -6754,7 +6748,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>18309</v>
+        <v>19273</v>
       </c>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n">
@@ -6767,10 +6761,10 @@
         <v>13.27</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>6.21</v>
+        <v>7.06</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>5.8</v>
+        <v>6.08</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -6796,7 +6790,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1334</v>
+        <v>1349</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -6805,10 +6799,10 @@
         <v>10.3</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>5.87</v>
+        <v>6.46</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>6.12</v>
+        <v>6.17</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -6834,7 +6828,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
@@ -6844,9 +6838,7 @@
       <c r="I7" s="9" t="n">
         <v>36.95</v>
       </c>
-      <c r="J7" s="9" t="n">
-        <v>8.02</v>
-      </c>
+      <c r="J7" s="9" t="n"/>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
     </row>
@@ -6872,7 +6864,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5099</v>
+        <v>5195</v>
       </c>
       <c r="F8" s="9" t="n"/>
       <c r="G8" s="9" t="n"/>
@@ -6908,7 +6900,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7011</v>
+        <v>8257</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -6919,10 +6911,10 @@
         <v>32.18</v>
       </c>
       <c r="J9" s="9" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="K9" s="9" t="n">
         <v>26.15</v>
-      </c>
-      <c r="K9" s="9" t="n">
-        <v>22.27</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -6948,7 +6940,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1265</v>
+        <v>1328</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>14.21</v>
@@ -6963,10 +6955,10 @@
         <v>18.39</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>12.99</v>
+        <v>13.36</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>9.220000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -6992,7 +6984,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2826</v>
+        <v>3129</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
@@ -7003,10 +6995,10 @@
         <v>20.62</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>19.15</v>
+        <v>22.04</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>13.17</v>
+        <v>14.44</v>
       </c>
       <c r="L11" s="9" t="n"/>
     </row>
@@ -7032,7 +7024,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>844</v>
+        <v>815</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>23.46</v>
@@ -7045,10 +7037,10 @@
         <v>14.78</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>9.869999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="L12" s="9" t="n"/>
     </row>
@@ -7074,7 +7066,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>37.11</v>
@@ -7089,10 +7081,10 @@
         <v>13.58</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>5.92</v>
+        <v>6.88</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>5.92</v>
+        <v>5.79</v>
       </c>
       <c r="L13" s="9" t="n"/>
     </row>
@@ -7118,7 +7110,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9161</v>
+        <v>9485</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>41.88</v>
@@ -7133,10 +7125,10 @@
         <v>59.99</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>50.51</v>
+        <v>55.63</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>27.77</v>
+        <v>28.85</v>
       </c>
       <c r="L14" s="9" t="n"/>
     </row>
@@ -7162,7 +7154,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>40326</v>
+        <v>41472</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>19.31</v>
@@ -7177,10 +7169,10 @@
         <v>34.46</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>23.22</v>
+        <v>22.44</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>17.78</v>
+        <v>18.22</v>
       </c>
       <c r="L15" s="9" t="n"/>
     </row>
@@ -7206,7 +7198,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>10582</v>
+        <v>11044</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>16.34</v>
@@ -7221,10 +7213,10 @@
         <v>36.3</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>40.64</v>
+        <v>40.52</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>27.03</v>
+        <v>28.13</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -7250,7 +7242,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9558</v>
+        <v>9886</v>
       </c>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n">
@@ -7263,10 +7255,10 @@
         <v>41.99</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>92.31</v>
+        <v>89.69</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>29.54</v>
+        <v>30.44</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -7292,7 +7284,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10282</v>
+        <v>10100</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>15.67</v>
@@ -7307,10 +7299,10 @@
         <v>26.64</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>15.41</v>
+        <v>15.43</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>11.21</v>
+        <v>11.18</v>
       </c>
       <c r="L18" s="9" t="n"/>
     </row>
@@ -7336,7 +7328,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>120289</v>
+        <v>120040</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>21.56</v>
@@ -7351,10 +7343,10 @@
         <v>22.08</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>17.24</v>
+        <v>17.21</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>16.05</v>
+        <v>16.02</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -7380,7 +7372,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>73126</v>
+        <v>73692</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>17.07</v>
@@ -7395,10 +7387,10 @@
         <v>19.36</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>17.76</v>
+        <v>17.9</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>16.92</v>
+        <v>17.05</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -7424,7 +7416,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>97175</v>
+        <v>96232</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>20.08</v>
@@ -7439,10 +7431,10 @@
         <v>21.62</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>21.14</v>
+        <v>20.95</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>19.33</v>
+        <v>19.12</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -7468,7 +7460,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>269518</v>
+        <v>265343</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>28.47</v>
@@ -7483,10 +7475,10 @@
         <v>36.57</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>27.72</v>
+        <v>27.29</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>25.56</v>
+        <v>25.16</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -7512,7 +7504,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11220</v>
+        <v>10975</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>15.9</v>
@@ -7527,10 +7519,10 @@
         <v>22.06</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>15.45</v>
+        <v>15.11</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>13.72</v>
+        <v>13.42</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -7556,7 +7548,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>56078</v>
+        <v>53637</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>17.03</v>
@@ -7596,7 +7588,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>775</v>
+        <v>752</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>16.56</v>
@@ -7636,7 +7628,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>33829</v>
+        <v>33466</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>5</v>
@@ -7676,7 +7668,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>33190</v>
+        <v>31792</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>24.79</v>
@@ -7716,7 +7708,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4990</v>
+        <v>5097</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>10.61</v>
@@ -7731,10 +7723,10 @@
         <v>47.5</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>11.01</v>
+        <v>10.58</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>9.43</v>
+        <v>9.6</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -7760,7 +7752,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4466</v>
+        <v>4397</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>5.38</v>
@@ -7775,10 +7767,10 @@
         <v>13.73</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>10.7</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>9.48</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -7804,7 +7796,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>7.23</v>
@@ -7840,7 +7832,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>378716</v>
+        <v>380870</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>18.45</v>
@@ -7855,10 +7847,10 @@
         <v>30</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>29.94</v>
+        <v>30.11</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>25.14</v>
+        <v>25.28</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -7884,7 +7876,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>187497</v>
+        <v>182688</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>16.58</v>
@@ -7899,10 +7891,10 @@
         <v>24.83</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>38.25</v>
+        <v>37.27</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>30.59</v>
+        <v>29.81</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -7928,7 +7920,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>17886</v>
+        <v>16867</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>10.64</v>
@@ -7943,10 +7935,10 @@
         <v>22.45</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>31.88</v>
+        <v>30.06</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>21.02</v>
+        <v>19.82</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -7972,7 +7964,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>43220</v>
+        <v>41747</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -7988,10 +7980,10 @@
         <v>14.4</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>15.55</v>
+        <v>16.21</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>13.49</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="35">
@@ -8016,7 +8008,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>8139</v>
+        <v>7804</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -8032,10 +8024,10 @@
         <v>15.32</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>14.18</v>
+        <v>13.35</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>12.21</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="36">
@@ -8060,7 +8052,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>74085</v>
+        <v>71495</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>11.71</v>
@@ -8100,7 +8092,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>27442</v>
+        <v>27156</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>31.28</v>
@@ -8115,10 +8107,10 @@
         <v>23.11</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>16.68</v>
+        <v>16.93</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>13.15</v>
+        <v>13.05</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -8144,7 +8136,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14276</v>
+        <v>14144</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>13.89</v>
@@ -8159,10 +8151,10 @@
         <v>20.71</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>11.28</v>
+        <v>12.14</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>8.83</v>
+        <v>8.94</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -8188,7 +8180,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>5.78</v>
@@ -8203,10 +8195,10 @@
         <v>8.390000000000001</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>7.63</v>
+        <v>7.34</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>6.27</v>
+        <v>6.03</v>
       </c>
       <c r="L39" s="9" t="n"/>
     </row>
@@ -8232,7 +8224,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>7.57</v>
@@ -8272,7 +8264,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>5.71</v>
@@ -8312,7 +8304,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>63718</v>
+        <v>62409</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>11.71</v>
@@ -8327,10 +8319,10 @@
         <v>20.48</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>20.51</v>
+        <v>20.07</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>17.66</v>
+        <v>17.26</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -8446,7 +8438,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34029</v>
+        <v>37480</v>
       </c>
       <c r="F2" s="9" t="n"/>
       <c r="G2" s="9" t="n">
@@ -8484,7 +8476,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19759</v>
+        <v>19558</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n">
@@ -8522,7 +8514,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13580</v>
+        <v>13630</v>
       </c>
       <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n">
@@ -8560,7 +8552,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>18309</v>
+        <v>19273</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>40.3</v>
@@ -8600,7 +8592,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1334</v>
+        <v>1349</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -8634,7 +8626,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>87.52</v>
@@ -8672,7 +8664,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5099</v>
+        <v>5195</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>991.9299999999999</v>
@@ -8712,7 +8704,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7011</v>
+        <v>8257</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -8748,7 +8740,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1265</v>
+        <v>1328</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>11.7</v>
@@ -8788,7 +8780,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2826</v>
+        <v>3129</v>
       </c>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n">
@@ -8826,7 +8818,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>844</v>
+        <v>815</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>11.21</v>
@@ -8866,7 +8858,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>15.59</v>
@@ -8906,7 +8898,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9161</v>
+        <v>9485</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>14.66</v>
@@ -8946,7 +8938,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>40326</v>
+        <v>41472</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>7.97</v>
@@ -8986,7 +8978,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>10582</v>
+        <v>11044</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>9.449999999999999</v>
@@ -9026,7 +9018,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9558</v>
+        <v>9886</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>13.88</v>
@@ -9066,7 +9058,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10282</v>
+        <v>10100</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>20.45</v>
@@ -9106,7 +9098,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>120289</v>
+        <v>120040</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>15.68</v>
@@ -9146,7 +9138,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>73126</v>
+        <v>73692</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>12.31</v>
@@ -9186,7 +9178,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>97175</v>
+        <v>96232</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>14.87</v>
@@ -9226,7 +9218,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>269518</v>
+        <v>265343</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>15.21</v>
@@ -9266,7 +9258,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11220</v>
+        <v>10975</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>10.08</v>
@@ -9306,7 +9298,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>56078</v>
+        <v>53637</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>8.5</v>
@@ -9346,7 +9338,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>775</v>
+        <v>752</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>9.84</v>
@@ -9386,7 +9378,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>33829</v>
+        <v>33466</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>4.69</v>
@@ -9426,7 +9418,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>33190</v>
+        <v>31792</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>11.71</v>
@@ -9466,7 +9458,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4990</v>
+        <v>5097</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>7.18</v>
@@ -9506,7 +9498,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4466</v>
+        <v>4397</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>3.59</v>
@@ -9546,7 +9538,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>6.74</v>
@@ -9586,7 +9578,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>378716</v>
+        <v>380870</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>13.46</v>
@@ -9626,7 +9618,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>187497</v>
+        <v>182688</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>13.71</v>
@@ -9666,7 +9658,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>17886</v>
+        <v>16867</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>10.23</v>
@@ -9706,7 +9698,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>43220</v>
+        <v>41747</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -9746,7 +9738,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>8139</v>
+        <v>7804</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -9786,7 +9778,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>74085</v>
+        <v>71495</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>7.78</v>
@@ -9826,7 +9818,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>27442</v>
+        <v>27156</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>18.39</v>
@@ -9866,7 +9858,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14276</v>
+        <v>14144</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>7.78</v>
@@ -9906,7 +9898,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>3.96</v>
@@ -9946,7 +9938,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>2.92</v>
@@ -9986,7 +9978,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>3</v>
@@ -10026,7 +10018,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>63718</v>
+        <v>62409</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>6.73</v>
@@ -10156,7 +10148,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34029</v>
+        <v>37480</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>1.95</v>
@@ -10171,10 +10163,10 @@
         <v>5.72</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>3.95</v>
+        <v>4.15</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -10200,7 +10192,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19759</v>
+        <v>19558</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>2.73</v>
@@ -10215,10 +10207,10 @@
         <v>5.64</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="K3" s="9" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -10244,7 +10236,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13580</v>
+        <v>13630</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>1.21</v>
@@ -10259,7 +10251,7 @@
         <v>4.96</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>3.61</v>
+        <v>3.54</v>
       </c>
       <c r="K4" s="9" t="n">
         <v>2.76</v>
@@ -10288,7 +10280,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>18309</v>
+        <v>19273</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.51</v>
@@ -10303,10 +10295,10 @@
         <v>2.17</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -10332,7 +10324,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1334</v>
+        <v>1349</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -10341,10 +10333,10 @@
         <v>2.35</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -10370,7 +10362,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.85</v>
@@ -10384,9 +10376,7 @@
       <c r="I7" s="9" t="n">
         <v>2.84</v>
       </c>
-      <c r="J7" s="9" t="n">
-        <v>1.84</v>
-      </c>
+      <c r="J7" s="9" t="n"/>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
     </row>
@@ -10412,7 +10402,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5099</v>
+        <v>5195</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>1.54</v>
@@ -10427,10 +10417,10 @@
         <v>5.43</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="L8" s="9" t="n"/>
     </row>
@@ -10456,7 +10446,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7011</v>
+        <v>8257</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -10467,10 +10457,10 @@
         <v>10.52</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>9.17</v>
+        <v>10.95</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>7.61</v>
+        <v>8.94</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -10496,7 +10486,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1265</v>
+        <v>1328</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1.05</v>
@@ -10511,10 +10501,10 @@
         <v>6.21</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>3.44</v>
+        <v>2.86</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -10540,7 +10530,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2826</v>
+        <v>3129</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>2.39</v>
@@ -10555,10 +10545,10 @@
         <v>6.44</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>5.03</v>
+        <v>5.62</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>3.64</v>
+        <v>4.05</v>
       </c>
       <c r="L11" s="9" t="n"/>
     </row>
@@ -10584,7 +10574,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>844</v>
+        <v>815</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>1.18</v>
@@ -10599,10 +10589,10 @@
         <v>2.59</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="L12" s="9" t="n"/>
     </row>
@@ -10628,7 +10618,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>2.1</v>
@@ -10643,10 +10633,10 @@
         <v>2.93</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="L13" s="9" t="n"/>
     </row>
@@ -10672,7 +10662,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9161</v>
+        <v>9485</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>3.47</v>
@@ -10687,10 +10677,10 @@
         <v>6.09</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>5.98</v>
+        <v>6.37</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>5.32</v>
+        <v>5.49</v>
       </c>
       <c r="L14" s="9" t="n"/>
     </row>
@@ -10716,7 +10706,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>40326</v>
+        <v>41472</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>1.32</v>
@@ -10731,10 +10721,10 @@
         <v>5</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>4.52</v>
+        <v>4.74</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="L15" s="9" t="n"/>
     </row>
@@ -10760,7 +10750,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>10582</v>
+        <v>11044</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>2.15</v>
@@ -10775,10 +10765,10 @@
         <v>6.43</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>8.48</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>6.71</v>
+        <v>6.98</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -10804,7 +10794,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9558</v>
+        <v>9886</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.99</v>
@@ -10819,10 +10809,10 @@
         <v>2.1</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>2.32</v>
+        <v>2.69</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -10848,7 +10838,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10282</v>
+        <v>10100</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>2.04</v>
@@ -10863,10 +10853,10 @@
         <v>6.66</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="L18" s="9" t="n"/>
     </row>
@@ -10892,7 +10882,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>120289</v>
+        <v>120040</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>13.34</v>
@@ -10907,10 +10897,10 @@
         <v>16.48</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>11.81</v>
+        <v>11.79</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>8.65</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -10936,7 +10926,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>73126</v>
+        <v>73692</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>5.46</v>
@@ -10951,10 +10941,10 @@
         <v>4.86</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -10980,7 +10970,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>97175</v>
+        <v>96232</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>3.67</v>
@@ -10995,10 +10985,10 @@
         <v>3.55</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -11024,7 +11014,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>269518</v>
+        <v>265343</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>2.04</v>
@@ -11039,10 +11029,10 @@
         <v>3.77</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -11068,7 +11058,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11220</v>
+        <v>10975</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>2.64</v>
@@ -11083,10 +11073,10 @@
         <v>2.63</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -11112,7 +11102,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>56078</v>
+        <v>53637</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>2.86</v>
@@ -11127,10 +11117,10 @@
         <v>14.29</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>8.09</v>
+        <v>7.75</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>6.57</v>
+        <v>6.3</v>
       </c>
       <c r="L24" s="9" t="n"/>
     </row>
@@ -11156,7 +11146,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>775</v>
+        <v>752</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>2.35</v>
@@ -11200,7 +11190,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>33829</v>
+        <v>33466</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.65</v>
@@ -11215,10 +11205,10 @@
         <v>2.97</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -11244,7 +11234,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>33190</v>
+        <v>31792</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1.85</v>
@@ -11259,10 +11249,10 @@
         <v>6.69</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>6.35</v>
+        <v>6.16</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>5.43</v>
+        <v>5.26</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -11288,7 +11278,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4990</v>
+        <v>5097</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -11303,10 +11293,10 @@
         <v>2.61</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1.18</v>
+        <v>2.83</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -11332,7 +11322,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4466</v>
+        <v>4397</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -11347,10 +11337,10 @@
         <v>0.77</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -11376,7 +11366,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -11416,7 +11406,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>378716</v>
+        <v>380870</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>7.79</v>
@@ -11431,10 +11421,10 @@
         <v>12.5</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>12.35</v>
+        <v>12.42</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>9.06</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -11460,7 +11450,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>187497</v>
+        <v>182688</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>5.84</v>
@@ -11475,10 +11465,10 @@
         <v>4.81</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>6.45</v>
+        <v>6.28</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>5.68</v>
+        <v>5.53</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -11504,7 +11494,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>17886</v>
+        <v>16867</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>3.12</v>
@@ -11519,10 +11509,10 @@
         <v>1.48</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -11548,7 +11538,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>43220</v>
+        <v>41747</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -11564,10 +11554,10 @@
         <v>1.54</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="35">
@@ -11592,7 +11582,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>8139</v>
+        <v>7804</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -11608,10 +11598,10 @@
         <v>1.25</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="36">
@@ -11636,7 +11626,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>74085</v>
+        <v>71495</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>2.36</v>
@@ -11651,10 +11641,10 @@
         <v>3.37</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="L36" s="9" t="n"/>
     </row>
@@ -11680,7 +11670,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>27442</v>
+        <v>27156</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>2.06</v>
@@ -11695,10 +11685,10 @@
         <v>2.2</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -11724,7 +11714,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14276</v>
+        <v>14144</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>1.12</v>
@@ -11739,10 +11729,10 @@
         <v>2.25</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -11768,7 +11758,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>1.25</v>
@@ -11783,10 +11773,10 @@
         <v>0.92</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="L39" s="9" t="n"/>
     </row>
@@ -11812,7 +11802,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.5600000000000001</v>
@@ -11852,7 +11842,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.88</v>
@@ -11892,7 +11882,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>63718</v>
+        <v>62409</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>3.49</v>
@@ -11907,10 +11897,10 @@
         <v>5.69</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>5.53</v>
+        <v>5.42</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -12026,7 +12016,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34029</v>
+        <v>37480</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>-6.66</v>
@@ -12041,7 +12031,7 @@
         <v>18.82</v>
       </c>
       <c r="J2" s="11" t="n">
-        <v>30.98</v>
+        <v>30.52</v>
       </c>
       <c r="K2" s="11" t="n">
         <v>27.39</v>
@@ -12070,7 +12060,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19759</v>
+        <v>19558</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>-234.21</v>
@@ -12085,10 +12075,10 @@
         <v>22.59</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>27.32</v>
+        <v>26.58</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>21.57</v>
+        <v>21.78</v>
       </c>
       <c r="L3" s="11" t="n"/>
     </row>
@@ -12114,7 +12104,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13580</v>
+        <v>13630</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>-17.23</v>
@@ -12129,7 +12119,7 @@
         <v>13.74</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>20.18</v>
+        <v>21.73</v>
       </c>
       <c r="K4" s="11" t="n">
         <v>24.71</v>
@@ -12158,7 +12148,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>18309</v>
+        <v>19273</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>-2.23</v>
@@ -12173,7 +12163,7 @@
         <v>17.78</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>27.18</v>
+        <v>24.77</v>
       </c>
       <c r="K5" s="11" t="n">
         <v>23.63</v>
@@ -12202,7 +12192,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1334</v>
+        <v>1349</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>-7.73</v>
@@ -12217,7 +12207,7 @@
         <v>32.19</v>
       </c>
       <c r="J6" s="11" t="n">
-        <v>24.95</v>
+        <v>22.79</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>19.48</v>
@@ -12246,7 +12236,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>-13.03</v>
@@ -12260,9 +12250,7 @@
       <c r="I7" s="11" t="n">
         <v>10.15</v>
       </c>
-      <c r="J7" s="11" t="n">
-        <v>24.85</v>
-      </c>
+      <c r="J7" s="11" t="n"/>
       <c r="K7" s="11" t="n"/>
       <c r="L7" s="11" t="n"/>
     </row>
@@ -12288,7 +12276,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5099</v>
+        <v>5195</v>
       </c>
       <c r="F8" s="11" t="n">
         <v>-52.75</v>
@@ -12332,7 +12320,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7011</v>
+        <v>8257</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>57.58</v>
@@ -12347,7 +12335,7 @@
         <v>33.73</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>38.53</v>
+        <v>37.81</v>
       </c>
       <c r="K9" s="11" t="n">
         <v>37.64</v>
@@ -12376,7 +12364,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1265</v>
+        <v>1328</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>7.36</v>
@@ -12391,7 +12379,7 @@
         <v>41.36</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>26.46</v>
+        <v>24</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>25.85</v>
@@ -12420,7 +12408,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2826</v>
+        <v>3129</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>-18.17</v>
@@ -12435,10 +12423,10 @@
         <v>36.6</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>30.33</v>
+        <v>29.23</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>32.03</v>
+        <v>32.59</v>
       </c>
       <c r="L11" s="11" t="n"/>
     </row>
@@ -12464,7 +12452,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>844</v>
+        <v>815</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>5.01</v>
@@ -12479,7 +12467,7 @@
         <v>19.3</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>18.45</v>
+        <v>19.11</v>
       </c>
       <c r="K12" s="11" t="n">
         <v>19.15</v>
@@ -12508,7 +12496,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>5.67</v>
@@ -12523,7 +12511,7 @@
         <v>24.23</v>
       </c>
       <c r="J13" s="11" t="n">
-        <v>29.46</v>
+        <v>24.74</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>23.13</v>
@@ -12552,7 +12540,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9161</v>
+        <v>9485</v>
       </c>
       <c r="F14" s="11" t="n">
         <v>8.300000000000001</v>
@@ -12567,10 +12555,10 @@
         <v>10.51</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>12.47</v>
+        <v>11.95</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>20.59</v>
+        <v>20.45</v>
       </c>
       <c r="L14" s="11" t="n"/>
     </row>
@@ -12596,7 +12584,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>40326</v>
+        <v>41472</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>6.84</v>
@@ -12611,7 +12599,7 @@
         <v>19.14</v>
       </c>
       <c r="J15" s="11" t="n">
-        <v>21.52</v>
+        <v>23.15</v>
       </c>
       <c r="K15" s="11" t="n">
         <v>23.48</v>
@@ -12640,7 +12628,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>10582</v>
+        <v>11044</v>
       </c>
       <c r="F16" s="11" t="n">
         <v>13.15</v>
@@ -12655,10 +12643,10 @@
         <v>19.2</v>
       </c>
       <c r="J16" s="11" t="n">
-        <v>22.68</v>
+        <v>23.25</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>27.48</v>
+        <v>27.46</v>
       </c>
       <c r="L16" s="11" t="n"/>
     </row>
@@ -12684,7 +12672,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9558</v>
+        <v>9886</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>-3.83</v>
@@ -12699,7 +12687,7 @@
         <v>6.6</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="K17" s="11" t="n">
         <v>8.65</v>
@@ -12728,7 +12716,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10282</v>
+        <v>10100</v>
       </c>
       <c r="F18" s="11" t="n">
         <v>13.01</v>
@@ -12743,10 +12731,10 @@
         <v>30.05</v>
       </c>
       <c r="J18" s="11" t="n">
-        <v>25.7</v>
+        <v>25.21</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>27.68</v>
+        <v>27.27</v>
       </c>
       <c r="L18" s="11" t="n"/>
     </row>
@@ -12772,7 +12760,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>120289</v>
+        <v>120040</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>61.86</v>
@@ -12787,10 +12775,10 @@
         <v>76.87</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>82.53</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>62.2</v>
+        <v>62.21</v>
       </c>
       <c r="L19" s="11" t="n"/>
     </row>
@@ -12816,7 +12804,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>73126</v>
+        <v>73692</v>
       </c>
       <c r="F20" s="11" t="n">
         <v>31.97</v>
@@ -12860,7 +12848,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>97175</v>
+        <v>96232</v>
       </c>
       <c r="F21" s="11" t="n">
         <v>18.26</v>
@@ -12875,10 +12863,10 @@
         <v>17.66</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>16.99</v>
+        <v>16.98</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>16.73</v>
+        <v>16.75</v>
       </c>
       <c r="L21" s="11" t="n"/>
     </row>
@@ -12904,7 +12892,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>269518</v>
+        <v>265343</v>
       </c>
       <c r="F22" s="11" t="n">
         <v>7.16</v>
@@ -12948,7 +12936,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11220</v>
+        <v>10975</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>16.6</v>
@@ -12992,7 +12980,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>56078</v>
+        <v>53637</v>
       </c>
       <c r="F24" s="11" t="n">
         <v>16.81</v>
@@ -13007,10 +12995,10 @@
         <v>15.36</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>31.14</v>
+        <v>31.17</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>37.01</v>
+        <v>36.99</v>
       </c>
       <c r="L24" s="11" t="n"/>
     </row>
@@ -13036,7 +13024,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>775</v>
+        <v>752</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>14.19</v>
@@ -13051,10 +13039,10 @@
         <v>17.62</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>19.84</v>
+        <v>19.87</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>20.55</v>
+        <v>20.57</v>
       </c>
       <c r="L25" s="11" t="n"/>
     </row>
@@ -13080,7 +13068,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>33829</v>
+        <v>33466</v>
       </c>
       <c r="F26" s="11" t="n">
         <v>12.91</v>
@@ -13098,7 +13086,7 @@
         <v>13.7</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>14.91</v>
+        <v>14.89</v>
       </c>
       <c r="L26" s="11" t="n"/>
     </row>
@@ -13124,7 +13112,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>33190</v>
+        <v>31792</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>7.44</v>
@@ -13142,7 +13130,7 @@
         <v>17.2</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>18.63</v>
+        <v>18.76</v>
       </c>
       <c r="L27" s="11" t="n"/>
     </row>
@@ -13168,7 +13156,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4990</v>
+        <v>5097</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>7.62</v>
@@ -13183,7 +13171,7 @@
         <v>5.74</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>16.32</v>
+        <v>30.59</v>
       </c>
       <c r="K28" s="11" t="n">
         <v>25.82</v>
@@ -13212,7 +13200,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4466</v>
+        <v>4397</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>12.82</v>
@@ -13227,7 +13215,7 @@
         <v>5.71</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>7.52</v>
+        <v>8</v>
       </c>
       <c r="K29" s="11" t="n">
         <v>8.130000000000001</v>
@@ -13256,7 +13244,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F30" s="11" t="n">
         <v>11.21</v>
@@ -13296,7 +13284,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>378716</v>
+        <v>380870</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>42.25</v>
@@ -13340,7 +13328,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>187497</v>
+        <v>182688</v>
       </c>
       <c r="F32" s="11" t="n">
         <v>35.19</v>
@@ -13384,7 +13372,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>17886</v>
+        <v>16867</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>29.29</v>
@@ -13428,7 +13416,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>43220</v>
+        <v>41747</v>
       </c>
       <c r="F34" s="11" t="n"/>
       <c r="G34" s="11" t="n">
@@ -13444,10 +13432,10 @@
         <v>11.26</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>11.97</v>
+        <v>10.93</v>
       </c>
       <c r="L34" s="11" t="n">
-        <v>12.9</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="35">
@@ -13472,7 +13460,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>8139</v>
+        <v>7804</v>
       </c>
       <c r="F35" s="11" t="n"/>
       <c r="G35" s="11" t="n">
@@ -13491,7 +13479,7 @@
         <v>9.73</v>
       </c>
       <c r="L35" s="11" t="n">
-        <v>10.74</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="36">
@@ -13516,7 +13504,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>74085</v>
+        <v>71495</v>
       </c>
       <c r="F36" s="11" t="n">
         <v>20.11</v>
@@ -13534,7 +13522,7 @@
         <v>23.11</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>24.11</v>
+        <v>24.12</v>
       </c>
       <c r="L36" s="11" t="n"/>
     </row>
@@ -13560,7 +13548,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>27442</v>
+        <v>27156</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>6.6</v>
@@ -13575,10 +13563,10 @@
         <v>10.49</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>11.97</v>
+        <v>11.67</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>13.89</v>
+        <v>13.87</v>
       </c>
       <c r="L37" s="11" t="n"/>
     </row>
@@ -13604,7 +13592,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14276</v>
+        <v>14144</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>8.1</v>
@@ -13619,10 +13607,10 @@
         <v>10.96</v>
       </c>
       <c r="J38" s="11" t="n">
-        <v>13.73</v>
+        <v>12.65</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>16.74</v>
+        <v>16.42</v>
       </c>
       <c r="L38" s="11" t="n"/>
     </row>
@@ -13648,7 +13636,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F39" s="11" t="n">
         <v>21.69</v>
@@ -13692,7 +13680,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>7.43</v>
@@ -13732,7 +13720,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>15.47</v>
@@ -13772,7 +13760,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>63718</v>
+        <v>62409</v>
       </c>
       <c r="F42" s="11" t="n">
         <v>29.81</v>
@@ -13787,10 +13775,10 @@
         <v>28.36</v>
       </c>
       <c r="J42" s="11" t="n">
-        <v>30.34</v>
+        <v>30.36</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>27.78</v>
+        <v>27.82</v>
       </c>
       <c r="L42" s="11" t="n"/>
     </row>
@@ -13906,7 +13894,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="n">
-        <v>34029</v>
+        <v>37480</v>
       </c>
       <c r="F2" s="9" t="n">
         <v>1.14</v>
@@ -13921,10 +13909,10 @@
         <v>3.04</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="K2" s="9" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="L2" s="9" t="n"/>
     </row>
@@ -13950,7 +13938,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>19759</v>
+        <v>19558</v>
       </c>
       <c r="F3" s="9" t="n">
         <v>0.42</v>
@@ -13965,10 +13953,10 @@
         <v>2.72</v>
       </c>
       <c r="J3" s="9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="K3" s="9" t="n">
         <v>1.67</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>1.7</v>
       </c>
       <c r="L3" s="9" t="n"/>
     </row>
@@ -13994,7 +13982,7 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>13580</v>
+        <v>13630</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>0.73</v>
@@ -14038,7 +14026,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>18309</v>
+        <v>19273</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0.29</v>
@@ -14053,10 +14041,10 @@
         <v>0.96</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L5" s="9" t="n"/>
     </row>
@@ -14082,7 +14070,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1334</v>
+        <v>1349</v>
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="9" t="n"/>
@@ -14091,10 +14079,10 @@
         <v>2.09</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="L6" s="9" t="n"/>
     </row>
@@ -14120,7 +14108,7 @@
         </is>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0.18</v>
@@ -14160,7 +14148,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5099</v>
+        <v>5195</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>0.12</v>
@@ -14175,10 +14163,10 @@
         <v>0.61</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="L8" s="9" t="n"/>
     </row>
@@ -14204,7 +14192,7 @@
         </is>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7011</v>
+        <v>8257</v>
       </c>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
@@ -14215,10 +14203,10 @@
         <v>4.38</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>4.06</v>
+        <v>4.77</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>3.53</v>
+        <v>4.14</v>
       </c>
       <c r="L9" s="9" t="n"/>
     </row>
@@ -14244,7 +14232,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1265</v>
+        <v>1328</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1.13</v>
@@ -14259,10 +14247,10 @@
         <v>7.54</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="L10" s="9" t="n"/>
     </row>
@@ -14288,7 +14276,7 @@
         </is>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2826</v>
+        <v>3129</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>0.6899999999999999</v>
@@ -14303,10 +14291,10 @@
         <v>2.61</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>2.36</v>
+        <v>2.57</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="L11" s="9" t="n"/>
     </row>
@@ -14332,7 +14320,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>844</v>
+        <v>815</v>
       </c>
       <c r="F12" s="9" t="n">
         <v>1.29</v>
@@ -14347,10 +14335,10 @@
         <v>1.65</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="L12" s="9" t="n"/>
     </row>
@@ -14376,7 +14364,7 @@
         </is>
       </c>
       <c r="E13" s="7" t="n">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>0.72</v>
@@ -14391,10 +14379,10 @@
         <v>1.02</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="L13" s="9" t="n"/>
     </row>
@@ -14420,7 +14408,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>9161</v>
+        <v>9485</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>1.78</v>
@@ -14435,10 +14423,10 @@
         <v>3.02</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="L14" s="9" t="n"/>
     </row>
@@ -14464,7 +14452,7 @@
         </is>
       </c>
       <c r="E15" s="7" t="n">
-        <v>40326</v>
+        <v>41472</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>0.53</v>
@@ -14479,10 +14467,10 @@
         <v>1.81</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="L15" s="9" t="n"/>
     </row>
@@ -14508,7 +14496,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>10582</v>
+        <v>11044</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.9</v>
@@ -14523,10 +14511,10 @@
         <v>2.14</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="L16" s="9" t="n"/>
     </row>
@@ -14552,7 +14540,7 @@
         </is>
       </c>
       <c r="E17" s="7" t="n">
-        <v>9558</v>
+        <v>9886</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>0.9</v>
@@ -14567,10 +14555,10 @@
         <v>2.78</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="L17" s="9" t="n"/>
     </row>
@@ -14596,7 +14584,7 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10282</v>
+        <v>10100</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>0.98</v>
@@ -14611,10 +14599,10 @@
         <v>3.51</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="L18" s="9" t="n"/>
     </row>
@@ -14640,7 +14628,7 @@
         </is>
       </c>
       <c r="E19" s="7" t="n">
-        <v>120289</v>
+        <v>120040</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>1.87</v>
@@ -14655,10 +14643,10 @@
         <v>1.48</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="L19" s="9" t="n"/>
     </row>
@@ -14684,7 +14672,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>73126</v>
+        <v>73692</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>2.28</v>
@@ -14699,10 +14687,10 @@
         <v>1.93</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="L20" s="9" t="n"/>
     </row>
@@ -14728,7 +14716,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>97175</v>
+        <v>96232</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>1.73</v>
@@ -14743,10 +14731,10 @@
         <v>1.73</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="L21" s="9" t="n"/>
     </row>
@@ -14772,7 +14760,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>269518</v>
+        <v>265343</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>2.21</v>
@@ -14787,10 +14775,10 @@
         <v>2.78</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="L22" s="9" t="n"/>
     </row>
@@ -14816,7 +14804,7 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>11220</v>
+        <v>10975</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>0.86</v>
@@ -14831,10 +14819,10 @@
         <v>1.07</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="L23" s="9" t="n"/>
     </row>
@@ -14860,7 +14848,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>56078</v>
+        <v>53637</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>1.26</v>
@@ -14875,10 +14863,10 @@
         <v>7.21</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>3.46</v>
+        <v>3.31</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="L24" s="9" t="n"/>
     </row>
@@ -14904,7 +14892,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>775</v>
+        <v>752</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>1.24</v>
@@ -14948,7 +14936,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>33829</v>
+        <v>33466</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>0.32</v>
@@ -14963,10 +14951,10 @@
         <v>1.45</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="L26" s="9" t="n"/>
     </row>
@@ -14992,7 +14980,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>33190</v>
+        <v>31792</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1.3</v>
@@ -15007,10 +14995,10 @@
         <v>3.66</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="L27" s="9" t="n"/>
     </row>
@@ -15036,7 +15024,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4990</v>
+        <v>5097</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>0.34</v>
@@ -15051,10 +15039,10 @@
         <v>1.25</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="L28" s="9" t="n"/>
     </row>
@@ -15080,7 +15068,7 @@
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>4466</v>
+        <v>4397</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>0.4</v>
@@ -15095,10 +15083,10 @@
         <v>0.63</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="L29" s="9" t="n"/>
     </row>
@@ -15124,7 +15112,7 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>0.19</v>
@@ -15164,7 +15152,7 @@
         </is>
       </c>
       <c r="E31" s="7" t="n">
-        <v>378716</v>
+        <v>380870</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>2.08</v>
@@ -15179,10 +15167,10 @@
         <v>3.94</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>4.78</v>
+        <v>4.81</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="L31" s="9" t="n"/>
     </row>
@@ -15208,7 +15196,7 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>187497</v>
+        <v>182688</v>
       </c>
       <c r="F32" s="9" t="n">
         <v>2.31</v>
@@ -15223,10 +15211,10 @@
         <v>2.79</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>4.56</v>
+        <v>4.44</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="L32" s="9" t="n"/>
     </row>
@@ -15252,7 +15240,7 @@
         </is>
       </c>
       <c r="E33" s="7" t="n">
-        <v>17886</v>
+        <v>16867</v>
       </c>
       <c r="F33" s="9" t="n">
         <v>0.92</v>
@@ -15267,10 +15255,10 @@
         <v>0.63</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="L33" s="9" t="n"/>
     </row>
@@ -15296,7 +15284,7 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>43220</v>
+        <v>41747</v>
       </c>
       <c r="F34" s="9" t="n"/>
       <c r="G34" s="9" t="n">
@@ -15312,10 +15300,10 @@
         <v>1.31</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="35">
@@ -15340,7 +15328,7 @@
         </is>
       </c>
       <c r="E35" s="7" t="n">
-        <v>8139</v>
+        <v>7804</v>
       </c>
       <c r="F35" s="9" t="n"/>
       <c r="G35" s="9" t="n">
@@ -15356,10 +15344,10 @@
         <v>0.8</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="36">
@@ -15384,7 +15372,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>74085</v>
+        <v>71495</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>0.8100000000000001</v>
@@ -15399,10 +15387,10 @@
         <v>1.26</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="L36" s="9" t="n"/>
     </row>
@@ -15428,7 +15416,7 @@
         </is>
       </c>
       <c r="E37" s="7" t="n">
-        <v>27442</v>
+        <v>27156</v>
       </c>
       <c r="F37" s="9" t="n">
         <v>1.66</v>
@@ -15443,10 +15431,10 @@
         <v>2.17</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="L37" s="9" t="n"/>
     </row>
@@ -15472,7 +15460,7 @@
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>14276</v>
+        <v>14144</v>
       </c>
       <c r="F38" s="9" t="n">
         <v>0.64</v>
@@ -15490,7 +15478,7 @@
         <v>0.83</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="L38" s="9" t="n"/>
     </row>
@@ -15516,7 +15504,7 @@
         </is>
       </c>
       <c r="E39" s="7" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F39" s="9" t="n">
         <v>0.49</v>
@@ -15531,10 +15519,10 @@
         <v>0.59</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="L39" s="9" t="n"/>
     </row>
@@ -15560,7 +15548,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F40" s="9" t="n">
         <v>0.32</v>
@@ -15600,7 +15588,7 @@
         </is>
       </c>
       <c r="E41" s="7" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F41" s="9" t="n">
         <v>0.5</v>
@@ -15640,7 +15628,7 @@
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>63718</v>
+        <v>62409</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>2.12</v>
@@ -15655,10 +15643,10 @@
         <v>3.17</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>3.59</v>
+        <v>3.52</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="L42" s="9" t="n"/>
     </row>
@@ -16122,7 +16110,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>436500</v>
+        <v>479000</v>
       </c>
       <c r="H6" s="17" t="n">
         <v>31175.2</v>
@@ -16140,17 +16128,17 @@
         <v>12097690124766.46</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>14.11</v>
+        <v>15.36</v>
       </c>
       <c r="N6" s="17" t="n"/>
       <c r="O6" s="17" t="n">
-        <v>3.95</v>
+        <v>4.15</v>
       </c>
       <c r="P6" s="17" t="n">
-        <v>30.98</v>
+        <v>30.52</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="R6" s="17" t="inlineStr">
         <is>
@@ -16195,7 +16183,7 @@
         </is>
       </c>
       <c r="G7" s="17" t="n">
-        <v>436500</v>
+        <v>479000</v>
       </c>
       <c r="H7" s="17" t="n">
         <v>35696.77</v>
@@ -16213,17 +16201,17 @@
         <v>15253493850623.39</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>12.23</v>
+        <v>13.42</v>
       </c>
       <c r="N7" s="17" t="n"/>
       <c r="O7" s="17" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P7" s="17" t="n">
         <v>27.39</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="R7" s="17" t="inlineStr">
         <is>
@@ -16617,35 +16605,35 @@
         </is>
       </c>
       <c r="G13" s="17" t="n">
-        <v>86800</v>
+        <v>85600</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>6366.76</v>
+        <v>6173.04</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>26504.84</v>
+        <v>26311.12</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>15901006750000</v>
+        <v>15927238960000</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>1950757967098.494</v>
+        <v>1891401968679.605</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>8121009511148.494</v>
+        <v>8061653512729.605</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>13.46</v>
+        <v>13.87</v>
       </c>
       <c r="N13" s="17" t="n"/>
       <c r="O13" s="17" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="P13" s="17" t="n">
-        <v>27.32</v>
+        <v>26.58</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R13" s="17" t="inlineStr">
         <is>
@@ -16690,35 +16678,35 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>86800</v>
+        <v>85600</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>6407.04</v>
+        <v>6429.76</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>32911.89</v>
+        <v>32740.89</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>15625263740000</v>
+        <v>15659930410000</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>1963099645790.854</v>
+        <v>1970061602673.868</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>10084109156939.35</v>
+        <v>10031715115403.47</v>
       </c>
       <c r="M14" s="17" t="n">
-        <v>13.55</v>
+        <v>13.31</v>
       </c>
       <c r="N14" s="17" t="n"/>
       <c r="O14" s="17" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="P14" s="17" t="n">
-        <v>21.57</v>
+        <v>21.78</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R14" s="17" t="inlineStr">
         <is>
@@ -17128,14 +17116,14 @@
         <v>5160222652769.023</v>
       </c>
       <c r="M20" s="17" t="n">
-        <v>20.37</v>
+        <v>18.07</v>
       </c>
       <c r="N20" s="17" t="n"/>
       <c r="O20" s="17" t="n">
-        <v>3.61</v>
+        <v>3.54</v>
       </c>
       <c r="P20" s="17" t="n">
-        <v>20.18</v>
+        <v>21.73</v>
       </c>
       <c r="Q20" s="17" t="n">
         <v>1.42</v>
@@ -17607,7 +17595,7 @@
         </is>
       </c>
       <c r="G27" s="17" t="n">
-        <v>348500</v>
+        <v>365500</v>
       </c>
       <c r="H27" s="17" t="n">
         <v>51760.25</v>
@@ -17625,17 +17613,17 @@
         <v>16263290290871.05</v>
       </c>
       <c r="M27" s="17" t="n">
-        <v>6.21</v>
+        <v>7.06</v>
       </c>
       <c r="N27" s="17" t="n"/>
       <c r="O27" s="17" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="P27" s="17" t="n">
-        <v>27.18</v>
+        <v>24.77</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="R27" s="17" t="inlineStr">
         <is>
@@ -17680,7 +17668,7 @@
         </is>
       </c>
       <c r="G28" s="17" t="n">
-        <v>348500</v>
+        <v>365500</v>
       </c>
       <c r="H28" s="17" t="n">
         <v>60133.68</v>
@@ -17698,17 +17686,17 @@
         <v>19722136500824.19</v>
       </c>
       <c r="M28" s="17" t="n">
-        <v>5.8</v>
+        <v>6.08</v>
       </c>
       <c r="N28" s="17" t="n"/>
       <c r="O28" s="17" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="P28" s="17" t="n">
         <v>23.63</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R28" s="17" t="inlineStr">
         <is>
@@ -18076,7 +18064,7 @@
         </is>
       </c>
       <c r="G34" s="17" t="n">
-        <v>46950</v>
+        <v>47300</v>
       </c>
       <c r="H34" s="17" t="n">
         <v>7317.5</v>
@@ -18094,17 +18082,17 @@
         <v>1363491609003.722</v>
       </c>
       <c r="M34" s="17" t="n">
-        <v>5.87</v>
+        <v>6.46</v>
       </c>
       <c r="N34" s="17" t="n"/>
       <c r="O34" s="17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P34" s="17" t="n">
-        <v>24.95</v>
+        <v>22.79</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
@@ -18149,7 +18137,7 @@
         </is>
       </c>
       <c r="G35" s="17" t="n">
-        <v>46950</v>
+        <v>47300</v>
       </c>
       <c r="H35" s="17" t="n">
         <v>7666.2</v>
@@ -18167,17 +18155,17 @@
         <v>1647518204706.319</v>
       </c>
       <c r="M35" s="17" t="n">
-        <v>6.12</v>
+        <v>6.17</v>
       </c>
       <c r="N35" s="17" t="n"/>
       <c r="O35" s="17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P35" s="17" t="n">
         <v>19.48</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
@@ -18569,7 +18557,7 @@
         </is>
       </c>
       <c r="G41" s="17" t="n">
-        <v>16110</v>
+        <v>15990</v>
       </c>
       <c r="H41" s="17" t="n"/>
       <c r="I41" s="17" t="n"/>
@@ -18578,16 +18566,10 @@
       </c>
       <c r="K41" s="18" t="n"/>
       <c r="L41" s="18" t="n"/>
-      <c r="M41" s="17" t="n">
-        <v>8.02</v>
-      </c>
+      <c r="M41" s="17" t="n"/>
       <c r="N41" s="17" t="n"/>
-      <c r="O41" s="17" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="P41" s="17" t="n">
-        <v>24.85</v>
-      </c>
+      <c r="O41" s="17" t="n"/>
+      <c r="P41" s="17" t="n"/>
       <c r="Q41" s="17" t="n"/>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -18632,7 +18614,7 @@
         </is>
       </c>
       <c r="G42" s="17" t="n">
-        <v>16110</v>
+        <v>15990</v>
       </c>
       <c r="H42" s="17" t="n"/>
       <c r="I42" s="17" t="n"/>
@@ -19056,13 +19038,13 @@
       <c r="M48" s="17" t="n"/>
       <c r="N48" s="17" t="n"/>
       <c r="O48" s="17" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="P48" s="17" t="n">
         <v>16.62</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -19125,13 +19107,13 @@
       <c r="M49" s="17" t="n"/>
       <c r="N49" s="17" t="n"/>
       <c r="O49" s="17" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="P49" s="17" t="n">
         <v>20</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
@@ -19509,35 +19491,35 @@
         </is>
       </c>
       <c r="G55" s="17" t="n">
-        <v>210500</v>
+        <v>247000</v>
       </c>
       <c r="H55" s="17" t="n">
-        <v>7767.72</v>
+        <v>7741.59</v>
       </c>
       <c r="I55" s="17" t="n">
-        <v>22571.32</v>
+        <v>22557.28</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>2323641630000</v>
+        <v>2320660330000</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>348237212674.865</v>
+        <v>347065994047.99</v>
       </c>
       <c r="L55" s="18" t="n">
-        <v>1011902357272.74</v>
+        <v>1011272827260.795</v>
       </c>
       <c r="M55" s="17" t="n">
-        <v>26.15</v>
+        <v>31.91</v>
       </c>
       <c r="N55" s="17" t="n"/>
       <c r="O55" s="17" t="n">
-        <v>9.17</v>
+        <v>10.95</v>
       </c>
       <c r="P55" s="17" t="n">
-        <v>38.53</v>
+        <v>37.81</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>4.06</v>
+        <v>4.77</v>
       </c>
       <c r="R55" s="17" t="inlineStr">
         <is>
@@ -19582,35 +19564,35 @@
         </is>
       </c>
       <c r="G56" s="17" t="n">
-        <v>210500</v>
+        <v>247000</v>
       </c>
       <c r="H56" s="17" t="n">
-        <v>9452.709999999999</v>
+        <v>9447.08</v>
       </c>
       <c r="I56" s="17" t="n">
-        <v>27652.15</v>
+        <v>27635.08</v>
       </c>
       <c r="J56" s="18" t="n">
-        <v>2676693990000</v>
+        <v>2675633640000</v>
       </c>
       <c r="K56" s="18" t="n">
-        <v>423777698330.52</v>
+        <v>423524984095.1251</v>
       </c>
       <c r="L56" s="18" t="n">
-        <v>1239682870125.395</v>
+        <v>1238917506211.924</v>
       </c>
       <c r="M56" s="17" t="n">
-        <v>22.27</v>
+        <v>26.15</v>
       </c>
       <c r="N56" s="17" t="n"/>
       <c r="O56" s="17" t="n">
-        <v>7.61</v>
+        <v>8.94</v>
       </c>
       <c r="P56" s="17" t="n">
         <v>37.64</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>3.53</v>
+        <v>4.14</v>
       </c>
       <c r="R56" s="17" t="inlineStr">
         <is>
@@ -20008,7 +19990,7 @@
         </is>
       </c>
       <c r="G62" s="17" t="n">
-        <v>50200</v>
+        <v>52500</v>
       </c>
       <c r="H62" s="17" t="n">
         <v>3930.5</v>
@@ -20026,17 +20008,17 @@
         <v>622240560926.5</v>
       </c>
       <c r="M62" s="17" t="n">
-        <v>12.99</v>
+        <v>13.36</v>
       </c>
       <c r="N62" s="17" t="n"/>
       <c r="O62" s="17" t="n">
-        <v>3.44</v>
+        <v>2.86</v>
       </c>
       <c r="P62" s="17" t="n">
-        <v>26.46</v>
+        <v>24</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="R62" s="17" t="inlineStr">
         <is>
@@ -20081,7 +20063,7 @@
         </is>
       </c>
       <c r="G63" s="17" t="n">
-        <v>50200</v>
+        <v>52500</v>
       </c>
       <c r="H63" s="17" t="n">
         <v>5446</v>
@@ -20099,17 +20081,17 @@
         <v>806976902884.5</v>
       </c>
       <c r="M63" s="17" t="n">
-        <v>9.220000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="N63" s="17" t="n"/>
       <c r="O63" s="17" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="P63" s="17" t="n">
         <v>25.85</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="R63" s="17" t="inlineStr">
         <is>
@@ -20501,35 +20483,35 @@
         </is>
       </c>
       <c r="G69" s="17" t="n">
-        <v>45600</v>
+        <v>50300</v>
       </c>
       <c r="H69" s="17" t="n">
-        <v>2412.78</v>
+        <v>2281.89</v>
       </c>
       <c r="I69" s="17" t="n">
-        <v>9078.639999999999</v>
+        <v>8947.75</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>1610128790000</v>
+        <v>1631819770000</v>
       </c>
       <c r="K69" s="18" t="n">
-        <v>201287095264.946</v>
+        <v>190367860690.936</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>757389995184.946</v>
+        <v>746470760610.936</v>
       </c>
       <c r="M69" s="17" t="n">
-        <v>19.15</v>
+        <v>22.04</v>
       </c>
       <c r="N69" s="17" t="n"/>
       <c r="O69" s="17" t="n">
-        <v>5.03</v>
+        <v>5.62</v>
       </c>
       <c r="P69" s="17" t="n">
-        <v>30.33</v>
+        <v>29.23</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>2.36</v>
+        <v>2.57</v>
       </c>
       <c r="R69" s="17" t="inlineStr">
         <is>
@@ -20574,35 +20556,35 @@
         </is>
       </c>
       <c r="G70" s="17" t="n">
-        <v>45600</v>
+        <v>50300</v>
       </c>
       <c r="H70" s="17" t="n">
-        <v>3462.71</v>
+        <v>3484.13</v>
       </c>
       <c r="I70" s="17" t="n">
-        <v>12541.35</v>
+        <v>12431.88</v>
       </c>
       <c r="J70" s="18" t="n">
-        <v>2147608440000</v>
+        <v>2185487500000</v>
       </c>
       <c r="K70" s="18" t="n">
-        <v>288878801372.204</v>
+        <v>290665459314.871</v>
       </c>
       <c r="L70" s="18" t="n">
-        <v>1046268796557.15</v>
+        <v>1037136219925.807</v>
       </c>
       <c r="M70" s="17" t="n">
-        <v>13.17</v>
+        <v>14.44</v>
       </c>
       <c r="N70" s="17" t="n"/>
       <c r="O70" s="17" t="n">
-        <v>3.64</v>
+        <v>4.05</v>
       </c>
       <c r="P70" s="17" t="n">
-        <v>32.03</v>
+        <v>32.59</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="R70" s="17" t="inlineStr">
         <is>
@@ -20998,7 +20980,7 @@
         </is>
       </c>
       <c r="G76" s="17" t="n">
-        <v>22550</v>
+        <v>21700</v>
       </c>
       <c r="H76" s="17" t="n">
         <v>2393.79</v>
@@ -21016,17 +20998,17 @@
         <v>681678021001.8715</v>
       </c>
       <c r="M76" s="17" t="n">
-        <v>9.869999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="N76" s="17" t="n"/>
       <c r="O76" s="17" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="P76" s="17" t="n">
-        <v>18.45</v>
+        <v>19.11</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="R76" s="17" t="inlineStr">
         <is>
@@ -21071,7 +21053,7 @@
         </is>
       </c>
       <c r="G77" s="17" t="n">
-        <v>22550</v>
+        <v>21700</v>
       </c>
       <c r="H77" s="17" t="n">
         <v>2818.93</v>
@@ -21089,17 +21071,17 @@
         <v>801213744014.1482</v>
       </c>
       <c r="M77" s="17" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="N77" s="17" t="n"/>
       <c r="O77" s="17" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="P77" s="17" t="n">
         <v>19.15</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="R77" s="17" t="inlineStr">
         <is>
@@ -21497,7 +21479,7 @@
         </is>
       </c>
       <c r="G83" s="17" t="n">
-        <v>17160</v>
+        <v>16790</v>
       </c>
       <c r="H83" s="17" t="n">
         <v>2442</v>
@@ -21515,17 +21497,17 @@
         <v>331992443278</v>
       </c>
       <c r="M83" s="17" t="n">
-        <v>5.92</v>
+        <v>6.88</v>
       </c>
       <c r="N83" s="17" t="n"/>
       <c r="O83" s="17" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="P83" s="17" t="n">
-        <v>29.46</v>
+        <v>24.74</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="R83" s="17" t="inlineStr">
         <is>
@@ -21570,7 +21552,7 @@
         </is>
       </c>
       <c r="G84" s="17" t="n">
-        <v>17160</v>
+        <v>16790</v>
       </c>
       <c r="H84" s="17" t="n">
         <v>2901</v>
@@ -21588,17 +21570,17 @@
         <v>418828450507</v>
       </c>
       <c r="M84" s="17" t="n">
-        <v>5.92</v>
+        <v>5.79</v>
       </c>
       <c r="N84" s="17" t="n"/>
       <c r="O84" s="17" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P84" s="17" t="n">
         <v>23.13</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="R84" s="17" t="inlineStr">
         <is>
@@ -21996,7 +21978,7 @@
         </is>
       </c>
       <c r="G90" s="17" t="n">
-        <v>126500</v>
+        <v>130500</v>
       </c>
       <c r="H90" s="17" t="n">
         <v>2345.72</v>
@@ -22005,7 +21987,7 @@
         <v>20476.64</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>5369467450000</v>
+        <v>5363531540000</v>
       </c>
       <c r="K90" s="18" t="n">
         <v>228649113041.826</v>
@@ -22014,17 +21996,17 @@
         <v>1995963043226.628</v>
       </c>
       <c r="M90" s="17" t="n">
-        <v>50.51</v>
+        <v>55.63</v>
       </c>
       <c r="N90" s="17" t="n"/>
       <c r="O90" s="17" t="n">
-        <v>5.98</v>
+        <v>6.37</v>
       </c>
       <c r="P90" s="17" t="n">
-        <v>12.47</v>
+        <v>11.95</v>
       </c>
       <c r="Q90" s="17" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="R90" s="17" t="inlineStr">
         <is>
@@ -22069,35 +22051,35 @@
         </is>
       </c>
       <c r="G91" s="17" t="n">
-        <v>126500</v>
+        <v>130500</v>
       </c>
       <c r="H91" s="17" t="n">
-        <v>4555.93</v>
+        <v>4522.94</v>
       </c>
       <c r="I91" s="17" t="n">
-        <v>23780.15</v>
+        <v>23756.23</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>6652413670000</v>
+        <v>6650915760000</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>444089959184.724</v>
+        <v>440874060454.58</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>2317972672631.471</v>
+        <v>2315640824462.244</v>
       </c>
       <c r="M91" s="17" t="n">
-        <v>27.77</v>
+        <v>28.85</v>
       </c>
       <c r="N91" s="17" t="n"/>
       <c r="O91" s="17" t="n">
-        <v>5.32</v>
+        <v>5.49</v>
       </c>
       <c r="P91" s="17" t="n">
-        <v>20.59</v>
+        <v>20.45</v>
       </c>
       <c r="Q91" s="17" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="R91" s="17" t="inlineStr">
         <is>
@@ -22495,7 +22477,7 @@
         </is>
       </c>
       <c r="G97" s="17" t="n">
-        <v>1055000</v>
+        <v>1081000</v>
       </c>
       <c r="H97" s="17" t="n">
         <v>48183.27</v>
@@ -22513,17 +22495,17 @@
         <v>11736255268615.88</v>
       </c>
       <c r="M97" s="17" t="n">
-        <v>23.22</v>
+        <v>22.44</v>
       </c>
       <c r="N97" s="17" t="n"/>
       <c r="O97" s="17" t="n">
-        <v>4.52</v>
+        <v>4.74</v>
       </c>
       <c r="P97" s="17" t="n">
-        <v>21.52</v>
+        <v>23.15</v>
       </c>
       <c r="Q97" s="17" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R97" s="17" t="inlineStr">
         <is>
@@ -22568,7 +22550,7 @@
         </is>
       </c>
       <c r="G98" s="17" t="n">
-        <v>1055000</v>
+        <v>1081000</v>
       </c>
       <c r="H98" s="17" t="n">
         <v>59324.66</v>
@@ -22586,17 +22568,17 @@
         <v>14261935583756.64</v>
       </c>
       <c r="M98" s="17" t="n">
-        <v>17.78</v>
+        <v>18.22</v>
       </c>
       <c r="N98" s="17" t="n"/>
       <c r="O98" s="17" t="n">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="P98" s="17" t="n">
         <v>23.48</v>
       </c>
       <c r="Q98" s="17" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="R98" s="17" t="inlineStr">
         <is>
@@ -22994,35 +22976,35 @@
         </is>
       </c>
       <c r="G104" s="17" t="n">
-        <v>652000</v>
+        <v>678000</v>
       </c>
       <c r="H104" s="17" t="n">
-        <v>16754.84</v>
+        <v>16731.12</v>
       </c>
       <c r="I104" s="17" t="n">
-        <v>78450.03</v>
+        <v>78431.64999999999</v>
       </c>
       <c r="J104" s="18" t="n">
         <v>5160017030000</v>
       </c>
       <c r="K104" s="18" t="n">
-        <v>366013755891</v>
+        <v>365495499180</v>
       </c>
       <c r="L104" s="18" t="n">
-        <v>1713760610815.525</v>
+        <v>1713358961864.5</v>
       </c>
       <c r="M104" s="17" t="n">
-        <v>40.64</v>
+        <v>40.52</v>
       </c>
       <c r="N104" s="17" t="n"/>
       <c r="O104" s="17" t="n">
-        <v>8.48</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="P104" s="17" t="n">
-        <v>22.68</v>
+        <v>23.25</v>
       </c>
       <c r="Q104" s="17" t="n">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="R104" s="17" t="inlineStr">
         <is>
@@ -23067,35 +23049,35 @@
         </is>
       </c>
       <c r="G105" s="17" t="n">
-        <v>652000</v>
+        <v>678000</v>
       </c>
       <c r="H105" s="17" t="n">
-        <v>24122.73</v>
+        <v>24106.6</v>
       </c>
       <c r="I105" s="17" t="n">
-        <v>97145.14999999999</v>
+        <v>97114.25999999999</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>6147462670000</v>
+        <v>6160377260000</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>526967045687.25</v>
+        <v>526614616269</v>
       </c>
       <c r="L105" s="18" t="n">
-        <v>2122160071223.144</v>
+        <v>2121485289472.975</v>
       </c>
       <c r="M105" s="17" t="n">
-        <v>27.03</v>
+        <v>28.13</v>
       </c>
       <c r="N105" s="17" t="n"/>
       <c r="O105" s="17" t="n">
-        <v>6.71</v>
+        <v>6.98</v>
       </c>
       <c r="P105" s="17" t="n">
-        <v>27.48</v>
+        <v>27.46</v>
       </c>
       <c r="Q105" s="17" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R105" s="17" t="inlineStr">
         <is>
@@ -23491,7 +23473,7 @@
         </is>
       </c>
       <c r="G111" s="17" t="n">
-        <v>68800</v>
+        <v>70900</v>
       </c>
       <c r="H111" s="17" t="n">
         <v>790.5</v>
@@ -23509,17 +23491,17 @@
         <v>4924009921049.891</v>
       </c>
       <c r="M111" s="17" t="n">
-        <v>92.31</v>
+        <v>89.69</v>
       </c>
       <c r="N111" s="17" t="n"/>
       <c r="O111" s="17" t="n">
-        <v>2.32</v>
+        <v>2.69</v>
       </c>
       <c r="P111" s="17" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="Q111" s="17" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="R111" s="17" t="inlineStr">
         <is>
@@ -23564,7 +23546,7 @@
         </is>
       </c>
       <c r="G112" s="17" t="n">
-        <v>68800</v>
+        <v>70900</v>
       </c>
       <c r="H112" s="17" t="n">
         <v>2329</v>
@@ -23582,17 +23564,17 @@
         <v>5144333066583.118</v>
       </c>
       <c r="M112" s="17" t="n">
-        <v>29.54</v>
+        <v>30.44</v>
       </c>
       <c r="N112" s="17" t="n"/>
       <c r="O112" s="17" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="P112" s="17" t="n">
         <v>8.65</v>
       </c>
       <c r="Q112" s="17" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="R112" s="17" t="inlineStr">
         <is>
@@ -23990,35 +23972,35 @@
         </is>
       </c>
       <c r="G118" s="17" t="n">
-        <v>126800</v>
+        <v>124100</v>
       </c>
       <c r="H118" s="17" t="n">
-        <v>8113.99</v>
+        <v>8043.6</v>
       </c>
       <c r="I118" s="17" t="n">
-        <v>35667.03</v>
+        <v>35602.36</v>
       </c>
       <c r="J118" s="18" t="n">
-        <v>6781021630000</v>
+        <v>6769708300000</v>
       </c>
       <c r="K118" s="18" t="n">
-        <v>885579179294.8789</v>
+        <v>877897220830.5325</v>
       </c>
       <c r="L118" s="18" t="n">
-        <v>3892781692167.539</v>
+        <v>3885722740488.56</v>
       </c>
       <c r="M118" s="17" t="n">
-        <v>15.41</v>
+        <v>15.43</v>
       </c>
       <c r="N118" s="17" t="n"/>
       <c r="O118" s="17" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="P118" s="17" t="n">
-        <v>25.7</v>
+        <v>25.21</v>
       </c>
       <c r="Q118" s="17" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R118" s="17" t="inlineStr">
         <is>
@@ -24063,35 +24045,35 @@
         </is>
       </c>
       <c r="G119" s="17" t="n">
-        <v>126800</v>
+        <v>124100</v>
       </c>
       <c r="H119" s="17" t="n">
-        <v>11310.84</v>
+        <v>11099.67</v>
       </c>
       <c r="I119" s="17" t="n">
-        <v>46060.57</v>
+        <v>45801.84</v>
       </c>
       <c r="J119" s="18" t="n">
-        <v>8139996120000</v>
+        <v>8088418350000</v>
       </c>
       <c r="K119" s="18" t="n">
-        <v>1234491449925.292</v>
+        <v>1211443217058.724</v>
       </c>
       <c r="L119" s="18" t="n">
-        <v>5027155892910.839</v>
+        <v>4998917919912.48</v>
       </c>
       <c r="M119" s="17" t="n">
-        <v>11.21</v>
+        <v>11.18</v>
       </c>
       <c r="N119" s="17" t="n"/>
       <c r="O119" s="17" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="P119" s="17" t="n">
-        <v>27.68</v>
+        <v>27.27</v>
       </c>
       <c r="Q119" s="17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R119" s="17" t="inlineStr">
         <is>
@@ -24489,7 +24471,7 @@
         </is>
       </c>
       <c r="G125" s="17" t="n">
-        <v>525.28</v>
+        <v>524.1900000000001</v>
       </c>
       <c r="H125" s="17" t="n">
         <v>30.46</v>
@@ -24498,26 +24480,26 @@
         <v>44.48</v>
       </c>
       <c r="J125" s="18" t="n">
-        <v>80960773760</v>
+        <v>80954417760</v>
       </c>
       <c r="K125" s="18" t="n">
-        <v>6976391110</v>
+        <v>6974888870</v>
       </c>
       <c r="L125" s="18" t="n">
-        <v>10186173464.337</v>
+        <v>10185427301.729</v>
       </c>
       <c r="M125" s="17" t="n">
-        <v>17.24</v>
+        <v>17.21</v>
       </c>
       <c r="N125" s="17" t="n"/>
       <c r="O125" s="17" t="n">
-        <v>11.81</v>
+        <v>11.79</v>
       </c>
       <c r="P125" s="17" t="n">
-        <v>82.53</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="Q125" s="17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R125" s="17" t="inlineStr">
         <is>
@@ -24562,35 +24544,35 @@
         </is>
       </c>
       <c r="G126" s="17" t="n">
-        <v>525.28</v>
+        <v>524.1900000000001</v>
       </c>
       <c r="H126" s="17" t="n">
-        <v>32.72</v>
+        <v>32.73</v>
       </c>
       <c r="I126" s="17" t="n">
         <v>60.73</v>
       </c>
       <c r="J126" s="18" t="n">
-        <v>85415234360</v>
+        <v>85457048360</v>
       </c>
       <c r="K126" s="18" t="n">
-        <v>7493415860.000001</v>
+        <v>7494517350</v>
       </c>
       <c r="L126" s="18" t="n">
-        <v>13908153121.999</v>
+        <v>13907954069.474</v>
       </c>
       <c r="M126" s="17" t="n">
-        <v>16.05</v>
+        <v>16.02</v>
       </c>
       <c r="N126" s="17" t="n"/>
       <c r="O126" s="17" t="n">
-        <v>8.65</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="P126" s="17" t="n">
-        <v>62.2</v>
+        <v>62.21</v>
       </c>
       <c r="Q126" s="17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R126" s="17" t="inlineStr">
         <is>
@@ -24988,7 +24970,7 @@
         </is>
       </c>
       <c r="G132" s="17" t="n">
-        <v>514.98</v>
+        <v>518.97</v>
       </c>
       <c r="H132" s="17" t="n">
         <v>28.99</v>
@@ -25006,17 +24988,17 @@
         <v>19560796522.68309</v>
       </c>
       <c r="M132" s="17" t="n">
-        <v>17.76</v>
+        <v>17.9</v>
       </c>
       <c r="N132" s="17" t="n"/>
       <c r="O132" s="17" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="P132" s="17" t="n">
         <v>22.72</v>
       </c>
       <c r="Q132" s="17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R132" s="17" t="inlineStr">
         <is>
@@ -25061,7 +25043,7 @@
         </is>
       </c>
       <c r="G133" s="17" t="n">
-        <v>514.98</v>
+        <v>518.97</v>
       </c>
       <c r="H133" s="17" t="n">
         <v>30.44</v>
@@ -25079,17 +25061,17 @@
         <v>22591656618.88455</v>
       </c>
       <c r="M133" s="17" t="n">
-        <v>16.92</v>
+        <v>17.05</v>
       </c>
       <c r="N133" s="17" t="n"/>
       <c r="O133" s="17" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="P133" s="17" t="n">
         <v>20.51</v>
       </c>
       <c r="Q133" s="17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R133" s="17" t="inlineStr">
         <is>
@@ -25487,35 +25469,35 @@
         </is>
       </c>
       <c r="G139" s="17" t="n">
-        <v>359.39</v>
+        <v>355.9</v>
       </c>
       <c r="H139" s="17" t="n">
-        <v>17</v>
+        <v>16.99</v>
       </c>
       <c r="I139" s="17" t="n">
         <v>105.35</v>
       </c>
       <c r="J139" s="18" t="n">
-        <v>55923031580</v>
+        <v>55895186720</v>
       </c>
       <c r="K139" s="18" t="n">
-        <v>4596344697.65064</v>
+        <v>4593657023.44618</v>
       </c>
       <c r="L139" s="18" t="n">
-        <v>28486442015.57588</v>
+        <v>28484767057.01166</v>
       </c>
       <c r="M139" s="17" t="n">
-        <v>21.14</v>
+        <v>20.95</v>
       </c>
       <c r="N139" s="17" t="n"/>
       <c r="O139" s="17" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="P139" s="17" t="n">
-        <v>16.99</v>
+        <v>16.98</v>
       </c>
       <c r="Q139" s="17" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R139" s="17" t="inlineStr">
         <is>
@@ -25560,35 +25542,35 @@
         </is>
       </c>
       <c r="G140" s="17" t="n">
-        <v>359.39</v>
+        <v>355.9</v>
       </c>
       <c r="H140" s="17" t="n">
-        <v>18.59</v>
+        <v>18.61</v>
       </c>
       <c r="I140" s="17" t="n">
-        <v>116.94</v>
+        <v>116.95</v>
       </c>
       <c r="J140" s="18" t="n">
-        <v>58536910550</v>
+        <v>58565479680</v>
       </c>
       <c r="K140" s="18" t="n">
-        <v>5027773189.31586</v>
+        <v>5032775399.857361</v>
       </c>
       <c r="L140" s="18" t="n">
-        <v>31619750267.15752</v>
+        <v>31621192686.20277</v>
       </c>
       <c r="M140" s="17" t="n">
-        <v>19.33</v>
+        <v>19.12</v>
       </c>
       <c r="N140" s="17" t="n"/>
       <c r="O140" s="17" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="P140" s="17" t="n">
-        <v>16.73</v>
+        <v>16.75</v>
       </c>
       <c r="Q140" s="17" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R140" s="17" t="inlineStr">
         <is>
@@ -25986,7 +25968,7 @@
         </is>
       </c>
       <c r="G146" s="17" t="n">
-        <v>200.79</v>
+        <v>197.68</v>
       </c>
       <c r="H146" s="17" t="n">
         <v>7.24</v>
@@ -26004,17 +25986,17 @@
         <v>70225512519.7807</v>
       </c>
       <c r="M146" s="17" t="n">
-        <v>27.72</v>
+        <v>27.29</v>
       </c>
       <c r="N146" s="17" t="n"/>
       <c r="O146" s="17" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="P146" s="17" t="n">
         <v>14.35</v>
       </c>
       <c r="Q146" s="17" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="R146" s="17" t="inlineStr">
         <is>
@@ -26059,7 +26041,7 @@
         </is>
       </c>
       <c r="G147" s="17" t="n">
-        <v>200.79</v>
+        <v>197.68</v>
       </c>
       <c r="H147" s="17" t="n">
         <v>7.86</v>
@@ -26077,17 +26059,17 @@
         <v>75627625676.04219</v>
       </c>
       <c r="M147" s="17" t="n">
-        <v>25.56</v>
+        <v>25.16</v>
       </c>
       <c r="N147" s="17" t="n"/>
       <c r="O147" s="17" t="n">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="P147" s="17" t="n">
         <v>14.46</v>
       </c>
       <c r="Q147" s="17" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="R147" s="17" t="inlineStr">
         <is>
@@ -26485,7 +26467,7 @@
         </is>
       </c>
       <c r="G153" s="17" t="n">
-        <v>285.93</v>
+        <v>279.69</v>
       </c>
       <c r="H153" s="17" t="n">
         <v>18.51</v>
@@ -26503,17 +26485,17 @@
         <v>5561910169.971308</v>
       </c>
       <c r="M153" s="17" t="n">
-        <v>15.45</v>
+        <v>15.11</v>
       </c>
       <c r="N153" s="17" t="n"/>
       <c r="O153" s="17" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="P153" s="17" t="n">
         <v>13.66</v>
       </c>
       <c r="Q153" s="17" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="R153" s="17" t="inlineStr">
         <is>
@@ -26558,7 +26540,7 @@
         </is>
       </c>
       <c r="G154" s="17" t="n">
-        <v>285.93</v>
+        <v>279.69</v>
       </c>
       <c r="H154" s="17" t="n">
         <v>20.83</v>
@@ -26576,17 +26558,17 @@
         <v>6112146741.053395</v>
       </c>
       <c r="M154" s="17" t="n">
-        <v>13.72</v>
+        <v>13.42</v>
       </c>
       <c r="N154" s="17" t="n"/>
       <c r="O154" s="17" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="P154" s="17" t="n">
         <v>14.01</v>
       </c>
       <c r="Q154" s="17" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="R154" s="17" t="inlineStr">
         <is>
@@ -26985,30 +26967,30 @@
       </c>
       <c r="G160" s="17" t="n"/>
       <c r="H160" s="17" t="n">
-        <v>37.24</v>
+        <v>37.29</v>
       </c>
       <c r="I160" s="17" t="n">
-        <v>130.03</v>
+        <v>130.05</v>
       </c>
       <c r="J160" s="18" t="n">
-        <v>13961205280</v>
+        <v>13946205280</v>
       </c>
       <c r="K160" s="18" t="n">
-        <v>1708828409.7131</v>
+        <v>1710747613.198</v>
       </c>
       <c r="L160" s="18" t="n">
-        <v>5965722432.506709</v>
+        <v>5966794691.493723</v>
       </c>
       <c r="M160" s="17" t="n"/>
       <c r="N160" s="17" t="n"/>
       <c r="O160" s="17" t="n">
-        <v>8.09</v>
+        <v>7.75</v>
       </c>
       <c r="P160" s="17" t="n">
-        <v>31.14</v>
+        <v>31.17</v>
       </c>
       <c r="Q160" s="17" t="n">
-        <v>3.46</v>
+        <v>3.31</v>
       </c>
       <c r="R160" s="17" t="inlineStr">
         <is>
@@ -27054,30 +27036,30 @@
       </c>
       <c r="G161" s="17" t="n"/>
       <c r="H161" s="17" t="n">
-        <v>53.68</v>
+        <v>53.64</v>
       </c>
       <c r="I161" s="17" t="n">
         <v>160.02</v>
       </c>
       <c r="J161" s="18" t="n">
-        <v>18701268180</v>
+        <v>18646268180</v>
       </c>
       <c r="K161" s="18" t="n">
-        <v>2462837715.5434</v>
+        <v>2461168563.672</v>
       </c>
       <c r="L161" s="18" t="n">
-        <v>7341709864.180807</v>
+        <v>7341849568.017269</v>
       </c>
       <c r="M161" s="17" t="n"/>
       <c r="N161" s="17" t="n"/>
       <c r="O161" s="17" t="n">
-        <v>6.57</v>
+        <v>6.3</v>
       </c>
       <c r="P161" s="17" t="n">
-        <v>37.01</v>
+        <v>36.99</v>
       </c>
       <c r="Q161" s="17" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="R161" s="17" t="inlineStr">
         <is>
@@ -27482,13 +27464,13 @@
         <v>4.43</v>
       </c>
       <c r="J167" s="18" t="n">
-        <v>33295251610</v>
+        <v>33180119160</v>
       </c>
       <c r="K167" s="18" t="n">
-        <v>2455321885.86264</v>
+        <v>2458483357.5852</v>
       </c>
       <c r="L167" s="18" t="n">
-        <v>12962308973.02548</v>
+        <v>12963826163.30514</v>
       </c>
       <c r="M167" s="17" t="n"/>
       <c r="N167" s="17" t="n"/>
@@ -27496,7 +27478,7 @@
         <v>0.04</v>
       </c>
       <c r="P167" s="17" t="n">
-        <v>19.84</v>
+        <v>19.87</v>
       </c>
       <c r="Q167" s="17" t="n">
         <v>0.02</v>
@@ -27551,13 +27533,13 @@
         <v>4.89</v>
       </c>
       <c r="J168" s="18" t="n">
-        <v>36342933340</v>
+        <v>36216381490</v>
       </c>
       <c r="K168" s="18" t="n">
-        <v>2802088497.20936</v>
+        <v>2805659789.3404</v>
       </c>
       <c r="L168" s="18" t="n">
-        <v>14307031242.83625</v>
+        <v>14310262296.20959</v>
       </c>
       <c r="M168" s="17" t="n"/>
       <c r="N168" s="17" t="n"/>
@@ -27565,7 +27547,7 @@
         <v>0.04</v>
       </c>
       <c r="P168" s="17" t="n">
-        <v>20.55</v>
+        <v>20.57</v>
       </c>
       <c r="Q168" s="17" t="n">
         <v>0.02</v>
@@ -27973,24 +27955,24 @@
         <v>18.18</v>
       </c>
       <c r="J174" s="18" t="n">
-        <v>22326243840</v>
+        <v>22326228840</v>
       </c>
       <c r="K174" s="18" t="n">
-        <v>1373438681.59342</v>
+        <v>1373484837.12726</v>
       </c>
       <c r="L174" s="18" t="n">
-        <v>10489955331.3069</v>
+        <v>10489986583.21887</v>
       </c>
       <c r="M174" s="17" t="n"/>
       <c r="N174" s="17" t="n"/>
       <c r="O174" s="17" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="P174" s="17" t="n">
         <v>13.7</v>
       </c>
       <c r="Q174" s="17" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R174" s="17" t="inlineStr">
         <is>
@@ -28042,24 +28024,24 @@
         <v>20.11</v>
       </c>
       <c r="J175" s="18" t="n">
-        <v>24744432810</v>
+        <v>24733603910</v>
       </c>
       <c r="K175" s="18" t="n">
-        <v>1647019838.98829</v>
+        <v>1644896684.43165</v>
       </c>
       <c r="L175" s="18" t="n">
-        <v>11605152464.28588</v>
+        <v>11603746128.24754</v>
       </c>
       <c r="M175" s="17" t="n"/>
       <c r="N175" s="17" t="n"/>
       <c r="O175" s="17" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="P175" s="17" t="n">
-        <v>14.91</v>
+        <v>14.89</v>
       </c>
       <c r="Q175" s="17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="R175" s="17" t="inlineStr">
         <is>
@@ -28464,7 +28446,7 @@
         <v>92.81999999999999</v>
       </c>
       <c r="J181" s="18" t="n">
-        <v>97824460000</v>
+        <v>97786114940</v>
       </c>
       <c r="K181" s="18" t="n">
         <v>8030719972.51368</v>
@@ -28475,13 +28457,13 @@
       <c r="M181" s="17" t="n"/>
       <c r="N181" s="17" t="n"/>
       <c r="O181" s="17" t="n">
-        <v>6.35</v>
+        <v>6.16</v>
       </c>
       <c r="P181" s="17" t="n">
         <v>17.2</v>
       </c>
       <c r="Q181" s="17" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="R181" s="17" t="inlineStr">
         <is>
@@ -28527,30 +28509,30 @@
       </c>
       <c r="G182" s="17" t="n"/>
       <c r="H182" s="17" t="n">
-        <v>18.74</v>
+        <v>18.89</v>
       </c>
       <c r="I182" s="17" t="n">
-        <v>108.42</v>
+        <v>108.54</v>
       </c>
       <c r="J182" s="18" t="n">
         <v>118685164060</v>
       </c>
       <c r="K182" s="18" t="n">
-        <v>10100122457.1528</v>
+        <v>10181082532.89816</v>
       </c>
       <c r="L182" s="18" t="n">
-        <v>58431739406.94032</v>
+        <v>58499146766.0059</v>
       </c>
       <c r="M182" s="17" t="n"/>
       <c r="N182" s="17" t="n"/>
       <c r="O182" s="17" t="n">
-        <v>5.43</v>
+        <v>5.26</v>
       </c>
       <c r="P182" s="17" t="n">
-        <v>18.63</v>
+        <v>18.76</v>
       </c>
       <c r="Q182" s="17" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="R182" s="17" t="inlineStr">
         <is>
@@ -28948,7 +28930,7 @@
         </is>
       </c>
       <c r="G188" s="17" t="n">
-        <v>140000</v>
+        <v>142500</v>
       </c>
       <c r="H188" s="17" t="n">
         <v>13470</v>
@@ -28966,17 +28948,17 @@
         <v>2419672871894.003</v>
       </c>
       <c r="M188" s="17" t="n">
-        <v>11.01</v>
+        <v>10.58</v>
       </c>
       <c r="N188" s="17" t="n"/>
       <c r="O188" s="17" t="n">
-        <v>1.18</v>
+        <v>2.83</v>
       </c>
       <c r="P188" s="17" t="n">
-        <v>16.32</v>
+        <v>30.59</v>
       </c>
       <c r="Q188" s="17" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="R188" s="17" t="inlineStr">
         <is>
@@ -29021,7 +29003,7 @@
         </is>
       </c>
       <c r="G189" s="17" t="n">
-        <v>140000</v>
+        <v>142500</v>
       </c>
       <c r="H189" s="17" t="n">
         <v>14842.75</v>
@@ -29039,17 +29021,17 @@
         <v>3096745015201.536</v>
       </c>
       <c r="M189" s="17" t="n">
-        <v>9.43</v>
+        <v>9.6</v>
       </c>
       <c r="N189" s="17" t="n"/>
       <c r="O189" s="17" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="P189" s="17" t="n">
         <v>25.82</v>
       </c>
       <c r="Q189" s="17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="R189" s="17" t="inlineStr">
         <is>
@@ -29447,7 +29429,7 @@
         </is>
       </c>
       <c r="G195" s="17" t="n">
-        <v>62800</v>
+        <v>61600</v>
       </c>
       <c r="H195" s="17" t="n">
         <v>6179.71</v>
@@ -29465,17 +29447,17 @@
         <v>7589662196632.624</v>
       </c>
       <c r="M195" s="17" t="n">
-        <v>10.7</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="N195" s="17" t="n"/>
       <c r="O195" s="17" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="P195" s="17" t="n">
-        <v>7.52</v>
+        <v>8</v>
       </c>
       <c r="Q195" s="17" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="R195" s="17" t="inlineStr">
         <is>
@@ -29520,7 +29502,7 @@
         </is>
       </c>
       <c r="G196" s="17" t="n">
-        <v>62800</v>
+        <v>61600</v>
       </c>
       <c r="H196" s="17" t="n">
         <v>6625.59</v>
@@ -29538,17 +29520,17 @@
         <v>8016959738234.411</v>
       </c>
       <c r="M196" s="17" t="n">
-        <v>9.48</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N196" s="17" t="n"/>
       <c r="O196" s="17" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="P196" s="17" t="n">
         <v>8.130000000000001</v>
       </c>
       <c r="Q196" s="17" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="R196" s="17" t="inlineStr">
         <is>
@@ -29942,7 +29924,7 @@
         </is>
       </c>
       <c r="G202" s="17" t="n">
-        <v>8400</v>
+        <v>8110</v>
       </c>
       <c r="H202" s="17" t="n"/>
       <c r="I202" s="17" t="n"/>
@@ -29999,7 +29981,7 @@
         </is>
       </c>
       <c r="G203" s="17" t="n">
-        <v>8400</v>
+        <v>8110</v>
       </c>
       <c r="H203" s="17" t="n"/>
       <c r="I203" s="17" t="n"/>
@@ -30409,7 +30391,7 @@
         </is>
       </c>
       <c r="G209" s="17" t="n">
-        <v>813.9400000000001</v>
+        <v>818.5700000000001</v>
       </c>
       <c r="H209" s="17" t="n">
         <v>27.19</v>
@@ -30427,17 +30409,17 @@
         <v>30677414343.27097</v>
       </c>
       <c r="M209" s="17" t="n">
-        <v>29.94</v>
+        <v>30.11</v>
       </c>
       <c r="N209" s="17" t="n"/>
       <c r="O209" s="17" t="n">
-        <v>12.35</v>
+        <v>12.42</v>
       </c>
       <c r="P209" s="17" t="n">
         <v>48.66</v>
       </c>
       <c r="Q209" s="17" t="n">
-        <v>4.78</v>
+        <v>4.81</v>
       </c>
       <c r="R209" s="17" t="inlineStr">
         <is>
@@ -30482,7 +30464,7 @@
         </is>
       </c>
       <c r="G210" s="17" t="n">
-        <v>813.9400000000001</v>
+        <v>818.5700000000001</v>
       </c>
       <c r="H210" s="17" t="n">
         <v>32.38</v>
@@ -30500,17 +30482,17 @@
         <v>41823834814.59047</v>
       </c>
       <c r="M210" s="17" t="n">
-        <v>25.14</v>
+        <v>25.28</v>
       </c>
       <c r="N210" s="17" t="n"/>
       <c r="O210" s="17" t="n">
-        <v>9.06</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="P210" s="17" t="n">
         <v>41.56</v>
       </c>
       <c r="Q210" s="17" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="R210" s="17" t="inlineStr">
         <is>
@@ -30908,7 +30890,7 @@
         </is>
       </c>
       <c r="G216" s="17" t="n">
-        <v>693.53</v>
+        <v>675.74</v>
       </c>
       <c r="H216" s="17" t="n">
         <v>18.13</v>
@@ -30926,17 +30908,17 @@
         <v>29086374878.3913</v>
       </c>
       <c r="M216" s="17" t="n">
-        <v>38.25</v>
+        <v>37.27</v>
       </c>
       <c r="N216" s="17" t="n"/>
       <c r="O216" s="17" t="n">
-        <v>6.45</v>
+        <v>6.28</v>
       </c>
       <c r="P216" s="17" t="n">
         <v>17.81</v>
       </c>
       <c r="Q216" s="17" t="n">
-        <v>4.56</v>
+        <v>4.44</v>
       </c>
       <c r="R216" s="17" t="inlineStr">
         <is>
@@ -30981,7 +30963,7 @@
         </is>
       </c>
       <c r="G217" s="17" t="n">
-        <v>693.53</v>
+        <v>675.74</v>
       </c>
       <c r="H217" s="17" t="n">
         <v>22.67</v>
@@ -30999,17 +30981,17 @@
         <v>33007534064.01535</v>
       </c>
       <c r="M217" s="17" t="n">
-        <v>30.59</v>
+        <v>29.81</v>
       </c>
       <c r="N217" s="17" t="n"/>
       <c r="O217" s="17" t="n">
-        <v>5.68</v>
+        <v>5.53</v>
       </c>
       <c r="P217" s="17" t="n">
         <v>19.74</v>
       </c>
       <c r="Q217" s="17" t="n">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="R217" s="17" t="inlineStr">
         <is>
@@ -31407,7 +31389,7 @@
         </is>
       </c>
       <c r="G223" s="17" t="n">
-        <v>14.4</v>
+        <v>13.58</v>
       </c>
       <c r="H223" s="17" t="n">
         <v>0.45</v>
@@ -31425,17 +31407,17 @@
         <v>8066654189.696636</v>
       </c>
       <c r="M223" s="17" t="n">
-        <v>31.88</v>
+        <v>30.06</v>
       </c>
       <c r="N223" s="17" t="n"/>
       <c r="O223" s="17" t="n">
-        <v>2.22</v>
+        <v>2.09</v>
       </c>
       <c r="P223" s="17" t="n">
         <v>7.1</v>
       </c>
       <c r="Q223" s="17" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="R223" s="17" t="inlineStr">
         <is>
@@ -31480,7 +31462,7 @@
         </is>
       </c>
       <c r="G224" s="17" t="n">
-        <v>14.4</v>
+        <v>13.58</v>
       </c>
       <c r="H224" s="17" t="n">
         <v>0.6899999999999999</v>
@@ -31498,17 +31480,17 @@
         <v>8577262027.41866</v>
       </c>
       <c r="M224" s="17" t="n">
-        <v>21.02</v>
+        <v>19.82</v>
       </c>
       <c r="N224" s="17" t="n"/>
       <c r="O224" s="17" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="P224" s="17" t="n">
         <v>10.23</v>
       </c>
       <c r="Q224" s="17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="R224" s="17" t="inlineStr">
         <is>
@@ -31906,35 +31888,35 @@
         </is>
       </c>
       <c r="G230" s="17" t="n">
-        <v>7493</v>
+        <v>7114</v>
       </c>
       <c r="H230" s="17" t="n">
-        <v>481.98</v>
+        <v>438.93</v>
       </c>
       <c r="I230" s="17" t="n">
-        <v>4156.85</v>
+        <v>4133.56</v>
       </c>
       <c r="J230" s="18" t="n">
-        <v>4351984533599</v>
+        <v>4363584533599</v>
       </c>
       <c r="K230" s="18" t="n">
-        <v>434310577780.9013</v>
+        <v>395517352597.6937</v>
       </c>
       <c r="L230" s="18" t="n">
-        <v>3745730013893.256</v>
+        <v>3724742879845.005</v>
       </c>
       <c r="M230" s="17" t="n">
-        <v>15.55</v>
+        <v>16.21</v>
       </c>
       <c r="N230" s="17" t="n"/>
       <c r="O230" s="17" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="P230" s="17" t="n">
-        <v>11.97</v>
+        <v>10.93</v>
       </c>
       <c r="Q230" s="17" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="R230" s="17" t="inlineStr">
         <is>
@@ -31979,35 +31961,35 @@
         </is>
       </c>
       <c r="G231" s="17" t="n">
-        <v>7493</v>
+        <v>7114</v>
       </c>
       <c r="H231" s="17" t="n">
-        <v>555.5</v>
+        <v>480.38</v>
       </c>
       <c r="I231" s="17" t="n">
-        <v>4457.38</v>
+        <v>4393.44</v>
       </c>
       <c r="J231" s="18" t="n">
-        <v>4490768251270</v>
+        <v>4509222796730</v>
       </c>
       <c r="K231" s="18" t="n">
-        <v>500563107286.091</v>
+        <v>432866424018.5521</v>
       </c>
       <c r="L231" s="18" t="n">
-        <v>4016534644923.769</v>
+        <v>3958923606581.714</v>
       </c>
       <c r="M231" s="17" t="n">
-        <v>13.49</v>
+        <v>14.81</v>
       </c>
       <c r="N231" s="17" t="n"/>
       <c r="O231" s="17" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="P231" s="17" t="n">
-        <v>12.9</v>
+        <v>11.27</v>
       </c>
       <c r="Q231" s="17" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="R231" s="17" t="inlineStr">
         <is>
@@ -32405,35 +32387,35 @@
         </is>
       </c>
       <c r="G237" s="17" t="n">
-        <v>5977</v>
+        <v>5633</v>
       </c>
       <c r="H237" s="17" t="n">
-        <v>421.59</v>
+        <v>422</v>
       </c>
       <c r="I237" s="17" t="n">
-        <v>4438.54</v>
+        <v>4438.75</v>
       </c>
       <c r="J237" s="18" t="n">
-        <v>1474454185460</v>
+        <v>1463792609300</v>
       </c>
       <c r="K237" s="18" t="n">
-        <v>89687739247.02324</v>
+        <v>89775397147.96313</v>
       </c>
       <c r="L237" s="18" t="n">
-        <v>944238555065.9872</v>
+        <v>944281630158.509</v>
       </c>
       <c r="M237" s="17" t="n">
-        <v>14.18</v>
+        <v>13.35</v>
       </c>
       <c r="N237" s="17" t="n"/>
       <c r="O237" s="17" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="P237" s="17" t="n">
         <v>9.73</v>
       </c>
       <c r="Q237" s="17" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="R237" s="17" t="inlineStr">
         <is>
@@ -32478,35 +32460,35 @@
         </is>
       </c>
       <c r="G238" s="17" t="n">
-        <v>5977</v>
+        <v>5633</v>
       </c>
       <c r="H238" s="17" t="n">
-        <v>489.48</v>
+        <v>493.57</v>
       </c>
       <c r="I238" s="17" t="n">
-        <v>4679.07</v>
+        <v>4681.29</v>
       </c>
       <c r="J238" s="18" t="n">
-        <v>1515254307950</v>
+        <v>1520309863510</v>
       </c>
       <c r="K238" s="18" t="n">
-        <v>104129595949.5115</v>
+        <v>104999452498.8457</v>
       </c>
       <c r="L238" s="18" t="n">
-        <v>995407838515.5771</v>
+        <v>995878361116.4418</v>
       </c>
       <c r="M238" s="17" t="n">
-        <v>12.21</v>
+        <v>11.41</v>
       </c>
       <c r="N238" s="17" t="n"/>
       <c r="O238" s="17" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="P238" s="17" t="n">
-        <v>10.74</v>
+        <v>10.82</v>
       </c>
       <c r="Q238" s="17" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="R238" s="17" t="inlineStr">
         <is>
@@ -32911,24 +32893,24 @@
         <v>98.89</v>
       </c>
       <c r="J244" s="18" t="n">
-        <v>496510915310</v>
+        <v>497752494260</v>
       </c>
       <c r="K244" s="18" t="n">
-        <v>43840637229.93564</v>
+        <v>43848994718.00088</v>
       </c>
       <c r="L244" s="18" t="n">
-        <v>201086912514.9956</v>
+        <v>201091238350.5674</v>
       </c>
       <c r="M244" s="17" t="n"/>
       <c r="N244" s="17" t="n"/>
       <c r="O244" s="17" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="P244" s="17" t="n">
         <v>23.11</v>
       </c>
       <c r="Q244" s="17" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="R244" s="17" t="inlineStr">
         <is>
@@ -32974,30 +32956,30 @@
       </c>
       <c r="G245" s="17" t="n"/>
       <c r="H245" s="17" t="n">
-        <v>25.43</v>
+        <v>25.44</v>
       </c>
       <c r="I245" s="17" t="n">
-        <v>112.05</v>
+        <v>112.06</v>
       </c>
       <c r="J245" s="18" t="n">
-        <v>540009724169</v>
+        <v>541284574170</v>
       </c>
       <c r="K245" s="18" t="n">
-        <v>51713187642.18332</v>
+        <v>51728743550.62592</v>
       </c>
       <c r="L245" s="18" t="n">
-        <v>227853656887.194</v>
+        <v>227866034460.5091</v>
       </c>
       <c r="M245" s="17" t="n"/>
       <c r="N245" s="17" t="n"/>
       <c r="O245" s="17" t="n">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="P245" s="17" t="n">
-        <v>24.11</v>
+        <v>24.12</v>
       </c>
       <c r="Q245" s="17" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="R245" s="17" t="inlineStr">
         <is>
@@ -33395,35 +33377,35 @@
         </is>
       </c>
       <c r="G251" s="17" t="n">
-        <v>20</v>
+        <v>19.78</v>
       </c>
       <c r="H251" s="17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="I251" s="17" t="n">
-        <v>10.43</v>
+        <v>10.41</v>
       </c>
       <c r="J251" s="18" t="n">
-        <v>103700366140</v>
+        <v>104038852480</v>
       </c>
       <c r="K251" s="18" t="n">
-        <v>11027660771.33847</v>
+        <v>10742983433.96895</v>
       </c>
       <c r="L251" s="18" t="n">
-        <v>95898425041.84567</v>
+        <v>95703079447.24916</v>
       </c>
       <c r="M251" s="17" t="n">
-        <v>16.68</v>
+        <v>16.93</v>
       </c>
       <c r="N251" s="17" t="n"/>
       <c r="O251" s="17" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="P251" s="17" t="n">
-        <v>11.97</v>
+        <v>11.67</v>
       </c>
       <c r="Q251" s="17" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R251" s="17" t="inlineStr">
         <is>
@@ -33468,35 +33450,35 @@
         </is>
       </c>
       <c r="G252" s="17" t="n">
-        <v>20</v>
+        <v>19.78</v>
       </c>
       <c r="H252" s="17" t="n">
         <v>1.52</v>
       </c>
       <c r="I252" s="17" t="n">
-        <v>11.47</v>
+        <v>11.45</v>
       </c>
       <c r="J252" s="18" t="n">
-        <v>117329033660</v>
+        <v>118137033660</v>
       </c>
       <c r="K252" s="18" t="n">
-        <v>13989003900.31869</v>
+        <v>13933833873.69669</v>
       </c>
       <c r="L252" s="18" t="n">
-        <v>105497679798.0244</v>
+        <v>105264476530.0565</v>
       </c>
       <c r="M252" s="17" t="n">
-        <v>13.15</v>
+        <v>13.05</v>
       </c>
       <c r="N252" s="17" t="n"/>
       <c r="O252" s="17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="P252" s="17" t="n">
-        <v>13.89</v>
+        <v>13.87</v>
       </c>
       <c r="Q252" s="17" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="R252" s="17" t="inlineStr">
         <is>
@@ -33894,32 +33876,32 @@
         </is>
       </c>
       <c r="G258" s="17" t="n">
-        <v>8.140000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="H258" s="17" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="I258" s="17" t="n">
-        <v>5.37</v>
+        <v>5.35</v>
       </c>
       <c r="J258" s="18" t="n">
-        <v>114720037870</v>
+        <v>114353945310</v>
       </c>
       <c r="K258" s="18" t="n">
-        <v>8482472829.43386</v>
+        <v>7802328311.90052</v>
       </c>
       <c r="L258" s="18" t="n">
-        <v>63082618877.36219</v>
+        <v>62872386186.58829</v>
       </c>
       <c r="M258" s="17" t="n">
-        <v>11.28</v>
+        <v>12.14</v>
       </c>
       <c r="N258" s="17" t="n"/>
       <c r="O258" s="17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P258" s="17" t="n">
-        <v>13.73</v>
+        <v>12.65</v>
       </c>
       <c r="Q258" s="17" t="n">
         <v>0.83</v>
@@ -33967,35 +33949,35 @@
         </is>
       </c>
       <c r="G259" s="17" t="n">
-        <v>8.140000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="H259" s="17" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="I259" s="17" t="n">
-        <v>5.65</v>
+        <v>5.63</v>
       </c>
       <c r="J259" s="18" t="n">
-        <v>131296032459</v>
+        <v>131317082850</v>
       </c>
       <c r="K259" s="18" t="n">
-        <v>10839531460.69896</v>
+        <v>10592366449.4025</v>
       </c>
       <c r="L259" s="18" t="n">
-        <v>66433118377.05018</v>
+        <v>66146486973.8696</v>
       </c>
       <c r="M259" s="17" t="n">
-        <v>8.83</v>
+        <v>8.94</v>
       </c>
       <c r="N259" s="17" t="n"/>
       <c r="O259" s="17" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P259" s="17" t="n">
-        <v>16.74</v>
+        <v>16.42</v>
       </c>
       <c r="Q259" s="17" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="R259" s="17" t="inlineStr">
         <is>
@@ -34393,7 +34375,7 @@
         </is>
       </c>
       <c r="G265" s="17" t="n">
-        <v>13180</v>
+        <v>12680</v>
       </c>
       <c r="H265" s="17" t="n">
         <v>1728</v>
@@ -34411,17 +34393,17 @@
         <v>328971474869.7184</v>
       </c>
       <c r="M265" s="17" t="n">
-        <v>7.63</v>
+        <v>7.34</v>
       </c>
       <c r="N265" s="17" t="n"/>
       <c r="O265" s="17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="P265" s="17" t="n">
         <v>11.18</v>
       </c>
       <c r="Q265" s="17" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="R265" s="17" t="inlineStr">
         <is>
@@ -34466,7 +34448,7 @@
         </is>
       </c>
       <c r="G266" s="17" t="n">
-        <v>13180</v>
+        <v>12680</v>
       </c>
       <c r="H266" s="17" t="n">
         <v>2102</v>
@@ -34484,17 +34466,17 @@
         <v>367213567791.274</v>
       </c>
       <c r="M266" s="17" t="n">
-        <v>6.27</v>
+        <v>6.03</v>
       </c>
       <c r="N266" s="17" t="n"/>
       <c r="O266" s="17" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="P266" s="17" t="n">
         <v>12.24</v>
       </c>
       <c r="Q266" s="17" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="R266" s="17" t="inlineStr">
         <is>
@@ -34892,7 +34874,7 @@
         </is>
       </c>
       <c r="G272" s="17" t="n">
-        <v>11540</v>
+        <v>11280</v>
       </c>
       <c r="H272" s="17" t="n"/>
       <c r="I272" s="17" t="n"/>
@@ -34949,7 +34931,7 @@
         </is>
       </c>
       <c r="G273" s="17" t="n">
-        <v>11540</v>
+        <v>11280</v>
       </c>
       <c r="H273" s="17" t="n"/>
       <c r="I273" s="17" t="n"/>
@@ -35359,7 +35341,7 @@
         </is>
       </c>
       <c r="G279" s="17" t="n">
-        <v>6520</v>
+        <v>6620</v>
       </c>
       <c r="H279" s="17" t="n"/>
       <c r="I279" s="17" t="n"/>
@@ -35416,7 +35398,7 @@
         </is>
       </c>
       <c r="G280" s="17" t="n">
-        <v>6520</v>
+        <v>6620</v>
       </c>
       <c r="H280" s="17" t="n"/>
       <c r="I280" s="17" t="n"/>
@@ -35826,35 +35808,35 @@
         </is>
       </c>
       <c r="G286" s="17" t="n">
-        <v>1009.86</v>
+        <v>989.12</v>
       </c>
       <c r="H286" s="17" t="n">
-        <v>49.24</v>
+        <v>49.29</v>
       </c>
       <c r="I286" s="17" t="n">
-        <v>182.46</v>
+        <v>182.5</v>
       </c>
       <c r="J286" s="18" t="n">
-        <v>17739955600</v>
+        <v>17746037900</v>
       </c>
       <c r="K286" s="18" t="n">
-        <v>3106619048.2677</v>
+        <v>3109809180.5109</v>
       </c>
       <c r="L286" s="18" t="n">
-        <v>11512631631.36988</v>
+        <v>11515244668.65839</v>
       </c>
       <c r="M286" s="17" t="n">
-        <v>20.51</v>
+        <v>20.07</v>
       </c>
       <c r="N286" s="17" t="n"/>
       <c r="O286" s="17" t="n">
-        <v>5.53</v>
+        <v>5.42</v>
       </c>
       <c r="P286" s="17" t="n">
-        <v>30.34</v>
+        <v>30.36</v>
       </c>
       <c r="Q286" s="17" t="n">
-        <v>3.59</v>
+        <v>3.52</v>
       </c>
       <c r="R286" s="17" t="inlineStr">
         <is>
@@ -35899,35 +35881,35 @@
         </is>
       </c>
       <c r="G287" s="17" t="n">
-        <v>1009.86</v>
+        <v>989.12</v>
       </c>
       <c r="H287" s="17" t="n">
-        <v>57.19</v>
+        <v>57.3</v>
       </c>
       <c r="I287" s="17" t="n">
-        <v>229.3</v>
+        <v>229.44</v>
       </c>
       <c r="J287" s="18" t="n">
-        <v>19284488790</v>
+        <v>19300284520</v>
       </c>
       <c r="K287" s="18" t="n">
-        <v>3608177747.2335</v>
+        <v>3615418640.7507</v>
       </c>
       <c r="L287" s="18" t="n">
-        <v>14468089988.04707</v>
+        <v>14476634041.1431</v>
       </c>
       <c r="M287" s="17" t="n">
-        <v>17.66</v>
+        <v>17.26</v>
       </c>
       <c r="N287" s="17" t="n"/>
       <c r="O287" s="17" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="P287" s="17" t="n">
-        <v>27.78</v>
+        <v>27.82</v>
       </c>
       <c r="Q287" s="17" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="R287" s="17" t="inlineStr">
         <is>
@@ -36235,7 +36217,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05T08:38:22+09:00</t>
+          <t>2026-09-12T08:47:20+09:00</t>
         </is>
       </c>
     </row>
